--- a/egais.xlsx
+++ b/egais.xlsx
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -4930,7 +4930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ51"/>
+  <dimension ref="A1:AJ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -5131,7 +5131,11 @@
           <t>AvitoStatus</t>
         </is>
       </c>
-      <c r="AJ2" s="7" t="n"/>
+      <c r="AJ2" s="7" t="inlineStr">
+        <is>
+          <t>DateBegin</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -11855,6 +11859,1881 @@
       <c r="AI51" t="inlineStr">
         <is>
           <t>Активно</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>7689904523</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Лес с делянки пиловочник(QR код на вывоз)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Краснодар и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/01/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/01/01_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/01/01_03.jpg</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Краснодарский край, Краснодар</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>2026-08-14T18:13:40+03:00</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>2026-07-15T20:13:40+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>8383903623</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Лес есть документов нет(кругляк ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Тула и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/02/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/02/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/02/02_03.jpg</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Тульская область, Тула</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>2026-08-15T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>2026-07-16T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>8998350344</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Лес хвоя от заготовителя(QR код на лес)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Москва и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/03/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/03/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/03/03_03.jpg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Москва, Москва</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>2026-08-15T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>2026-07-16T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4426873387</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Кругляк сосна с делянки(документы ФГИС)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Санкт-Петербург и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/04/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/04/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/04/04_03.jpg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Санкт-Петербург, Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>2026-08-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>2026-07-16T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>5316950583</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Пиловочник ель(ЭСД и QR на перевозку)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Екатеринбург и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/05/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/05/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/05/05_03.jpg</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Свердловская область, Екатеринбург</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>2026-08-15T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>2026-07-16T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4184632336</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Продам лес кругляк(расхождения ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Новосибирск и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/06/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/06/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/06/06_03.jpg</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Новосибирская область, Новосибирск</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>2026-08-15T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>2026-07-16T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4497916722</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Лес кругляк берёза(документы на лес)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Казань и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/07/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/07/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/07/07_03.jpg</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Республика Татарстан, Казань</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>2026-08-15T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>2026-07-16T13:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1060900463</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Лес с делянки хвоя(QR код на вывозку)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Нижний Новгород и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/08/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/08/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/08/08_03.jpg</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Нижегородская область, Нижний Новгород</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>2026-08-15T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>2026-07-16T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4896104218</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Кругляк сосна свежий спил(ЭСД на рейс)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Самара и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/09/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/09/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/09/09_03.jpg</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Самарская область, Самара</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>2026-08-16T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>2026-07-17T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6407106167</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Лес есть учёта нет(кругляк ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Ростов-на-Дону и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/10/10_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/10/10_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/10/10_03.jpg</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Ростовская область, Ростов-на-Дону</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>2026-08-16T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>2026-07-17T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>5211829099</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Пиловочник лиственница(QR код и ЭСД)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Воронеж и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/11/11_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/11/11_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/11/11_03.jpg</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Воронежская область, Воронеж</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>2026-08-16T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>2026-07-17T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>5538956737</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Лес от заготовителя(документы ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Челябинск и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/12/12_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/12/12_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/12/12_03.jpg</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Челябинская область, Челябинск</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>2026-08-16T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>2026-07-17T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>9583135422</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Кругляк ель сосна(закрываем расхождения)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Пермь и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/13/13_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/13/13_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/13/13_03.jpg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Пермский край, Пермь</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>2026-08-16T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>8588178728</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Лес зимней заготовки(QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Уфа и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/14/14_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/14/14_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/14/14_03.jpg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан, Уфа</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>2026-08-16T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>2026-07-17T13:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>5855204542</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Продам лес кругляк(помощь с учётом ФГИС)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Волгоград и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/15/15_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/15/15_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/15/15_03.jpg</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Волгоградская область, Волгоград</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>6100</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>2026-08-16T13:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -1679,7 +1679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -1836,7 +1836,11 @@
           <t>AvitoDateEnd</t>
         </is>
       </c>
-      <c r="AC2" s="7" t="n"/>
+      <c r="AC2" s="7" t="inlineStr">
+        <is>
+          <t>DateBegin</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -2707,6 +2711,246 @@
       <c r="Z9" t="inlineStr">
         <is>
           <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4008346466</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4008346466/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4008346466/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4008346466/05_03.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>350</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ель пиловочник (документы ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ель, пиловочник хвойный. Диаметр от 18 до 40 см, длина 4 и 6 метров, рубка свежая, зимней заготовки. Партии от вагона и больше, объём под ваш запрос собираем с делянки в Архангельской области.&lt;br&gt;&lt;br&gt;Ставлю ваш лес на баланс официально: закрепляю древесину за вами в ФГИС ЛК через договор, оформляю постановку на учёт, чтобы вы законно продавали и возили. Делаю QR-код и ЭСД на перевозку, закрываю расхождения объёмов, готовлю отчёты и декларации. Работаю сам, знаю систему изнутри как заготовитель.&lt;br&gt;&lt;br&gt;Напишите в сообщения, разберу вашу ситуацию и отвечу за пару минут. Пришлите замеры, посчитаю сегодня.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Архангельская область, Мирный, ул. Мира, 40</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2026-08-21T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-07-22T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4374877725</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4374877725/15_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4374877725/15_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4374877725/15_03.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>300</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Кедр кругляк (QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Кедр с делянки, диаметр от 20 до 44 см, длина 4 и 6 метров. Зимняя заготовка, деловой сортимент, партия от 200 кубов и больше. Отгрузка с площадки в Молчаново, лес чистый, замеры честные по факту.&lt;br&gt;&lt;br&gt;Второе направление у меня по документам. Сам вожу лес и сам оформляю, поэтому знаю кухню изнутри. Делаю QR код и ЭСД на вывоз леса, чтобы первый же рейс ушёл без риска штрафов от лесного контроля. Работаю как посредник и консультант: разберу вашу ситуацию по вывозке, подскажу как правильно поставить объём и закрыть перевозку в системе ФГИС ЛК. Всё удалённо, по фото замеров, без вашего приезда, быстро.&lt;br&gt;&lt;br&gt;Пришлите фото замеров в сообщения, посчитаю и подскажу по срокам сегодня.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Томская область, Молчаново, ул. Мира, 20</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2026-08-23T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-07-24T10:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="25"/>
@@ -3487,7 +3731,11 @@
           <t>AvitoStatus</t>
         </is>
       </c>
-      <c r="AC2" s="7" t="n"/>
+      <c r="AC2" s="7" t="inlineStr">
+        <is>
+          <t>DateBegin</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -4279,6 +4527,402 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>Активно</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2495576390</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2495576390/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2495576390/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2495576390/08_03.jpg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>400</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Берёза кругляк (поставить лес на баланс)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Берёза кругляк и балансы, диаметр от 16 до 32 см, длина 4 и 6 метров. Заготовка свежая, партии от машины и до вагона, отгрузка по Ярославлю и области.&lt;br&gt;&lt;br&gt;Веду документы ФГИС ЛК. Если лес заготовлен, а в системе его нет, официально ставлю древесину на баланс вашей компании через договор купли-продажи. Объём закрепляется за вами, дальше можно законно продавать и возить. Оформляю QR и ЭСД на перевозку, закрываю расхождения, готовлю отчёты и декларации. Консультирую по всей цепочке, разберу вашу ситуацию с нуля.&lt;br&gt;&lt;br&gt;Напишите в сообщения ваш объём и регион, посчитаю сегодня и подскажу по срокам, отвечаю за пару минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Ярославская область, Ярославль, ул. Транспортная, 61</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-22T04:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-07-23T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8857956292</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8857956292/18_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8857956292/18_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8857956292/18_03.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>300</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Ель кругляк (документы ФГИС ЛК удалённо)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ель кругляк и пиловочник, диаметр от 18 до 34 см, длина 4 и 6 метров. Свежая заготовка из Коми, партии от машины и больше, отгрузка по запросу.&lt;br&gt;&lt;br&gt;Веду всю документацию ФГИС ЛК удалённо, без ваших поездок в кабинет. Оформляю QR и ЭСД на перевозку, ставлю лес на баланс через договор, закрываю расхождения объёмов, готовлю отчёты, декларации и сопроводительные. Достаточно прислать фото замеров, дальше всё делаю сам и держу связь по каждому шагу.&lt;br&gt;&lt;br&gt;Напишите в сообщения, что нужно закрыть по бумагам, разберу вашу ситуацию и отвечу за пару минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Республика Коми, Микунь, ул. Транспортная, 41</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-24T04:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-07-25T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1505263438</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1505263438/22_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1505263438/22_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1505263438/22_03.jpg</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>350</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Берёза кругляк (закрытие расхождений ФГИС)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Берёза кругляк и деловая древесина, диаметр от 16 до 32 см, длина 4 и 6 метров. Заготовка свежая, партии от машины и больше, отгрузка по Чебоксарам и региону.&lt;br&gt;&lt;br&gt;Веду документы ФГИС ЛК. Закрываю расхождения объёмов официально через договор купли-продажи, когда в системе цифры не сходятся с фактом. Готовлю лесные декларации и отчётность в срок, ставлю древесину на баланс, оформляю QR и ЭСД на перевозку. Разбираю запутанные остатки, даже если минус ушёл давно.&lt;br&gt;&lt;br&gt;Пришлите ваши цифры по бумагам и по факту, посмотрю сегодня и скажу, как свести. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Чувашская Республика, Чебоксары, ул. Заводская, 69</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-24T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-07-25T13:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -4930,7 +5574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ66"/>
+  <dimension ref="A1:AJ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -13734,6 +14378,1821 @@
       <c r="AJ66" t="inlineStr">
         <is>
           <t>2026-07-17T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>5937878704</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (QR код и ЭСД на перевозку)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Лес есть, а документов на вывоз нет. Знакомая история. У нас сосновый пиловочник свежей заготовки, диаметр от 18 до 32 см, длина 4 и 6 метров, партия отгружается машинами.&lt;br&gt;&lt;br&gt;По бумагам закрываем всё в ФГИС ЛК: оформляем QR код и ЭСД на рейс, чтобы первая же машина ушла без риска штрафов от лесконтроля. Считаем по фото замеров удалённо, раньше это звалось ЛесЕГАИС, суть та же. Делаем быстро и без ваших поездок в кабинет.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и подскажу по срокам.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_03.jpg</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Республика Карелия, Беломорск, ул. Лесная, 12</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>210</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>2026-08-20T18:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>2026-07-21T20:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>6036836126</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Лиственница пиловочник (QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Лиственница, пиловочник свежей заготовки. Диаметр от 18 до 40 см, длина 4 и 6 метров, рубка этого сезона. Партия от лесовоза и больше, отгружаем с делянки без простоев. Лес ровный, сухостоя нет.&lt;br&gt;&lt;br&gt;Второе, чем занимаюсь по документам ФГИС ЛК. Оформляю QR код и ЭСД на вывоз леса, чтобы первый же рейс ушёл без риска штрафов от лесного контроля. Работаю удалённо по фото ваших замеров, ничего никуда везти не надо. QR готов за пару минут, вы сразу грузите и едете. Всё чисто по декларации и остаткам на балансе.&lt;br&gt;&lt;br&gt;Пришлите фото замеров в сообщения, посчитаю и выдам QR сегодня, отвечу в течение пары минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_03.jpg</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Иркутская область, Нижнеудинск, ул. Заводская, 19</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Лиственница</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>220</v>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>2026-08-20T19:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3305654333</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Берёза пиловочник (не сходятся объёмы ФГИС)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Берёза, пиловочник и балансы. Диаметр 16-32 см, длина 4 и 6 метров, свежая зимняя заготовка со своих делянок. Партии от машины и больше, отгрузка с площадки под Мурашами.&lt;br&gt;&lt;br&gt;Отдельно ведём документы ФГИС ЛК. Знакомая история: по факту один объём, а в системе цифры не сходятся, остаток то в минус, то в плюс, перевозку не оформить. Закрываем расхождения официально, через договор купли-продажи, ставим лес на баланс и делаем QR-код с ЭСД на любой объём. Работаем чисто, без серых схем.&lt;br&gt;&lt;br&gt;Напишите в сообщения ваши остатки и замеры, посмотрю сегодня и скажу, как ровно свести объём.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_03.jpg</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Кировская область, Мураши, ул. Советская, 26</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>2026-08-21T04:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>2026-07-22T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1048199473</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (QR и ЭСД на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Сосна пиловочник свежей заготовки. Диаметр от 18 до 34 см, длина 4 и 6 метров, рубка этого сезона. Партии от машины и до крупного опта, отгрузка по Омску и области идёт постоянно, поэтому объём держим стабильно.&lt;br&gt;&lt;br&gt;Омск город большой, машины уходят потоком, и на каждый рейс нужны чистые документы ФГИС ЛК. Оформляю QR код и ЭСД на вывоз леса, чтобы первый же рейс прошёл без риска штрафов от лесного контроля. Работаю по фото ваших замеров, удалённо и быстро, ставлю объём на баланс, закрываю расхождения, готовлю отчёты и декларации.&lt;br&gt;&lt;br&gt;Пришлите фото замеров в сообщения, посчитаю и оформлю сегодня, отвечаю в течение пары минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1048199473/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1048199473/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1048199473/04_03.jpg</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Омская область, Омск, ул. Промышленная, 33</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>240</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>2026-08-21T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>2026-07-22T08:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>5783794994</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Сосна с делянки в Костромской области, свежая заготовка. Пиловочник диаметр от 18 до 34 см, длина 4 и 6 метров, комель ровный, без гнили. Партия от 50 кубов, отгрузка с площадки под Буем, лесовозами.&lt;br&gt;&lt;br&gt;По документам работаю сам, оформляю QR код и ЭСД на вывоз леса удалённо. Присылаете фото замеров, готовлю сопроводиловку на первый рейс так, чтобы лесконтроль на дороге вопросов не задал и штрафов не прилетело. Ставлю лес на баланс, закрываю расхождения объёмов, веду отчёты и декларации в ФГИС ЛК.&lt;br&gt;&lt;br&gt;Напишите в сообщения, отвечу за пару минут и посчитаю ваш рейс сегодня.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_03.jpg</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Костромская область, Буй, ул. Октябрьская, 47</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB71" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>2026-07-22T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>7025347023</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Хвоя пиловочник (ЭСД на перевозку)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Хвойный пиловочник с делянки под Воркутой. Сосна и ель, диаметр от 18 до 34 см, длина 4 и 6 метров, свежая зимняя заготовка. Партии от машины до вагона, объём набираем под ваш вывоз, отсортировано по длинам.&lt;br&gt;&lt;br&gt;Веду документы ФГИС ЛК под перевозку. Оформляю QR-код и ЭСД на вывоз леса так, чтобы первый же рейс шёл без риска штрафов от лесконтроля. Работаю по фото ваших замеров удалённо, отдельная ЭСД на каждую машину, ничего не путается на посту. Ставлю лес на баланс, закрываю расхождения по объёму, готовлю отчёты и декларацию.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и отдам ЭСД к загрузке.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7025347023/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7025347023/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7025347023/07_03.jpg</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Республика Коми, Воркута, пр-т Ленина, 54</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>210</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>2026-08-21T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>2026-07-22T13:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3645797250</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Сосна кругляк зимник (ЭСД и QR на вагон)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Сосна пиловочник зимней заготовки, диаметр от 18 до 36 см, длина 4 и 6 метров. Лес с делянки, вывозка по зимнику, набираем вагонные объёмы под отгрузку.&lt;br&gt;&lt;br&gt;По документам ФГИС ЛК работаю сам. Оформляю QR код и ЭСД на вывоз леса под вагон и под каждую машину, чтобы отгрузка ушла без риска штрафов от лесного контроля. Считаю по фото ваших замеров удалённо, документы держу готовыми к рейсу. Ставлю объём на баланс, закрываю расхождения, веду отчёты и декларации.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и оформлю к отгрузке, отвечу за пару минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3645797250/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3645797250/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3645797250/09_03.jpg</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Красноярский край, Дивногорск, ул. Гагарина, 68</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>2026-08-22T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>2026-07-23T08:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1173035880</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Ель пиловочник (не сходятся объёмы ФГИС)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ель, пиловочник свежей заготовки. Диаметр от 18 до 34 см, длина 4 и 6 метров, рубка зимняя, вывозим с делянки под Никольском. Партии от машины и до вагонных объёмов, комель ровный, гнили нет. Отгружаем по вашему запросу, замеры честные.&lt;br&gt;&lt;br&gt;Отдельно веду документы ФГИС ЛК. Знакомая история: по бумагам один объём, по факту на складе другой, и цифры не сходятся. Закрываю такое расхождение официально, через договор купли-продажи, ставлю недостающий объём на баланс. Делаю QR и ЭСД на перевозку, отчёты и декларации. Объём любой, привязка к вашим фактическим замерам.&lt;br&gt;&lt;br&gt;Пришлите свои цифры по бумагам и по факту, за пару минут гляну и скажу, как свести. Пишите прямо в сообщения.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1173035880/10_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1173035880/10_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1173035880/10_03.jpg</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Вологодская область, Никольск, ул. Строителей, 75</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB74" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>240</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>2026-08-22T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>2026-07-23T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8614045973</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Осина пиловочник (QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Осина с делянки, свежая заготовка. Пиловочник диаметром от 14 до 30 см, длина 4 и 6 метров, есть дровяная часть на топливо. Партия от 50 кубов, отгрузка прямо с площадки, плечо короткое, лесовоз обернётся за день.&lt;br&gt;&lt;br&gt;Оформляю QR код и ЭСД на вывоз леса. Первый рейс уходит без риска штрафов от лесконтроля. Работаю по фото ваших замеров удалённо, документы на перевозку готовлю быстро, водителю остаётся только загрузиться и выехать.&lt;br&gt;&lt;br&gt;Пришлите фото замеров, посчитаю сегодня и пришлю QR к рейсу, отвечу в сообщениях за пару минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8614045973/12_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8614045973/12_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8614045973/12_03.jpg</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Новгородская область, Старая Русса, ул. Заводская, 89</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Осина</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>2026-08-22T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>2026-07-23T13:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>7435263739</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (ЭСД и QR на рейс)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Сосна свежего спила, деляна своя. Диаметр 18-32 см, длина 4 и 6 метров, распил под ваш размер. Партия от 50 кубов, отгрузка с площадки под Иваново.&lt;br&gt;&lt;br&gt;Работаем по документам ФГИС ЛК: оформляем QR код и ЭСД на вывоз леса, чтобы первый же рейс ушёл без риска штрафов от лесконтроля. Достаточно прислать фото замеров, всё считаем удалённо и быстро, вы получаете готовый электронный сопроводительный на машину.&lt;br&gt;&lt;br&gt;Иваново город крупный, спокойно берём и на товарный тест малой партией, чтобы вы проверили качество и документы. Пришлите замеры, посчитаю сегодня и оформлю на первый рейс.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7435263739/13_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7435263739/13_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7435263739/13_03.jpg</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Ивановская область, Иваново, ул. Советская, 6</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB76" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>210</v>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>2026-08-23T04:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>2026-07-24T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>5855275648</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Берёза пиловочник (лес на баланс ФГИС)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Берёза свежей заготовки, диаметр от 18 до 34 см, длина 4 и 6 метров. Пиловочник ровный, без гнили и синевы, партии от 20 кубов и выше, отгрузка с делянки под Нелидово.&lt;br&gt;&lt;br&gt;Отдельно ставлю лес на баланс в ФГИС ЛК. Оформляю договор, закрепляю древесину за вами официально, чтобы возить и продавать законно. Сделаю QR и ЭСД на перевозку, закрою расхождения объёмов, подготовлю отчёты и декларацию. Работаю сам, сроки короткие, всё по факту заготовки.&lt;br&gt;&lt;br&gt;Пришлите замеры и объём, посчитаю по вашей партии сегодня и подскажу, что нужно для баланса. Напишите в сообщения, отвечу в течение пары минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_03.jpg</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Тверская область, Нелидово, ул. Промышленная, 13</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB77" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>220</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>2026-08-23T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>2026-07-24T08:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1803116670</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ель пиловочник (закрытие расхождений ФГИС)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ель, пиловочник хвойный. Диаметр 18-32 см, длина 4 и 6 метров, свежая зимняя заготовка со своих делянок в Карелии. Отбираем по качеству, торцовка ровная, без гнили и обзола. Партия от кубометра до крупного объёма под вагон.&lt;br&gt;&lt;br&gt;Отдельно работаем с документами по лесу. Если в ФГИС ЛК цифры не сходятся с фактом, помогаем закрыть расхождение официально через договор купли-продажи. Ставим объём на баланс, оформляем QR-код и ЭСД на перевозку, готовим отчёты и декларацию. Объём любой, разберёмся даже если минус ушёл давно.&lt;br&gt;&lt;br&gt;Пришлите свои замеры и остатки по системе, посчитаю сегодня и скажу, как закрыть. Пишите в сообщения, отвечаю в течение пары минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1803116670/16_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1803116670/16_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1803116670/16_03.jpg</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Республика Карелия, Лахденпохья, ул. Октябрьская, 27</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB78" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>240</v>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>2026-08-23T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>2026-07-24T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>9140846526</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (ЭСД на перевозку леса)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Сосна, пиловочник хвойный. Диаметр от 18 до 34 см, длина 4 и 6 метров. Зимняя заготовка, древесина ровная, без синевы и гнили. Партия от 30 кубов, отгрузка с площадки во Владимире, объём набираем под ваш запрос.&lt;br&gt;&lt;br&gt;По документам ФГИС ЛК веду сам. Оформляю QR-код и ЭСД на вывоз леса ровно под ваш объём, чтобы первый рейс ушёл спокойно, без риска штрафов от лесного контроля. Работаю по фото замеров, удалённо и быстро. Город крупный, машины ходят часто, поэтому документы держу готовыми заранее. Декларации и отчёты тоже закрою.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и скажу, что нужно для перевозки.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/9140846526/17_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/9140846526/17_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/9140846526/17_03.jpg</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Владимирская область, Владимир, пр-т Ленина, 34</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB79" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>250</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>2026-08-23T11:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>2026-07-24T13:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>7232164186</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (ЭСД и QR к сделке)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Сосна пиловочник свежей заготовки, диаметр от 18 до 34 см, длина 4 и 6 метров. Партии от машины и выше, отгрузка с площадки под Тихвином.&lt;br&gt;&lt;br&gt;По документам ФГИС ЛК оформляю QR код и ЭСД под сделку и первый рейс, чтобы машина ушла без риска штрафов от лесконтроля, а покупатель получил чистый объём на балансе. Работаю по фото ваших замеров удалённо, документы готовлю к дате отгрузки. Ставлю лес на баланс, закрываю расхождения, веду отчёты и декларации.&lt;br&gt;&lt;br&gt;Пришлите замеры и дату рейса, посчитаю сегодня и оформлю к сделке. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_03.jpg</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Ленинградская область, Тихвин, ул. Гагарина, 48</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>250</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB80" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>210</v>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>2026-08-24T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2872293673</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (QR код на отгрузку)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Сосна пиловочник с делянки под Галичем, диаметр от 18 до 34 см, длина 4 и 6 метров. Свежая заготовка, партия под отгрузку от 50 кубов, лес ровный, без гнили.&lt;br&gt;&lt;br&gt;Оформляю QR код и ЭСД на вывоз леса под вашу партию. Первый рейс уходит без риска штрафов от лесного контроля, документы считаю по фото замеров удалённо и быстро. Ставлю объём на баланс, закрываю расхождения, готовлю отчёты и декларации в ФГИС ЛК.&lt;br&gt;&lt;br&gt;Пришлите фото замеров в сообщения, посчитаю сегодня и выдам QR к отгрузке, отвечу за пару минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_03.jpg</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Костромская область, Галич, ул. Лесная, 62</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB81" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>2026-08-24T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>2026-07-25T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -15130,7 +17589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="14"/>
@@ -15240,7 +17699,11 @@
           <t>CompanyName</t>
         </is>
       </c>
-      <c r="T2" s="7" t="n"/>
+      <c r="T2" s="7" t="inlineStr">
+        <is>
+          <t>DateBegin</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -16037,6 +18500,176 @@
       <c r="S11" t="inlineStr">
         <is>
           <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4287305104</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4287305104/11_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4287305104/11_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4287305104/11_03.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>350</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (документы и учёт ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Сосна пиловочник со своей делянки под Кунгуром. Диаметр от 18 до 34 см, длина 4 и 6 метров, рубка свежая, зимней и летней заготовки. Отгружаем партиями от машины и больше, объём набираем под ваш запрос.&lt;br&gt;&lt;br&gt;Отдельно веду документы ФГИС ЛК. Официально ставлю лес на баланс и закрепляю древесину за вами через договор, чтобы вы могли законно возить и продавать. Делаю обработку материалов лесосеки, свожу учёт остатков, оформляю QR и ЭСД на перевозку, закрываю расхождения по объёму, готовлю отчёты и декларации.&lt;br&gt;&lt;br&gt;Пришлите замеры и породу, посчитаю сегодня и скажу, что нужно по бумагам. Напишите в сообщения, отвечу в течение пары минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Пермский край, Кунгур, ул. Лесная, 82</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Оборудование, производство</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Производство, обработка</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Обработка материалов</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-08-22T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-07-23T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8855945319</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8855945319/20_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8855945319/20_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8855945319/20_03.jpg</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>400</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Берёза кругляк (лес на баланс складской учёт)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Берёза кругляк и балансы, диаметр от 16 до 32 см, длина 4 и 6 метров. Заготовка свежая, партии от машины и до крупного опта, отгрузка по Оренбургу и области.&lt;br&gt;&lt;br&gt;Ставлю лес на баланс в ФГИС ЛК и свожу складской учёт остатков. Официально закрепляю древесину за вашей компанией через договор, чтобы объём в системе совпадал с фактом на площадке. Делаю обработку данных по лесосеке, оформляю QR и ЭСД на перевозку, закрываю расхождения, готовлю отчёты и декларации.&lt;br&gt;&lt;br&gt;Пришлите остатки по системе и по факту, посчитаю сегодня и скажу, как ровно свести учёт. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Оренбургская область, Оренбург, ул. Строителей, 55</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Оборудование, производство</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Производство, обработка</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Обработка материалов</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-08-24T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-07-25T10:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -2755,7 +2755,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Ель, пиловочник хвойный. Диаметр от 18 до 40 см, длина 4 и 6 метров, рубка свежая, зимней заготовки. Партии от вагона и больше, объём под ваш запрос собираем с делянки в Архангельской области.&lt;br&gt;&lt;br&gt;Ставлю ваш лес на баланс официально: закрепляю древесину за вами в ФГИС ЛК через договор, оформляю постановку на учёт, чтобы вы законно продавали и возили. Делаю QR-код и ЭСД на перевозку, закрываю расхождения объёмов, готовлю отчёты и декларации. Работаю сам, знаю систему изнутри как заготовитель.&lt;br&gt;&lt;br&gt;Напишите в сообщения, разберу вашу ситуацию и отвечу за пару минут. Пришлите замеры, посчитаю сегодня.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на лес в ФГИС ЛК. Сам лес не продаём, работаем только по бумагам официально через договор, город Мирный.&lt;br&gt;&lt;br&gt;Если у вас есть заготовленный лес, а в системе его нет, ставим древесину на баланс компании через договор и закрепляем объём в ФГИС ЛК, чтобы можно было законно продавать и возить.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;QR-код и ЭСД на перевозку, чтобы лесовоз шёл с документами.&lt;br&gt;Закрываем расхождения по кубам, когда замеры на деляне не сошлись с системой.&lt;br&gt;Ель, кругляк, пиловочник, балансы, дрова с делянки, вывозка. Если лес есть, а документов нет, оформим.&lt;br&gt;Ведём декларации и отчёты.&lt;br&gt;&lt;br&gt;Пришлите замеры по своей деляне, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Кедр с делянки, диаметр от 20 до 44 см, длина 4 и 6 метров. Зимняя заготовка, деловой сортимент, партия от 200 кубов и больше. Отгрузка с площадки в Молчаново, лес чистый, замеры честные по факту.&lt;br&gt;&lt;br&gt;Второе направление у меня по документам. Сам вожу лес и сам оформляю, поэтому знаю кухню изнутри. Делаю QR код и ЭСД на вывоз леса, чтобы первый же рейс ушёл без риска штрафов от лесного контроля. Работаю как посредник и консультант: разберу вашу ситуацию по вывозке, подскажу как правильно поставить объём и закрыть перевозку в системе ФГИС ЛК. Всё удалённо, по фото замеров, без вашего приезда, быстро.&lt;br&gt;&lt;br&gt;Пришлите фото замеров в сообщения, посчитаю и подскажу по срокам сегодня.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Сразу к делу: мы оформляем документы на лес в системе ФГИС ЛК, а сам лес не продаём. Если у вас есть кедр, кругляк, пиловочник, балансы или дрова, а бумаг на вывозку нет, мы всё посчитаем и оформим.&lt;br&gt;&lt;br&gt;Готовим QR-код и ЭСД на перевозку, чтобы лесовоз прошёл лесной контроль без штрафов. Считаем удалённо по фото ваших замеров: скидываете кубы с деляны, мы переводим в документ.&lt;br&gt;&lt;br&gt;Закрываем расхождения по объёмам, ставим лес на баланс, делаем декларации и отчёты. Работаем как посредник и консультант по всей вывозке, из Молчаново, разберём вашу ситуацию по шагам.&lt;br&gt;&lt;br&gt;Напишите в сообщения, отвечу за пару минут. Пришлите замеры с делянки, посчитаю сегодня.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Берёза кругляк и балансы, диаметр от 16 до 32 см, длина 4 и 6 метров. Заготовка свежая, партии от машины и до вагона, отгрузка по Ярославлю и области.&lt;br&gt;&lt;br&gt;Веду документы ФГИС ЛК. Если лес заготовлен, а в системе его нет, официально ставлю древесину на баланс вашей компании через договор купли-продажи. Объём закрепляется за вами, дальше можно законно продавать и возить. Оформляю QR и ЭСД на перевозку, закрываю расхождения, готовлю отчёты и декларации. Консультирую по всей цепочке, разберу вашу ситуацию с нуля.&lt;br&gt;&lt;br&gt;Напишите в сообщения ваш объём и регион, посчитаю сегодня и подскажу по срокам, отвечаю за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Сразу по делу: мы оформляем документы на лес в ФГИС ЛК, сам лес не продаём. Если у вас есть берёза, кругляк, пиловочник, балансы или дрова, а бумаг на них нет, приходите, всё сделаем по закону.&lt;br&gt;&lt;br&gt;Что закрываем: QR-код и ЭСД на перевозку, чтобы лесовоз шёл с документами. Расхождения по объёмам и кубам приводим в порядок. Замеры с деляны сверим и пересчитаем.&lt;br&gt;&lt;br&gt;Отдельно про баланс. Лес заготовлен, а в системе его нет: ставим древесину на баланс компании через договор и закрепляем объём в ФГИС ЛК. После этого можно законно возить и продавать.&lt;br&gt;&lt;br&gt;Работаем из Ярославля, консультируем по всем вопросам. Напишите в сообщения, отвечу за пару минут. Пришлите замеры, посчитаю сегодня.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Ель кругляк и пиловочник, диаметр от 18 до 34 см, длина 4 и 6 метров. Свежая заготовка из Коми, партии от машины и больше, отгрузка по запросу.&lt;br&gt;&lt;br&gt;Веду всю документацию ФГИС ЛК удалённо, без ваших поездок в кабинет. Оформляю QR и ЭСД на перевозку, ставлю лес на баланс через договор, закрываю расхождения объёмов, готовлю отчёты, декларации и сопроводительные. Достаточно прислать фото замеров, дальше всё делаю сам и держу связь по каждому шагу.&lt;br&gt;&lt;br&gt;Напишите в сообщения, что нужно закрыть по бумагам, разберу вашу ситуацию и отвечу за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на лес в ФГИС ЛК удалённо, сам лес мы не продаём. Если у вас заготовлена ель, кругляк, пиловочник или балансы, а в системе леса нет или бумаги не в порядке, ведём всю документацию за вас.&lt;br&gt;&lt;br&gt;Ставим древесину на баланс компании через договор и закрепляем объём в ФГИС ЛК, чтобы можно было законно возить и продавать. Делаем QR-код и ЭСД на перевозку, закрываем расхождения по кубам, готовим декларации, отчёты и сопроводительные.&lt;br&gt;&lt;br&gt;Работаем по Микуни и всему району, без ваших поездок в кабинет. Достаточно прислать фото замеров с деляны.&lt;br&gt;&lt;br&gt;Напишите в сообщения, что нужно закрыть по бумагам, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Берёза кругляк и деловая древесина, диаметр от 16 до 32 см, длина 4 и 6 метров. Заготовка свежая, партии от машины и больше, отгрузка по Чебоксарам и региону.&lt;br&gt;&lt;br&gt;Веду документы ФГИС ЛК. Закрываю расхождения объёмов официально через договор купли-продажи, когда в системе цифры не сходятся с фактом. Готовлю лесные декларации и отчётность в срок, ставлю древесину на баланс, оформляю QR и ЭСД на перевозку. Разбираю запутанные остатки, даже если минус ушёл давно.&lt;br&gt;&lt;br&gt;Пришлите ваши цифры по бумагам и по факту, посмотрю сегодня и скажу, как свести. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на лес в ФГИС ЛК. Сам лес мы не продаём и не покупаем, работаем только по бумагам. Если у вас есть берёза, кругляк, пиловочник, балансы или дрова, а документов на них нет или они не сходятся, приводим всё в порядок официально.&lt;br&gt;&lt;br&gt;Делаем QR-код и ЭСД на перевозку, ставим лес на баланс, закрываем расхождения объёмов. Когда по системе один объём, а на деляне или складе по факту другой, сводим цифры через договор купли-продажи, чтобы вывозка лесовозом шла чисто и без вопросов.&lt;br&gt;&lt;br&gt;Работаем по всей Чувашии, база в Чебоксарах. Ведём декларации и отчётность, если своими силами разбираться некогда.&lt;br&gt;&lt;br&gt;Пришлите замеры по кубам, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Берёза, пиловочник и балансы. Диаметр 16-32 см, длина 4 и 6 метров, свежая зимняя заготовка со своих делянок. Партии от машины и больше, отгрузка с площадки под Мурашами.&lt;br&gt;&lt;br&gt;Отдельно ведём документы ФГИС ЛК. Знакомая история: по факту один объём, а в системе цифры не сходятся, остаток то в минус, то в плюс, перевозку не оформить. Закрываем расхождения официально, через договор купли-продажи, ставим лес на баланс и делаем QR-код с ЭСД на любой объём. Работаем чисто, без серых схем.&lt;br&gt;&lt;br&gt;Напишите в сообщения ваши остатки и замеры, посмотрю сегодня и скажу, как ровно свести объём.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Это услуга по бумагам, а не торговля кругляком.&lt;br&gt;&lt;br&gt;Работаю по Мурашам и району. Если по системе один объём, а на деляне или на складе по факту другой, свожу это официально. Берёза, пиловочник, балансы, дрова, осиновый кругляк, любой сортимент. Замерили лесовоз, а цифры в ФГИС не сходятся, расхождение висит и мешает вывозке, закрою через договор купли-продажи и приведу объём в порядок.&lt;br&gt;&lt;br&gt;Делаю QR и ЭСД на перевозку, ставлю лес на баланс, готовлю декларации и отчёты. Если у вас есть лес, а документов на него нет, оформлю.&lt;br&gt;&lt;br&gt;Пришлите замеры по делянке, посчитаю сегодня и скажу, как свести объёмы. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сосна пиловочник свежей заготовки. Диаметр от 18 до 34 см, длина 4 и 6 метров, рубка этого сезона. Партии от машины и до крупного опта, отгрузка по Омску и области идёт постоянно, поэтому объём держим стабильно.&lt;br&gt;&lt;br&gt;Омск город большой, машины уходят потоком, и на каждый рейс нужны чистые документы ФГИС ЛК. Оформляю QR код и ЭСД на вывоз леса, чтобы первый же рейс прошёл без риска штрафов от лесного контроля. Работаю по фото ваших замеров, удалённо и быстро, ставлю объём на баланс, закрываю расхождения, готовлю отчёты и декларации.&lt;br&gt;&lt;br&gt;Пришлите фото замеров в сообщения, посчитаю и оформлю сегодня, отвечаю в течение пары минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляю документы на лес в системе ФГИС ЛК, сам лес не продаю. Если у вас есть кругляк, пиловочник, балансы или дрова с деляны, а бумаг на них нет, помогу привести всё в порядок по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код и ЭСД на вывоз леса, чтобы лесовоз прошёл лесной контроль без штрафов. Считаю по фото замеров, удалённо, вам никуда ехать не надо.&lt;br&gt;&lt;br&gt;Закрываю расхождения по кубам, ставлю сосну и другой лес на баланс, готовлю декларации и отчёты. Работаю по Омску и области, объёмы любые, вывозка хоть каждый день.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и скажу, что нужно для документов. Отвечаю в течение пары минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сосна с делянки в Костромской области, свежая заготовка. Пиловочник диаметр от 18 до 34 см, длина 4 и 6 метров, комель ровный, без гнили. Партия от 50 кубов, отгрузка с площадки под Буем, лесовозами.&lt;br&gt;&lt;br&gt;По документам работаю сам, оформляю QR код и ЭСД на вывоз леса удалённо. Присылаете фото замеров, готовлю сопроводиловку на первый рейс так, чтобы лесконтроль на дороге вопросов не задал и штрафов не прилетело. Ставлю лес на баланс, закрываю расхождения объёмов, веду отчёты и декларации в ФГИС ЛК.&lt;br&gt;&lt;br&gt;Напишите в сообщения, отвечу за пару минут и посчитаю ваш рейс сегодня.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Сразу к делу: мы не продаём лес, мы оформляем на него документы в системе ФГИС ЛК. Если у вас есть кругляк, пиловочник сосны, балансы или дрова с деляны, а бумаг на вывоз нет, мы их сделаем.&lt;br&gt;&lt;br&gt;Готовим QR-код и ЭСД (электронный сопроводительный документ) на перевозку, чтобы лесовоз прошёл лесной контроль и первый же рейс ушёл без штрафов. Работаем удалённо: пришлите фото замеров по кубам, посчитаем объём и оформим сами.&lt;br&gt;&lt;br&gt;Также закрываем расхождения объёмов, ставим лес на баланс, готовим декларации и отчёты. Город Буй, работаем со всеми регионами.&lt;br&gt;&lt;br&gt;Есть делянка, вывозка на носу, а документов нет: напишите в сообщения, отвечу за пару минут. Пришлите замеры сегодня, посчитаю сегодня.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -15009,7 +15009,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Хвойный пиловочник с делянки под Воркутой. Сосна и ель, диаметр от 18 до 34 см, длина 4 и 6 метров, свежая зимняя заготовка. Партии от машины до вагона, объём набираем под ваш вывоз, отсортировано по длинам.&lt;br&gt;&lt;br&gt;Веду документы ФГИС ЛК под перевозку. Оформляю QR-код и ЭСД на вывоз леса так, чтобы первый же рейс шёл без риска штрафов от лесконтроля. Работаю по фото ваших замеров удалённо, отдельная ЭСД на каждую машину, ничего не путается на посту. Ставлю лес на баланс, закрываю расхождения по объёму, готовлю отчёты и декларацию.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и отдам ЭСД к загрузке.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на лес в системе ФГИС ЛК. Сам лес мы не продаём и не покупаем, только делаем бумаги на него.&lt;br&gt;&lt;br&gt;Если у вас есть кругляк, пиловочник, хвоя, балансы или дрова, а машину надо отправить в рейс и провезти через лесной контроль без штрафов, мы оформим QR-код и ЭСД (электронный сопроводительный документ) на каждый лесовоз.&lt;br&gt;&lt;br&gt;Работаем удалённо по всей Воркуте и району. Считаем по фото ваших замеров с деляны: скинете кубы и породу, посчитаем объём и подготовим ЭСД, чтобы лесовоз ушёл в путь с чистыми документами.&lt;br&gt;&lt;br&gt;Также закрываем расхождения по объёмам, ставим лес на баланс, готовим декларации и отчёты.&lt;br&gt;&lt;br&gt;Напишите в сообщения, отвечу за пару минут. Пришлите замеры, посчитаю сегодня.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сосна пиловочник зимней заготовки, диаметр от 18 до 36 см, длина 4 и 6 метров. Лес с делянки, вывозка по зимнику, набираем вагонные объёмы под отгрузку.&lt;br&gt;&lt;br&gt;По документам ФГИС ЛК работаю сам. Оформляю QR код и ЭСД на вывоз леса под вагон и под каждую машину, чтобы отгрузка ушла без риска штрафов от лесного контроля. Считаю по фото ваших замеров удалённо, документы держу готовыми к рейсу. Ставлю объём на баланс, закрываю расхождения, веду отчёты и декларации.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и оформлю к отгрузке, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас есть сосна, кругляк, пиловочник или балансы с деляны, а бумаг на вывозку нет, всё сделаю по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код и ЭСД на перевозку, чтобы лесовоз и вагон ушли с чистыми документами и прошли лесной контроль без штрафов. Работаю по зимнику, считаю по фото ваших замеров удалённо, под каждую машину и под отгрузку вагоном отдельный документ.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по кубам, ставлю лес на баланс, готовлю декларации и отчёты. Дивногорск и район, объёмы любые.&lt;br&gt;&lt;br&gt;Пришлите замеры с делянки, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Ель, пиловочник свежей заготовки. Диаметр от 18 до 34 см, длина 4 и 6 метров, рубка зимняя, вывозим с делянки под Никольском. Партии от машины и до вагонных объёмов, комель ровный, гнили нет. Отгружаем по вашему запросу, замеры честные.&lt;br&gt;&lt;br&gt;Отдельно веду документы ФГИС ЛК. Знакомая история: по бумагам один объём, по факту на складе другой, и цифры не сходятся. Закрываю такое расхождение официально, через договор купли-продажи, ставлю недостающий объём на баланс. Делаю QR и ЭСД на перевозку, отчёты и декларации. Объём любой, привязка к вашим фактическим замерам.&lt;br&gt;&lt;br&gt;Пришлите свои цифры по бумагам и по факту, за пару минут гляну и скажу, как свести. Пишите прямо в сообщения.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас есть кругляк, пиловочник, балансы или дрова, а бумаг на них нет или они не сходятся, привожу всё в порядок.&lt;br&gt;&lt;br&gt;Работаю по Никольску и району. Частый случай: по бумагам один объём, а по факту на деляне или на складе кубов другое количество. Закрываю это расхождение официально через договор купли-продажи и свожу объём, чтобы цифры бились.&lt;br&gt;&lt;br&gt;Делаю QR-код и ЭСД на вывозку, ставлю лес на баланс, готовлю декларации и отчёты. Ель, сосна, любой сортимент. Есть замеры с делянки, лесовоз готов ехать, а с системой затык, разберусь.&lt;br&gt;&lt;br&gt;Напишите в сообщения, отвечу за пару минут. Пришлите замеры, посчитаю сегодня.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Осина с делянки, свежая заготовка. Пиловочник диаметром от 14 до 30 см, длина 4 и 6 метров, есть дровяная часть на топливо. Партия от 50 кубов, отгрузка прямо с площадки, плечо короткое, лесовоз обернётся за день.&lt;br&gt;&lt;br&gt;Оформляю QR код и ЭСД на вывоз леса. Первый рейс уходит без риска штрафов от лесконтроля. Работаю по фото ваших замеров удалённо, документы на перевозку готовлю быстро, водителю остаётся только загрузиться и выехать.&lt;br&gt;&lt;br&gt;Пришлите фото замеров, посчитаю сегодня и пришлю QR к рейсу, отвечу в сообщениях за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на лес в системе ФГИС ЛК, сам лес мы не продаём. Если у вас есть кругляк, пиловочник, осина, балансы или дрова, а бумаг на них нет, поможем всё провести по системе.&lt;br&gt;&lt;br&gt;Собрался короткий рейс с дровами по Старой Руссе или рядом, а машину нечем закрыть по лесному контролю. Сделаем QR-код и ЭСД (электронный сопроводительный документ) на вывозку, чтобы лесовоз прошёл без штрафов. Считаем по фото замеров, удалённо, вам никуда ехать не нужно.&lt;br&gt;&lt;br&gt;Также ставим лес на баланс, закрываем расхождения по кубам, готовим декларации и отчёты по вашей деляне.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и скажу, что нужно для документов.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сосна свежего спила, деляна своя. Диаметр 18-32 см, длина 4 и 6 метров, распил под ваш размер. Партия от 50 кубов, отгрузка с площадки под Иваново.&lt;br&gt;&lt;br&gt;Работаем по документам ФГИС ЛК: оформляем QR код и ЭСД на вывоз леса, чтобы первый же рейс ушёл без риска штрафов от лесконтроля. Достаточно прислать фото замеров, всё считаем удалённо и быстро, вы получаете готовый электронный сопроводительный на машину.&lt;br&gt;&lt;br&gt;Иваново город крупный, спокойно берём и на товарный тест малой партией, чтобы вы проверили качество и документы. Пришлите замеры, посчитаю сегодня и оформлю на первый рейс.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас есть сосна, кругляк, пиловочник или дрова с деляны, а бумаг на них нет, приведу всё в порядок по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код и ЭСД на рейс, чтобы лесовоз прошёл лесной контроль без штрафов. Считаю по фото ваших замеров удалённо, вам никуда ехать не надо, на каждую машину свой документ под вывозку.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по объёмам, ставлю лес на баланс, готовлю декларации и отчёты. Иваново и область, объёмы любые, хоть малой партией на пробу.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня. Отвечаю за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Берёза свежей заготовки, диаметр от 18 до 34 см, длина 4 и 6 метров. Пиловочник ровный, без гнили и синевы, партии от 20 кубов и выше, отгрузка с делянки под Нелидово.&lt;br&gt;&lt;br&gt;Отдельно ставлю лес на баланс в ФГИС ЛК. Оформляю договор, закрепляю древесину за вами официально, чтобы возить и продавать законно. Сделаю QR и ЭСД на перевозку, закрою расхождения объёмов, подготовлю отчёты и декларацию. Работаю сам, сроки короткие, всё по факту заготовки.&lt;br&gt;&lt;br&gt;Пришлите замеры и объём, посчитаю по вашей партии сегодня и подскажу, что нужно для баланса. Напишите в сообщения, отвечу в течение пары минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас на деляне лежит заготовленная берёза, кругляк или пиловочник, а в системе его нет, помогу поставить древесину на баланс. Заключаем договор, закрепляем объём в ФГИС ЛК, и лес становится вашим официально, можно законно возить и продавать.&lt;br&gt;&lt;br&gt;Работаю по Нелидово и району. Балансы, дрова, делянка, вывозка лесовозами, замеры в кубах, любой объём. Сделаю QR и ЭСД на перевозку, закрою расхождение по объёмам, подготовлю декларации и отчёты.&lt;br&gt;&lt;br&gt;Пришлите замеры с делянки, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Ель, пиловочник хвойный. Диаметр 18-32 см, длина 4 и 6 метров, свежая зимняя заготовка со своих делянок в Карелии. Отбираем по качеству, торцовка ровная, без гнили и обзола. Партия от кубометра до крупного объёма под вагон.&lt;br&gt;&lt;br&gt;Отдельно работаем с документами по лесу. Если в ФГИС ЛК цифры не сходятся с фактом, помогаем закрыть расхождение официально через договор купли-продажи. Ставим объём на баланс, оформляем QR-код и ЭСД на перевозку, готовим отчёты и декларацию. Объём любой, разберёмся даже если минус ушёл давно.&lt;br&gt;&lt;br&gt;Пришлите свои замеры и остатки по системе, посчитаю сегодня и скажу, как закрыть. Пишите в сообщения, отвечаю в течение пары минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Мы не продаём лес, мы оформляем на него документы в ФГИС ЛК. Заготовили кругляк, а по бумагам он не бьётся или его вообще нет в системе. Мы это закрываем.&lt;br&gt;&lt;br&gt;Работаем по расхождениям. Когда по учёту один объём, а на деляне или на складе по факту другой, сводим кубы официально через договор купли-продажи. Ель, сосна, пиловочник, балансы, дрова, любой сортимент.&lt;br&gt;&lt;br&gt;Что делаем: ставим лес на баланс, закрываем расхождение объёмов, оформляем QR и ЭСД на вывозку, готовим декларации и отчёты. Если есть замеры с делянки, а лесовоз уже стоит, поможем оформить перевозку по закону.&lt;br&gt;&lt;br&gt;Лахденпохья и вся Карелия, работаем и по соседним районам. Напишите в сообщения свою ситуацию, отвечу за пару минут. Пришлите замеры, посчитаю сегодня.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -15856,7 +15856,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сосна, пиловочник хвойный. Диаметр от 18 до 34 см, длина 4 и 6 метров. Зимняя заготовка, древесина ровная, без синевы и гнили. Партия от 30 кубов, отгрузка с площадки во Владимире, объём набираем под ваш запрос.&lt;br&gt;&lt;br&gt;По документам ФГИС ЛК веду сам. Оформляю QR-код и ЭСД на вывоз леса ровно под ваш объём, чтобы первый рейс ушёл спокойно, без риска штрафов от лесного контроля. Работаю по фото замеров, удалённо и быстро. Город крупный, машины ходят часто, поэтому документы держу готовыми заранее. Декларации и отчёты тоже закрою.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и скажу, что нужно для перевозки.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на лес в системе ФГИС ЛК, сам лес мы не продаём. Если у вас есть кругляк, пиловочник, балансы или дрова, а бумаг на вывоз нет, мы закроем этот вопрос удалённо.&lt;br&gt;&lt;br&gt;Делаем QR-код и ЭСД (электронный сопроводительный документ) на перевозку, чтобы лесовоз прошёл лесной контроль и не поймал штраф. Считаем по фото замеров: скидываете кубы с деляны, мы оформляем ЭСД под ваш объём. Работаем по Владимиру и области, город крупный, объёмы тянем большие.&lt;br&gt;&lt;br&gt;Также ставим лес на баланс, закрываем расхождения по кубам, готовим декларации и отчёты.&lt;br&gt;&lt;br&gt;Напишите в сообщения, отвечу за пару минут. Пришлите замеры с деляны, посчитаю сегодня.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сосна пиловочник свежей заготовки, диаметр от 18 до 34 см, длина 4 и 6 метров. Партии от машины и выше, отгрузка с площадки под Тихвином.&lt;br&gt;&lt;br&gt;По документам ФГИС ЛК оформляю QR код и ЭСД под сделку и первый рейс, чтобы машина ушла без риска штрафов от лесконтроля, а покупатель получил чистый объём на балансе. Работаю по фото ваших замеров удалённо, документы готовлю к дате отгрузки. Ставлю лес на баланс, закрываю расхождения, веду отчёты и декларации.&lt;br&gt;&lt;br&gt;Пришлите замеры и дату рейса, посчитаю сегодня и оформлю к сделке. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Сразу главное: сам лес мы не продаём. Мы оформляем документы на лес в системе ФГИС ЛК, работаем из Тихвина удалённо.&lt;br&gt;&lt;br&gt;Если у вас есть сосна, пиловочник, кругляк, балансы или дрова на деляне, а бумаг на них нет, мы всё оформим. Поставим лес на баланс, закроем расхождения по кубам, сделаем декларации и отчёты.&lt;br&gt;&lt;br&gt;Отдельно по вывозке: делаем QR-код и ЭСД к сделке, чтобы лесовоз прошёл лесной контроль без штрафов. Считаем по фото замеров с деляны, ничего никуда везти не нужно.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и скажу, что нужно для перевозки. Отвечаю за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сосна пиловочник с делянки под Галичем, диаметр от 18 до 34 см, длина 4 и 6 метров. Свежая заготовка, партия под отгрузку от 50 кубов, лес ровный, без гнили.&lt;br&gt;&lt;br&gt;Оформляю QR код и ЭСД на вывоз леса под вашу партию. Первый рейс уходит без риска штрафов от лесного контроля, документы считаю по фото замеров удалённо и быстро. Ставлю объём на баланс, закрываю расхождения, готовлю отчёты и декларации в ФГИС ЛК.&lt;br&gt;&lt;br&gt;Пришлите фото замеров в сообщения, посчитаю сегодня и выдам QR к отгрузке, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на лес в системе ФГИС ЛК. Сам лес мы не продаём, делаем только бумаги на него. Если у вас есть своя партия под отгрузку в Галиче, сосна пиловочник, кругляк, балансы или дрова, а документов на неё нет, оформим всё по правилам.&lt;br&gt;&lt;br&gt;Сделаем QR-код и ЭСД на вывозку, чтобы лесовоз с грузом прошёл лесной контроль без штрафов. Закрываем расхождения по кубам, ставим лес на баланс, готовим декларации и отчёты.&lt;br&gt;&lt;br&gt;Считаем по фото ваших замеров, работаем удалённо, деляна может быть где угодно. Напишите в сообщения, отвечу за пару минут. Пришлите замеры с делянки, посчитаю сегодня.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сосна пиловочник со своей делянки под Кунгуром. Диаметр от 18 до 34 см, длина 4 и 6 метров, рубка свежая, зимней и летней заготовки. Отгружаем партиями от машины и больше, объём набираем под ваш запрос.&lt;br&gt;&lt;br&gt;Отдельно веду документы ФГИС ЛК. Официально ставлю лес на баланс и закрепляю древесину за вами через договор, чтобы вы могли законно возить и продавать. Делаю обработку материалов лесосеки, свожу учёт остатков, оформляю QR и ЭСД на перевозку, закрываю расхождения по объёму, готовлю отчёты и декларации.&lt;br&gt;&lt;br&gt;Пришлите замеры и породу, посчитаю сегодня и скажу, что нужно по бумагам. Напишите в сообщения, отвечу в течение пары минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на лес в ФГИС ЛК, сам лес мы не продаём и не покупаем. Если у вас есть кругляк, пиловочник сосны, балансы или дрова с деляны, а бумаг на них нет, мы всё проведём по системе.&lt;br&gt;&lt;br&gt;Что делаем: QR-код и ЭСД на перевозку, чтобы лесовоз шёл с чистой вывозкой. Закрываем расхождения по кубам, когда замеры на делянке и в системе не сходятся. Ставим заготовленную древесину на баланс компании через договор и закрепляем объём в ФГИС ЛК, чтобы можно было законно возить и продавать.&lt;br&gt;&lt;br&gt;Работаем по обработке материалов и учёту остатков, город Кунгур. Пришлите свои замеры, посчитаю остаток сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Берёза кругляк и балансы, диаметр от 16 до 32 см, длина 4 и 6 метров. Заготовка свежая, партии от машины и до крупного опта, отгрузка по Оренбургу и области.&lt;br&gt;&lt;br&gt;Ставлю лес на баланс в ФГИС ЛК и свожу складской учёт остатков. Официально закрепляю древесину за вашей компанией через договор, чтобы объём в системе совпадал с фактом на площадке. Делаю обработку данных по лесосеке, оформляю QR и ЭСД на перевозку, закрываю расхождения, готовлю отчёты и декларации.&lt;br&gt;&lt;br&gt;Пришлите остатки по системе и по факту, посчитаю сегодня и скажу, как ровно свести учёт. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Сразу к делу: мы оформляем документы на лес в ФГИС ЛК, сам лес не продаём. Если у вас есть древесина, а бумаг на неё нет, приводим всё в порядок по системе.&lt;br&gt;&lt;br&gt;Работаем по Оренбургу и области, ведём складской учёт по кубам. Берёза, кругляк, пиловочник, балансы, дрова лежат на площадке или на деляне, а в системе их не значится. Ставим заготовленный лес на баланс компании через договор, закрепляем объём в ФГИС ЛК, и дальше его можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Делаем QR и ЭСД на каждую вывозку, чтобы лесовоз шёл с чистыми документами. Закрываем расхождения по объёмам, готовим декларации и отчёты.&lt;br&gt;&lt;br&gt;Пришлите замеры по делянке, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -14404,7 +14404,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Лес есть, а документов на вывоз нет. Знакомая история. У нас сосновый пиловочник свежей заготовки, диаметр от 18 до 32 см, длина 4 и 6 метров, партия отгружается машинами.&lt;br&gt;&lt;br&gt;По бумагам закрываем всё в ФГИС ЛК: оформляем QR код и ЭСД на рейс, чтобы первая же машина ушла без риска штрафов от лесконтроля. Считаем по фото замеров удалённо, раньше это звалось ЛесЕГАИС, суть та же. Делаем быстро и без ваших поездок в кабинет.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и подскажу по срокам.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Раньше система звалась ЛесЕГАИС, суть та же. Если у вас есть сосна, кругляк, пиловочник или балансы с деляны, а бумаг на них нет, всё сделаю по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код и ЭСД на перевозку, чтобы лесовоз прошёл лесной контроль без штрафов. Считаю по фото ваших замеров удалённо, вам никуда ехать не надо.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по кубам, ставлю лес на баланс, готовлю декларации и отчёты. Беломорск и район, объёмы любые.&lt;br&gt;&lt;br&gt;Пришлите замеры с делянки, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Лиственница, пиловочник свежей заготовки. Диаметр от 18 до 40 см, длина 4 и 6 метров, рубка этого сезона. Партия от лесовоза и больше, отгружаем с делянки без простоев. Лес ровный, сухостоя нет.&lt;br&gt;&lt;br&gt;Второе, чем занимаюсь по документам ФГИС ЛК. Оформляю QR код и ЭСД на вывоз леса, чтобы первый же рейс ушёл без риска штрафов от лесного контроля. Работаю удалённо по фото ваших замеров, ничего никуда везти не надо. QR готов за пару минут, вы сразу грузите и едете. Всё чисто по декларации и остаткам на балансе.&lt;br&gt;&lt;br&gt;Пришлите фото замеров в сообщения, посчитаю и выдам QR сегодня, отвечу в течение пары минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас есть лиственница, кругляк, пиловочник или балансы с деляны, а бумаг на вывозку нет, приведу всё в порядок по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код на вывоз леса, чтобы лесовоз прошёл лесной контроль без штрафов. Считаю по фото ваших замеров удалённо и быстро, вам никуда ехать не надо.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по объёмам, ставлю лес на баланс, готовлю декларации и отчёты. Нижнеудинск и район, объёмы любые.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня. Отвечаю за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -5574,7 +5574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ81"/>
+  <dimension ref="A1:AJ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -16193,6 +16193,1942 @@
       <c r="AJ81" t="inlineStr">
         <is>
           <t>2026-07-25T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>6521830331</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Сосна с делянки документов нет(помощь с учётом)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Оформление документов на древесину в ФГИС ЛК: кругляк, пиловочник, балансовая древесина, дрова. Работаем с лесозаготовителями, продавцами и покупателями леса.&lt;br&gt;&lt;br&gt;Что оформляем:&lt;br&gt;- электронный сопроводительный документ (ЭСД) на транспортировку древесины&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- постановку объёма на учёт и баланс, если древесина нигде не числится&lt;br&gt;- декларацию о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Присылаете породу, кубатуру, маршрут и данные сторон. Оформляем документ и передаём водителю в электронном виде.&lt;br&gt;&lt;br&gt;Срок по ЭСД обычно 15 минут с момента получения данных. Постановка объёма на учёт занимает дольше, скажу сразу по вашей ситуации.&lt;br&gt;&lt;br&gt;Свой личный кабинет в системе, электронная подпись и лесная декларация вам не нужны, оформление идёт с нашей стороны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Сосна, ель, лиственные породы, любые сортименты и объёмы, от одной лесовозной машины до постоянных отгрузок.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок и срок.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_3.jpg</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан, Белорецк, ул. Ленина, 24</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB82" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>2026-08-27T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4661388548</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Лес с делянки документов нет(QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>QR коды и электронные сопроводительные документы на вывоз древесины через ФГИС ЛК. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена, на постах проверяют QR код с данными рейса. Оформляем его на каждую лесовозную машину.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- сопровождение постоянных перевозок, документ на каждый рейс&lt;br&gt;- постановка древесины на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок работы. От вас данные машины, отправителя и получателя, порода и кубатура в кубометрах. Дальше оформление на нас, QR код приходит водителю на телефон.&lt;br&gt;&lt;br&gt;Обычно занимает 15 минут с момента, когда получили данные.&lt;br&gt;&lt;br&gt;Личный кабинет ФГИС ЛК, электронная подпись и собственная декларация не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и всему Приуралью. Сосновый и еловый пиловочник, лес с делянки, древесина оптом, формат любой.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_3.jpg</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан, Янаул, ул. Победы, 16</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB83" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>2026-08-27T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>2026-07-29T11:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>6175129265</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Кругляк с делянки бумаг нет(документы фгис лк)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Полный пакет документов на древесину в ФГИС ЛК для заготовителей, продавцов и перевозчиков леса.&lt;br&gt;&lt;br&gt;В работе:&lt;br&gt;- электронный сопроводительный документ на транспортировку кругляка и пиловочника&lt;br&gt;- QR код на рейс для проверки на посту&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- лесная декларация и декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования древесины&lt;br&gt;&lt;br&gt;Как это работает. Вы присылаете породу, кубатуру, маршрут и реквизиты. Мы оформляем документы в системе и передаём их в готовом виде.&lt;br&gt;&lt;br&gt;ЭСД обычно готов за 15 минут. Постановка объёма на учёт и работа с декларацией занимают дольше, срок называю до начала работы.&lt;br&gt;&lt;br&gt;Заводить свой кабинет и электронную подпись не нужно, оформление ведём со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Хвойный кругляк, лесоматериалы круглые, баланс, любые объёмы с делянки и со склада.&lt;br&gt;&lt;br&gt;Напишите кубатуру и куда везёте, скажу срок.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_3.jpg</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан, Дюртюли, ул. Чеверева, 8</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>2026-08-27T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3494661466</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Пиловочник от заготовителя(помощь с учётом леса)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Учёт древесины и документы в ФГИС ЛК под ключ. Кругляк, пиловочник сосна и ель, баланс, дрова.&lt;br&gt;&lt;br&gt;Основной запрос: древесина заготовлена, но в системе не отражена, поэтому её нельзя ни продать, ни вывезти. Ставим объём на учёт и дальше ведём документооборот.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка объёма древесины на баланс&lt;br&gt;- ЭСД и QR код на каждую отгрузку лесовозом&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт по местам складирования (МСД)&lt;br&gt;- сопровождение отгрузок на постоянной основе&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и данные сторон. Остальное на нашей стороне.&lt;br&gt;&lt;br&gt;Рутинный ЭСД занимает около 15 минут. Постановка на учёт зависит от ситуации, срок скажу честно до начала.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и Приуралью, берём и разовые задачи, и постоянное ведение по объёмам с лесосеки.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, отвечу быстро.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_3.jpg</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан, Мелеуз, ул. Ленина, 137</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB85" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>2026-08-27T19:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>2026-07-29T19:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2394430844</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Лес есть документов нет(QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Электронные сопроводительные документы и QR коды на вывоз леса через ФГИС ЛК. Кругляк, пиловочник, лесоматериалы круглые.&lt;br&gt;&lt;br&gt;Без ЭСД перевозка древесины запрещена, на постах смотрят QR код. Оформляем документ на каждый рейс, чтобы машина шла легально.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины&lt;br&gt;- QR код водителю на телефон&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные лесовозной машины, породу, кубатуру и маршрут. Оформляем и отдаём готовый документ.&lt;br&gt;&lt;br&gt;Обычно 15 минут после получения данных.&lt;br&gt;&lt;br&gt;Свой кабинет ФГИС ЛК, электронная подпись и декларация не нужны, работаем со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Алтайскому краю и Сибири. Сосновый и еловый пиловочник, баланс, дрова, древесина оптом, разница во времени не мешает.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_3.jpg</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Алтайский край, Заринск, ул. Строителей, 21</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB86" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>2026-08-28T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>3236944872</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Сосна есть учёта нет(помощь с учётом леса)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Постановка древесины на учёт и ведение документов в ФГИС ЛК. Работаем с кругляком, пиловочником, балансом и дровами.&lt;br&gt;&lt;br&gt;Если объём не отражён в системе, лес формально не существует: ни продать, ни вывезти его нельзя. Приводим учёт в порядок и дальше сопровождаем отгрузки.&lt;br&gt;&lt;br&gt;Что входит:&lt;br&gt;- постановка объёма древесины на баланс&lt;br&gt;- электронный сопроводительный документ на каждый рейс&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования&lt;br&gt;&lt;br&gt;От вас порода, кубатура в кубометрах, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Сроки честные: ЭСД около 15 минут, работа с учётом дольше, называю срок до начала.&lt;br&gt;&lt;br&gt;Заводить кабинет и электронную подпись не потребуется.&lt;br&gt;&lt;br&gt;Работаем по Алтайскому краю и всей Сибири. Хвойный пиловочник, лес с делянки, любые объёмы под продажу и отгрузку.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок работы.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_3.jpg</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Алтайский край, Бийск, ул. Советская, 205</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB87" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>2026-08-28T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>2026-07-30T11:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2312387978</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Кругляк есть документов нет(документы фгис лк)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Документы на древесину в ФГИС ЛК для лесозаготовителей, продавцов и покупателей леса.&lt;br&gt;&lt;br&gt;Оформляем:&lt;br&gt;- электронный сопроводительный документ на транспортировку кругляка&lt;br&gt;- QR код на рейс&lt;br&gt;- постановку объёма на учёт, если древесина не отражена в системе&lt;br&gt;- лесную декларацию и декларацию о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Вы даёте породу, кубатуру, маршрут и данные сторон. Мы оформляем в системе и передаём готовые документы.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут. Задачи по учёту и декларации занимают дольше, срок озвучиваю заранее.&lt;br&gt;&lt;br&gt;Личный кабинет, электронная подпись и своя декларация не нужны.&lt;br&gt;&lt;br&gt;Работаем по Пермскому краю и Приуралью. Пиловочник сосна и ель, балансовая древесина, дрова, отгрузка лесовозом, разовые рейсы и постоянное сопровождение.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу быстро.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_3.jpg</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Пермский край, Чусовой, ул. Ленина, 32</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB88" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>2026-08-28T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2058067807</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ель с делянки бумаг нет(QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>QR коды и ЭСД на перевозку древесины через ФГИС ЛК. Кругляк, пиловочник, баланс, лесоматериалы круглые.&lt;br&gt;&lt;br&gt;Вывоз леса без электронного сопроводительного документа запрещён. На посту проверяют QR код, в нём данные рейса, объёма и сторон сделки.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- ЭСД на транспортировку с QR кодом&lt;br&gt;- документ на каждый рейс при постоянных перевозках&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- отчёт 1-ИЛ и декларация о сделке&lt;br&gt;&lt;br&gt;От вас данные лесовозной машины, порода, кубатура, откуда и куда идёт груз.&lt;br&gt;&lt;br&gt;Оформление занимает около 15 минут с момента получения данных.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронная подпись не потребуются, всё делаем со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Пермскому краю и соседним регионам. Еловый и сосновый пиловочник, лес с делянки, древесина оптом.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_08_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_08_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_08_3.jpg</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Пермский край, Лысьва, ул. Мира, 26</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB89" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>2026-08-28T19:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>2026-07-30T19:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>9553367742</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Пиловочник есть учёта нет(помощь с учётом леса)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Учёт древесины в ФГИС ЛК и сопровождение отгрузок. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Древесина без учёта в системе не продаётся и не перевозится. Ставим объём на баланс, оформляем документы и дальше ведём отгрузки, чтобы каждый рейс был закрыт.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- постановка объёма древесины на учёт&lt;br&gt;- ЭСД и QR код на транспортировку&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования&lt;br&gt;- постоянное ведение документооборота&lt;br&gt;&lt;br&gt;Нужны порода, кубатура, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Рутинный ЭСД около 15 минут, постановка на учёт дольше, срок называю сразу.&lt;br&gt;&lt;br&gt;Кабинет в системе и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Работаем по Удмуртии и Поволжью. Хвойный кругляк, лесоматериалы, продажа и покупка древесины, от одной машины до постоянного потока.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, скажу срок.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_3.jpg</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Удмуртская Республика, Глазов, ул. Кирова, 49</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>550</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB90" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>2026-08-29T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2285712624</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Лес заготовлен бумаг нет(документы фгис лк)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Оформление документов на заготовленную древесину в ФГИС ЛК. Кругляк, пиловочник, балансовая древесина.&lt;br&gt;&lt;br&gt;Частая ситуация: лес заготовлен и лежит на делянке, а по документам в системе не проведён. Разбираем и приводим в порядок.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- электронный сопроводительный документ на вывоз&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- лесная декларация, декларация о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования&lt;br&gt;&lt;br&gt;От вас порода, кубатура и данные перевозки.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут после получения данных. Работа с учётом и декларацией занимает дольше, срок скажу до начала.&lt;br&gt;&lt;br&gt;Своя декларация и кабинет в системе не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Удмуртии и соседним регионам. Сосна, ель, лиственные, любые сортименты под продажу и отгрузку лесовозом.&lt;br&gt;&lt;br&gt;Напишите кубатуру, отвечу быстро.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_3.jpg</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Удмуртская Республика, Можга, ул. Наговицына, 60</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB91" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>2026-08-29T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>2026-07-31T11:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>5905323698</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Сосна с делянки бумаг нет(QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>QR коды и электронные сопроводительные документы на древесину. Кругляк, пиловочник сосна и ель, баланс.&lt;br&gt;&lt;br&gt;На постах проверяют QR код ЭСД, без него вывоз леса запрещён. Оформляем документ на каждую лесовозную машину через ФГИС ЛК.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины&lt;br&gt;- QR код водителю в электронном виде&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные машины, отправителя и получателя, породу и кубатуру. Оформление на нас.&lt;br&gt;&lt;br&gt;Обычно 15 минут с момента получения данных.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и Сибири. Лес с делянки и со склада, древесина оптом, часовой пояс не помеха.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_3.jpg</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Кемеровская область, Таштагол, ул. Ленина, 60</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB92" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>2026-08-29T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>2026-07-31T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>8540422936</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Лес есть учёта нет(помощь с учётом леса)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Постановка древесины на учёт и документы в ФГИС ЛК. Кругляк, пиловочник, лесоматериалы круглые, дрова.&lt;br&gt;&lt;br&gt;Пока объём не стоит на балансе в системе, лес нельзя ни продать, ни вывезти. Ставим на учёт и дальше ведём документы на отгрузки.&lt;br&gt;&lt;br&gt;Что входит:&lt;br&gt;- постановка объёма древесины на учёт и баланс&lt;br&gt;- ЭСД и QR код на каждый рейс&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и реквизиты.&lt;br&gt;&lt;br&gt;ЭСД около 15 минут, работа с учётом занимает дольше, срок озвучиваю честно.&lt;br&gt;&lt;br&gt;Свой кабинет и электронная подпись не требуются.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и всей Сибири. Хвойный пиловочник, баланс, продажа древесины с лесосеки, разовые и постоянные отгрузки.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу что дальше.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_3.jpg</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Кемеровская область, Мыски, ул. Советская, 43</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB93" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>2026-08-29T19:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>2026-07-31T19:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>8088623974</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Кругляк заготовлен бумаг нет(документы фгис лк)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Документы в ФГИС ЛК на заготовленную древесину. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Оформляем:&lt;br&gt;- постановку объёма на учёт&lt;br&gt;- электронный сопроводительный документ на транспортировку&lt;br&gt;- QR код на рейс&lt;br&gt;- лесную декларацию и декларацию о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования&lt;br&gt;&lt;br&gt;Как работаем. От вас порода, кубатура, маршрут и данные сторон. Оформление в системе полностью на нашей стороне, документы приходят готовыми.&lt;br&gt;&lt;br&gt;Срок по ЭСД обычно 15 минут. Постановка на учёт и декларация занимают дольше, называю срок заранее.&lt;br&gt;&lt;br&gt;Заводить кабинет и электронную подпись не нужно.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и соседним регионам. Сосновый и еловый кругляк, лесоматериалы, отгрузка лесовозом, любые объёмы.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу быстро.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_3.jpg</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Кемеровская область, Юрга, ул. Машиностроителей, 39</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB94" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>2026-08-30T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>2026-08-01T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2671009093</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Лес с делянки бумаг нет(QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Электронные сопроводительные документы и QR коды на вывоз древесины. Кругляк, пиловочник, баланс.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена, на постах проверяют QR код из ФГИС ЛК. Оформление у нас поставлено на поток.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- документ на каждый рейс при регулярных перевозках&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- отчёт 1-ИЛ, декларация о сделке&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные лесовозной машины, отправителя, получателя и кубатуру, дальше QR код у водителя на экране.&lt;br&gt;&lt;br&gt;Обычно 15 минут.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронная подпись не нужны.&lt;br&gt;&lt;br&gt;Работаем по Красноярскому краю и всей Сибири. Хвойный кругляк с делянки, лиственные породы, древесина оптом, часовой пояс не проблема.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_3.jpg</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Красноярский край, Богучаны, ул. Ленина, 27</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB95" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>2026-08-30T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>2026-08-01T11:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>6664478711</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Ель есть документов нет(помощь с учётом леса)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Учёт древесины и оформление документов в ФГИС ЛК. Кругляк, пиловочник ель и сосна, баланс, дрова.&lt;br&gt;&lt;br&gt;Древесина должна стоять на учёте, иначе её не продать и не вывезти. Ставим объём на баланс, оформляем сопроводительные документы, ведём отчётность.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка объёма древесины на учёт&lt;br&gt;- ЭСД и QR код на транспортировку&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт в местах складирования&lt;br&gt;- сопровождение постоянных отгрузок&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Рутинный ЭСД около 15 минут, задачи по учёту дольше, срок называю до начала работы.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Лесоматериалы круглые, продажа и покупка леса, отгрузка лесовозными машинами.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, отвечу быстро.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_3.jpg</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Челябинская область, Сатка, ул. Солнечная, 12</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>550</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB96" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>2026-08-30T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>2026-08-01T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2657040747</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Сосна заготовлена бумаг нет(документы фгис лк)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Оформление документов на древесину в ФГИС ЛК для заготовителей, продавцов и перевозчиков. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;В работе:&lt;br&gt;- электронный сопроводительный документ на транспортировку древесины&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- лесная декларация, декларация о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования древесины (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Вы присылаете породу, кубатуру, маршрут и данные сторон. Мы оформляем в системе и передаём готовый пакет.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут после получения данных. Учёт и декларация занимают дольше, срок озвучиваю заранее.&lt;br&gt;&lt;br&gt;Свой кабинет, электронная подпись и декларация вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Сосновый пиловочник, лес с делянки, древесина оптом, разовые задачи и постоянное ведение.&lt;br&gt;&lt;br&gt;Напишите кубатуру, скажу срок и порядок.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_3.jpg</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Челябинская область, Катав-Ивановск, ул. Ленина, 19</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB97" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>2026-08-30T19:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>2026-08-01T19:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -5574,7 +5574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ97"/>
+  <dimension ref="A1:AJ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -18129,6 +18129,248 @@
       <c r="AJ97" t="inlineStr">
         <is>
           <t>2026-08-01T19:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>8424443532</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Лес заготовлен документов нет(помощь с учётом)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Учёт древесины и оформление документов в ФГИС ЛК. Кругляк, пиловочник сосна и ель, балансовая древесина, дрова.&lt;br&gt;&lt;br&gt;Ситуация, с которой чаще всего приходят: лес заготовлен и лежит, покупатель есть, а в системе объём не проведён. Пока древесина не на учёте, продать и вывезти её нельзя.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка заготовленного объёма на учёт и баланс&lt;br&gt;- электронный сопроводительный документ (ЭСД) на транспортировку&lt;br&gt;- QR код водителю для проверки на посту&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;Порядок. От вас порода, кубатура в кубометрах, маршрут и реквизиты сторон. Оформление в системе полностью на нашей стороне.&lt;br&gt;&lt;br&gt;Рутинный ЭСД занимает около 15 минут после получения данных. Постановка объёма на учёт дольше, срок называю честно до начала работы.&lt;br&gt;&lt;br&gt;Свой личный кабинет, электронная подпись и лесная декларация вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Хвойный кругляк с делянки и со склада, лесоматериалы круглые, древесина оптом, отгрузка лесовозными машинами.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок и срок.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_3.jpg</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан, Ишимбай, ул. Советская, 15</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB98" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>2026-08-26T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2960453369</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Сосна есть документов нет(QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>QR коды и электронные сопроводительные документы на вывоз древесины через ФГИС ЛК. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена. На посту проверяют QR код, в нём данные рейса, объёма и сторон сделки. Оформляем документ на каждую лесовозную машину.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- документ на каждый рейс при постоянных перевозках&lt;br&gt;- постановка объёма древесины на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок работы. Присылаете данные машины, отправителя и получателя, породу и кубатуру. Дальше оформление на нас, QR код приходит водителю на телефон.&lt;br&gt;&lt;br&gt;Обычно занимает 15 минут с момента получения данных.&lt;br&gt;&lt;br&gt;Личный кабинет ФГИС ЛК, электронная подпись и собственная декларация не потребуются, работаем со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Пермскому краю и Приуралью. Сосновый и еловый пиловочник, лес с делянки, лесоматериалы круглые, продажа и покупка древесины, любые объёмы.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_3.jpg</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Пермский край, Кунгур, ул. Ленина, 40</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>450</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB99" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>2026-08-26T17:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -1679,7 +1679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2951,6 +2951,128 @@
       <c r="AC11" t="inlineStr">
         <is>
           <t>2026-07-24T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2714361279</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/11_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/11_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/11_03.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Документы на лес ФГИС ЛК под ключ</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Заготовили лес и не хотите тонуть в ФГИС ЛК - ведём документы за вас под ключ. Ставим объём на учёт, оформляем ЭСД и QR на перевозку, проводим сделку.&lt;/p&gt;&lt;p&gt;Можно разово под конкретную задачу или взять ваш аккаунт на постоянное сопровождение. Данные проверяем, чтобы не было отказов и штрафов.&lt;/p&gt;&lt;p&gt;Свой кабинет и электронная подпись вам не нужны, всё делаем сами. От вас исходники по лесу и отгрузкам.&lt;/p&gt;&lt;p&gt;Пакет от 3000 рублей, точная цена по объёму работ. Напишите, что у вас с лесом и документами, разложу по шагам.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан, Уфа, ул. Мира, 14</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Услуги посредников</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Консультации</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2026-09-06T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-07T11:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="25"/>
@@ -3989,7 +4111,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4128,7 +4250,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4267,7 +4389,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4399,7 +4521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4923,6 +5045,140 @@
       <c r="AC11" t="inlineStr">
         <is>
           <t>2026-07-25T13:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4876797967</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/10_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/10_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/10_03.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ЭСД и QR код на лес через ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Оформляем ЭСД и QR код на перевозку леса через ФГИС ЛК. Коротко: машина под погрузкой, а документа на рейс нет - мы его выпускаем, и водитель едет.&lt;/p&gt;&lt;p&gt;Что делаем: ЭСД и QR на каждую машину, проверяем объём и породу до отгрузки, чтобы на посту не завернули.&lt;/p&gt;&lt;p&gt;Всё с нашей стороны. Свой кабинет в системе, декларация, электронная подпись - ничего заводить не нужно. Работаем и когда своих остатков в системе пока нет.&lt;/p&gt;&lt;p&gt;От 500 рублей за рейс, объём считаем отдельно. Напишите маршрут и кубатуру, скажу срок сегодня.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Пермский край, Пермь, ул. Ленина, 50</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-06T03:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-07T05:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ99"/>
+  <dimension ref="A1:AJ108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -6095,7 +6351,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6227,7 +6483,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6364,7 +6620,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6501,7 +6757,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6638,7 +6894,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6775,7 +7031,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6912,7 +7168,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7049,7 +7305,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7186,7 +7442,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7323,7 +7579,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -7460,7 +7716,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -7597,7 +7853,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -7734,7 +7990,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -7871,7 +8127,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8008,7 +8264,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8145,7 +8401,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8282,7 +8538,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8419,7 +8675,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8556,7 +8812,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8693,7 +8949,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8830,7 +9086,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8967,7 +9223,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -9104,7 +9360,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9241,7 +9497,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -9378,7 +9634,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9515,7 +9771,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9652,7 +9908,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9789,7 +10045,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9926,7 +10182,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10063,7 +10319,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -10200,7 +10456,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10332,7 +10588,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10469,7 +10725,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10606,7 +10862,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10743,7 +10999,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10880,7 +11136,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11017,7 +11273,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11154,7 +11410,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -11291,7 +11547,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -11428,7 +11684,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -11560,7 +11816,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -11697,7 +11953,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -11829,7 +12085,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -11966,7 +12222,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -12103,7 +12359,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -12240,7 +12496,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -12377,7 +12633,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -18371,6 +18627,1113 @@
       <c r="AJ99" t="inlineStr">
         <is>
           <t>2026-07-28T17:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5600427421</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Ель кругляк с делянки(помощь с учётом)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Лес есть, а с документами в ФГИС ЛК вечно возня. Возьмём её на себя. Поставим ваш объём на баланс, оформим ЭСД и QR код на каждую машину, дальше просто ведём учёт, чтобы вы про это не думали.&lt;br&gt;&lt;br&gt;Лес еловый, кругляк с делянки, 6 метров, диаметр от 20 см. Есть и другие сортименты.&lt;br&gt;&lt;br&gt;От вас только данные по объёму и рейсу. Свой кабинет в системе, декларацию и электронную подпись заводить не нужно, всё оформляем мы.&lt;br&gt;&lt;br&gt;Я по Башкортостану и соседним регионам. Напишите, что у вас по лесу, подскажу порядок и сроки.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_03.jpg</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан, Белорецк, ул. Ленина, 15</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB100" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>2026-09-06T01:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>2026-08-07T03:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2999877744</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Сосна кругляк с делянки(QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Делаем QR код на вывоз леса и ЭСД через ФГИС ЛК. Машина уже под погрузкой, а документа на рейс нет - обычно решаем в тот же день.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, есть и другой хвойный сортимент.&lt;br&gt;&lt;br&gt;QR код и ЭСД приходят водителю на телефон. Перед этим сверяем объём и породу, чтобы на посту не развернули. Свой кабинет и подпись вам не нужны.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири, разница по времени не мешает. Напишите, что по рейсу, отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_03.jpg</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Алтайский край, Бийск, ул. Советская, 8</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB101" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>2026-09-07T02:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4426292302</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Сосна кругляк под погрузку(QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет - обычная история. Оформим QR код на вывоз и ЭСД через ФГИС ЛК, документ придёт водителю на экран перед выездом.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Объём и породу проверяем заранее, чтобы потом не переделывать. Всё оформление на нас, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Кемеровской области и Сибири, часовой пояс не помеха. Напишите объём и куда везёте, отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_03.jpg</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Кемеровская область, Таштагол, ул. Ленина, 22</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB102" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>2026-09-05T16:45:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:45:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2587611012</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Лиственница кругляк(ЭСД на перевозку)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Делаем ЭСД на перевозку леса через ФГИС ЛК. Если возите объёмами, на каждый рейс нужен свой документ - держим это на потоке, чтобы машины не стояли.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см. Есть сосна и ель.&lt;br&gt;&lt;br&gt;Данные проверяем до выпуска, чтобы не было отказа. Оформляем, даже если своей декларации у вас пока нет.&lt;br&gt;&lt;br&gt;Я по Красноярскому краю и Сибири. Напишите объём и маршрут, скажу срок сегодня.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_03.jpg</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Красноярский край, Богучаны, ул. Октябрьская, 5</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Лиственница</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB103" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>2026-09-07T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>7413907762</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Ель кругляк с делянки(помощь с учётом)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Кто возит лес, тот знает: без учёта в ФГИС ЛК никуда. Поможем с учётом - поставим объём на баланс, оформим ЭСД и QR на рейсы, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, кругляк с делянки, 6 метров, диаметр от 20 см. Любой объём.&lt;br&gt;&lt;br&gt;От вас только данные, остальное на нас. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Челябинской области и Уралу. Напишите породу и кубатуру, подскажу сроки.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_03.jpg</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Челябинская область, Сатка, ул. Пролетарская, 12</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB104" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>2026-09-07T04:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>2026-08-08T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>8170157355</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Сосна от заготовителя(QR код на вывоз леса)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Машина готова, лес на месте, а QR кода на вывоз нет. Сделаем QR и ЭСД через ФГИС ЛК на каждую машину, придёт водителю на телефон.&lt;br&gt;&lt;br&gt;Сосновый кругляк напрямую от заготовителя, 6 метров, диаметр от 20 см.&lt;br&gt;&lt;br&gt;Перед отгрузкой сверяем объём и породу. Оформление целиком с нашей стороны, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Башкортостану и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_03.jpg</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан, Сибай, ул. Заводская, 3</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB105" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>2026-09-06T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>2026-08-07T07:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>3173084587</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник с делянки(документы фгис лк)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Кто работает с лесом, тому нужны документы в ФГИС ЛК, а времени на систему нет. Оформим за вас - ЭСД и QR на перевозку, поставим объём на учёт, проведём сделку.&lt;br&gt;&lt;br&gt;Сосновый пиловочник с делянки, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Кабинет и подпись заводить не надо, ведём всё сами.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири. Напишите кубатуру и маршрут, отвечу быстро.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_03.jpg</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Алтайский край, Заринск, ул. Металлургов, 9</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB106" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>2026-09-08T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1583205196</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Лиственница кругляк с делянки(ЭСД на вывоз)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Оформляем ЭСД на вывоз леса через ФГИС ЛК. Лес готов, машина под погрузкой, а документа на рейс нет - выпустим, и водитель едет.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см, плотная древесина.&lt;br&gt;&lt;br&gt;Данные проверяем заранее. Если что-то оформлено с ошибкой, аннулируем и делаем заново по правилам. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Пермскому краю и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_03.jpg</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Пермский край, Чусовой, ул. Ленина, 30</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Лиственница</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB107" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>2026-09-06T07:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>3881738547</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Ель пиловочник с делянки(помощь с учётом)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Лес есть, а документов нет, и учёт в ФГИС ЛК висит мёртвым грузом. Разгрузим - поставим объём на баланс, сделаем ЭСД и QR на каждый рейс, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, пиловочник с делянки, 6 метров, диаметр от 20 см. Хвоя.&lt;br&gt;&lt;br&gt;От вас данные, остальное наша забота. Свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Я по Удмуртии и Поволжью. Напишите породу и кубатуру, подскажу сроки.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_03.jpg</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Удмуртская Республика, Можга, ул. Наговицына, 7</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB108" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>2026-09-08T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>2026-08-09T08:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19767,7 +21130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="14"/>
@@ -20045,7 +21408,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -20137,7 +21500,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -20229,7 +21592,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -20321,7 +21684,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -20413,7 +21776,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -20505,7 +21868,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -20597,7 +21960,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -20848,6 +22211,93 @@
       <c r="T13" t="inlineStr">
         <is>
           <t>2026-07-25T10:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4138475016</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/12_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/12_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/12_03.jpg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Учёт леса в ФГИС ЛК, помощь с балансом</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Лес есть, а объём в ФГИС ЛК не сходится или вообще не заведён - приведём в порядок. Поставим древесину на баланс, дальше держим учёт и документы на потоке.&lt;/p&gt;&lt;p&gt;Что берём на себя: постановку объёма на учёт, ЭСД и QR на рейсы, отчётность по вашим отгрузкам.&lt;/p&gt;&lt;p&gt;Оформление с нашей стороны, свой кабинет и подпись заводить не нужно. Работаю по Костромской области и центральным регионам.&lt;/p&gt;&lt;p&gt;От 990 рублей за объём, сопровождение считаем отдельно. Напишите, что по лесу и учёту, подскажу порядок.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Костромская область, Кострома, ул. Советская, 20</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Оборудование, производство</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Производство, обработка</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Обработка материалов</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-09-07T09:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-08-08T11:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-07-21T12:35:45+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:49+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-07-30T15:05:39+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-07-31T13:26:06+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -2713,6 +2713,11 @@
           <t>ЕГАИС ЛЕС документация</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2026-08-01T00:00:00+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2825,7 +2830,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-21T08:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2945,7 +2950,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-23T08:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -4233,7 +4238,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-26T10:49:46+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -4372,7 +4377,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-30T12:05:47+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -4504,7 +4509,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-06T07:35:20+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -4643,7 +4648,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-02T15:36:11+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -4775,7 +4780,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-22T04:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4907,7 +4912,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-24T04:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5039,7 +5044,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-24T11:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -6466,7 +6471,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-08-08T09:35:33+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -6598,7 +6603,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-08-07T13:35:35+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -6735,7 +6740,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-08-09T09:36:41+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -6872,7 +6877,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026-08-05T13:06:19+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -7009,7 +7014,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026-08-05T17:06:01+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -7146,7 +7151,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026-08-08T14:06:15+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -7283,7 +7288,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026-07-30T07:09:04+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -7420,7 +7425,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-07-29T18:06:22+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -7557,7 +7562,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2026-08-07T14:05:43+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -7694,7 +7699,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026-07-29T17:06:01+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -7831,7 +7836,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2026-08-07T16:05:46+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -7968,7 +7973,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026-08-06T10:36:16+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -8105,7 +8110,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2026-08-09T08:06:44+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -8242,7 +8247,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2026-07-29T16:06:41+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -8379,7 +8384,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2026-08-09T14:06:27+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -8516,7 +8521,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2026-08-01T16:05:08+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -8653,7 +8658,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2026-08-05T15:35:42+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -8790,7 +8795,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2026-07-29T15:36:03+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -8927,7 +8932,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2026-08-08T06:35:26+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -9064,7 +9069,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>2026-08-01T12:06:18+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -9201,7 +9206,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>2026-08-08T08:06:35+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -9338,7 +9343,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>2026-08-08T12:36:18+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -9475,7 +9480,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>2026-08-08T15:36:22+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -9612,7 +9617,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>2026-07-30T05:05:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -9749,7 +9754,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>2026-08-06T06:05:10+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -9886,7 +9891,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>2026-07-30T08:22:02+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -10023,7 +10028,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>2026-08-02T05:35:32+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -10160,7 +10165,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>2026-08-09T05:05:01+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -10297,7 +10302,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>2026-07-30T10:05:18+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -10434,7 +10439,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>2026-08-09T15:36:17+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -10571,7 +10576,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>2026-08-08T11:05:20+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
@@ -10703,7 +10708,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>2026-08-09T11:06:03+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -10840,7 +10845,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>2026-07-30T09:10:16+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -10977,7 +10982,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>2026-08-01T15:06:09+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -11114,7 +11119,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>2026-07-30T06:19:03+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -11251,7 +11256,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>2026-08-06T17:05:57+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -11388,7 +11393,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>2026-08-06T13:36:15+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -11525,7 +11530,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>2026-08-06T09:06:32+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -11662,7 +11667,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>2026-08-05T12:05:15+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -11799,7 +11804,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>2026-08-08T05:04:57+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
@@ -11931,7 +11936,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>2026-08-05T14:06:49+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -12068,7 +12073,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>2026-08-09T12:35:41+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
@@ -12200,7 +12205,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>2026-08-06T12:05:58+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -12337,7 +12342,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>2026-08-01T13:05:58+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -12474,7 +12479,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>2026-08-01T14:05:54+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -12611,7 +12616,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>2026-07-30T13:05:45+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -12748,7 +12753,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>2026-08-07T15:06:30+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -12878,7 +12883,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>2026-08-14T18:13:40+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -13003,7 +13008,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>2026-08-15T04:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -13128,7 +13133,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>2026-08-15T05:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -13253,7 +13258,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>2026-08-15T07:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -13378,7 +13383,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>2026-08-15T08:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -13503,7 +13508,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>2026-08-15T10:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -13628,7 +13633,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>2026-08-15T11:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -13753,7 +13758,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>2026-08-15T13:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -13878,7 +13883,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>2026-08-16T04:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -14003,7 +14008,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>2026-08-16T05:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -14128,7 +14133,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>2026-08-16T07:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -14253,7 +14258,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>2026-08-16T08:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -14378,7 +14383,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>2026-08-16T10:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -14503,7 +14508,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>2026-08-16T11:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -14628,7 +14633,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>2026-08-16T13:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -14749,7 +14754,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>2026-08-20T18:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -14870,7 +14875,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>2026-08-20T19:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -14991,7 +14996,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>2026-08-21T04:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -15112,7 +15117,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>2026-08-21T06:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -15233,7 +15238,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>2026-08-21T10:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -15354,7 +15359,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>2026-08-21T11:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -15475,7 +15480,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>2026-08-22T06:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -15596,7 +15601,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>2026-08-22T08:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -15717,7 +15722,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>2026-08-22T11:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -15838,7 +15843,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>2026-08-23T04:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
@@ -15959,7 +15964,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>2026-08-23T06:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -16080,7 +16085,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -16201,7 +16206,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>2026-08-23T11:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -16322,7 +16327,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>2026-08-24T06:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
@@ -16443,7 +16448,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>2026-08-24T10:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -16564,7 +16569,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>2026-08-27T07:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -16685,7 +16690,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>2026-08-27T11:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -16806,7 +16811,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>2026-08-27T15:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -16927,7 +16932,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>2026-08-27T19:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
@@ -17048,7 +17053,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>2026-08-28T07:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -17169,7 +17174,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>2026-08-28T11:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -17290,7 +17295,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>2026-08-28T15:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -17411,7 +17416,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>2026-08-28T19:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -17532,7 +17537,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>2026-08-29T07:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
@@ -17653,7 +17658,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>2026-08-29T11:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -17774,7 +17779,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>2026-08-29T15:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -17895,7 +17900,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>2026-08-29T19:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -18016,7 +18021,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>2026-08-30T07:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -18137,7 +18142,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>2026-08-30T11:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -18258,7 +18263,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>2026-08-30T15:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -18379,7 +18384,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>2026-08-30T19:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -18500,7 +18505,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>2026-08-26T14:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -18621,7 +18626,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>2026-08-26T17:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -21483,7 +21488,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-07-24T16:06:34+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -21575,7 +21580,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-07-30T11:36:45+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -21667,7 +21672,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-06T15:06:02+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -21759,7 +21764,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-02T08:06:18+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -21851,7 +21856,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-02T10:50:49+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -21943,7 +21948,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-07-30T14:05:58+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -22035,7 +22040,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-05T14:06:16+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -22115,7 +22120,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-08-22T10:00:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -22200,7 +22205,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-08-24T08:30:00+03:00</t>
+          <t>2026-08-01T00:00:00+03:00</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -18744,12 +18744,12 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>2026-09-06T11:30:00+03:00</t>
+          <t>2026-09-06T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>2026-08-07T13:30:00+03:00</t>
+          <t>2026-08-07T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -18867,12 +18867,12 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>2026-09-06T13:00:00+03:00</t>
+          <t>2026-09-06T11:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>2026-08-07T15:00:00+03:00</t>
+          <t>2026-08-07T13:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -18990,12 +18990,12 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>2026-09-06T14:30:00+03:00</t>
+          <t>2026-09-06T13:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>2026-08-07T16:30:00+03:00</t>
+          <t>2026-08-07T15:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19113,12 +19113,12 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>2026-09-07T02:00:00+03:00</t>
+          <t>2026-09-07T01:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>2026-08-08T04:00:00+03:00</t>
+          <t>2026-08-08T03:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19236,12 +19236,12 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>2026-09-07T04:00:00+03:00</t>
+          <t>2026-09-07T03:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>2026-08-08T06:00:00+03:00</t>
+          <t>2026-08-08T05:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>2026-09-07T06:00:00+03:00</t>
+          <t>2026-09-07T04:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>2026-08-08T08:00:00+03:00</t>
+          <t>2026-08-08T06:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19482,12 +19482,12 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>2026-09-07T08:00:00+03:00</t>
+          <t>2026-09-07T06:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>2026-08-08T10:00:00+03:00</t>
+          <t>2026-08-08T08:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19605,12 +19605,12 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>2026-09-07T10:00:00+03:00</t>
+          <t>2026-09-07T07:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>2026-08-08T12:00:00+03:00</t>
+          <t>2026-08-08T09:30:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -18744,12 +18744,12 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>2026-09-06T10:00:00+03:00</t>
+          <t>2026-09-06T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>2026-08-07T12:00:00+03:00</t>
+          <t>2026-08-07T14:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -18867,12 +18867,12 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>2026-09-06T11:30:00+03:00</t>
+          <t>2026-09-06T13:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>2026-08-07T13:30:00+03:00</t>
+          <t>2026-08-07T15:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -18990,12 +18990,12 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>2026-09-06T13:00:00+03:00</t>
+          <t>2026-09-06T15:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>2026-08-07T15:00:00+03:00</t>
+          <t>2026-08-07T17:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19113,12 +19113,12 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>2026-09-07T01:30:00+03:00</t>
+          <t>2026-09-07T04:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>2026-08-08T03:30:00+03:00</t>
+          <t>2026-08-08T06:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19236,12 +19236,12 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>2026-09-07T03:00:00+03:00</t>
+          <t>2026-09-07T05:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>2026-08-08T05:00:00+03:00</t>
+          <t>2026-08-08T07:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>2026-09-07T04:30:00+03:00</t>
+          <t>2026-09-07T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>2026-08-08T06:30:00+03:00</t>
+          <t>2026-08-08T09:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19482,12 +19482,12 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>2026-09-07T06:00:00+03:00</t>
+          <t>2026-09-07T08:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>2026-08-08T08:00:00+03:00</t>
+          <t>2026-08-08T10:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19605,12 +19605,12 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>2026-09-07T07:30:00+03:00</t>
+          <t>2026-09-07T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>2026-08-08T09:30:00+03:00</t>
+          <t>2026-08-08T12:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -15326,7 +15326,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>2026-08-07T15:30:00+03:00</t>
+          <t>2026-08-10T06:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -15449,7 +15449,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>2026-08-07T17:00:00+03:00</t>
+          <t>2026-08-10T08:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -3699,7 +3699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="25"/>
@@ -5179,6 +5179,2118 @@
       <c r="AC12" t="inlineStr">
         <is>
           <t>2026-08-09T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3415388891</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/13_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>550</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Лесная декларация и отчётность по лесу</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Готовим лесную декларацию и отчётность по использованию лесов. Услуга для арендаторов и заготовителей.&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- лесная декларация на период&lt;br&gt;- отчёт 1-ИЛ по фактической заготовке&lt;br&gt;- сверка заявленного с фактическим до подачи&lt;br&gt;- учёт мест складирования&lt;/p&gt;&lt;p&gt;Работаем по срокам, а не в последний день. Если период заканчивается, скажите сразу.&lt;/p&gt;&lt;p&gt;Кемеровская область.&lt;/p&gt;&lt;p&gt;Напишите участок и период.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Мариинск, Кемеровская обл., ул. Ленина, 41</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-12T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2403782347</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/3_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>700</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Сопровождение сделок с древесиной</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ведём документальную часть сделок с древесиной. Услуга от подготовки до закрытия периода.&lt;/p&gt;&lt;p&gt;Что берём:&lt;br&gt;- проверку, что объём на учёте и его хватает под сделку&lt;br&gt;- декларацию о сделке&lt;br&gt;- ЭСД и QR на все отгрузки по сделке&lt;br&gt;- контроль, что отгруженное сошлось с заявленным&lt;br&gt;- отчёт 1-ИЛ по итогам&lt;/p&gt;&lt;p&gt;Нужно, когда сделка крупная и разбита на много рейсов. Там легче всего потерять объём между документами.&lt;/p&gt;&lt;p&gt;Пермский край.&lt;/p&gt;&lt;p&gt;Напишите объём сделки и число отгрузок.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Кудымкар, Пермский край, ул. 50 лет Октября, 12</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-13T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-14T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6132305285</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/5_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>900</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Сопровождение ФГИС ЛК для лесозаготовителя</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ведём документооборот по древесине для лесозаготовителей. Услуга на постоянной основе.&lt;/p&gt;&lt;p&gt;Что закрываем:&lt;br&gt;- постановку объёмов на учёт&lt;br&gt;- ЭСД и QR на отгрузки, в том числе потоком&lt;br&gt;- декларации о сделках&lt;br&gt;- отчёт 1-ИЛ и лесную декларацию&lt;br&gt;- места складирования&lt;/p&gt;&lt;p&gt;Вы отгружаете, мы ведём бумаги. Кабинетов, подписей и обученных людей с вашей стороны не нужно.&lt;/p&gt;&lt;p&gt;Считаем помесячно. При регулярных отгрузках дешевле, чем держать своего специалиста.&lt;/p&gt;&lt;p&gt;Иркутская область.&lt;/p&gt;&lt;p&gt;Напишите объёмы и частоту отгрузок.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Усть-Кут, Иркутская обл., ул. Кирова, 18</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-14T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6104679278</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__3.jpg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1100</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Учёт древесины в ФГИС ЛК для делянки</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ведём учёт древесины для тех, кто заготавливает сам. Услуга от делянки до отгрузки.&lt;/p&gt;&lt;p&gt;Порядок: ставим заготовленный объём на учёт, привязываем места складирования, дальше каждая отгрузка уходит с ЭСД и QR, сделки закрываются декларациями, период закрывается отчётом 1-ИЛ.&lt;/p&gt;&lt;p&gt;Отдельно сверяем три числа: заготовлено, отгружено, числится в системе. Они должны совпадать.&lt;/p&gt;&lt;p&gt;Красноярский край.&lt;/p&gt;&lt;p&gt;Напишите объёмы заготовки.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Ачинск, Красноярский край, ул. Назарова, 16</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-14T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-15T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2592034142</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/17_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Документы на древесину удалённо, ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Оформляем документы на древесину дистанционно. Услуга без личных встреч, всё в электронном виде.&lt;/p&gt;&lt;p&gt;Закрываем: постановку объёмов на учёт, ЭСД и QR на рейсы, декларации о сделках, отчёт 1-ИЛ, лесную декларацию, места складирования.&lt;/p&gt;&lt;p&gt;Как начинаем: описываете ситуацию, мы уточняем детали и называем, что нужно оформить, за какой срок и сколько стоит. Потом беремся.&lt;/p&gt;&lt;p&gt;Свердловская область.&lt;/p&gt;&lt;p&gt;Напишите, что за задача.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Серов, Свердловская обл., ул. Ленина, 128</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-14T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-08-15T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1444249205</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real1_1__image2.jpg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Ведение учёта древесины в ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ведём учёт древесины в ФГИС ЛК как внешний исполнитель. Услуга по подписке.&lt;/p&gt;&lt;p&gt;Ежедневно: ЭСД на рейсы, QR коды, контроль остатков по складам.&lt;br&gt;Периодически: декларации о сделках, отчёт 1-ИЛ, сверка объёмов.&lt;br&gt;Разово: постановка на учёт, разбор расхождений с фактом.&lt;/p&gt;&lt;p&gt;Ставка зависит от числа отгрузок в месяц.&lt;/p&gt;&lt;p&gt;Марий Эл.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в месяц.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Йошкар-Ола, Республика Марий Эл, ул. Волкова, 60</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-15T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2026-08-16T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2893712453</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__image3.jpg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>550</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Места складирования древесины, МСД и учёт</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ставим на учёт места складирования древесины и ведём остатки. Услуга по складу.&lt;/p&gt;&lt;p&gt;Если древесина где-то лежит, место должно быть заведено в системе, а объём биться с фактом. Иначе отгрузка со склада встанет.&lt;/p&gt;&lt;p&gt;Что делаем: заводим места складирования, ставим объёмы на учёт, ведём приход и расход, оформляем ЭСД на отгрузки, закрываем отчётность.&lt;/p&gt;&lt;p&gt;Отдельно приводим в порядок склады, где остаток давно разошёлся с реальным.&lt;/p&gt;&lt;p&gt;Татарстан.&lt;/p&gt;&lt;p&gt;Напишите число площадок и объёмы.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Агрыз, Республика Татарстан, ул. Гагарина, 15</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-15T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2026-08-16T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>9984019968</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/16_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>700</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ЭСД на древесину, оформление за 15 минут</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Оформляем сопроводительные документы на перевозку древесины. Это наша услуга.&lt;/p&gt;&lt;p&gt;Кому нужно:&lt;br&gt;- перевозчику, чтобы рейс не встал на посту&lt;br&gt;- продавцу, чтобы отгрузка была законной&lt;br&gt;- покупателю, чтобы принять объём без вопросов&lt;/p&gt;&lt;p&gt;Что входит: ЭСД с QR, декларация о сделке, постановка на учёт, отчёт 1-ИЛ, места складирования.&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Челябинская область и Урал.&lt;/p&gt;&lt;p&gt;Напишите маршрут и объём.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Миасс, Челябинская обл., пр-т Автозаводцев, 12</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-15T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-08-16T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2886065351</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_11__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>900</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Оформление документов на лес ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Оформляем документы на лес в ФГИС ЛК. Полный пакет, одна услуга, один исполнитель.&lt;/p&gt;&lt;p&gt;В пакет входит:&lt;br&gt;- ЭСД на каждый рейс с QR кодом&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- отчёт 1-ИЛ и места складирования&lt;/p&gt;&lt;p&gt;Работаем от одной машины. Выручаем, когда покупатель ждёт, а оформлять некому.&lt;/p&gt;&lt;p&gt;Чувашия.&lt;/p&gt;&lt;p&gt;Напишите, что нужно и к какому сроку.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Шумерля, Чувашская Республика, ул. Ленина, 22</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4413366036</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1100</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>QR код на перевозку леса, оформим сегодня</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Оформляем QR код и ЭСД на перевозку леса. Услуга, делаем в день обращения.&lt;/p&gt;&lt;p&gt;От вас: порода, объём, маршрут, реквизиты сторон, номер машины.&lt;br&gt;Водителю: документ с QR кодом в электронном виде. На посту сканируют и пропускают.&lt;/p&gt;&lt;p&gt;Если объёма нет в системе, сначала ставим на учёт, иначе документ выписывать не на что.&lt;/p&gt;&lt;p&gt;Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите маршрут и объём.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Шахунья, Нижегородская обл., ул. Советская, 14</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-17T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-18T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2640679107</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/13_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Документы на лес ФГИС ЛК под ключ</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Оформляем документы на древесину в ФГИС ЛК. Услуга: вы отгружаете лес, мы делаем бумаги.&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- ЭСД на рейс с QR кодом для поста&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- отчёт 1-ИЛ, места складирования&lt;/p&gt;&lt;p&gt;От вас: порода, объём, маршрут, реквизиты сторон.&lt;br&gt;От нас: готовый документ водителю до выезда.&lt;/p&gt;&lt;p&gt;ЭСД: 15 минут. Постановка на учёт: срок называем после разбора ситуации.&lt;/p&gt;&lt;p&gt;Кабинет в системе и электронная подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Башкортостан и Приуралье. ИП и ООО.&lt;/p&gt;&lt;p&gt;Напишите объём и маршрут.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Кумертау, Республика Башкортостан, ул. Ленина, 14</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-17T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2026-08-18T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5708843369</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/3_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Декларация о сделке с древесиной</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Готовим и подаём декларацию о сделке с древесиной. Услуга под ключ.&lt;/p&gt;&lt;p&gt;Без декларации сделка не оформлена, отгружать нельзя.&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- составляем декларацию и подаём в систему&lt;br&gt;- сверяем объёмы и сортименты с фактом&lt;br&gt;- оформляем ЭСД и QR по отгрузкам сделки&lt;/p&gt;&lt;p&gt;Работаем с обеими сторонами. Частый случай: покупатель требует декларацию, у продавца нет ни кабинета, ни подписи.&lt;/p&gt;&lt;p&gt;Башкортостан и соседние регионы.&lt;/p&gt;&lt;p&gt;Напишите объём сделки.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Стерлитамак, Республика Башкортостан, ул. Мира, 18</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-17T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2026-08-18T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4860890388</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/5_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>550</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Отчёт 1-ИЛ и лесная декларация</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Сдаём отчёт 1-ИЛ и лесную декларацию за вас. Услуга по отчётности.&lt;/p&gt;&lt;p&gt;Что входит:&lt;br&gt;- лесная декларация на период&lt;br&gt;- отчёт 1-ИЛ по фактическим объёмам&lt;br&gt;- сверка заявленного с фактом до подачи&lt;br&gt;- учёт мест складирования&lt;/p&gt;&lt;p&gt;Сверяем до подачи. Разойдётся объём, и вопросы будут уже к вам.&lt;/p&gt;&lt;p&gt;Новосибирская область.&lt;/p&gt;&lt;p&gt;Напишите, что и за какой период сдаём.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Куйбышев, Новосибирская обл., ул. Краскома, 24</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-17T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2026-08-18T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2623788059</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>700</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ЭСД на лесовоз, документы на каждый рейс</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Оформляем ЭСД на рейсы лесовозов. Услуга для перевозчиков и заготовителей с постоянными отгрузками.&lt;/p&gt;&lt;p&gt;Как на потоке: утром присылаете список машин на день, к выезду каждый водитель получает свой ЭСД с QR кодом. Рейсы не стоят.&lt;/p&gt;&lt;p&gt;Дополнительно: декларации по сделкам, отчёт 1-ИЛ, остатки по складам.&lt;/p&gt;&lt;p&gt;При постоянном объёме считаем помесячно, выходит дешевле поштучного оформления.&lt;/p&gt;&lt;p&gt;Смоленская область.&lt;/p&gt;&lt;p&gt;Напишите число рейсов в неделю.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Рославль, Смоленская обл., ул. Пролетарская, 68</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2026-08-19T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>9660447079</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/17_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>900</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Документы на лес для ИП и ООО</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Оформляем документы на древесину для ИП и ООО. Услуга разово и на постоянной основе.&lt;/p&gt;&lt;p&gt;Что чаще всего нужно:&lt;br&gt;- ЭСД и QR коды на отгрузки&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- отчёт 1-ИЛ и лесная декларация&lt;br&gt;- места складирования&lt;/p&gt;&lt;p&gt;Отдельно помогаем тем, кто начинает работать с лесом и не знает, какие документы нужны. Объясним порядок и сделаем первый комплект.&lt;/p&gt;&lt;p&gt;Курганская область.&lt;/p&gt;&lt;p&gt;Напишите задачу и объём.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Шадринск, Курганская обл., ул. Октябрьская, 90</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-18T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2026-08-19T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>8254940849</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real1_1__image2.jpg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1100</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Поставить лес на учёт в ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Ставим заготовленную древесину на учёт в ФГИС ЛК. Это услуга, лес не продаём.&lt;/p&gt;&lt;p&gt;Проблема: лес заготовлен, покупатель есть, а в системе объёма нет. Отгрузить нельзя.&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- разбираем происхождение партии, подбираем основание&lt;br&gt;- заводим объём в систему&lt;br&gt;- дальше ведём отгрузки: ЭСД, QR, декларация&lt;/p&gt;&lt;p&gt;Срок зависит от исходных документов: от двух дней до недели. Называем до начала работы.&lt;/p&gt;&lt;p&gt;Тюменская область и юг Западной Сибири.&lt;/p&gt;&lt;p&gt;Опишите ситуацию.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Ишим, Тюменская обл., ул. Республики, 42</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-18T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -5830,7 +7942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ82"/>
+  <dimension ref="A1:AJ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -16188,6 +18300,1942 @@
       <c r="AJ82" t="inlineStr">
         <is>
           <t>2026-08-09T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2634568371</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Лес кругляк ель сосна, ЭСД на отгрузку</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Оформляем ЭСД на еловый и сосновый кругляк. Услуга по документам отгрузки.&lt;br&gt;&lt;br&gt;На каждую машину сопроводительный документ с QR кодом, водителю до выезда. Если объём не заведён в системе, сначала ставим на учёт.&lt;br&gt;&lt;br&gt;Закрываем декларацию о сделке и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Галич, Костромская обл., ул. Свободы, 11</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>900</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB83" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>2026-09-12T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>2026-08-13T18:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>4149246617</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Пиловочник сосна, полный пакет документов</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Оформляем полный пакет документов на сосновый пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;В пакет входит: постановка на учёт, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ, места складирования, коды ОКПД2.&lt;br&gt;&lt;br&gt;От вас данные, от нас готовые документы. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Омская область.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Тара, Омская обл., ул. Ленина, 9</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>2026-09-13T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>2026-08-14T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1099424133</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Лес кругляк ель, ЭСД и постановка на учёт</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Оформляем ЭСД на еловый кругляк и ставим объём на учёт. Услуга по документам.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сопроводительный документ выписывать не на что. Поэтому сначала учёт, потом отгрузки.&lt;br&gt;&lt;br&gt;Дальше: ЭСД с QR на каждый рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Нижегородская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Урень, Нижегородская обл., ул. Ленина, 47</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB85" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>2026-09-13T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>2026-08-14T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1198010038</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Пиловочник сосна, оформим ЭСД на рейс</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Оформляем ЭСД на сосновый пиловочник. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждый рейс: сопроводительный документ с QR кодом, водителю до выезда. Срок 15 минут.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сначала ставим на учёт, потом отгружаете.&lt;br&gt;&lt;br&gt;Ивановская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Юрьевец, Ивановская обл., ул. Советская, 26</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB86" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>2026-09-13T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>2026-08-14T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>3451367236</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Кругляк хвойный, поставим на учёт и вывезем</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ставим хвойный кругляк на учёт в ФГИС ЛК и оформляем вывоз. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Основная проблема не в лесе, а в бумагах: объём есть, в системе его нет, вывезти нельзя.&lt;br&gt;&lt;br&gt;Ставим на учёт, дальше каждый рейс уходит с ЭСД и QR, сделка закрывается декларацией, период отчётом 1-ИЛ.&lt;br&gt;&lt;br&gt;Владимирская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__3.jpg</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Вязники, Владимирская обл., ул. Ленина, 33</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB87" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>2026-09-14T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>2026-08-15T05:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>7655959812</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Лес кругляк сосна, ЭСД на каждый рейс</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Оформляем ЭСД на сосновый кругляк. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждую машину готовим сопроводительный документ с QR кодом. Водитель получает до выезда.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;Алтайский край.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Камень-на-Оби, Алтайский край, ул. Ленина, 48</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB88" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>2026-09-14T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>2026-08-15T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>9790831721</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Баланс хвойный, ЭСД и документы на вывоз</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Оформляем документы на хвойный баланс в ФГИС ЛК. Услуга, баланс не продаём.&lt;br&gt;&lt;br&gt;Закрываем: постановку объёма на учёт, ЭСД с QR на каждую отгрузку, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;ЭСД делаем за 15 минут после получения данных.&lt;br&gt;&lt;br&gt;Рязанская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Касимов, Рязанская обл., ул. Советская, 18</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB89" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>2026-08-15T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>4870626062</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Пиловочник ель сосна, ЭСД и учёт</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Оформляем документы на пиловочник ели и сосны. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Закрываем учёт и сопроводительные документы: постановка объёма на баланс, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут, реквизиты. ЭСД за 15 минут.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Мантурово, Костромская обл., ул. Советская, 22</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>2800</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB90" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>2026-09-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>2026-08-16T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>7622497474</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Лес кругляк сосна, документы и ЭСД</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Оформляем документы на сосновый кругляк в ФГИС ЛК. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;В работу входит: ЭСД на рейс, QR код для поста, декларация о сделке, отчёт 1-ИЛ. Если объём не заведён, ставим на учёт.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, маршрут, реквизиты. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Красноярский край, Ангара и Енисей.&lt;br&gt;&lt;br&gt;Напишите, что везёте и куда.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real234__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Лесосибирск, Красноярский край, ул. Победы, 31</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB91" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>2026-09-15T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>2026-08-16T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4897973128</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Пиловочник ель, ЭСД и QR код на вывоз</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Оформляем ЭСД на еловый пиловочник. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Порядок: присылаете маршрут и реквизиты, получаете ЭСД с QR кодом водителю на телефон. На посту проверка занимает минуту.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;ЭСД: 15 минут.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Чусовой, Пермский край, ул. Ленина, 34</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB92" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>2026-09-16T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>2026-08-17T07:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>5975623537</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Кругляк сосна и баланс, документы на вывоз</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Оформляем документы на сосновый кругляк и баланс. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Что делаем: ЭСД с QR на рейс, декларация о сделке, постановка объёма на учёт, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Типовой ЭСД 15 минут. По постановке на учёт срок называем после разбора документов.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Красновишерск, Пермский край, ул. Гагарина, 6</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB93" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>2026-09-16T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>2026-08-17T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>8561800688</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Баланс ель на комбинат, ЭСД по договору</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ведём документы по поставкам балансовой древесины на комбинат. Услуга по договору.&lt;br&gt;&lt;br&gt;При регулярных поставках документы идут потоком. Оформляем ЭСД на каждую машину, ведём декларации, закрываем отчётность.&lt;br&gt;&lt;br&gt;Отдельно следим, чтобы объёмы по документам сходились с принятыми. Расхождение всплывает на приёмке.&lt;br&gt;&lt;br&gt;Томская область.&lt;br&gt;&lt;br&gt;Напишите объём в месяц.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Асино, Томская обл., ул. Ленина, 42</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB94" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>2026-09-16T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>2026-08-17T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2239987508</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Пиловочник хвойный, оформим вывоз и учёт</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Оформляем документы на хвойный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Берём на себя постановку объёма на учёт, ЭСД с QR на каждую машину, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Работаем и с разовой отгрузкой, и с регулярными поставками. Во втором случае удобнее вести одним исполнителем, чтобы объёмы не разъезжались между документами.&lt;br&gt;&lt;br&gt;Вологодская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Великий Устюг, Вологодская обл., ул. Красная, 12</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB95" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>2026-08-17T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>8000860251</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Лес кругляк ель, поставим на учёт</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ставим еловый кругляк на учёт в ФГИС ЛК. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Если объём нигде не числится, партию нельзя ни продать, ни вывезти. Это решается.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём на баланс, оформляем ЭСД с QR на отгрузки, закрываем декларацию и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Шарья, Костромская обл., ул. Октябрьская, 15</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>2600</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB96" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>2026-09-17T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>2026-08-18T09:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1901670741</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Пиловочник лиственница, документы на лес</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Оформляем документы на лиственничный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;По лиственнице чаще цепляются к сортименту и кодам. Подбираем ОКПД2 под фактический сортимент, чтобы партия прошла без задержек.&lt;br&gt;&lt;br&gt;Закрываем: ЭСД с QR, декларацию о сделке, постановку объёма на учёт.&lt;br&gt;&lt;br&gt;Челябинская область.&lt;br&gt;&lt;br&gt;Напишите сортимент и объём.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Кыштым, Челябинская обл., ул. Калинина, 11</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Лиственница</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB97" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>2026-09-18T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>2026-08-19T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>5972697353</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Лес кругляк ель, документы ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Оформляем документы на еловый кругляк в ФГИС ЛК. Лес не продаём, продаём услугу оформления.&lt;br&gt;&lt;br&gt;Что закрываем:&lt;br&gt;- ЭСД на каждую машину с QR кодом&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- декларация о сделке&lt;br&gt;- отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Без ЭСД рейс встанет на посту. Делаем документ за 15 минут после ваших данных.&lt;br&gt;&lt;br&gt;Удмуртия и Приуралье.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Игра, Удмуртская Республика, ул. Советская, 29</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB98" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>2026-08-19T14:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -3147,7 +3147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:X34"/>
+  <dimension ref="A1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7365,7 +7365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:W34"/>
+  <dimension ref="A1:W34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2026-07-22T13:30:00+03:00</t>
+          <t>2026-08-17T11:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>2026-07-23T08:30:00+03:00</t>
+          <t>2026-08-17T13:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14167,7 +14167,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2026-07-23T10:30:00+03:00</t>
+          <t>2026-08-17T15:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>2026-07-23T13:30:00+03:00</t>
+          <t>2026-08-17T17:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2026-07-24T06:30:00+03:00</t>
+          <t>2026-08-17T19:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14651,7 +14651,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>2026-07-24T12:00:00+03:00</t>
+          <t>2026-08-18T10:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2026-07-24T13:30:00+03:00</t>
+          <t>2026-08-18T16:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -15982,7 +15982,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2026-07-30T19:00:00+03:00</t>
+          <t>2026-08-19T10:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>2026-08-15T09:00:00+03:00</t>
+          <t>2026-08-19T16:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -20328,7 +20328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AD45"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22757,7 +22757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -6498,7 +6498,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-18T05:00:00+03:00</t>
+          <t>2026-08-17T16:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-18T07:00:00+03:00</t>
+          <t>2026-08-17T17:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-18T12:00:00+03:00</t>
+          <t>2026-08-18T05:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-18T14:00:00+03:00</t>
+          <t>2026-08-18T07:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-19T05:00:00+03:00</t>
+          <t>2026-08-18T09:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-19T07:00:00+03:00</t>
+          <t>2026-08-18T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-19T09:00:00+03:00</t>
+          <t>2026-08-18T14:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2026-08-17T11:00:00+03:00</t>
+          <t>2026-08-19T09:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>2026-08-17T13:00:00+03:00</t>
+          <t>2026-08-19T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14167,7 +14167,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2026-08-17T15:00:00+03:00</t>
+          <t>2026-08-19T14:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>2026-08-17T17:00:00+03:00</t>
+          <t>2026-08-20T05:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2026-08-17T19:00:00+03:00</t>
+          <t>2026-08-20T07:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14651,7 +14651,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>2026-08-18T10:00:00+03:00</t>
+          <t>2026-08-20T09:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2026-08-18T16:00:00+03:00</t>
+          <t>2026-08-20T12:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -15982,7 +15982,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2026-08-19T10:00:00+03:00</t>
+          <t>2026-08-20T14:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>2026-08-19T16:00:00+03:00</t>
+          <t>2026-08-17T13:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>2026-08-17T14:00:00+03:00</t>
+          <t>2026-08-17T14:30:00+03:00</t>
         </is>
       </c>
     </row>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>2026-08-18T09:00:00+03:00</t>
+          <t>2026-08-17T19:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>2026-08-19T12:00:00+03:00</t>
+          <t>2026-08-19T05:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -20235,7 +20235,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>2026-08-19T14:00:00+03:00</t>
+          <t>2026-08-19T07:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -13920,7 +13920,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>2026-08-21T11:30:00+03:00</t>
+          <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>2026-08-22T06:30:00+03:00</t>
+          <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>2026-08-22T08:30:00+03:00</t>
+          <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>2026-08-22T11:30:00+03:00</t>
+          <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>2026-08-23T04:30:00+03:00</t>
+          <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>2026-08-23T10:00:00+03:00</t>
+          <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>2026-08-23T11:30:00+03:00</t>
+          <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>2026-08-28T19:00:00+03:00</t>
+          <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -13923,11 +13923,6 @@
           <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>2026-08-19T09:00:00+03:00</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14044,11 +14039,6 @@
           <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>2026-08-19T12:00:00+03:00</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14165,11 +14155,6 @@
           <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>2026-08-19T14:00:00+03:00</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14286,11 +14271,6 @@
           <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>2026-08-20T05:00:00+03:00</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14407,11 +14387,6 @@
           <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>2026-08-20T07:00:00+03:00</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14649,11 +14624,6 @@
           <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>2026-08-20T09:00:00+03:00</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -14770,11 +14740,6 @@
           <t>2026-08-16T23:59:00+03:00</t>
         </is>
       </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>2026-08-20T12:00:00+03:00</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -15978,11 +15943,6 @@
       <c r="AG63" t="inlineStr">
         <is>
           <t>2026-08-16T23:59:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>2026-08-20T14:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -3147,7 +3147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X34"/>
+  <dimension ref="B1:X34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7365,7 +7365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W34"/>
+  <dimension ref="B1:W34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7942,7 +7942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ98"/>
+  <dimension ref="A1:AJ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -8458,7 +8458,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5218613131</t>
+          <t>7414184773</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8167450776</t>
+          <t>8167437487</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8478,17 +8478,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Пиловочник сосна(документы на древесину)</t>
+          <t>Пиловочник ель (не сходятся объёмы)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Сосна пиловочник, свежая делянка, диаметр от 18 до 28, длина 6.1. Лес ровный, сучок мелкий, заготовка аккуратная.&lt;br&gt;&lt;br&gt;Отдельно про бумаги, потому что без них этот лес просто брёвна. Если древесина есть по факту, но не проведена в ФГИС ЛК, вы не сможете ни продать её официально, ни отправить машину с документами. Ставим лес на баланс вашей компании через договор купли-продажи, объём появляется в системе и закрепляется за вами. Дальше отгрузки, ЭСД и отчёты уже техника, тоже берём на себя.&lt;br&gt;&lt;br&gt;Пишите в сообщения или звоните, разберём за один разговор.</t>
+          <t>Приёмка не сошлась по кубатуре, и в системе учёта леса повисла разница? Такое тянется месяцами, если не заняться, а при проверке всплывает в самый неудобный момент.&lt;br&gt;&lt;br&gt;Разбираем расхождения по объёмам: поднимаем движение древесины по вашим документам, находим где разошлись цифры и официально приводим учёт к факту через ФГИС ЛК. Старые хвосты тоже переносим и закрываем без потерь.&lt;br&gt;&lt;br&gt;Пиловочник, кругляк, дрова, любые породы. Нягань, ХМАО, работа полностью удалённая.&lt;br&gt;&lt;br&gt;Опишите какая разница в цифрах, скажем честно что реально закрыть и в какой срок.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.Ubwp-Law_VUfT39YB5ED8wRY_1WZUfVfnw.VlYGla7NRF9UNY7LU-qMNbedLXNdV3ZufGT473K_1Tg | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.vNtMKLawEDJ6n5I_OE7NlWGIEjL8gRg4-g.GYIasJYjTLHkGR4WIucAgjIZQHRFt9EgDCjtGJkNxCw | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.tR4F6rawGfczXZv6Y5jhUShKG_e1QxH9sw.Mhf26rKxH_HC7t4CL8b-3w_VeCt1u1LM-rkI1IunEMY</t>
+          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.sbBLPLawHVl9i59UJQbp_2acH1n7lRVT_Q.1u8tIfkkWxNhhmo6QdWnooj9XIkN6L-u7NxwbmkpKZs | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.-RGp_7awVfifSNf11_jRXoRfV_gZVl3yHw.cp_VxnKLGv4usil7RYgbVUjaKCCDYhqRDwiIadXYl7E | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.lfyfVrawORWp4bsYuRTlsrL2OxUv_zEfKQ.yJtQ5UTuml1vHJTrxa3svcgdVWBQitER7MR8Ly9H3L4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Архангельская обл., Онега, пр-т Ленина, 60</t>
+          <t>Ханты-Мансийский автономный округ — Югра, Нягань, ул. Ленина, 10</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -8558,12 +8558,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -8578,7 +8578,12 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-08-08T09:35:33+03:00</t>
+          <t>2026-08-05T17:06:01+03:00</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>не опт</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -8590,7 +8595,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9359828024</t>
+          <t>9124825228</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8600,7 +8605,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8167326153</t>
+          <t>8135617392</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8610,17 +8615,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Кругляк сосна ель с делянки(отчёты фгис лк)</t>
+          <t>Лес с делянки бревна сосны(документация фгис)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Кругляк сосна и ель с делянки, 6 метров, диаметры от 18. Лес северный, плотный.&lt;br&gt;&lt;br&gt;Теперь про отчёты, ради которых сюда обычно приходят. ФГИС ЛК требует, чтобы объёмы по сделкам, перевозкам и остаткам сходились между собой. Не сдали отчёт вовремя или сдали с ошибкой, появляется расхождение, за ним вопросы от лесничества и риск блокировки. Мы готовим и сдаём отчёты за вас, выравниваем остатки, закрываем старые хвосты официально.&lt;br&gt;&lt;br&gt;Берём как разовые задачи, так и полное сопровождение месяц за месяцем. Напишите, какой у вас случай, ответим в тот же день.</t>
+          <t>В лесу работаю давно и знаю, как обидно терять день из-за бумажки. Лес на делянке готов, покупатель ждёт, а вывезти нельзя, потому что нет сопроводительного документа.&lt;br&gt;&lt;br&gt;Помогаю с этим: оформляю ЭСД и QR коды на перевозку через ФГИС ЛК, ставлю древесину на учёт, чтобы и продажа, и вывоз шли спокойно. Всё делается удалённо, от вас только данные по лесу и машине.&lt;br&gt;&lt;br&gt;Сосна, ель, берёза, кругляк, пиловочник, дрова. Работаю по Свердловской области, ХМАО, Тюменской и соседним регионам.&lt;br&gt;&lt;br&gt;Позвоните, обсудим вашу делянку и сразу начнём.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.iZ8p8rawJXYfRad7N4D50QRSJ3aZWy18nw.h5fFkbsAVMKKco3jQMsmRpeUlULT9okeOEICP0ICVpA | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.sE92bLawHKZA256rGjbPAlvMHqbGxRSswA.PJ2B4fnVWXSeyg-7zdh4dyCCGGTNxdrNJegB-tOHQqg | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.z5bFU7awY3_z5OFy12Tn2ejzYX91-mt1cw.TgUTSFl8Y5Igl1jr4TLzTt2orkpuvLan0ohM0maPhTM</t>
+          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.PtViv7awkjxUCBAxEpt5nE8fkDzSFpo21A.cK7Lr53CUzm3KaEkxVu9VUUo48F0tycTQe6b2duunvc | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.b5bZG7aww3_vrEFyiz422fS7wX9psst1bw.NZTu-CfwwK5BzVQcvGj5_Wy0CiedXOaQSy1tW9HmolI | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.Az1OxLawr9R4cy3ZRJxacmNkrdT-bafe-A.7sBitZzsLAW5-4zmh62VS9-wUihb2ByzkccYK8JMpVg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8635,7 +8640,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Республика Карелия, Костомукша, ул. Ленина, 10</t>
+          <t>Свердловская обл., Североуральск, ул. Ленина, 30</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -8645,7 +8650,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>500</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -8690,12 +8695,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -8710,7 +8715,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-08-09T09:36:41+03:00</t>
+          <t>2026-08-01T16:05:08+03:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -8727,7 +8732,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7414184773</t>
+          <t>7547977722</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8737,7 +8742,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8167437487</t>
+          <t>8167233705</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8747,17 +8752,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Пиловочник ель (не сходятся объёмы)</t>
+          <t>Кругляк ель и сосна (учёт объёмов фгис)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Приёмка не сошлась по кубатуре, и в системе учёта леса повисла разница? Такое тянется месяцами, если не заняться, а при проверке всплывает в самый неудобный момент.&lt;br&gt;&lt;br&gt;Разбираем расхождения по объёмам: поднимаем движение древесины по вашим документам, находим где разошлись цифры и официально приводим учёт к факту через ФГИС ЛК. Старые хвосты тоже переносим и закрываем без потерь.&lt;br&gt;&lt;br&gt;Пиловочник, кругляк, дрова, любые породы. Нягань, ХМАО, работа полностью удалённая.&lt;br&gt;&lt;br&gt;Опишите какая разница в цифрах, скажем честно что реально закрыть и в какой срок.</t>
+          <t>Заготовили кругляк, а в системе учёта древесины он не отражён. Или наоборот: по системе объём есть, а по факту лес уже ушёл. Обе ситуации разбираются.&lt;br&gt;&lt;br&gt;Наводим порядок в учёте: ставим объёмы на баланс, сводим остатки с фактом, закрываем накопившиеся расхождения. Всё проводится официально, результат сразу виден в вашем кабинете.&lt;br&gt;&lt;br&gt;Ель, сосна, берёза, пиловочник, балансы, дрова. Кондопога, Карелия и любые другие регионы, работа полностью удалённая.&lt;br&gt;&lt;br&gt;Расскажите что числится и что лежит на самом деле, оценим и назовём срок.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.sbBLPLawHVl9i59UJQbp_2acH1n7lRVT_Q.1u8tIfkkWxNhhmo6QdWnooj9XIkN6L-u7NxwbmkpKZs | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.-RGp_7awVfifSNf11_jRXoRfV_gZVl3yHw.cp_VxnKLGv4usil7RYgbVUjaKCCDYhqRDwiIadXYl7E | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.lfyfVrawORWp4bsYuRTlsrL2OxUv_zEfKQ.yJtQ5UTuml1vHJTrxa3svcgdVWBQitER7MR8Ly9H3L4</t>
+          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.JepDtLawiQN1AwsOBeBVpG4UiwPzHYEJ9Q.pjSiU_YYQsPm6AGkGpt1XA8gaBPPJXIPxvkYx90YTEA | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.qbB5vLawBVlPC4dUJ5Ly_1QcB1nJFQ1Tzw.XlNv5AYotwO48ecUTzh6xt1svuN-C4xHQl5eZsKNqvw | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.0EW0bLawfKyC2_6hmBf3CpnMfqwExXSmAg.bdQXPOIF7G8meWWxRRq9a84Yy3_D7ruXfGoTkF7s3e0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8772,7 +8777,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ — Югра, Нягань, ул. Ленина, 10</t>
+          <t>Республика Карелия, Кондопога, Пролетарская ул., 22</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -8782,7 +8787,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>800</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -8832,7 +8837,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -8847,7 +8852,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-08-05T17:06:01+03:00</t>
+          <t>2026-08-06T09:06:32+03:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -8864,7 +8869,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9174335479</t>
+          <t>6839713385</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8874,7 +8879,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8167025303</t>
+          <t>8167153384</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8884,17 +8889,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Лес с делянки пиловочник(QR код на вывоз леса)</t>
+          <t>Доска обрезная сосна (QR код на перевозку)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Пиловочник с делянки, сосна, длина 6 метров, диаметр от 20. Отгрузка лесовозными пачками.&lt;br&gt;&lt;br&gt;Тем, кто повезёт, пригодится следующее. Вывоз леса без электронного сопроводительного документа запрещён, на постах проверяют QR код из ФГИС ЛК. Оформление у нас поставлено на поток: скинули данные машины, отправителя, получателя и объём, через 15 минут ЭСД с QR кодом у водителя на экране.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и всем соседним регионам, часовой пояс не проблема. Один рейс или постоянные перевозки, берём любой формат. Наберите или напишите, ответим сразу.</t>
+          <t>Купили или напилили доску, машина загружена, а на перевозку древесины нужен электронный документ. Без него рейс могут остановить на первом же посту.&lt;br&gt;&lt;br&gt;Оформляем ЭСД и QR код через государственную систему ФГИС ЛК. От вас: порода, объём в кубах, госномер машины и маршрут. От нас: готовый QR водителю на телефон, обычно в течение пятнадцати минут.&lt;br&gt;&lt;br&gt;Работаем с любым грузом: доска обрезная, брус, кругляк, дрова. Канск, Красноярский край и любой другой регион, всё удалённо.&lt;br&gt;&lt;br&gt;Позвоните или напишите перед рейсом, оформим без задержек.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.YHX5B7awzJzPsE6RtTYUONSnzpxJrsSWTw.6jttPVf8yKySV3-o41qp2nqo7GlP8EA_XSJRcRR7CG0 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.KHP5ELawhJrPpwaXpUA8O9SwhppJuYyQTw.n1VrT3pQHZLP5I3wQxrjmXAepZRN9dz1DrnN_P478bA | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.YWwpw7awzYUfdE-IZ6oOJARjz4WZasWPnw.JR6Dx6LapzYhqfUcA2YzMeG3Vkpirapc6oI2N2eXUgw</t>
+          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.T4V23raw42xAaWFhZIsTylt-4WzGd-tmwA.naTaOrISfdpzrCyOVYgxhlU8ReRoOCYcp2g7jZTz2mw | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.WgdRALaw9u5nt3TjaT1OT3yg9O7hqf7k5w.6IjqZCf13Ub7dT-UtiujNhIsHyIvKvDbcUHCmtxKMxg | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.4EMiLLawTKoUm86nbjOVDQ-MTqqShUSglA.EGzp9y4Qzcxyafcc5AhBL8A_wWbVV5Gw3QXbZZNsA9g</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8909,7 +8914,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Уфа, пр-т Октября, 82</t>
+          <t>Красноярский край, Канск, Московская ул., 18</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -8919,7 +8924,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>400</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -8984,7 +8989,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026-08-08T14:06:15+03:00</t>
+          <t>2026-08-05T14:06:49+03:00</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -9001,7 +9006,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3458655411</t>
+          <t>7747398644</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9011,7 +9016,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8167152085</t>
+          <t>8167232117</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9021,17 +9026,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Лес зимней заготовки(эсд на перевозку леса)</t>
+          <t>Пиломатериал сосна (документы на древесину)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Лес зимней заготовки, хвоя, кругляк ровный, длина 6 метров. Погрузка манипулятором, отгружаем с площадки.&lt;br&gt;&lt;br&gt;Дальше о том, что спрашивают на каждом посту. Перевозка древесины без ЭСД запрещена, документ оформляется в ФГИС ЛК и содержит QR код, который читает инспектор. Мы делаем такие документы каждый день: вы присылаете данные машины, отправителя, получателя и объём, через 15 минут у водителя на телефоне готовый ЭСД.&lt;br&gt;&lt;br&gt;Если рейс срочный или ночной, тоже решаем. Постоянным перевозчикам ведём все рейсы подряд, вы просто скидываете заявки. Звоните, отвечаем быстро.</t>
+          <t>Напилили доску или брус, покупатель готов брать, а древесина по документам нигде не числится. Сделка встаёт, потому что без учёта в системе лес не продать и не увезти.&lt;br&gt;&lt;br&gt;Ставим объёмы на баланс официально, через договор. После оформления древесина видна в вашем кабинете, дальше спокойно делаются и продажа, и перевозка с QR кодом.&lt;br&gt;&lt;br&gt;Работаем с пиломатериалом, кругляком и дровами, породы любые. Барнаул, Алтайский край и другие регионы, всё удалённо, документы отдаём на руки.&lt;br&gt;&lt;br&gt;Напишите сколько кубов и что за материал, подскажем первый шаг и срок.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.cgDCkLaw3un0J1zkqskvT-8w3OlyOdbjdA.YItTMAwRszP0Tz3KPvqyfS2L_jjrm9mJ62go0R-yD1Y | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.9VpAqbawWbN2Htu-JqaYEm0JW7PwAFG59g.AtPIdx_QQbF6ATxn4DRiqnD_dYKQPuEt94iQeo9xQOE | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.15b917awe3_LYPly3-id2NB3eX9NfnN1Sw.h7PEblC4fd1aQhKg69FD2LrwIrIK4dOl3IlvzVSoaE4</t>
+          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.g0xi7LawL6VUW62oaM73Ak9MLaXSRSev1A.5GDX7MxGI7NNz-rUIL41SCxn-rLlK6i-pi01hWUYYn4 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.hnmIAbawKpC-tqidiB_1N6WhKJA4qCKaPg.yB0yOlMZ2pL8owZGAnqGNdGC4XhXW3Z1szElUnAB9SM | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.aE9GbLawxKZw20arGjURAmvMxqb2xcys8A.Fh2qeK_jCtuamMKg5_zf3p3wuHODTMmGvyDbynaXpmw</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9046,7 +9051,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Архангельская обл., Няндома, ул. Ленина, 21</t>
+          <t>Алтайский край, Барнаул, ул. Попова, 55</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -9056,7 +9061,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>700</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -9106,7 +9111,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -9121,7 +9126,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026-08-07T16:05:46+03:00</t>
+          <t>2026-08-06T12:05:58+03:00</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -9138,7 +9143,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5531207647</t>
+          <t>5953556065</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9148,7 +9153,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8167693343</t>
+          <t>8134916629</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9158,17 +9163,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Берёза кругляк свежий спил(документы на лес)</t>
+          <t>Пиловочник ель сосна(эсд и QR код фгис)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Берёза кругляк, свежий спил, 4 и 6 метров, диаметр от 16 до 24. Под пиление и под дрова уходит хорошо.&lt;br&gt;&lt;br&gt;Главная услуга в скобках заголовка. Когда лес есть, а документов на него нет, это тупик: ни продать, ни вывезти, ни показать проверке. Мы делаем так, чтобы ваша древесина официально числилась за вами в ФГИС ЛК. Договор купли-продажи, внесение объёма в систему, закрепление за вашим ИНН. Затем при необходимости ЭСД на перевозку и отчётность.&lt;br&gt;&lt;br&gt;Вопрос решается быстрее, чем кажется. Позвоните или напишите, объясним на вашем примере.</t>
+          <t>Оформляем перевозочные документы на лес для заготовителей и водителей.&lt;br&gt;&lt;br&gt;Как это выглядит по шагам:&lt;br&gt;1. Вы присылаете данные: порода, объём, номер машины, откуда и куда рейс.&lt;br&gt;2. Мы вносим всё в систему ФГИС ЛК и формируем электронный сопроводительный документ.&lt;br&gt;3. Водителю уходит QR код, который он показывает при проверке на посту.&lt;br&gt;&lt;br&gt;Работаем официально, каждый документ реально числится в системе, любая проверка это подтверждает. Порода и объём любые: сосна, ель, лиственница, берёза, кругляк, пиловочник, дрова.&lt;br&gt;&lt;br&gt;Пишите, ответим быстро и возьмём рейс в работу.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.K6excbawh06HxgVD6yVf6pzRhU4B2I9EBw.56ndumjpKo2kEmff9hCrwQPtfGSyNVs5itqYDUtay8k | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.PtUTErawkjwlpRAxYwJ0mz6ykDyju5o2pQ.9fgqrBWqu4HKzPOKJxbG8TdStJW5iTI-baRebCHLL00 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.T3dS3raw455kaWGTQMNbP39-4Z7id-uU5A.cM1lcySuHSTfOuKVZf_sv-NynFLQqtphc3Q_dI9lPyA</t>
+          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.8OQFC7awXA0zvN4AaVzirCirXg21olQHsw.s1dHKZ5xRK6_nBw6r9iJWP0hayhHfaZMYATdUa_myZM | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.uXTtW7awFZ3b7JeQk0nhO8D7F51d8h2XWw.V4u6_es2DGDvywvxy14vERfmJQtT-py_Hn_seEi6AWo | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.0E9SLLawfKZkm_6rfjOrAn-MfqbihXSs5A.dkNrPRJA4Vfjh7cfrFC0Lq7D38umYIlK-cMhm57oL70</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9183,7 +9188,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Кировская обл., Котельнич, Советская ул., 83</t>
+          <t>Ямало-Ненецкий автономный округ, Ноябрьск, ул. Ленина, 22</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -9193,7 +9198,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -9228,7 +9233,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -9238,12 +9243,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9258,7 +9263,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026-08-09T08:06:44+03:00</t>
+          <t>2026-08-01T14:05:54+03:00</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -9275,17 +9280,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3867391339</t>
+          <t>6407106167</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>8167743594</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9295,17 +9295,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Лес кругляк хвоя с делянки(эсд на перевозку)</t>
+          <t>Лес есть учёта нет(кругляк ФГИС ЛК)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Лес кругляк хвоя с делянки, ель и сосна, 4 и 6 метров. Под лежнёвку и отсыпку берут отсюда постоянно.&lt;br&gt;&lt;br&gt;По перевозке. Каждый рейс с лесом должен сопровождаться ЭСД из ФГИС ЛК, инспектор на посту сканирует QR код. Оформляем такие документы удалённо для перевозчиков по всему ЯНАО: присылаете номер машины и прицепа, ИНН отправителя и получателя, породу и объём, через 15 минут водитель едет с готовым документом.&lt;br&gt;&lt;br&gt;Часовые пояса и ночные рейсы не мешают, на связи почти круглосуточно. Напишите в сообщения, ответим быстро и по делу.</t>
+          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Ростов-на-Дону и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.hF9MfLawKLZ6y6q7SB7cEGHcKrb81SC8-g.L3m-gFiMZpiKzVQl5zae7OcnRWdCrfniG2NfodS0Mi8 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.YAt5B7awzOJPsE7vNV4bRlSnzuLJrsTozw.AupmGk9rzStBwKiCH-EA85eOn1vCGhgxug6SZCKbeJ4 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.71HL6bawQ7j9XsG1mcqiH-ZJQbh7QEuyfQ.0uKPfONxs6oCshoTwDsIBKIhLZJqi9RAcRS1hrI1Iew</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/10/10_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/10/10_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/10/10_03.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ, Лабытнанги, ул. Гагарина, 14</t>
+          <t>Ростовская область, Ростов-на-Дону</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -9328,10 +9328,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="P11" t="n">
+        <v>300</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -9365,7 +9363,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -9375,12 +9373,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -9395,34 +9393,24 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026-08-09T14:06:27+03:00</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-16T05:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>2026-07-17T07:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9124825228</t>
+          <t>5937878704</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>8135617392</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -9432,17 +9420,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Лес с делянки бревна сосны(документация фгис)</t>
+          <t>Сосна пиловочник (QR код и ЭСД на перевозку)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>В лесу работаю давно и знаю, как обидно терять день из-за бумажки. Лес на делянке готов, покупатель ждёт, а вывезти нельзя, потому что нет сопроводительного документа.&lt;br&gt;&lt;br&gt;Помогаю с этим: оформляю ЭСД и QR коды на перевозку через ФГИС ЛК, ставлю древесину на учёт, чтобы и продажа, и вывоз шли спокойно. Всё делается удалённо, от вас только данные по лесу и машине.&lt;br&gt;&lt;br&gt;Сосна, ель, берёза, кругляк, пиловочник, дрова. Работаю по Свердловской области, ХМАО, Тюменской и соседним регионам.&lt;br&gt;&lt;br&gt;Позвоните, обсудим вашу делянку и сразу начнём.</t>
+          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Раньше система звалась ЛесЕГАИС, суть та же. Если у вас есть сосна, кругляк, пиловочник или балансы с деляны, а бумаг на них нет, всё сделаю по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код и ЭСД на перевозку, чтобы лесовоз прошёл лесной контроль без штрафов. Считаю по фото ваших замеров удалённо, вам никуда ехать не надо.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по кубам, ставлю лес на баланс, готовлю декларации и отчёты. Беломорск и район, объёмы любые.&lt;br&gt;&lt;br&gt;Пришлите замеры с делянки, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.PtViv7awkjxUCBAxEpt5nE8fkDzSFpo21A.cK7Lr53CUzm3KaEkxVu9VUUo48F0tycTQe6b2duunvc | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.b5bZG7aww3_vrEFyiz422fS7wX9psst1bw.NZTu-CfwwK5BzVQcvGj5_Wy0CiedXOaQSy1tW9HmolI | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.Az1OxLawr9R4cy3ZRJxacmNkrdT-bafe-A.7sBitZzsLAW5-4zmh62VS9-wUihb2ByzkccYK8JMpVg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_03.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -9457,7 +9445,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Свердловская обл., Североуральск, ул. Ленина, 30</t>
+          <t>Республика Карелия, Беломорск, ул. Лесная, 12</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -9465,10 +9453,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="P12" t="n">
+        <v>250</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -9510,15 +9496,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
+      <c r="AB12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>210</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -9532,34 +9514,24 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-08-01T16:05:08+03:00</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-20T18:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>2026-07-21T20:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2360715780</t>
+          <t>6036836126</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>8167402342</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9569,17 +9541,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Кругляк хвоя(QR код на перевозку леса)</t>
+          <t>Лиственница пиловочник (QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Кругляк хвоя от заготовителя, сосна и лиственница, 6 метров. Объёмы стабильные, грузим лесовозами.&lt;br&gt;&lt;br&gt;Теперь важное для тех, кто возит. Каждый лесовоз должен идти с электронным сопроводительным документом из ФГИС ЛК, в документе QR код. Проверяют на постах и на весовых. Нет QR, машина стоит, водитель платит.&lt;br&gt;&lt;br&gt;Мы оформляем ЭСД на любой рейс за 15 минут. Присылаете реквизиты отправителя и получателя, госномер тягача и прицепа, породу и кубатуру. Готовый документ уходит водителю в мессенджер. Берём и разовые рейсы, и постоянку. На связи с раннего утра.</t>
+          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас есть лиственница, кругляк, пиловочник или балансы с деляны, а бумаг на вывозку нет, приведу всё в порядок по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код на вывоз леса, чтобы лесовоз прошёл лесной контроль без штрафов. Считаю по фото ваших замеров удалённо и быстро, вам никуда ехать не надо.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по объёмам, ставлю лес на баланс, готовлю декларации и отчёты. Нижнеудинск и район, объёмы любые.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня. Отвечаю за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.Q2xuj7aw74VYOG2IZMovJEMv7YXeJueP2A.1xFcPzRFwn9_Vx-iOyHpDmdinaH1V_ibZq_Jg-5o6nw | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.0bBBPLawfVl3i_9Ub1eJ_2ycf1nxlXVT9w.1dG3drtkJqbb3c2_M0pULVNwAh4n-de_Va73QzVg45g | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.tBCww7awGPmGdJr01PXfWJ1jGvkAahDzBg.DcqdGoH4xvzvDaHHr_kuPwif3KeXz_y8NGa2YPGGeAM</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_03.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9594,7 +9566,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Иркутская обл., Тулун, ул. Ленина, 13</t>
+          <t>Иркутская область, Нижнеудинск, ул. Заводская, 19</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -9602,10 +9574,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
+      <c r="P13" t="n">
+        <v>200</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -9639,7 +9609,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Лиственница</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -9647,15 +9617,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="AB13" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>220</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -9669,34 +9635,24 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2026-08-08T06:35:26+03:00</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-20T19:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1450333833</t>
+          <t>3305654333</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>8166925539</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9706,17 +9662,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Лес кругляк берёза(не сходятся объёмы фгис)</t>
+          <t>Берёза пиловочник (не сходятся объёмы ФГИС)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Берёза кругляк, 4 метра, диаметр от 16. Лес с делянки, вывезен на площадку.&lt;br&gt;&lt;br&gt;А теперь о том, из-за чего обычно звонят. Приёмка показала одно, в документах другое, и разница повисла в ФГИС ЛК. Пока расхождение не закрыто, система не даёт нормально отгружать, и с каждым рейсом яма только растёт. Мы разбираем такие ситуации: смотрим, откуда взялась разница, и закрываем её официально, через договор и корректные записи в системе.&lt;br&gt;&lt;br&gt;Чем раньше начать разбор, тем дешевле он обходится. Позвоните или напишите, посмотрим вашу картину по объёмам и скажем, как выровнять.</t>
+          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Это услуга по бумагам, а не торговля кругляком.&lt;br&gt;&lt;br&gt;Работаю по Мурашам и району. Если по системе один объём, а на деляне или на складе по факту другой, свожу это официально. Берёза, пиловочник, балансы, дрова, осиновый кругляк, любой сортимент. Замерили лесовоз, а цифры в ФГИС не сходятся, расхождение висит и мешает вывозке, закрою через договор купли-продажи и приведу объём в порядок.&lt;br&gt;&lt;br&gt;Делаю QR и ЭСД на перевозку, ставлю лес на баланс, готовлю декларации и отчёты. Если у вас есть лес, а документов на него нет, оформлю.&lt;br&gt;&lt;br&gt;Пришлите замеры по делянке, посчитаю сегодня и скажу, как свести объёмы. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.w5Jxcbawb3tHxu12ex6631zRbXvB2Gdxxw.__9O9jP_Skfc1BgTTkVL9Lt8CRThcLEjIU8rDRmDf0Y | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.N6DY3rawm0nuaRlEutZ97vV-mUlod5NDbg.S_SsdypRtg928k4jELD6VurF_ovxDlu7VrKTVfm9qE8 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.JGtMKLawiIJ6nwqPCHxUJWGIioL8gYCI-g.CB2H0iQDpAf6IC6g6LViRA-0eX9g3SyVX4f-vFMgb9A</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_03.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9731,7 +9687,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Республика Коми, Сосногорск, ул. Куратова, 4</t>
+          <t>Кировская область, Мураши, ул. Советская, 26</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -9739,10 +9695,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
+      <c r="P14" t="n">
+        <v>300</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -9784,15 +9738,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="AB14" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>230</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -9806,34 +9756,24 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026-08-08T08:06:35+03:00</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-21T04:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>2026-07-22T06:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6127988561</t>
+          <t>5783794994</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>8167643129</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9843,17 +9783,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Кругляк ель сосна(лес на баланс фгис)</t>
+          <t>Сосна пиловочник (QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Кругляк ель и сосна, 6 метров, диаметр от 18 до 26. Лес карельский, плотный, лежит близко к трассе.&lt;br&gt;&lt;br&gt;Кому нужнее документы, чем брёвна, читайте дальше. Купили лес без бумаг, приняли больше, чем по накладной, осталась древесина после стройки или разбора. Во всех этих случаях в ФГИС ЛК объёма нет, а по факту он есть. Мы оформляем его законно: договор купли-продажи, внесение сделки в систему, объём на балансе вашей компании. После этого лес можно возить и продавать открыто.&lt;br&gt;&lt;br&gt;Звоните или пишите, расскажем по шагам, что и в какой срок делается.</t>
+          <t>&lt;p&gt;Сразу к делу: мы не продаём лес, мы оформляем на него документы в системе ФГИС ЛК. Если у вас есть кругляк, пиловочник сосны, балансы или дрова с деляны, а бумаг на вывоз нет, мы их сделаем.&lt;br&gt;&lt;br&gt;Готовим QR-код и ЭСД (электронный сопроводительный документ) на перевозку, чтобы лесовоз прошёл лесной контроль и первый же рейс ушёл без штрафов. Работаем удалённо: пришлите фото замеров по кубам, посчитаем объём и оформим сами.&lt;br&gt;&lt;br&gt;Также закрываем расхождения объёмов, ставим лес на баланс, готовим декларации и отчёты. Город Буй, работаем со всеми регионами.&lt;br&gt;&lt;br&gt;Есть делянка, вывозка на носу, а документов нет: напишите в сообщения, отвечу за пару минут. Пришлите замеры сегодня, посчитаю сегодня.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.1tUA_rawejw2SfgxIN2Dmi1eeDywV3I2tg.qcGgz6HW12OPo2MJFXnm97eAwvad0HgXamuKm_B8iL8 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.DCdMNbawoM56giLDWC1GaWGVos78nKjE-g.Qf-cBAUe7v1KDPQysUKckBlfS4KrAw5mCWH1_5PYcTE | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.LfiXVrawgRGh4QMcwRJZtrr2gxEn_4kbIQ.DfMY9Nh-B4BiQgluCll8kEcUOjfI169JrzhXWgF8QqA</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_03.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9868,7 +9808,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Республика Карелия, Петрозаводск, пр-т Ленина, 15</t>
+          <t>Костромская область, Буй, ул. Октябрьская, 47</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -9876,10 +9816,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
+      <c r="P15" t="n">
+        <v>250</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -9913,7 +9851,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -9921,15 +9859,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="AB15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>200</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -9943,34 +9877,24 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2026-08-08T12:36:18+03:00</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-21T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>2026-07-22T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5589051838</t>
+          <t>5855275648</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>8167110560</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9980,17 +9904,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Кругляк сосна зимний лес(эсд и QR на перевозку)</t>
+          <t>Берёза пиловочник (лес на баланс ФГИС)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Кругляк сосна, зимний лес, сухой, ровный, 6 метров. Для отсыпки, лежнёвки и стройки подходит.&lt;br&gt;&lt;br&gt;Север возит лес постоянно, и на каждом рейсе нужен ЭСД с QR кодом из ФГИС ЛК. Без него машину останавливают, а простой на зимнике обходится дороже самого леса. Мы оформляем сопроводительные документы удалённо, за 15 минут, в любое время: данные машины и сторон, порода, кубатура, и QR код уже у водителя в телефоне.&lt;br&gt;&lt;br&gt;Ведём перевозчиков ЯНАО и ХМАО на постоянной основе, знаем местную специфику. Пишите в сообщения или звоните, поможем с первым рейсом сегодня.</t>
+          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас на деляне лежит заготовленная берёза, кругляк или пиловочник, а в системе его нет, помогу поставить древесину на баланс. Заключаем договор, закрепляем объём в ФГИС ЛК, и лес становится вашим официально, можно законно возить и продавать.&lt;br&gt;&lt;br&gt;Работаю по Нелидово и району. Балансы, дрова, делянка, вывозка лесовозами, замеры в кубах, любой объём. Сделаю QR и ЭСД на перевозку, закрою расхождение по объёмам, подготовлю декларации и отчёты.&lt;br&gt;&lt;br&gt;Пришлите замеры с делянки, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.BtUOxLawqjw4cygxDowimiNkqDy-baI2uA.zAt9zXTV6NPZ7dwsPNspYpxivljKeyfGnS6fUXSfdYY | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.wEk5C7awbKAPvO6tNXSzBxSrbqCJomSqjw.fSV3vBW2dQRgEsEY7KzU36_QD3FEax-mpAOh9jxUvKg | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.saI3PLawHUsBi59GWWbO7xqcH0uHlRVBgQ.3m-7LdeInuG7uWeOEFrEbb5NkvyRwh_N2vB62Ytmyc8</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_03.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10005,7 +9929,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ, Надым, ул. Зверева, 7</t>
+          <t>Тверская область, Нелидово, ул. Промышленная, 13</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -10013,10 +9937,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
+      <c r="P16" t="n">
+        <v>250</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -10050,7 +9972,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Берёза</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -10058,15 +9980,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="AB16" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>220</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -10080,34 +9998,24 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026-08-08T15:36:22+03:00</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-23T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>2026-07-24T08:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2038772371</t>
+          <t>7232164186</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>8166963291</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10117,17 +10025,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Продам пиловочник ель(закрытие расхождений фгис)</t>
+          <t>Сосна пиловочник (ЭСД и QR к сделке)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Пиловочник ель, диаметр от 18 до 28, длина 6 метров, заготовка свежая.&lt;br&gt;&lt;br&gt;Теперь то, ради чего это объявление. Если по вашей древесине в ФГИС ЛК висят расхождения, куплено одно количество, оприходовано другое, отгружено третье, рано или поздно система заблокирует движение объёмов. Мы разбираем цепочку, находим точку, где разошлось, и закрываем разницу официально. Составляем договор, проводим корректные записи, восстанавливаем нормальную работу.&lt;br&gt;&lt;br&gt;Опыт по лесным регионам большой, случаи видели разные. Позвоните, разбор ситуации ни к чему не обязывает.</t>
+          <t>&lt;p&gt;Сразу главное: сам лес мы не продаём. Мы оформляем документы на лес в системе ФГИС ЛК, работаем из Тихвина удалённо.&lt;br&gt;&lt;br&gt;Если у вас есть сосна, пиловочник, кругляк, балансы или дрова на деляне, а бумаг на них нет, мы всё оформим. Поставим лес на баланс, закроем расхождения по кубам, сделаем декларации и отчёты.&lt;br&gt;&lt;br&gt;Отдельно по вывозке: делаем QR-код и ЭСД к сделке, чтобы лесовоз прошёл лесной контроль без штрафов. Считаем по фото замеров с деляны, ничего никуда везти не нужно.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и скажу, что нужно для перевозки. Отвечаю за пару минут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.4z_85LawT9bKU83btvuWcdFETdZMTUfcSg.Zg2sTBVqdsVbDgp7v3--P8LPET-RxNDzbGkR0etQDgY | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.BBCN_7awqPm7SCr0ifcVWKBfqvk9VqDzOw.aonWbzS-IsIyPXP93INRDqmuP28KnWW0khpNlY3aPHY | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.IfTtULawjR3b5w8Qoxx5u8Dwjx1d-YUXWw.M7_4NpuTdmOa9n61IGiPpHb5KVKj-8Kcoa_NG14_LDQ</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_03.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10142,7 +10050,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Красноярский край, Минусинск, Абаканская ул., 51</t>
+          <t>Ленинградская область, Тихвин, ул. Гагарина, 48</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -10150,10 +10058,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
+      <c r="P17" t="n">
+        <v>250</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -10187,7 +10093,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -10195,15 +10101,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="AB17" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>210</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -10217,34 +10119,24 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2026-08-09T05:05:01+03:00</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-24T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>2026-07-25T08:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6166079937</t>
+          <t>2872293673</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>8166930148</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10254,17 +10146,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Продам лес пиловочник сосна(помощь с учётом леса)</t>
+          <t>Сосна пиловочник (QR код на отгрузку)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Пиловочник сосна, 6 метров, диаметр от 20 до 30, зимней заготовки. Лес чистый, ровный, хранится правильно.&lt;br&gt;&lt;br&gt;И про учёт, с которым помогаем. Если вы купили древесину без документов, получили её по бартеру или объём просто не был проведён, в ФГИС ЛК его нет, и работать с ним легально нельзя. Мы закрепляем лес за вашей компанией официально: договор купли-продажи, внесение в систему, порядок в остатках. Потом сопровождаем отгрузки и отчёты, чтобы учёт не разъезжался.&lt;br&gt;&lt;br&gt;Звоните или пишите, спокойно разберём вашу ситуацию и наметим шаги.</t>
+          <t>&lt;p&gt;Оформляем документы на лес в системе ФГИС ЛК. Сам лес мы не продаём, делаем только бумаги на него. Если у вас есть своя партия под отгрузку в Галиче, сосна пиловочник, кругляк, балансы или дрова, а документов на неё нет, оформим всё по правилам.&lt;br&gt;&lt;br&gt;Сделаем QR-код и ЭСД на вывозку, чтобы лесовоз с грузом прошёл лесной контроль без штрафов. Закрываем расхождения по кубам, ставим лес на баланс, готовим декларации и отчёты.&lt;br&gt;&lt;br&gt;Считаем по фото ваших замеров, работаем удалённо, деляна может быть где угодно. Напишите в сообщения, отвечу за пару минут. Пришлите замеры с делянки, посчитаю сегодня.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.lGAiWbawOIkU7rqEBhvkLg_5OomS8DCDlA.Edm7twEXidWB4hky46EyDQLpM98q16TmmVXI9pIU2PM | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.sEXJrLawHKz_G56hpYqYCuQMHqx5BRSmfw.5eIMnNGxIyoxXDEOFOefF_ZjnY91RXk6sRJsz6U95Zw | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.tBFo87awGPheRJr1DPXvXkVTGvjYWhDy3g.CtyNPepMrv2BIsVK-NZ0IHuNa7P3A9ZrMQEtPvN-m5o</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_03.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10279,7 +10171,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ — Югра, Югорск, ул. Ленина, 29</t>
+          <t>Костромская область, Галич, ул. Лесная, 62</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -10287,10 +10179,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
+      <c r="P18" t="n">
+        <v>200</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -10332,15 +10222,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>230</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -10354,34 +10240,24 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2026-08-09T15:36:17+03:00</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-24T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>2026-07-25T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6184130138</t>
+          <t>6521830331</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>8167790778</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10391,17 +10267,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Продам лес кругляк хвоя(расхождения по кубам)</t>
+          <t>Сосна с делянки документов нет(помощь с учётом)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Лес кругляк хвоя, сосна с елью вперемешку, 6 метров, диаметры рабочие, от 18 до 30.&lt;br&gt;&lt;br&gt;Дальше честно. Основной наш профиль не продажа, а учёт. К нам приходят, когда кубы по приёмке не бьются с кубами по документам. Разница висит в ФГИС ЛК, отгрузки встают, инспекция задаёт вопросы. Мы находим, где именно разошлось, и закрываем расхождение официально, с договором и правильными проводками объёмов в системе.&lt;br&gt;&lt;br&gt;Работаем аккуратно, без серых схем, поэтому результат держится. Опишите ситуацию в сообщении, объёмы и регион, ответим быстро и по существу.</t>
+          <t>Оформление документов на древесину в ФГИС ЛК: кругляк, пиловочник, балансовая древесина, дрова. Работаем с лесозаготовителями, продавцами и покупателями леса.&lt;br&gt;&lt;br&gt;Что оформляем:&lt;br&gt;- электронный сопроводительный документ (ЭСД) на транспортировку древесины&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- постановку объёма на учёт и баланс, если древесина нигде не числится&lt;br&gt;- декларацию о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Присылаете породу, кубатуру, маршрут и данные сторон. Оформляем документ и передаём водителю в электронном виде.&lt;br&gt;&lt;br&gt;Срок по ЭСД обычно 15 минут с момента получения данных. Постановка объёма на учёт занимает дольше, скажу сразу по вашей ситуации.&lt;br&gt;&lt;br&gt;Свой личный кабинет в системе, электронная подпись и лесная декларация вам не нужны, оформление идёт с нашей стороны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Сосна, ель, лиственные породы, любые сортименты и объёмы, от одной лесовозной машины до постоянных отгрузок.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок и срок.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.krklSbawPlAT_rxdDTvc9wjpPFCV4DZakw.4J-Pw0lKdQUZIrq9c78kwPIfcvR4GIiAG9Apql1v7wA | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.uGQbJ7awFI0tkJaAZznvKzaHFo2rjhyHrQ.DLjPhmbZ24p02Kmx7DKxZYkFj0Y-CHzgWBE9hLaLE5M | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.4EV-rLawTKxIG86hMvveClMMTqzOBUSmyA.PokskJfBa6mXjeISGYz-bOw0mn-IWAlgV5_L0LyxKl8</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_3.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10416,7 +10292,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Кировская обл., Кирово-Чепецк, пр-т Мира, 20</t>
+          <t>Республика Башкортостан, Белорецк, ул. Ленина, 24</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -10424,10 +10300,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>3200</t>
-        </is>
+      <c r="P19" t="n">
+        <v>500</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -10461,7 +10335,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -10469,15 +10343,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="AB19" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>230</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -10491,29 +10361,24 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2026-08-08T11:05:20+03:00</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-27T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>2026-07-29T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3929552218</t>
+          <t>4661388548</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>8167560474</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -10523,17 +10388,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Лес хвоя от заготовителя(QR код на лес)</t>
+          <t>Лес с делянки документов нет(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Лес хвоя от заготовителя, кругляк 6 метров, сосна. Грузим полными машинами, объём есть постоянно.&lt;br&gt;&lt;br&gt;Дальше о документах на рейс. QR код на перевозку леса оформляется через ФГИС ЛК, без него машина с древесиной вне закона. Мы делаем ЭСД быстро и без ошибок: от вас данные тягача и прицепа, ИНН сторон, порода и кубы. Через 15 минут документ с QR кодом у водителя.&lt;br&gt;&lt;br&gt;Возите регулярно, договоримся о сопровождении всех рейсов, вы будете просто присылать заявки списком. Работаем без выходных, звоните или пишите в сообщения.</t>
+          <t>QR коды и электронные сопроводительные документы на вывоз древесины через ФГИС ЛК. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена, на постах проверяют QR код с данными рейса. Оформляем его на каждую лесовозную машину.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- сопровождение постоянных перевозок, документ на каждый рейс&lt;br&gt;- постановка древесины на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок работы. От вас данные машины, отправителя и получателя, порода и кубатура в кубометрах. Дальше оформление на нас, QR код приходит водителю на телефон.&lt;br&gt;&lt;br&gt;Обычно занимает 15 минут с момента, когда получили данные.&lt;br&gt;&lt;br&gt;Личный кабинет ФГИС ЛК, электронная подпись и собственная декларация не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и всему Приуралью. Сосновый и еловый пиловочник, лес с делянки, древесина оптом, формат любой.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.C4xhuLawp2VXDyVoe4Aqw0wYpWXREa9v1w.AVo2fmsChGtbcwrrKOk2PYSQVt6K8RLzt8mDr-jhpNk | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.heJDiLawKQt1P6sGRdrJrG4oKwvzISEB9Q.zp8SLWj-6m9tOCLAE_v-QsTcM8Kf2Z6M4OMAH_808RU | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.G4Wxcbawt2yHxjVhi2VnyJzRtWwB2L9mBw.jG7yKwmXLk7Ewc-xEHRyoL9LG5q1cFaG0XPhFoa6W4k</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_3.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -10548,7 +10413,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Учалы, ул. Ленина, 20</t>
+          <t>Республика Башкортостан, Янаул, ул. Победы, 16</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -10556,10 +10421,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
+      <c r="P20" t="n">
+        <v>400</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -10601,15 +10464,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="AB20" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>230</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -10623,34 +10482,24 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2026-08-09T11:06:03+03:00</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-27T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>2026-07-29T11:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7547977722</t>
+          <t>6175129265</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>8167233705</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -10660,17 +10509,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Кругляк ель и сосна (учёт объёмов фгис)</t>
+          <t>Кругляк с делянки бумаг нет(документы фгис лк)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Заготовили кругляк, а в системе учёта древесины он не отражён. Или наоборот: по системе объём есть, а по факту лес уже ушёл. Обе ситуации разбираются.&lt;br&gt;&lt;br&gt;Наводим порядок в учёте: ставим объёмы на баланс, сводим остатки с фактом, закрываем накопившиеся расхождения. Всё проводится официально, результат сразу виден в вашем кабинете.&lt;br&gt;&lt;br&gt;Ель, сосна, берёза, пиловочник, балансы, дрова. Кондопога, Карелия и любые другие регионы, работа полностью удалённая.&lt;br&gt;&lt;br&gt;Расскажите что числится и что лежит на самом деле, оценим и назовём срок.</t>
+          <t>Полный пакет документов на древесину в ФГИС ЛК для заготовителей, продавцов и перевозчиков леса.&lt;br&gt;&lt;br&gt;В работе:&lt;br&gt;- электронный сопроводительный документ на транспортировку кругляка и пиловочника&lt;br&gt;- QR код на рейс для проверки на посту&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- лесная декларация и декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования древесины&lt;br&gt;&lt;br&gt;Как это работает. Вы присылаете породу, кубатуру, маршрут и реквизиты. Мы оформляем документы в системе и передаём их в готовом виде.&lt;br&gt;&lt;br&gt;ЭСД обычно готов за 15 минут. Постановка объёма на учёт и работа с декларацией занимают дольше, срок называю до начала работы.&lt;br&gt;&lt;br&gt;Заводить свой кабинет и электронную подпись не нужно, оформление ведём со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Хвойный кругляк, лесоматериалы круглые, баланс, любые объёмы с делянки и со склада.&lt;br&gt;&lt;br&gt;Напишите кубатуру и куда везёте, скажу срок.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.JepDtLawiQN1AwsOBeBVpG4UiwPzHYEJ9Q.pjSiU_YYQsPm6AGkGpt1XA8gaBPPJXIPxvkYx90YTEA | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.qbB5vLawBVlPC4dUJ5Ly_1QcB1nJFQ1Tzw.XlNv5AYotwO48ecUTzh6xt1svuN-C4xHQl5eZsKNqvw | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.0EW0bLawfKyC2_6hmBf3CpnMfqwExXSmAg.bdQXPOIF7G8meWWxRRq9a84Yy3_D7ruXfGoTkF7s3e0</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_3.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10685,7 +10534,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Республика Карелия, Кондопога, Пролетарская ул., 22</t>
+          <t>Республика Башкортостан, Дюртюли, ул. Чеверева, 8</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -10693,10 +10542,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="P21" t="n">
+        <v>450</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -10730,7 +10577,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10738,15 +10585,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
+      <c r="AB21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>230</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -10760,34 +10603,24 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2026-08-06T09:06:32+03:00</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-27T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1299044918</t>
+          <t>3494661466</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>8166906259</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -10797,17 +10630,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Пиловочник сосна с делянки(документы фгис лк)</t>
+          <t>Пиловочник от заготовителя(помощь с учётом леса)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Пиловочник сосна с делянки, диаметр от 20 до 32, длина 6 метров. Сортировка по диаметрам, вершинка отдельно.&lt;br&gt;&lt;br&gt;Тем, кто берёт такой лес, знакома проблема: купили объём, а документов на него нет, в ФГИС ЛК он не отражён. Формально этого леса не существует, хотя вот он, лежит. Мы закрываем этот вопрос: составляем договор купли-продажи, вносим сделку в систему, объём закрепляется за вашим ИНН. Потом оформляем перевозку и отчёты, чтобы всё сходилось.&lt;br&gt;&lt;br&gt;Работаем по Красноярскому краю и всей стране удалённо. Напишите, что за лес и сколько кубов, ответим по делу.</t>
+          <t>Учёт древесины и документы в ФГИС ЛК под ключ. Кругляк, пиловочник сосна и ель, баланс, дрова.&lt;br&gt;&lt;br&gt;Основной запрос: древесина заготовлена, но в системе не отражена, поэтому её нельзя ни продать, ни вывезти. Ставим объём на учёт и дальше ведём документооборот.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка объёма древесины на баланс&lt;br&gt;- ЭСД и QR код на каждую отгрузку лесовозом&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт по местам складирования (МСД)&lt;br&gt;- сопровождение отгрузок на постоянной основе&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и данные сторон. Остальное на нашей стороне.&lt;br&gt;&lt;br&gt;Рутинный ЭСД занимает около 15 минут. Постановка на учёт зависит от ситуации, срок скажу честно до начала.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и Приуралью, берём и разовые задачи, и постоянное ведение по объёмам с лесосеки.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, отвечу быстро.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.r5aR0bawA3-nZoFyw-PV27xxAX8heAt1Jw._Wi2X0YGSZMAYinvu77aVyS4KASBrCD4wyLBIQcpbkY | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.DIdNmrawoG57LSJjWaIZz2A6om79M6hk-w.s4-8hCVN9jYjmpgOrzt1r1xYVM2uoD8NNv4WDNdh0xw | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.w7rxd7awb1PHwO1e-wiw9NzXbVNB3mdZRw.vWJ-WOl4NEe1mTHJtZ1GEpmG3QaRGqBV0c-Tn5PM-E8</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_3.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10822,7 +10655,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Красноярский край, Енисейск, ул. Ленина, 44</t>
+          <t>Республика Башкортостан, Мелеуз, ул. Ленина, 137</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10830,10 +10663,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>3800</t>
-        </is>
+      <c r="P22" t="n">
+        <v>500</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -10875,15 +10706,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
+      <c r="AB22" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>230</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -10897,29 +10724,24 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2026-08-08T05:04:57+03:00</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-27T19:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>2026-07-29T19:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6839713385</t>
+          <t>2394430844</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>8167153384</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -10929,17 +10751,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Доска обрезная сосна (QR код на перевозку)</t>
+          <t>Лес есть документов нет(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Купили или напилили доску, машина загружена, а на перевозку древесины нужен электронный документ. Без него рейс могут остановить на первом же посту.&lt;br&gt;&lt;br&gt;Оформляем ЭСД и QR код через государственную систему ФГИС ЛК. От вас: порода, объём в кубах, госномер машины и маршрут. От нас: готовый QR водителю на телефон, обычно в течение пятнадцати минут.&lt;br&gt;&lt;br&gt;Работаем с любым грузом: доска обрезная, брус, кругляк, дрова. Канск, Красноярский край и любой другой регион, всё удалённо.&lt;br&gt;&lt;br&gt;Позвоните или напишите перед рейсом, оформим без задержек.</t>
+          <t>Электронные сопроводительные документы и QR коды на вывоз леса через ФГИС ЛК. Кругляк, пиловочник, лесоматериалы круглые.&lt;br&gt;&lt;br&gt;Без ЭСД перевозка древесины запрещена, на постах смотрят QR код. Оформляем документ на каждый рейс, чтобы машина шла легально.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины&lt;br&gt;- QR код водителю на телефон&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные лесовозной машины, породу, кубатуру и маршрут. Оформляем и отдаём готовый документ.&lt;br&gt;&lt;br&gt;Обычно 15 минут после получения данных.&lt;br&gt;&lt;br&gt;Свой кабинет ФГИС ЛК, электронная подпись и декларация не нужны, работаем со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Алтайскому краю и Сибири. Сосновый и еловый пиловочник, баланс, дрова, древесина оптом, разница во времени не мешает.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.T4V23raw42xAaWFhZIsTylt-4WzGd-tmwA.naTaOrISfdpzrCyOVYgxhlU8ReRoOCYcp2g7jZTz2mw | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.WgdRALaw9u5nt3TjaT1OT3yg9O7hqf7k5w.6IjqZCf13Ub7dT-UtiujNhIsHyIvKvDbcUHCmtxKMxg | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.4EMiLLawTKoUm86nbjOVDQ-MTqqShUSglA.EGzp9y4Qzcxyafcc5AhBL8A_wWbVV5Gw3QXbZZNsA9g</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_3.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10954,7 +10776,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Красноярский край, Канск, Московская ул., 18</t>
+          <t>Алтайский край, Заринск, ул. Строителей, 21</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10962,10 +10784,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
+      <c r="P23" t="n">
+        <v>400</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -11007,15 +10827,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB23" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>230</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -11029,34 +10845,24 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2026-08-05T14:06:49+03:00</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-28T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4007897456</t>
+          <t>3236944872</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>8167622333</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -11066,17 +10872,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Пиловочник сосна кругляк(документация на лес)</t>
+          <t>Сосна есть учёта нет(помощь с учётом леса)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Пиловочник сосна, кругляк ровный, 6 метров, диаметр от 20 до 28. Лес алтайский, смолистый.&lt;br&gt;&lt;br&gt;О документации, потому что она тут главная. Любая древесина должна числиться в ФГИС ЛК, иначе для государства её нет, и любая проверка превращается в проблему. Оформляем лес официально: договор, постановка объёма на учёт, закрепление за вашей компанией. Дополнительно ведём сделки, отгрузки и отчёты, если нужно постоянное сопровождение.&lt;br&gt;&lt;br&gt;Расскажите свою ситуацию по телефону или в сообщениях, разберём и скажем, как поставить ваш объём на учёт без лишних движений.</t>
+          <t>Постановка древесины на учёт и ведение документов в ФГИС ЛК. Работаем с кругляком, пиловочником, балансом и дровами.&lt;br&gt;&lt;br&gt;Если объём не отражён в системе, лес формально не существует: ни продать, ни вывезти его нельзя. Приводим учёт в порядок и дальше сопровождаем отгрузки.&lt;br&gt;&lt;br&gt;Что входит:&lt;br&gt;- постановка объёма древесины на баланс&lt;br&gt;- электронный сопроводительный документ на каждый рейс&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования&lt;br&gt;&lt;br&gt;От вас порода, кубатура в кубометрах, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Сроки честные: ЭСД около 15 минут, работа с учётом дольше, называю срок до начала.&lt;br&gt;&lt;br&gt;Заводить кабинет и электронную подпись не потребуется.&lt;br&gt;&lt;br&gt;Работаем по Алтайскому краю и всей Сибири. Хвойный пиловочник, лес с делянки, любые объёмы под продажу и отгрузку.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок работы.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.hXJDYbawKZt11quWRXugPW7BK5vzyCGR9Q.GPobLevXk2PF6rn_ci2rei3l_80S3UgQ5cGhJ2IfsCc | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.Iihd1bawjsFrYgzMFbF-Z3B1jMHtfIbL6w.XJzriKkD7B8hQBdrUJshWFvZmeLvkXRfkV-CAPwwByI | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.KRyp6rawhfWfXQf494ZRUYRKh_UZQ43_Hw.JiRl5oQr_NWhByTtUYMWCmqjZTDQrzWlNaFLmvyCDpA</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_3.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11091,7 +10897,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Алтайский край, Рубцовск, пр-т Ленина, 40</t>
+          <t>Алтайский край, Бийск, ул. Советская, 205</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -11099,10 +10905,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
+      <c r="P24" t="n">
+        <v>600</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -11144,15 +10948,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB24" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>230</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -11166,29 +10966,24 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>2026-08-09T12:35:41+03:00</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-28T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>2026-07-30T11:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7747398644</t>
+          <t>2312387978</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>8167232117</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -11198,17 +10993,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Пиломатериал сосна (документы на древесину)</t>
+          <t>Кругляк есть документов нет(документы фгис лк)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Напилили доску или брус, покупатель готов брать, а древесина по документам нигде не числится. Сделка встаёт, потому что без учёта в системе лес не продать и не увезти.&lt;br&gt;&lt;br&gt;Ставим объёмы на баланс официально, через договор. После оформления древесина видна в вашем кабинете, дальше спокойно делаются и продажа, и перевозка с QR кодом.&lt;br&gt;&lt;br&gt;Работаем с пиломатериалом, кругляком и дровами, породы любые. Барнаул, Алтайский край и другие регионы, всё удалённо, документы отдаём на руки.&lt;br&gt;&lt;br&gt;Напишите сколько кубов и что за материал, подскажем первый шаг и срок.</t>
+          <t>Документы на древесину в ФГИС ЛК для лесозаготовителей, продавцов и покупателей леса.&lt;br&gt;&lt;br&gt;Оформляем:&lt;br&gt;- электронный сопроводительный документ на транспортировку кругляка&lt;br&gt;- QR код на рейс&lt;br&gt;- постановку объёма на учёт, если древесина не отражена в системе&lt;br&gt;- лесную декларацию и декларацию о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Вы даёте породу, кубатуру, маршрут и данные сторон. Мы оформляем в системе и передаём готовые документы.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут. Задачи по учёту и декларации занимают дольше, срок озвучиваю заранее.&lt;br&gt;&lt;br&gt;Личный кабинет, электронная подпись и своя декларация не нужны.&lt;br&gt;&lt;br&gt;Работаем по Пермскому краю и Приуралью. Пиловочник сосна и ель, балансовая древесина, дрова, отгрузка лесовозом, разовые рейсы и постоянное сопровождение.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу быстро.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.g0xi7LawL6VUW62oaM73Ak9MLaXSRSev1A.5GDX7MxGI7NNz-rUIL41SCxn-rLlK6i-pi01hWUYYn4 | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.hnmIAbawKpC-tqidiB_1N6WhKJA4qCKaPg.yB0yOlMZ2pL8owZGAnqGNdGC4XhXW3Z1szElUnAB9SM | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.aE9GbLawxKZw20arGjURAmvMxqb2xcys8A.Fh2qeK_jCtuamMKg5_zf3p3wuHODTMmGvyDbynaXpmw</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_3.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -11223,7 +11018,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Алтайский край, Барнаул, ул. Попова, 55</t>
+          <t>Пермский край, Чусовой, ул. Ленина, 32</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -11231,10 +11026,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
+      <c r="P25" t="n">
+        <v>450</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -11276,15 +11069,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
+      <c r="AB25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>230</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -11298,34 +11087,24 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>2026-08-06T12:05:58+03:00</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-28T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>2026-07-30T15:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5953556065</t>
+          <t>9553367742</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>8134916629</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -11335,17 +11114,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Пиловочник ель сосна(эсд и QR код фгис)</t>
+          <t>Пиловочник есть учёта нет(помощь с учётом леса)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Оформляем перевозочные документы на лес для заготовителей и водителей.&lt;br&gt;&lt;br&gt;Как это выглядит по шагам:&lt;br&gt;1. Вы присылаете данные: порода, объём, номер машины, откуда и куда рейс.&lt;br&gt;2. Мы вносим всё в систему ФГИС ЛК и формируем электронный сопроводительный документ.&lt;br&gt;3. Водителю уходит QR код, который он показывает при проверке на посту.&lt;br&gt;&lt;br&gt;Работаем официально, каждый документ реально числится в системе, любая проверка это подтверждает. Порода и объём любые: сосна, ель, лиственница, берёза, кругляк, пиловочник, дрова.&lt;br&gt;&lt;br&gt;Пишите, ответим быстро и возьмём рейс в работу.</t>
+          <t>Учёт древесины в ФГИС ЛК и сопровождение отгрузок. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Древесина без учёта в системе не продаётся и не перевозится. Ставим объём на баланс, оформляем документы и дальше ведём отгрузки, чтобы каждый рейс был закрыт.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- постановка объёма древесины на учёт&lt;br&gt;- ЭСД и QR код на транспортировку&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования&lt;br&gt;- постоянное ведение документооборота&lt;br&gt;&lt;br&gt;Нужны порода, кубатура, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Рутинный ЭСД около 15 минут, постановка на учёт дольше, срок называю сразу.&lt;br&gt;&lt;br&gt;Кабинет в системе и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Работаем по Удмуртии и Поволжью. Хвойный кругляк, лесоматериалы, продажа и покупка древесины, от одной машины до постоянного потока.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, скажу срок.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.8OQFC7awXA0zvN4AaVzirCirXg21olQHsw.s1dHKZ5xRK6_nBw6r9iJWP0hayhHfaZMYATdUa_myZM | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.uXTtW7awFZ3b7JeQk0nhO8D7F51d8h2XWw.V4u6_es2DGDvywvxy14vERfmJQtT-py_Hn_seEi6AWo | http://avito.ru/autoload/1/items-to-feed/images?imageSlug=/image/1/1.0E9SLLawfKZkm_6rfjOrAn-MfqbihXSs5A.dkNrPRJA4Vfjh7cfrFC0Lq7D38umYIlK-cMhm57oL70</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_3.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -11360,7 +11139,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Ямало-Ненецкий автономный округ, Ноябрьск, ул. Ленина, 22</t>
+          <t>Удмуртская Республика, Глазов, ул. Кирова, 49</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -11368,10 +11147,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
+      <c r="P26" t="n">
+        <v>550</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -11405,7 +11182,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11413,15 +11190,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="AB26" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>230</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -11435,24 +11208,19 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>2026-08-01T14:05:54+03:00</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>не опт</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Активно</t>
+          <t>2026-08-29T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>2026-07-31T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7689904523</t>
+          <t>2285712624</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11467,17 +11235,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Лес с делянки пиловочник(QR код на вывоз)</t>
+          <t>Лес заготовлен бумаг нет(документы фгис лк)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Краснодар и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Оформление документов на заготовленную древесину в ФГИС ЛК. Кругляк, пиловочник, балансовая древесина.&lt;br&gt;&lt;br&gt;Частая ситуация: лес заготовлен и лежит на делянке, а по документам в системе не проведён. Разбираем и приводим в порядок.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- электронный сопроводительный документ на вывоз&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- лесная декларация, декларация о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования&lt;br&gt;&lt;br&gt;От вас порода, кубатура и данные перевозки.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут после получения данных. Работа с учётом и декларацией занимает дольше, срок скажу до начала.&lt;br&gt;&lt;br&gt;Своя декларация и кабинет в системе не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Удмуртии и соседним регионам. Сосна, ель, лиственные, любые сортименты под продажу и отгрузку лесовозом.&lt;br&gt;&lt;br&gt;Напишите кубатуру, отвечу быстро.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/01/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/01/01_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/01/01_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_3.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -11492,7 +11260,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Краснодарский край, Краснодар</t>
+          <t>Удмуртская Республика, Можга, ул. Наговицына, 60</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -11501,7 +11269,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -11543,15 +11311,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB27" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>230</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -11565,19 +11329,19 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>2026-08-14T18:13:40+03:00</t>
+          <t>2026-08-29T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2026-07-15T20:13:40+03:00</t>
+          <t>2026-07-31T11:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8383903623</t>
+          <t>5905323698</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11592,17 +11356,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Лес есть документов нет(кругляк ФГИС ЛК)</t>
+          <t>Сосна с делянки бумаг нет(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Тула и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>QR коды и электронные сопроводительные документы на древесину. Кругляк, пиловочник сосна и ель, баланс.&lt;br&gt;&lt;br&gt;На постах проверяют QR код ЭСД, без него вывоз леса запрещён. Оформляем документ на каждую лесовозную машину через ФГИС ЛК.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины&lt;br&gt;- QR код водителю в электронном виде&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные машины, отправителя и получателя, породу и кубатуру. Оформление на нас.&lt;br&gt;&lt;br&gt;Обычно 15 минут с момента получения данных.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и Сибири. Лес с делянки и со склада, древесина оптом, часовой пояс не помеха.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/02/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/02/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/02/02_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_3.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -11617,7 +11381,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Тульская область, Тула</t>
+          <t>Кемеровская область, Таштагол, ул. Ленина, 60</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -11626,7 +11390,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -11668,15 +11432,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB28" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>230</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -11690,19 +11450,19 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>2026-08-15T04:00:00+03:00</t>
+          <t>2026-08-29T15:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2026-07-16T06:00:00+03:00</t>
+          <t>2026-07-31T15:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8998350344</t>
+          <t>8540422936</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11717,17 +11477,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Лес хвоя от заготовителя(QR код на лес)</t>
+          <t>Лес есть учёта нет(помощь с учётом леса)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Москва и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Постановка древесины на учёт и документы в ФГИС ЛК. Кругляк, пиловочник, лесоматериалы круглые, дрова.&lt;br&gt;&lt;br&gt;Пока объём не стоит на балансе в системе, лес нельзя ни продать, ни вывезти. Ставим на учёт и дальше ведём документы на отгрузки.&lt;br&gt;&lt;br&gt;Что входит:&lt;br&gt;- постановка объёма древесины на учёт и баланс&lt;br&gt;- ЭСД и QR код на каждый рейс&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и реквизиты.&lt;br&gt;&lt;br&gt;ЭСД около 15 минут, работа с учётом занимает дольше, срок озвучиваю честно.&lt;br&gt;&lt;br&gt;Свой кабинет и электронная подпись не требуются.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и всей Сибири. Хвойный пиловочник, баланс, продажа древесины с лесосеки, разовые и постоянные отгрузки.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу что дальше.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/03/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/03/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/03/03_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_3.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -11742,7 +11502,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Москва, Москва</t>
+          <t>Кемеровская область, Мыски, ул. Советская, 43</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -11751,7 +11511,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -11793,15 +11553,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB29" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>230</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -11815,19 +11571,19 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>2026-08-15T05:30:00+03:00</t>
+          <t>2026-08-29T19:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2026-07-16T07:30:00+03:00</t>
+          <t>2026-07-31T19:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4426873387</t>
+          <t>8088623974</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11842,17 +11598,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Кругляк сосна с делянки(документы ФГИС)</t>
+          <t>Кругляк заготовлен бумаг нет(документы фгис лк)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Санкт-Петербург и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Документы в ФГИС ЛК на заготовленную древесину. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Оформляем:&lt;br&gt;- постановку объёма на учёт&lt;br&gt;- электронный сопроводительный документ на транспортировку&lt;br&gt;- QR код на рейс&lt;br&gt;- лесную декларацию и декларацию о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования&lt;br&gt;&lt;br&gt;Как работаем. От вас порода, кубатура, маршрут и данные сторон. Оформление в системе полностью на нашей стороне, документы приходят готовыми.&lt;br&gt;&lt;br&gt;Срок по ЭСД обычно 15 минут. Постановка на учёт и декларация занимают дольше, называю срок заранее.&lt;br&gt;&lt;br&gt;Заводить кабинет и электронную подпись не нужно.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и соседним регионам. Сосновый и еловый кругляк, лесоматериалы, отгрузка лесовозом, любые объёмы.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу быстро.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/04/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/04/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/04/04_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_3.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -11867,7 +11623,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Санкт-Петербург, Санкт-Петербург</t>
+          <t>Кемеровская область, Юрга, ул. Машиностроителей, 39</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -11876,7 +11632,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -11918,15 +11674,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB30" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>230</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -11940,19 +11692,19 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>2026-08-15T07:00:00+03:00</t>
+          <t>2026-08-30T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-07-16T09:00:00+03:00</t>
+          <t>2026-08-01T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5316950583</t>
+          <t>2671009093</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11967,17 +11719,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Пиловочник ель(ЭСД и QR на перевозку)</t>
+          <t>Лес с делянки бумаг нет(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Екатеринбург и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Электронные сопроводительные документы и QR коды на вывоз древесины. Кругляк, пиловочник, баланс.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена, на постах проверяют QR код из ФГИС ЛК. Оформление у нас поставлено на поток.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- документ на каждый рейс при регулярных перевозках&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- отчёт 1-ИЛ, декларация о сделке&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные лесовозной машины, отправителя, получателя и кубатуру, дальше QR код у водителя на экране.&lt;br&gt;&lt;br&gt;Обычно 15 минут.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронная подпись не нужны.&lt;br&gt;&lt;br&gt;Работаем по Красноярскому краю и всей Сибири. Хвойный кругляк с делянки, лиственные породы, древесина оптом, часовой пояс не проблема.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/05/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/05/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/05/05_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_3.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -11992,7 +11744,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Свердловская область, Екатеринбург</t>
+          <t>Красноярский край, Богучаны, ул. Ленина, 27</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -12001,7 +11753,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -12043,15 +11795,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB31" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>230</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -12065,19 +11813,19 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>2026-08-15T08:30:00+03:00</t>
+          <t>2026-08-30T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-07-16T10:30:00+03:00</t>
+          <t>2026-08-01T11:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4184632336</t>
+          <t>6664478711</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -12092,17 +11840,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Продам лес кругляк(расхождения ФГИС ЛК)</t>
+          <t>Ель есть документов нет(помощь с учётом леса)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Новосибирск и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Учёт древесины и оформление документов в ФГИС ЛК. Кругляк, пиловочник ель и сосна, баланс, дрова.&lt;br&gt;&lt;br&gt;Древесина должна стоять на учёте, иначе её не продать и не вывезти. Ставим объём на баланс, оформляем сопроводительные документы, ведём отчётность.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка объёма древесины на учёт&lt;br&gt;- ЭСД и QR код на транспортировку&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт в местах складирования&lt;br&gt;- сопровождение постоянных отгрузок&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Рутинный ЭСД около 15 минут, задачи по учёту дольше, срок называю до начала работы.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Лесоматериалы круглые, продажа и покупка леса, отгрузка лесовозными машинами.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, отвечу быстро.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/06/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/06/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/06/06_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_3.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -12117,7 +11865,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Новосибирская область, Новосибирск</t>
+          <t>Челябинская область, Сатка, ул. Солнечная, 12</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -12126,7 +11874,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -12160,7 +11908,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -12168,15 +11916,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB32" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>230</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -12190,19 +11934,19 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>2026-08-15T10:00:00+03:00</t>
+          <t>2026-08-30T15:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2026-07-16T12:00:00+03:00</t>
+          <t>2026-08-01T15:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4497916722</t>
+          <t>2657040747</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -12217,17 +11961,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Лес кругляк берёза(документы на лес)</t>
+          <t>Сосна заготовлена бумаг нет(документы фгис лк)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Казань и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Оформление документов на древесину в ФГИС ЛК для заготовителей, продавцов и перевозчиков. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;В работе:&lt;br&gt;- электронный сопроводительный документ на транспортировку древесины&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- лесная декларация, декларация о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования древесины (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Вы присылаете породу, кубатуру, маршрут и данные сторон. Мы оформляем в системе и передаём готовый пакет.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут после получения данных. Учёт и декларация занимают дольше, срок озвучиваю заранее.&lt;br&gt;&lt;br&gt;Свой кабинет, электронная подпись и декларация вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Сосновый пиловочник, лес с делянки, древесина оптом, разовые задачи и постоянное ведение.&lt;br&gt;&lt;br&gt;Напишите кубатуру, скажу срок и порядок.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/07/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/07/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/07/07_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_3.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -12242,7 +11986,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Республика Татарстан, Казань</t>
+          <t>Челябинская область, Катав-Ивановск, ул. Ленина, 19</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -12251,7 +11995,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -12293,15 +12037,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB33" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>230</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -12315,19 +12055,19 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>2026-08-15T11:30:00+03:00</t>
+          <t>2026-08-30T19:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2026-07-16T13:30:00+03:00</t>
+          <t>2026-08-01T19:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1060900463</t>
+          <t>8424443532</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -12342,17 +12082,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Лес с делянки хвоя(QR код на вывозку)</t>
+          <t>Лес заготовлен документов нет(помощь с учётом)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Нижний Новгород и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Учёт древесины и оформление документов в ФГИС ЛК. Кругляк, пиловочник сосна и ель, балансовая древесина, дрова.&lt;br&gt;&lt;br&gt;Ситуация, с которой чаще всего приходят: лес заготовлен и лежит, покупатель есть, а в системе объём не проведён. Пока древесина не на учёте, продать и вывезти её нельзя.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка заготовленного объёма на учёт и баланс&lt;br&gt;- электронный сопроводительный документ (ЭСД) на транспортировку&lt;br&gt;- QR код водителю для проверки на посту&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;Порядок. От вас порода, кубатура в кубометрах, маршрут и реквизиты сторон. Оформление в системе полностью на нашей стороне.&lt;br&gt;&lt;br&gt;Рутинный ЭСД занимает около 15 минут после получения данных. Постановка объёма на учёт дольше, срок называю честно до начала работы.&lt;br&gt;&lt;br&gt;Свой личный кабинет, электронная подпись и лесная декларация вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Хвойный кругляк с делянки и со склада, лесоматериалы круглые, древесина оптом, отгрузка лесовозными машинами.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок и срок.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/08/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/08/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/08/08_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_3.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -12367,7 +12107,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Нижегородская область, Нижний Новгород</t>
+          <t>Республика Башкортостан, Ишимбай, ул. Советская, 15</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -12376,7 +12116,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -12418,15 +12158,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB34" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>230</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -12440,19 +12176,19 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>2026-08-15T13:00:00+03:00</t>
+          <t>2026-08-26T14:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2026-07-16T15:00:00+03:00</t>
+          <t>2026-07-28T14:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4896104218</t>
+          <t>2960453369</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -12467,17 +12203,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Кругляк сосна свежий спил(ЭСД на рейс)</t>
+          <t>Сосна есть документов нет(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Самара и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>QR коды и электронные сопроводительные документы на вывоз древесины через ФГИС ЛК. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена. На посту проверяют QR код, в нём данные рейса, объёма и сторон сделки. Оформляем документ на каждую лесовозную машину.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- документ на каждый рейс при постоянных перевозках&lt;br&gt;- постановка объёма древесины на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок работы. Присылаете данные машины, отправителя и получателя, породу и кубатуру. Дальше оформление на нас, QR код приходит водителю на телефон.&lt;br&gt;&lt;br&gt;Обычно занимает 15 минут с момента получения данных.&lt;br&gt;&lt;br&gt;Личный кабинет ФГИС ЛК, электронная подпись и собственная декларация не потребуются, работаем со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Пермскому краю и Приуралью. Сосновый и еловый пиловочник, лес с делянки, лесоматериалы круглые, продажа и покупка древесины, любые объёмы.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/09/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/09/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/09/09_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_3.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -12492,7 +12228,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Самарская область, Самара</t>
+          <t>Пермский край, Кунгур, ул. Ленина, 40</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -12501,7 +12237,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -12543,15 +12279,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB35" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>230</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -12565,19 +12297,19 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>2026-08-16T04:00:00+03:00</t>
+          <t>2026-08-26T17:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2026-07-17T06:00:00+03:00</t>
+          <t>2026-07-28T17:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6407106167</t>
+          <t>1936930142</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -12592,17 +12324,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Лес есть учёта нет(кругляк ФГИС ЛК)</t>
+          <t>Ель кругляк с делянки(помощь с учётом)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Ростов-на-Дону и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Лес есть, а с документами в ФГИС ЛК вечно возня. Возьмём её на себя. Поставим ваш объём на баланс, оформим ЭСД и QR код на каждую машину, дальше просто ведём учёт, чтобы вы про это не думали.&lt;br&gt;&lt;br&gt;Лес еловый, кругляк с делянки, 6 метров, диаметр от 20 см. Есть и другие сортименты.&lt;br&gt;&lt;br&gt;От вас только данные по объёму и рейсу. Свой кабинет в системе, декларацию и электронную подпись заводить не нужно, всё оформляем мы.&lt;br&gt;&lt;br&gt;Я по Башкортостану и соседним регионам. Напишите, что у вас по лесу, подскажу порядок и сроки.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/10/10_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/10/10_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/10/10_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_03.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -12617,7 +12349,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Ростовская область, Ростов-на-Дону</t>
+          <t>Республика Башкортостан, Белорецк, ул. Ленина, 15</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -12625,8 +12357,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P36" t="n">
-        <v>300</v>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -12660,7 +12394,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -12668,15 +12402,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB36" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>230</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -12690,19 +12420,19 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>2026-08-16T05:30:00+03:00</t>
+          <t>2026-09-06T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2026-07-17T07:30:00+03:00</t>
+          <t>2026-08-07T14:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5211829099</t>
+          <t>7029554179</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12717,17 +12447,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Пиловочник лиственница(QR код и ЭСД)</t>
+          <t>Сосна кругляк с делянки(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Воронеж и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Делаем QR код на вывоз леса и ЭСД через ФГИС ЛК. Машина уже под погрузкой, а документа на рейс нет - обычно решаем в тот же день.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, есть и другой хвойный сортимент.&lt;br&gt;&lt;br&gt;QR код и ЭСД приходят водителю на телефон. Перед этим сверяем объём и породу, чтобы на посту не развернули. Свой кабинет и подпись вам не нужны.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири, разница по времени не мешает. Напишите, что по рейсу, отвечу сразу.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/11/11_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/11/11_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/11/11_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_03.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -12742,7 +12472,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Воронежская область, Воронеж</t>
+          <t>Алтайский край, Бийск, ул. Советская, 8</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -12750,8 +12480,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P37" t="n">
-        <v>400</v>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -12793,15 +12525,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB37" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>230</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -12815,19 +12543,19 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>2026-08-16T07:00:00+03:00</t>
+          <t>2026-09-06T13:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2026-07-17T09:00:00+03:00</t>
+          <t>2026-08-10T06:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5538956737</t>
+          <t>2323865424</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12842,17 +12570,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Лес от заготовителя(документы ФГИС ЛК)</t>
+          <t>Сосна кругляк под погрузку(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Челябинск и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Лес есть, а документов нет - обычная история. Оформим QR код на вывоз и ЭСД через ФГИС ЛК, документ придёт водителю на экран перед выездом.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Объём и породу проверяем заранее, чтобы потом не переделывать. Всё оформление на нас, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Кемеровской области и Сибири, часовой пояс не помеха. Напишите объём и куда везёте, отвечу сразу.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/12/12_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/12/12_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/12/12_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_03.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -12867,7 +12595,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Челябинская область, Челябинск</t>
+          <t>Кемеровская область, Таштагол, ул. Ленина, 22</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -12875,8 +12603,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P38" t="n">
-        <v>350</v>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -12918,15 +12648,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB38" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>230</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -12940,19 +12666,19 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>2026-08-16T08:30:00+03:00</t>
+          <t>2026-09-06T15:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>2026-07-17T10:30:00+03:00</t>
+          <t>2026-08-10T08:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9583135422</t>
+          <t>8579049856</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12967,17 +12693,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Кругляк ель сосна(закрываем расхождения)</t>
+          <t>Лиственница кругляк(ЭСД на перевозку)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Пермь и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Делаем ЭСД на перевозку леса через ФГИС ЛК. Если возите объёмами, на каждый рейс нужен свой документ - держим это на потоке, чтобы машины не стояли.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см. Есть сосна и ель.&lt;br&gt;&lt;br&gt;Данные проверяем до выпуска, чтобы не было отказа. Оформляем, даже если своей декларации у вас пока нет.&lt;br&gt;&lt;br&gt;Я по Красноярскому краю и Сибири. Напишите объём и маршрут, скажу срок сегодня.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/13/13_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/13/13_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/13/13_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_03.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -12992,7 +12718,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Пермский край, Пермь</t>
+          <t>Красноярский край, Богучаны, ул. Октябрьская, 5</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -13000,8 +12726,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P39" t="n">
-        <v>300</v>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -13035,7 +12763,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Лиственница</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -13043,15 +12771,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB39" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>230</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -13065,19 +12789,19 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>2026-08-16T10:00:00+03:00</t>
+          <t>2026-09-07T04:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>2026-07-17T12:00:00+03:00</t>
+          <t>2026-08-08T06:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8588178728</t>
+          <t>4561483668</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -13092,17 +12816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Лес зимней заготовки(QR код на перевозку)</t>
+          <t>Ель кругляк с делянки(помощь с учётом)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Уфа и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Кто возит лес, тот знает: без учёта в ФГИС ЛК никуда. Поможем с учётом - поставим объём на баланс, оформим ЭСД и QR на рейсы, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, кругляк с делянки, 6 метров, диаметр от 20 см. Любой объём.&lt;br&gt;&lt;br&gt;От вас только данные, остальное на нас. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Челябинской области и Уралу. Напишите породу и кубатуру, подскажу сроки.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/14/14_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/14/14_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/14/14_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_03.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -13117,7 +12841,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Уфа</t>
+          <t>Челябинская область, Сатка, ул. Пролетарская, 12</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -13125,8 +12849,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P40" t="n">
-        <v>350</v>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -13160,7 +12886,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -13168,15 +12894,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB40" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>230</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -13190,19 +12912,19 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>2026-08-16T11:30:00+03:00</t>
+          <t>2026-09-07T05:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2026-07-17T13:30:00+03:00</t>
+          <t>2026-08-08T07:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5855204542</t>
+          <t>2738165608</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -13217,17 +12939,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Продам лес кругляк(помощь с учётом ФГИС)</t>
+          <t>Сосна от заготовителя(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет? Или не сходятся объёмы в ФГИС ЛК? Помогу закрыть вопрос по бумагам под ключ, быстро и без нервов.&lt;br&gt;&lt;br&gt;Делаю куар код на перевозку, электронную накладную ЭСД, лесную декларацию, отчёт использования лесов, закрываю расхождения по объёмам и подбираю коды ОКПД2. Система государственная, документ в ней есть, поэтому на посту и при проверке вопросов не возникает.&lt;br&gt;&lt;br&gt;Работаю с Волгоград и всей Россией удалённо, с ИП и ООО. Оформляю за пятнадцать минут, нужны только данные машины, водителя, порода, кубатура и маршрут рейса.&lt;br&gt;&lt;br&gt;Напишите прямо сейчас в сообщения, отвечу за пару минут, посмотрю вашу ситуацию и скажу, какие документы нужны и в какой срок. Помогу даже в запутанном случае.</t>
+          <t>Машина готова, лес на месте, а QR кода на вывоз нет. Сделаем QR и ЭСД через ФГИС ЛК на каждую машину, придёт водителю на телефон.&lt;br&gt;&lt;br&gt;Сосновый кругляк напрямую от заготовителя, 6 метров, диаметр от 20 см.&lt;br&gt;&lt;br&gt;Перед отгрузкой сверяем объём и породу. Оформление целиком с нашей стороны, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Башкортостану и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/15/15_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/15/15_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/15/15_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_03.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -13242,7 +12964,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Волгоградская область, Волгоград</t>
+          <t>Республика Башкортостан, Сибай, ул. Заводская, 3</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -13250,8 +12972,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P41" t="n">
-        <v>300</v>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -13293,15 +13017,11 @@
           <t>Да</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>6100</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
+      <c r="AB41" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>230</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -13315,19 +13035,19 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>2026-08-16T13:00:00+03:00</t>
+          <t>2026-09-07T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>2026-07-17T15:00:00+03:00</t>
+          <t>2026-08-08T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5937878704</t>
+          <t>7680837833</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -13342,17 +13062,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (QR код и ЭСД на перевозку)</t>
+          <t>Сосна пиловочник с делянки(документы фгис лк)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Раньше система звалась ЛесЕГАИС, суть та же. Если у вас есть сосна, кругляк, пиловочник или балансы с деляны, а бумаг на них нет, всё сделаю по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код и ЭСД на перевозку, чтобы лесовоз прошёл лесной контроль без штрафов. Считаю по фото ваших замеров удалённо, вам никуда ехать не надо.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по кубам, ставлю лес на баланс, готовлю декларации и отчёты. Беломорск и район, объёмы любые.&lt;br&gt;&lt;br&gt;Пришлите замеры с делянки, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>Кто работает с лесом, тому нужны документы в ФГИС ЛК, а времени на систему нет. Оформим за вас - ЭСД и QR на перевозку, поставим объём на учёт, проведём сделку.&lt;br&gt;&lt;br&gt;Сосновый пиловочник с делянки, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Кабинет и подпись заводить не надо, ведём всё сами.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири. Напишите кубатуру и маршрут, отвечу быстро.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_03.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -13367,7 +13087,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Республика Карелия, Беломорск, ул. Лесная, 12</t>
+          <t>Алтайский край, Заринск, ул. Металлургов, 9</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -13375,8 +13095,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P42" t="n">
-        <v>250</v>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -13422,7 +13144,7 @@
         <v>6000</v>
       </c>
       <c r="AC42" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -13436,19 +13158,19 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>2026-08-20T18:00:00+03:00</t>
+          <t>2026-09-07T08:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00+03:00</t>
+          <t>2026-08-08T10:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6036836126</t>
+          <t>1951202398</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -13463,17 +13185,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Лиственница пиловочник (QR код на вывоз леса)</t>
+          <t>Лиственница кругляк с делянки(ЭСД на вывоз)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас есть лиственница, кругляк, пиловочник или балансы с деляны, а бумаг на вывозку нет, приведу всё в порядок по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код на вывоз леса, чтобы лесовоз прошёл лесной контроль без штрафов. Считаю по фото ваших замеров удалённо и быстро, вам никуда ехать не надо.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по объёмам, ставлю лес на баланс, готовлю декларации и отчёты. Нижнеудинск и район, объёмы любые.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня. Отвечаю за пару минут.&lt;/p&gt;</t>
+          <t>Оформляем ЭСД на вывоз леса через ФГИС ЛК. Лес готов, машина под погрузкой, а документа на рейс нет - выпустим, и водитель едет.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см, плотная древесина.&lt;br&gt;&lt;br&gt;Данные проверяем заранее. Если что-то оформлено с ошибкой, аннулируем и делаем заново по правилам. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Пермскому краю и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_03.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -13488,7 +13210,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Иркутская область, Нижнеудинск, ул. Заводская, 19</t>
+          <t>Пермский край, Чусовой, ул. Ленина, 30</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -13496,8 +13218,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P43" t="n">
-        <v>200</v>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -13543,7 +13267,7 @@
         <v>6000</v>
       </c>
       <c r="AC43" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -13557,19 +13281,19 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>2026-08-20T19:30:00+03:00</t>
+          <t>2026-09-07T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2026-07-21T21:30:00+03:00</t>
+          <t>2026-08-08T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3305654333</t>
+          <t>7192983965</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -13584,17 +13308,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Берёза пиловочник (не сходятся объёмы ФГИС)</t>
+          <t>Ель пиловочник с делянки(помощь с учётом)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Это услуга по бумагам, а не торговля кругляком.&lt;br&gt;&lt;br&gt;Работаю по Мурашам и району. Если по системе один объём, а на деляне или на складе по факту другой, свожу это официально. Берёза, пиловочник, балансы, дрова, осиновый кругляк, любой сортимент. Замерили лесовоз, а цифры в ФГИС не сходятся, расхождение висит и мешает вывозке, закрою через договор купли-продажи и приведу объём в порядок.&lt;br&gt;&lt;br&gt;Делаю QR и ЭСД на перевозку, ставлю лес на баланс, готовлю декларации и отчёты. Если у вас есть лес, а документов на него нет, оформлю.&lt;br&gt;&lt;br&gt;Пришлите замеры по делянке, посчитаю сегодня и скажу, как свести объёмы. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>Лес есть, а документов нет, и учёт в ФГИС ЛК висит мёртвым грузом. Разгрузим - поставим объём на баланс, сделаем ЭСД и QR на каждый рейс, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, пиловочник с делянки, 6 метров, диаметр от 20 см. Хвоя.&lt;br&gt;&lt;br&gt;От вас данные, остальное наша забота. Свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Я по Удмуртии и Поволжью. Напишите породу и кубатуру, подскажу сроки.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_03.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -13609,7 +13333,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Кировская область, Мураши, ул. Советская, 26</t>
+          <t>Удмуртская Республика, Можга, ул. Наговицына, 7</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -13617,8 +13341,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P44" t="n">
-        <v>300</v>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -13652,7 +13378,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -13678,19 +13404,19 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>2026-08-21T04:30:00+03:00</t>
+          <t>2026-09-08T03:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>2026-07-22T06:30:00+03:00</t>
+          <t>2026-08-09T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5783794994</t>
+          <t>2634568371</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -13705,17 +13431,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (QR код на вывоз леса)</t>
+          <t>Лес кругляк ель сосна, ЭСД на отгрузку</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сразу к делу: мы не продаём лес, мы оформляем на него документы в системе ФГИС ЛК. Если у вас есть кругляк, пиловочник сосны, балансы или дрова с деляны, а бумаг на вывоз нет, мы их сделаем.&lt;br&gt;&lt;br&gt;Готовим QR-код и ЭСД (электронный сопроводительный документ) на перевозку, чтобы лесовоз прошёл лесной контроль и первый же рейс ушёл без штрафов. Работаем удалённо: пришлите фото замеров по кубам, посчитаем объём и оформим сами.&lt;br&gt;&lt;br&gt;Также закрываем расхождения объёмов, ставим лес на баланс, готовим декларации и отчёты. Город Буй, работаем со всеми регионами.&lt;br&gt;&lt;br&gt;Есть делянка, вывозка на носу, а документов нет: напишите в сообщения, отвечу за пару минут. Пришлите замеры сегодня, посчитаю сегодня.&lt;/p&gt;</t>
+          <t>Оформляем ЭСД на еловый и сосновый кругляк. Услуга по документам отгрузки.&lt;br&gt;&lt;br&gt;На каждую машину сопроводительный документ с QR кодом, водителю до выезда. Если объём не заведён в системе, сначала ставим на учёт.&lt;br&gt;&lt;br&gt;Закрываем декларацию о сделке и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -13730,7 +13456,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Костромская область, Буй, ул. Октябрьская, 47</t>
+          <t>Галич, Костромская обл., ул. Свободы, 11</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -13739,7 +13465,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -13785,7 +13511,7 @@
         <v>6000</v>
       </c>
       <c r="AC45" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -13799,19 +13525,19 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>2026-08-21T10:00:00+03:00</t>
+          <t>2026-09-12T16:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>2026-07-22T12:00:00+03:00</t>
+          <t>2026-08-13T18:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7025347023</t>
+          <t>4149246617</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -13826,17 +13552,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Хвоя пиловочник (ЭСД на перевозку)</t>
+          <t>Пиловочник сосна, полный пакет документов</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на лес в системе ФГИС ЛК. Сам лес мы не продаём и не покупаем, только делаем бумаги на него.&lt;br&gt;&lt;br&gt;Если у вас есть кругляк, пиловочник, хвоя, балансы или дрова, а машину надо отправить в рейс и провезти через лесной контроль без штрафов, мы оформим QR-код и ЭСД (электронный сопроводительный документ) на каждый лесовоз.&lt;br&gt;&lt;br&gt;Работаем удалённо по всей Воркуте и району. Считаем по фото ваших замеров с деляны: скинете кубы и породу, посчитаем объём и подготовим ЭСД, чтобы лесовоз ушёл в путь с чистыми документами.&lt;br&gt;&lt;br&gt;Также закрываем расхождения по объёмам, ставим лес на баланс, готовим декларации и отчёты.&lt;br&gt;&lt;br&gt;Напишите в сообщения, отвечу за пару минут. Пришлите замеры, посчитаю сегодня.&lt;/p&gt;</t>
+          <t>Оформляем полный пакет документов на сосновый пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;В пакет входит: постановка на учёт, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ, места складирования, коды ОКПД2.&lt;br&gt;&lt;br&gt;От вас данные, от нас готовые документы. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Омская область.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7025347023/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7025347023/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7025347023/07_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -13851,7 +13577,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Республика Коми, Воркута, пр-т Ленина, 54</t>
+          <t>Тара, Омская обл., ул. Ленина, 9</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -13860,7 +13586,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -13906,7 +13632,7 @@
         <v>6000</v>
       </c>
       <c r="AC46" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -13920,14 +13646,19 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>2026-08-16T23:59:00+03:00</t>
+          <t>2026-09-13T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>2026-08-14T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3645797250</t>
+          <t>1099424133</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -13942,17 +13673,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Сосна кругляк зимник (ЭСД и QR на вагон)</t>
+          <t>Лес кругляк ель, ЭСД и постановка на учёт</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас есть сосна, кругляк, пиловочник или балансы с деляны, а бумаг на вывозку нет, всё сделаю по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код и ЭСД на перевозку, чтобы лесовоз и вагон ушли с чистыми документами и прошли лесной контроль без штрафов. Работаю по зимнику, считаю по фото ваших замеров удалённо, под каждую машину и под отгрузку вагоном отдельный документ.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по кубам, ставлю лес на баланс, готовлю декларации и отчёты. Дивногорск и район, объёмы любые.&lt;br&gt;&lt;br&gt;Пришлите замеры с делянки, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>Оформляем ЭСД на еловый кругляк и ставим объём на учёт. Услуга по документам.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сопроводительный документ выписывать не на что. Поэтому сначала учёт, потом отгрузки.&lt;br&gt;&lt;br&gt;Дальше: ЭСД с QR на каждый рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Нижегородская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3645797250/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3645797250/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3645797250/09_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -13967,7 +13698,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Красноярский край, Дивногорск, ул. Гагарина, 68</t>
+          <t>Урень, Нижегородская обл., ул. Ленина, 47</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -13976,7 +13707,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -14010,7 +13741,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -14036,14 +13767,19 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>2026-08-16T23:59:00+03:00</t>
+          <t>2026-09-13T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>2026-08-14T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1173035880</t>
+          <t>1198010038</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -14058,17 +13794,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ель пиловочник (не сходятся объёмы ФГИС)</t>
+          <t>Пиловочник сосна, оформим ЭСД на рейс</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас есть кругляк, пиловочник, балансы или дрова, а бумаг на них нет или они не сходятся, привожу всё в порядок.&lt;br&gt;&lt;br&gt;Работаю по Никольску и району. Частый случай: по бумагам один объём, а по факту на деляне или на складе кубов другое количество. Закрываю это расхождение официально через договор купли-продажи и свожу объём, чтобы цифры бились.&lt;br&gt;&lt;br&gt;Делаю QR-код и ЭСД на вывозку, ставлю лес на баланс, готовлю декларации и отчёты. Ель, сосна, любой сортимент. Есть замеры с делянки, лесовоз готов ехать, а с системой затык, разберусь.&lt;br&gt;&lt;br&gt;Напишите в сообщения, отвечу за пару минут. Пришлите замеры, посчитаю сегодня.&lt;/p&gt;</t>
+          <t>Оформляем ЭСД на сосновый пиловочник. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждый рейс: сопроводительный документ с QR кодом, водителю до выезда. Срок 15 минут.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сначала ставим на учёт, потом отгружаете.&lt;br&gt;&lt;br&gt;Ивановская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1173035880/10_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1173035880/10_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1173035880/10_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -14083,7 +13819,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Вологодская область, Никольск, ул. Строителей, 75</t>
+          <t>Юрьевец, Ивановская обл., ул. Советская, 26</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -14092,7 +13828,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>250</v>
+        <v>1800</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -14126,7 +13862,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -14138,7 +13874,7 @@
         <v>6000</v>
       </c>
       <c r="AC48" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -14152,14 +13888,19 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>2026-08-16T23:59:00+03:00</t>
+          <t>2026-09-13T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>2026-08-14T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8614045973</t>
+          <t>3451367236</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -14174,17 +13915,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Осина пиловочник (QR код на вывоз леса)</t>
+          <t>Кругляк хвойный, поставим на учёт и вывезем</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на лес в системе ФГИС ЛК, сам лес мы не продаём. Если у вас есть кругляк, пиловочник, осина, балансы или дрова, а бумаг на них нет, поможем всё провести по системе.&lt;br&gt;&lt;br&gt;Собрался короткий рейс с дровами по Старой Руссе или рядом, а машину нечем закрыть по лесному контролю. Сделаем QR-код и ЭСД (электронный сопроводительный документ) на вывозку, чтобы лесовоз прошёл без штрафов. Считаем по фото замеров, удалённо, вам никуда ехать не нужно.&lt;br&gt;&lt;br&gt;Также ставим лес на баланс, закрываем расхождения по кубам, готовим декларации и отчёты по вашей деляне.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и скажу, что нужно для документов.&lt;/p&gt;</t>
+          <t>Ставим хвойный кругляк на учёт в ФГИС ЛК и оформляем вывоз. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Основная проблема не в лесе, а в бумагах: объём есть, в системе его нет, вывезти нельзя.&lt;br&gt;&lt;br&gt;Ставим на учёт, дальше каждый рейс уходит с ЭСД и QR, сделка закрывается декларацией, период отчётом 1-ИЛ.&lt;br&gt;&lt;br&gt;Владимирская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8614045973/12_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8614045973/12_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8614045973/12_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__3.jpg</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -14199,7 +13940,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Новгородская область, Старая Русса, ул. Заводская, 89</t>
+          <t>Вязники, Владимирская обл., ул. Ленина, 33</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -14208,7 +13949,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -14242,7 +13983,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Осина</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -14254,7 +13995,7 @@
         <v>6000</v>
       </c>
       <c r="AC49" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -14268,14 +14009,19 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>2026-08-16T23:59:00+03:00</t>
+          <t>2026-09-14T03:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>2026-08-15T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7435263739</t>
+          <t>7655959812</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -14290,17 +14036,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (ЭСД и QR на рейс)</t>
+          <t>Лес кругляк сосна, ЭСД на каждый рейс</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас есть сосна, кругляк, пиловочник или дрова с деляны, а бумаг на них нет, приведу всё в порядок по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код и ЭСД на рейс, чтобы лесовоз прошёл лесной контроль без штрафов. Считаю по фото ваших замеров удалённо, вам никуда ехать не надо, на каждую машину свой документ под вывозку.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по объёмам, ставлю лес на баланс, готовлю декларации и отчёты. Иваново и область, объёмы любые, хоть малой партией на пробу.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня. Отвечаю за пару минут.&lt;/p&gt;</t>
+          <t>Оформляем ЭСД на сосновый кругляк. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждую машину готовим сопроводительный документ с QR кодом. Водитель получает до выезда.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;Алтайский край.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7435263739/13_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7435263739/13_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7435263739/13_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -14315,7 +14061,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Ивановская область, Иваново, ул. Советская, 6</t>
+          <t>Камень-на-Оби, Алтайский край, ул. Ленина, 48</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -14324,7 +14070,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>300</v>
+        <v>2200</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -14370,7 +14116,7 @@
         <v>6000</v>
       </c>
       <c r="AC50" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -14384,14 +14130,19 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>2026-08-16T23:59:00+03:00</t>
+          <t>2026-09-14T05:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>2026-08-15T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5855275648</t>
+          <t>9790831721</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -14406,17 +14157,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Берёза пиловочник (лес на баланс ФГИС)</t>
+          <t>Баланс хвойный, ЭСД и документы на вывоз</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас на деляне лежит заготовленная берёза, кругляк или пиловочник, а в системе его нет, помогу поставить древесину на баланс. Заключаем договор, закрепляем объём в ФГИС ЛК, и лес становится вашим официально, можно законно возить и продавать.&lt;br&gt;&lt;br&gt;Работаю по Нелидово и району. Балансы, дрова, делянка, вывозка лесовозами, замеры в кубах, любой объём. Сделаю QR и ЭСД на перевозку, закрою расхождение по объёмам, подготовлю декларации и отчёты.&lt;br&gt;&lt;br&gt;Пришлите замеры с делянки, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>Оформляем документы на хвойный баланс в ФГИС ЛК. Услуга, баланс не продаём.&lt;br&gt;&lt;br&gt;Закрываем: постановку объёма на учёт, ЭСД с QR на каждую отгрузку, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;ЭСД делаем за 15 минут после получения данных.&lt;br&gt;&lt;br&gt;Рязанская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -14431,7 +14182,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Тверская область, Нелидово, ул. Промышленная, 13</t>
+          <t>Касимов, Рязанская обл., ул. Советская, 18</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -14440,7 +14191,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -14474,7 +14225,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -14486,7 +14237,7 @@
         <v>6000</v>
       </c>
       <c r="AC51" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -14500,19 +14251,19 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>2026-08-23T06:30:00+03:00</t>
+          <t>2026-09-14T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>2026-07-24T08:30:00+03:00</t>
+          <t>2026-08-17T13:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1803116670</t>
+          <t>4870626062</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -14527,17 +14278,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ель пиловочник (закрытие расхождений ФГИС)</t>
+          <t>Пиловочник ель сосна, ЭСД и учёт</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Мы не продаём лес, мы оформляем на него документы в ФГИС ЛК. Заготовили кругляк, а по бумагам он не бьётся или его вообще нет в системе. Мы это закрываем.&lt;br&gt;&lt;br&gt;Работаем по расхождениям. Когда по учёту один объём, а на деляне или на складе по факту другой, сводим кубы официально через договор купли-продажи. Ель, сосна, пиловочник, балансы, дрова, любой сортимент.&lt;br&gt;&lt;br&gt;Что делаем: ставим лес на баланс, закрываем расхождение объёмов, оформляем QR и ЭСД на вывозку, готовим декларации и отчёты. Если есть замеры с делянки, а лесовоз уже стоит, поможем оформить перевозку по закону.&lt;br&gt;&lt;br&gt;Лахденпохья и вся Карелия, работаем и по соседним районам. Напишите в сообщения свою ситуацию, отвечу за пару минут. Пришлите замеры, посчитаю сегодня.&lt;/p&gt;</t>
+          <t>Оформляем документы на пиловочник ели и сосны. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Закрываем учёт и сопроводительные документы: постановка объёма на баланс, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут, реквизиты. ЭСД за 15 минут.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1803116670/16_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1803116670/16_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1803116670/16_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -14552,7 +14303,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Республика Карелия, Лахденпохья, ул. Октябрьская, 27</t>
+          <t>Мантурово, Костромская обл., ул. Советская, 22</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -14561,7 +14312,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -14595,7 +14346,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -14607,7 +14358,7 @@
         <v>6000</v>
       </c>
       <c r="AC52" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -14621,14 +14372,19 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>2026-08-16T23:59:00+03:00</t>
+          <t>2026-09-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>2026-08-16T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9140846526</t>
+          <t>7622497474</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -14643,17 +14399,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (ЭСД на перевозку леса)</t>
+          <t>Лес кругляк сосна, документы и ЭСД</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на лес в системе ФГИС ЛК, сам лес мы не продаём. Если у вас есть кругляк, пиловочник, балансы или дрова, а бумаг на вывоз нет, мы закроем этот вопрос удалённо.&lt;br&gt;&lt;br&gt;Делаем QR-код и ЭСД (электронный сопроводительный документ) на перевозку, чтобы лесовоз прошёл лесной контроль и не поймал штраф. Считаем по фото замеров: скидываете кубы с деляны, мы оформляем ЭСД под ваш объём. Работаем по Владимиру и области, город крупный, объёмы тянем большие.&lt;br&gt;&lt;br&gt;Также ставим лес на баланс, закрываем расхождения по кубам, готовим декларации и отчёты.&lt;br&gt;&lt;br&gt;Напишите в сообщения, отвечу за пару минут. Пришлите замеры с деляны, посчитаю сегодня.&lt;/p&gt;</t>
+          <t>Оформляем документы на сосновый кругляк в ФГИС ЛК. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;В работу входит: ЭСД на рейс, QR код для поста, декларация о сделке, отчёт 1-ИЛ. Если объём не заведён, ставим на учёт.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, маршрут, реквизиты. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Красноярский край, Ангара и Енисей.&lt;br&gt;&lt;br&gt;Напишите, что везёте и куда.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/9140846526/17_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/9140846526/17_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/9140846526/17_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real234__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -14668,7 +14424,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Владимирская область, Владимир, пр-т Ленина, 34</t>
+          <t>Лесосибирск, Красноярский край, ул. Победы, 31</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -14677,7 +14433,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>350</v>
+        <v>3000</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -14723,7 +14479,7 @@
         <v>6000</v>
       </c>
       <c r="AC53" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -14737,14 +14493,19 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>2026-08-16T23:59:00+03:00</t>
+          <t>2026-09-15T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>2026-08-16T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7232164186</t>
+          <t>4897973128</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -14759,17 +14520,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (ЭСД и QR к сделке)</t>
+          <t>Пиловочник ель, ЭСД и QR код на вывоз</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сразу главное: сам лес мы не продаём. Мы оформляем документы на лес в системе ФГИС ЛК, работаем из Тихвина удалённо.&lt;br&gt;&lt;br&gt;Если у вас есть сосна, пиловочник, кругляк, балансы или дрова на деляне, а бумаг на них нет, мы всё оформим. Поставим лес на баланс, закроем расхождения по кубам, сделаем декларации и отчёты.&lt;br&gt;&lt;br&gt;Отдельно по вывозке: делаем QR-код и ЭСД к сделке, чтобы лесовоз прошёл лесной контроль без штрафов. Считаем по фото замеров с деляны, ничего никуда везти не нужно.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и скажу, что нужно для перевозки. Отвечаю за пару минут.&lt;/p&gt;</t>
+          <t>Оформляем ЭСД на еловый пиловочник. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Порядок: присылаете маршрут и реквизиты, получаете ЭСД с QR кодом водителю на телефон. На посту проверка занимает минуту.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;ЭСД: 15 минут.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -14784,7 +14545,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ленинградская область, Тихвин, ул. Гагарина, 48</t>
+          <t>Чусовой, Пермский край, ул. Ленина, 34</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -14793,7 +14554,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -14827,7 +14588,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -14839,7 +14600,7 @@
         <v>6000</v>
       </c>
       <c r="AC54" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -14853,19 +14614,19 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>2026-08-24T06:30:00+03:00</t>
+          <t>2026-09-16T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2026-07-25T08:30:00+03:00</t>
+          <t>2026-08-17T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2872293673</t>
+          <t>5975623537</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -14880,17 +14641,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (QR код на отгрузку)</t>
+          <t>Кругляк сосна и баланс, документы на вывоз</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на лес в системе ФГИС ЛК. Сам лес мы не продаём, делаем только бумаги на него. Если у вас есть своя партия под отгрузку в Галиче, сосна пиловочник, кругляк, балансы или дрова, а документов на неё нет, оформим всё по правилам.&lt;br&gt;&lt;br&gt;Сделаем QR-код и ЭСД на вывозку, чтобы лесовоз с грузом прошёл лесной контроль без штрафов. Закрываем расхождения по кубам, ставим лес на баланс, готовим декларации и отчёты.&lt;br&gt;&lt;br&gt;Считаем по фото ваших замеров, работаем удалённо, деляна может быть где угодно. Напишите в сообщения, отвечу за пару минут. Пришлите замеры с делянки, посчитаю сегодня.&lt;/p&gt;</t>
+          <t>Оформляем документы на сосновый кругляк и баланс. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Что делаем: ЭСД с QR на рейс, декларация о сделке, постановка объёма на учёт, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Типовой ЭСД 15 минут. По постановке на учёт срок называем после разбора документов.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -14905,7 +14666,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Костромская область, Галич, ул. Лесная, 62</t>
+          <t>Красновишерск, Пермский край, ул. Гагарина, 6</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -14914,7 +14675,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>200</v>
+        <v>1400</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -14974,19 +14735,19 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>2026-08-24T10:00:00+03:00</t>
+          <t>2026-09-16T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>2026-07-25T12:00:00+03:00</t>
+          <t>2026-08-17T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6521830331</t>
+          <t>8561800688</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -15001,17 +14762,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Сосна с делянки документов нет(помощь с учётом)</t>
+          <t>Баланс ель на комбинат, ЭСД по договору</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Оформление документов на древесину в ФГИС ЛК: кругляк, пиловочник, балансовая древесина, дрова. Работаем с лесозаготовителями, продавцами и покупателями леса.&lt;br&gt;&lt;br&gt;Что оформляем:&lt;br&gt;- электронный сопроводительный документ (ЭСД) на транспортировку древесины&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- постановку объёма на учёт и баланс, если древесина нигде не числится&lt;br&gt;- декларацию о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Присылаете породу, кубатуру, маршрут и данные сторон. Оформляем документ и передаём водителю в электронном виде.&lt;br&gt;&lt;br&gt;Срок по ЭСД обычно 15 минут с момента получения данных. Постановка объёма на учёт занимает дольше, скажу сразу по вашей ситуации.&lt;br&gt;&lt;br&gt;Свой личный кабинет в системе, электронная подпись и лесная декларация вам не нужны, оформление идёт с нашей стороны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Сосна, ель, лиственные породы, любые сортименты и объёмы, от одной лесовозной машины до постоянных отгрузок.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок и срок.</t>
+          <t>Ведём документы по поставкам балансовой древесины на комбинат. Услуга по договору.&lt;br&gt;&lt;br&gt;При регулярных поставках документы идут потоком. Оформляем ЭСД на каждую машину, ведём декларации, закрываем отчётность.&lt;br&gt;&lt;br&gt;Отдельно следим, чтобы объёмы по документам сходились с принятыми. Расхождение всплывает на приёмке.&lt;br&gt;&lt;br&gt;Томская область.&lt;br&gt;&lt;br&gt;Напишите объём в месяц.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -15026,7 +14787,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Белорецк, ул. Ленина, 24</t>
+          <t>Асино, Томская обл., ул. Ленина, 42</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -15035,7 +14796,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -15069,7 +14830,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -15095,19 +14856,19 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>2026-08-27T07:00:00+03:00</t>
+          <t>2026-09-16T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2026-07-29T07:00:00+03:00</t>
+          <t>2026-08-17T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4661388548</t>
+          <t>2239987508</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -15122,17 +14883,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Лес с делянки документов нет(QR код на вывоз леса)</t>
+          <t>Пиловочник хвойный, оформим вывоз и учёт</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>QR коды и электронные сопроводительные документы на вывоз древесины через ФГИС ЛК. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена, на постах проверяют QR код с данными рейса. Оформляем его на каждую лесовозную машину.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- сопровождение постоянных перевозок, документ на каждый рейс&lt;br&gt;- постановка древесины на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок работы. От вас данные машины, отправителя и получателя, порода и кубатура в кубометрах. Дальше оформление на нас, QR код приходит водителю на телефон.&lt;br&gt;&lt;br&gt;Обычно занимает 15 минут с момента, когда получили данные.&lt;br&gt;&lt;br&gt;Личный кабинет ФГИС ЛК, электронная подпись и собственная декларация не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и всему Приуралью. Сосновый и еловый пиловочник, лес с делянки, древесина оптом, формат любой.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
+          <t>Оформляем документы на хвойный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Берём на себя постановку объёма на учёт, ЭСД с QR на каждую машину, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Работаем и с разовой отгрузкой, и с регулярными поставками. Во втором случае удобнее вести одним исполнителем, чтобы объёмы не разъезжались между документами.&lt;br&gt;&lt;br&gt;Вологодская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -15147,7 +14908,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Янаул, ул. Победы, 16</t>
+          <t>Великий Устюг, Вологодская обл., ул. Красная, 12</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -15156,7 +14917,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>400</v>
+        <v>2400</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -15216,19 +14977,19 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>2026-08-27T11:00:00+03:00</t>
+          <t>2026-09-16T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>2026-07-29T11:00:00+03:00</t>
+          <t>2026-08-17T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6175129265</t>
+          <t>8000860251</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -15243,17 +15004,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Кругляк с делянки бумаг нет(документы фгис лк)</t>
+          <t>Лес кругляк ель, поставим на учёт</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Полный пакет документов на древесину в ФГИС ЛК для заготовителей, продавцов и перевозчиков леса.&lt;br&gt;&lt;br&gt;В работе:&lt;br&gt;- электронный сопроводительный документ на транспортировку кругляка и пиловочника&lt;br&gt;- QR код на рейс для проверки на посту&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- лесная декларация и декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования древесины&lt;br&gt;&lt;br&gt;Как это работает. Вы присылаете породу, кубатуру, маршрут и реквизиты. Мы оформляем документы в системе и передаём их в готовом виде.&lt;br&gt;&lt;br&gt;ЭСД обычно готов за 15 минут. Постановка объёма на учёт и работа с декларацией занимают дольше, срок называю до начала работы.&lt;br&gt;&lt;br&gt;Заводить свой кабинет и электронную подпись не нужно, оформление ведём со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Хвойный кругляк, лесоматериалы круглые, баланс, любые объёмы с делянки и со склада.&lt;br&gt;&lt;br&gt;Напишите кубатуру и куда везёте, скажу срок.</t>
+          <t>Ставим еловый кругляк на учёт в ФГИС ЛК. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Если объём нигде не числится, партию нельзя ни продать, ни вывезти. Это решается.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём на баланс, оформляем ЭСД с QR на отгрузки, закрываем декларацию и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -15268,7 +15029,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Дюртюли, ул. Чеверева, 8</t>
+          <t>Шарья, Костромская обл., ул. Октябрьская, 15</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -15277,7 +15038,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>450</v>
+        <v>2600</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -15311,7 +15072,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -15337,19 +15098,19 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>2026-08-27T15:00:00+03:00</t>
+          <t>2026-09-17T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2026-07-29T15:00:00+03:00</t>
+          <t>2026-08-17T19:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3494661466</t>
+          <t>1901670741</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -15364,17 +15125,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Пиловочник от заготовителя(помощь с учётом леса)</t>
+          <t>Пиловочник лиственница, документы на лес</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Учёт древесины и документы в ФГИС ЛК под ключ. Кругляк, пиловочник сосна и ель, баланс, дрова.&lt;br&gt;&lt;br&gt;Основной запрос: древесина заготовлена, но в системе не отражена, поэтому её нельзя ни продать, ни вывезти. Ставим объём на учёт и дальше ведём документооборот.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка объёма древесины на баланс&lt;br&gt;- ЭСД и QR код на каждую отгрузку лесовозом&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт по местам складирования (МСД)&lt;br&gt;- сопровождение отгрузок на постоянной основе&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и данные сторон. Остальное на нашей стороне.&lt;br&gt;&lt;br&gt;Рутинный ЭСД занимает около 15 минут. Постановка на учёт зависит от ситуации, срок скажу честно до начала.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и Приуралью, берём и разовые задачи, и постоянное ведение по объёмам с лесосеки.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, отвечу быстро.</t>
+          <t>Оформляем документы на лиственничный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;По лиственнице чаще цепляются к сортименту и кодам. Подбираем ОКПД2 под фактический сортимент, чтобы партия прошла без задержек.&lt;br&gt;&lt;br&gt;Закрываем: ЭСД с QR, декларацию о сделке, постановку объёма на учёт.&lt;br&gt;&lt;br&gt;Челябинская область.&lt;br&gt;&lt;br&gt;Напишите сортимент и объём.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -15389,7 +15150,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Мелеуз, ул. Ленина, 137</t>
+          <t>Кыштым, Челябинская обл., ул. Калинина, 11</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -15398,7 +15159,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -15432,7 +15193,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Лиственница</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -15458,19 +15219,19 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>2026-08-27T19:00:00+03:00</t>
+          <t>2026-09-18T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>2026-07-29T19:00:00+03:00</t>
+          <t>2026-08-19T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2394430844</t>
+          <t>5972697353</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -15485,17 +15246,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Лес есть документов нет(QR код на вывоз леса)</t>
+          <t>Лес кругляк ель, документы ФГИС ЛК</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Электронные сопроводительные документы и QR коды на вывоз леса через ФГИС ЛК. Кругляк, пиловочник, лесоматериалы круглые.&lt;br&gt;&lt;br&gt;Без ЭСД перевозка древесины запрещена, на постах смотрят QR код. Оформляем документ на каждый рейс, чтобы машина шла легально.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины&lt;br&gt;- QR код водителю на телефон&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные лесовозной машины, породу, кубатуру и маршрут. Оформляем и отдаём готовый документ.&lt;br&gt;&lt;br&gt;Обычно 15 минут после получения данных.&lt;br&gt;&lt;br&gt;Свой кабинет ФГИС ЛК, электронная подпись и декларация не нужны, работаем со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Алтайскому краю и Сибири. Сосновый и еловый пиловочник, баланс, дрова, древесина оптом, разница во времени не мешает.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
+          <t>Оформляем документы на еловый кругляк в ФГИС ЛК. Лес не продаём, продаём услугу оформления.&lt;br&gt;&lt;br&gt;Что закрываем:&lt;br&gt;- ЭСД на каждую машину с QR кодом&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- декларация о сделке&lt;br&gt;- отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Без ЭСД рейс встанет на посту. Делаем документ за 15 минут после ваших данных.&lt;br&gt;&lt;br&gt;Удмуртия и Приуралье.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -15510,7 +15271,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Алтайский край, Заринск, ул. Строителей, 21</t>
+          <t>Игра, Удмуртская Республика, ул. Советская, 29</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -15519,7 +15280,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -15553,7 +15314,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -15579,4621 +15340,10 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>2026-08-28T07:00:00+03:00</t>
+          <t>2026-09-18T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
-        <is>
-          <t>2026-07-30T07:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>3236944872</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Сосна есть учёта нет(помощь с учётом леса)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Постановка древесины на учёт и ведение документов в ФГИС ЛК. Работаем с кругляком, пиловочником, балансом и дровами.&lt;br&gt;&lt;br&gt;Если объём не отражён в системе, лес формально не существует: ни продать, ни вывезти его нельзя. Приводим учёт в порядок и дальше сопровождаем отгрузки.&lt;br&gt;&lt;br&gt;Что входит:&lt;br&gt;- постановка объёма древесины на баланс&lt;br&gt;- электронный сопроводительный документ на каждый рейс&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования&lt;br&gt;&lt;br&gt;От вас порода, кубатура в кубометрах, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Сроки честные: ЭСД около 15 минут, работа с учётом дольше, называю срок до начала.&lt;br&gt;&lt;br&gt;Заводить кабинет и электронную подпись не потребуется.&lt;br&gt;&lt;br&gt;Работаем по Алтайскому краю и всей Сибири. Хвойный пиловочник, лес с делянки, любые объёмы под продажу и отгрузку.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок работы.</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_3.jpg</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Алтайский край, Бийск, ул. Советская, 205</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P61" t="n">
-        <v>600</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB61" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr">
-        <is>
-          <t>2026-08-28T11:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>2026-07-30T11:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2312387978</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Кругляк есть документов нет(документы фгис лк)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Документы на древесину в ФГИС ЛК для лесозаготовителей, продавцов и покупателей леса.&lt;br&gt;&lt;br&gt;Оформляем:&lt;br&gt;- электронный сопроводительный документ на транспортировку кругляка&lt;br&gt;- QR код на рейс&lt;br&gt;- постановку объёма на учёт, если древесина не отражена в системе&lt;br&gt;- лесную декларацию и декларацию о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Вы даёте породу, кубатуру, маршрут и данные сторон. Мы оформляем в системе и передаём готовые документы.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут. Задачи по учёту и декларации занимают дольше, срок озвучиваю заранее.&lt;br&gt;&lt;br&gt;Личный кабинет, электронная подпись и своя декларация не нужны.&lt;br&gt;&lt;br&gt;Работаем по Пермскому краю и Приуралью. Пиловочник сосна и ель, балансовая древесина, дрова, отгрузка лесовозом, разовые рейсы и постоянное сопровождение.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу быстро.</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_3.jpg</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Пермский край, Чусовой, ул. Ленина, 32</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P62" t="n">
-        <v>450</v>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB62" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>2026-08-28T15:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>2026-07-30T15:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2058067807</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Ель с делянки бумаг нет(QR код на вывоз леса)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>QR коды и ЭСД на перевозку древесины через ФГИС ЛК. Кругляк, пиловочник, баланс, лесоматериалы круглые.&lt;br&gt;&lt;br&gt;Вывоз леса без электронного сопроводительного документа запрещён. На посту проверяют QR код, в нём данные рейса, объёма и сторон сделки.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- ЭСД на транспортировку с QR кодом&lt;br&gt;- документ на каждый рейс при постоянных перевозках&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- отчёт 1-ИЛ и декларация о сделке&lt;br&gt;&lt;br&gt;От вас данные лесовозной машины, порода, кубатура, откуда и куда идёт груз.&lt;br&gt;&lt;br&gt;Оформление занимает около 15 минут с момента получения данных.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронная подпись не потребуются, всё делаем со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Пермскому краю и соседним регионам. Еловый и сосновый пиловочник, лес с делянки, древесина оптом.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_08_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_08_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_08_3.jpg</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Пермский край, Лысьва, ул. Мира, 26</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P63" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB63" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
-        <is>
-          <t>2026-08-16T23:59:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>9553367742</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Пиловочник есть учёта нет(помощь с учётом леса)</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Учёт древесины в ФГИС ЛК и сопровождение отгрузок. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Древесина без учёта в системе не продаётся и не перевозится. Ставим объём на баланс, оформляем документы и дальше ведём отгрузки, чтобы каждый рейс был закрыт.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- постановка объёма древесины на учёт&lt;br&gt;- ЭСД и QR код на транспортировку&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования&lt;br&gt;- постоянное ведение документооборота&lt;br&gt;&lt;br&gt;Нужны порода, кубатура, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Рутинный ЭСД около 15 минут, постановка на учёт дольше, срок называю сразу.&lt;br&gt;&lt;br&gt;Кабинет в системе и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Работаем по Удмуртии и Поволжью. Хвойный кругляк, лесоматериалы, продажа и покупка древесины, от одной машины до постоянного потока.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, скажу срок.</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_3.jpg</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Удмуртская Республика, Глазов, ул. Кирова, 49</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P64" t="n">
-        <v>550</v>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB64" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG64" t="inlineStr">
-        <is>
-          <t>2026-08-29T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>2026-07-31T07:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2285712624</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Лес заготовлен бумаг нет(документы фгис лк)</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Оформление документов на заготовленную древесину в ФГИС ЛК. Кругляк, пиловочник, балансовая древесина.&lt;br&gt;&lt;br&gt;Частая ситуация: лес заготовлен и лежит на делянке, а по документам в системе не проведён. Разбираем и приводим в порядок.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- электронный сопроводительный документ на вывоз&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- лесная декларация, декларация о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования&lt;br&gt;&lt;br&gt;От вас порода, кубатура и данные перевозки.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут после получения данных. Работа с учётом и декларацией занимает дольше, срок скажу до начала.&lt;br&gt;&lt;br&gt;Своя декларация и кабинет в системе не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Удмуртии и соседним регионам. Сосна, ель, лиственные, любые сортименты под продажу и отгрузку лесовозом.&lt;br&gt;&lt;br&gt;Напишите кубатуру, отвечу быстро.</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_3.jpg</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Удмуртская Республика, Можга, ул. Наговицына, 60</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P65" t="n">
-        <v>400</v>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB65" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t>2026-08-29T11:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>2026-07-31T11:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>5905323698</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Сосна с делянки бумаг нет(QR код на вывоз леса)</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>QR коды и электронные сопроводительные документы на древесину. Кругляк, пиловочник сосна и ель, баланс.&lt;br&gt;&lt;br&gt;На постах проверяют QR код ЭСД, без него вывоз леса запрещён. Оформляем документ на каждую лесовозную машину через ФГИС ЛК.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины&lt;br&gt;- QR код водителю в электронном виде&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные машины, отправителя и получателя, породу и кубатуру. Оформление на нас.&lt;br&gt;&lt;br&gt;Обычно 15 минут с момента получения данных.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и Сибири. Лес с делянки и со склада, древесина оптом, часовой пояс не помеха.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_3.jpg</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Кемеровская область, Таштагол, ул. Ленина, 60</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P66" t="n">
-        <v>450</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB66" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG66" t="inlineStr">
-        <is>
-          <t>2026-08-29T15:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>2026-07-31T15:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>8540422936</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Лес есть учёта нет(помощь с учётом леса)</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Постановка древесины на учёт и документы в ФГИС ЛК. Кругляк, пиловочник, лесоматериалы круглые, дрова.&lt;br&gt;&lt;br&gt;Пока объём не стоит на балансе в системе, лес нельзя ни продать, ни вывезти. Ставим на учёт и дальше ведём документы на отгрузки.&lt;br&gt;&lt;br&gt;Что входит:&lt;br&gt;- постановка объёма древесины на учёт и баланс&lt;br&gt;- ЭСД и QR код на каждый рейс&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и реквизиты.&lt;br&gt;&lt;br&gt;ЭСД около 15 минут, работа с учётом занимает дольше, срок озвучиваю честно.&lt;br&gt;&lt;br&gt;Свой кабинет и электронная подпись не требуются.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и всей Сибири. Хвойный пиловочник, баланс, продажа древесины с лесосеки, разовые и постоянные отгрузки.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу что дальше.</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_3.jpg</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Кемеровская область, Мыски, ул. Советская, 43</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P67" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB67" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>2026-08-29T19:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>2026-07-31T19:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>8088623974</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Кругляк заготовлен бумаг нет(документы фгис лк)</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Документы в ФГИС ЛК на заготовленную древесину. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Оформляем:&lt;br&gt;- постановку объёма на учёт&lt;br&gt;- электронный сопроводительный документ на транспортировку&lt;br&gt;- QR код на рейс&lt;br&gt;- лесную декларацию и декларацию о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования&lt;br&gt;&lt;br&gt;Как работаем. От вас порода, кубатура, маршрут и данные сторон. Оформление в системе полностью на нашей стороне, документы приходят готовыми.&lt;br&gt;&lt;br&gt;Срок по ЭСД обычно 15 минут. Постановка на учёт и декларация занимают дольше, называю срок заранее.&lt;br&gt;&lt;br&gt;Заводить кабинет и электронную подпись не нужно.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и соседним регионам. Сосновый и еловый кругляк, лесоматериалы, отгрузка лесовозом, любые объёмы.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу быстро.</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_3.jpg</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Кемеровская область, Юрга, ул. Машиностроителей, 39</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P68" t="n">
-        <v>450</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB68" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t>2026-08-30T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>2026-08-01T07:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2671009093</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Лес с делянки бумаг нет(QR код на вывоз леса)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Электронные сопроводительные документы и QR коды на вывоз древесины. Кругляк, пиловочник, баланс.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена, на постах проверяют QR код из ФГИС ЛК. Оформление у нас поставлено на поток.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- документ на каждый рейс при регулярных перевозках&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- отчёт 1-ИЛ, декларация о сделке&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные лесовозной машины, отправителя, получателя и кубатуру, дальше QR код у водителя на экране.&lt;br&gt;&lt;br&gt;Обычно 15 минут.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронная подпись не нужны.&lt;br&gt;&lt;br&gt;Работаем по Красноярскому краю и всей Сибири. Хвойный кругляк с делянки, лиственные породы, древесина оптом, часовой пояс не проблема.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_3.jpg</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Красноярский край, Богучаны, ул. Ленина, 27</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P69" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB69" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>2026-08-30T11:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>2026-08-01T11:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>6664478711</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Ель есть документов нет(помощь с учётом леса)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Учёт древесины и оформление документов в ФГИС ЛК. Кругляк, пиловочник ель и сосна, баланс, дрова.&lt;br&gt;&lt;br&gt;Древесина должна стоять на учёте, иначе её не продать и не вывезти. Ставим объём на баланс, оформляем сопроводительные документы, ведём отчётность.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка объёма древесины на учёт&lt;br&gt;- ЭСД и QR код на транспортировку&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт в местах складирования&lt;br&gt;- сопровождение постоянных отгрузок&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Рутинный ЭСД около 15 минут, задачи по учёту дольше, срок называю до начала работы.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Лесоматериалы круглые, продажа и покупка леса, отгрузка лесовозными машинами.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, отвечу быстро.</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_3.jpg</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Челябинская область, Сатка, ул. Солнечная, 12</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P70" t="n">
-        <v>550</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB70" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG70" t="inlineStr">
-        <is>
-          <t>2026-08-30T15:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>2026-08-01T15:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2657040747</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Сосна заготовлена бумаг нет(документы фгис лк)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Оформление документов на древесину в ФГИС ЛК для заготовителей, продавцов и перевозчиков. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;В работе:&lt;br&gt;- электронный сопроводительный документ на транспортировку древесины&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- лесная декларация, декларация о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования древесины (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Вы присылаете породу, кубатуру, маршрут и данные сторон. Мы оформляем в системе и передаём готовый пакет.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут после получения данных. Учёт и декларация занимают дольше, срок озвучиваю заранее.&lt;br&gt;&lt;br&gt;Свой кабинет, электронная подпись и декларация вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Сосновый пиловочник, лес с делянки, древесина оптом, разовые задачи и постоянное ведение.&lt;br&gt;&lt;br&gt;Напишите кубатуру, скажу срок и порядок.</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_3.jpg</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Челябинская область, Катав-Ивановск, ул. Ленина, 19</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P71" t="n">
-        <v>400</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB71" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG71" t="inlineStr">
-        <is>
-          <t>2026-08-30T19:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>2026-08-01T19:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>8424443532</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Лес заготовлен документов нет(помощь с учётом)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Учёт древесины и оформление документов в ФГИС ЛК. Кругляк, пиловочник сосна и ель, балансовая древесина, дрова.&lt;br&gt;&lt;br&gt;Ситуация, с которой чаще всего приходят: лес заготовлен и лежит, покупатель есть, а в системе объём не проведён. Пока древесина не на учёте, продать и вывезти её нельзя.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка заготовленного объёма на учёт и баланс&lt;br&gt;- электронный сопроводительный документ (ЭСД) на транспортировку&lt;br&gt;- QR код водителю для проверки на посту&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;Порядок. От вас порода, кубатура в кубометрах, маршрут и реквизиты сторон. Оформление в системе полностью на нашей стороне.&lt;br&gt;&lt;br&gt;Рутинный ЭСД занимает около 15 минут после получения данных. Постановка объёма на учёт дольше, срок называю честно до начала работы.&lt;br&gt;&lt;br&gt;Свой личный кабинет, электронная подпись и лесная декларация вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Хвойный кругляк с делянки и со склада, лесоматериалы круглые, древесина оптом, отгрузка лесовозными машинами.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок и срок.</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_3.jpg</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Республика Башкортостан, Ишимбай, ул. Советская, 15</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P72" t="n">
-        <v>500</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB72" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>2026-08-26T14:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>2026-07-28T14:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2960453369</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Сосна есть документов нет(QR код на вывоз леса)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>QR коды и электронные сопроводительные документы на вывоз древесины через ФГИС ЛК. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена. На посту проверяют QR код, в нём данные рейса, объёма и сторон сделки. Оформляем документ на каждую лесовозную машину.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- документ на каждый рейс при постоянных перевозках&lt;br&gt;- постановка объёма древесины на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок работы. Присылаете данные машины, отправителя и получателя, породу и кубатуру. Дальше оформление на нас, QR код приходит водителю на телефон.&lt;br&gt;&lt;br&gt;Обычно занимает 15 минут с момента получения данных.&lt;br&gt;&lt;br&gt;Личный кабинет ФГИС ЛК, электронная подпись и собственная декларация не потребуются, работаем со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Пермскому краю и Приуралью. Сосновый и еловый пиловочник, лес с делянки, лесоматериалы круглые, продажа и покупка древесины, любые объёмы.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_3.jpg</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Пермский край, Кунгур, ул. Ленина, 40</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P73" t="n">
-        <v>450</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB73" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG73" t="inlineStr">
-        <is>
-          <t>2026-08-26T17:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>2026-07-28T17:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>1936930142</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Ель кругляк с делянки(помощь с учётом)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Лес есть, а с документами в ФГИС ЛК вечно возня. Возьмём её на себя. Поставим ваш объём на баланс, оформим ЭСД и QR код на каждую машину, дальше просто ведём учёт, чтобы вы про это не думали.&lt;br&gt;&lt;br&gt;Лес еловый, кругляк с делянки, 6 метров, диаметр от 20 см. Есть и другие сортименты.&lt;br&gt;&lt;br&gt;От вас только данные по объёму и рейсу. Свой кабинет в системе, декларацию и электронную подпись заводить не нужно, всё оформляем мы.&lt;br&gt;&lt;br&gt;Я по Башкортостану и соседним регионам. Напишите, что у вас по лесу, подскажу порядок и сроки.</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_03.jpg</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Республика Башкортостан, Белорецк, ул. Ленина, 15</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB74" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG74" t="inlineStr">
-        <is>
-          <t>2026-09-06T12:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>2026-08-07T14:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>7029554179</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Сосна кругляк с делянки(QR код на вывоз леса)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Делаем QR код на вывоз леса и ЭСД через ФГИС ЛК. Машина уже под погрузкой, а документа на рейс нет - обычно решаем в тот же день.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, есть и другой хвойный сортимент.&lt;br&gt;&lt;br&gt;QR код и ЭСД приходят водителю на телефон. Перед этим сверяем объём и породу, чтобы на посту не развернули. Свой кабинет и подпись вам не нужны.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири, разница по времени не мешает. Напишите, что по рейсу, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_03.jpg</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Алтайский край, Бийск, ул. Советская, 8</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB75" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>2026-09-06T13:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>2026-08-10T06:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2323865424</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Сосна кругляк под погрузку(QR код на вывоз леса)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Лес есть, а документов нет - обычная история. Оформим QR код на вывоз и ЭСД через ФГИС ЛК, документ придёт водителю на экран перед выездом.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Объём и породу проверяем заранее, чтобы потом не переделывать. Всё оформление на нас, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Кемеровской области и Сибири, часовой пояс не помеха. Напишите объём и куда везёте, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_03.jpg</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Кемеровская область, Таштагол, ул. Ленина, 22</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB76" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
-        <is>
-          <t>2026-09-06T15:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>2026-08-10T08:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>8579049856</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Лиственница кругляк(ЭСД на перевозку)</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Делаем ЭСД на перевозку леса через ФГИС ЛК. Если возите объёмами, на каждый рейс нужен свой документ - держим это на потоке, чтобы машины не стояли.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см. Есть сосна и ель.&lt;br&gt;&lt;br&gt;Данные проверяем до выпуска, чтобы не было отказа. Оформляем, даже если своей декларации у вас пока нет.&lt;br&gt;&lt;br&gt;Я по Красноярскому краю и Сибири. Напишите объём и маршрут, скажу срок сегодня.</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_03.jpg</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Красноярский край, Богучаны, ул. Октябрьская, 5</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Лиственница</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB77" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>2026-09-07T04:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>2026-08-08T06:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>4561483668</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Ель кругляк с делянки(помощь с учётом)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Кто возит лес, тот знает: без учёта в ФГИС ЛК никуда. Поможем с учётом - поставим объём на баланс, оформим ЭСД и QR на рейсы, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, кругляк с делянки, 6 метров, диаметр от 20 см. Любой объём.&lt;br&gt;&lt;br&gt;От вас только данные, остальное на нас. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Челябинской области и Уралу. Напишите породу и кубатуру, подскажу сроки.</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_03.jpg</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Челябинская область, Сатка, ул. Пролетарская, 12</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB78" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG78" t="inlineStr">
-        <is>
-          <t>2026-09-07T05:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>2026-08-08T07:30:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2738165608</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Сосна от заготовителя(QR код на вывоз леса)</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Машина готова, лес на месте, а QR кода на вывоз нет. Сделаем QR и ЭСД через ФГИС ЛК на каждую машину, придёт водителю на телефон.&lt;br&gt;&lt;br&gt;Сосновый кругляк напрямую от заготовителя, 6 метров, диаметр от 20 см.&lt;br&gt;&lt;br&gt;Перед отгрузкой сверяем объём и породу. Оформление целиком с нашей стороны, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Башкортостану и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_03.jpg</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Республика Башкортостан, Сибай, ул. Заводская, 3</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB79" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG79" t="inlineStr">
-        <is>
-          <t>2026-09-07T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>2026-08-08T09:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>7680837833</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Сосна пиловочник с делянки(документы фгис лк)</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Кто работает с лесом, тому нужны документы в ФГИС ЛК, а времени на систему нет. Оформим за вас - ЭСД и QR на перевозку, поставим объём на учёт, проведём сделку.&lt;br&gt;&lt;br&gt;Сосновый пиловочник с делянки, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Кабинет и подпись заводить не надо, ведём всё сами.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири. Напишите кубатуру и маршрут, отвечу быстро.</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_03.jpg</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Алтайский край, Заринск, ул. Металлургов, 9</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB80" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC80" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG80" t="inlineStr">
-        <is>
-          <t>2026-09-07T08:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>2026-08-08T10:30:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>1951202398</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Лиственница кругляк с делянки(ЭСД на вывоз)</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на вывоз леса через ФГИС ЛК. Лес готов, машина под погрузкой, а документа на рейс нет - выпустим, и водитель едет.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см, плотная древесина.&lt;br&gt;&lt;br&gt;Данные проверяем заранее. Если что-то оформлено с ошибкой, аннулируем и делаем заново по правилам. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Пермскому краю и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_03.jpg</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Пермский край, Чусовой, ул. Ленина, 30</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Лиственница</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB81" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG81" t="inlineStr">
-        <is>
-          <t>2026-09-07T10:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>2026-08-08T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>7192983965</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Ель пиловочник с делянки(помощь с учётом)</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Лес есть, а документов нет, и учёт в ФГИС ЛК висит мёртвым грузом. Разгрузим - поставим объём на баланс, сделаем ЭСД и QR на каждый рейс, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, пиловочник с делянки, 6 метров, диаметр от 20 см. Хвоя.&lt;br&gt;&lt;br&gt;От вас данные, остальное наша забота. Свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Я по Удмуртии и Поволжью. Напишите породу и кубатуру, подскажу сроки.</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_03.jpg</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Удмуртская Республика, Можга, ул. Наговицына, 7</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB82" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG82" t="inlineStr">
-        <is>
-          <t>2026-09-08T03:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>2026-08-09T05:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2634568371</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Лес кругляк ель сосна, ЭСД на отгрузку</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на еловый и сосновый кругляк. Услуга по документам отгрузки.&lt;br&gt;&lt;br&gt;На каждую машину сопроводительный документ с QR кодом, водителю до выезда. Если объём не заведён в системе, сначала ставим на учёт.&lt;br&gt;&lt;br&gt;Закрываем декларацию о сделке и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Галич, Костромская обл., ул. Свободы, 11</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P83" t="n">
-        <v>900</v>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB83" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG83" t="inlineStr">
-        <is>
-          <t>2026-09-12T16:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>2026-08-13T18:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>4149246617</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Пиловочник сосна, полный пакет документов</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Оформляем полный пакет документов на сосновый пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;В пакет входит: постановка на учёт, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ, места складирования, коды ОКПД2.&lt;br&gt;&lt;br&gt;От вас данные, от нас готовые документы. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Омская область.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить.</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Тара, Омская обл., ул. Ленина, 9</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P84" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB84" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE84" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG84" t="inlineStr">
-        <is>
-          <t>2026-09-13T03:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>2026-08-14T05:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>1099424133</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Лес кругляк ель, ЭСД и постановка на учёт</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на еловый кругляк и ставим объём на учёт. Услуга по документам.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сопроводительный документ выписывать не на что. Поэтому сначала учёт, потом отгрузки.&lt;br&gt;&lt;br&gt;Дальше: ЭСД с QR на каждый рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Нижегородская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Урень, Нижегородская обл., ул. Ленина, 47</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P85" t="n">
-        <v>1500</v>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB85" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
-        <is>
-          <t>2026-09-13T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>2026-08-14T09:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>1198010038</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Пиловочник сосна, оформим ЭСД на рейс</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на сосновый пиловочник. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждый рейс: сопроводительный документ с QR кодом, водителю до выезда. Срок 15 минут.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сначала ставим на учёт, потом отгружаете.&lt;br&gt;&lt;br&gt;Ивановская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Юрьевец, Ивановская обл., ул. Советская, 26</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P86" t="n">
-        <v>1800</v>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB86" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC86" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG86" t="inlineStr">
-        <is>
-          <t>2026-09-13T10:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>2026-08-14T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>3451367236</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Кругляк хвойный, поставим на учёт и вывезем</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Ставим хвойный кругляк на учёт в ФГИС ЛК и оформляем вывоз. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Основная проблема не в лесе, а в бумагах: объём есть, в системе его нет, вывезти нельзя.&lt;br&gt;&lt;br&gt;Ставим на учёт, дальше каждый рейс уходит с ЭСД и QR, сделка закрывается декларацией, период отчётом 1-ИЛ.&lt;br&gt;&lt;br&gt;Владимирская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__3.jpg</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Вязники, Владимирская обл., ул. Ленина, 33</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P87" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB87" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC87" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>2026-09-14T03:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>2026-08-15T05:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>7655959812</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Лес кругляк сосна, ЭСД на каждый рейс</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на сосновый кругляк. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждую машину готовим сопроводительный документ с QR кодом. Водитель получает до выезда.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;Алтайский край.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Камень-на-Оби, Алтайский край, ул. Ленина, 48</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P88" t="n">
-        <v>2200</v>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB88" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC88" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG88" t="inlineStr">
-        <is>
-          <t>2026-09-14T05:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>2026-08-15T07:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>9790831721</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Баланс хвойный, ЭСД и документы на вывоз</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Оформляем документы на хвойный баланс в ФГИС ЛК. Услуга, баланс не продаём.&lt;br&gt;&lt;br&gt;Закрываем: постановку объёма на учёт, ЭСД с QR на каждую отгрузку, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;ЭСД делаем за 15 минут после получения данных.&lt;br&gt;&lt;br&gt;Рязанская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Касимов, Рязанская обл., ул. Советская, 18</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P89" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB89" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC89" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE89" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG89" t="inlineStr">
-        <is>
-          <t>2026-09-14T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>2026-08-17T13:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>4870626062</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Пиловочник ель сосна, ЭСД и учёт</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Оформляем документы на пиловочник ели и сосны. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Закрываем учёт и сопроводительные документы: постановка объёма на баланс, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут, реквизиты. ЭСД за 15 минут.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Мантурово, Костромская обл., ул. Советская, 22</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P90" t="n">
-        <v>2800</v>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB90" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC90" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>2026-09-15T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>2026-08-16T09:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>7622497474</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Лес кругляк сосна, документы и ЭСД</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Оформляем документы на сосновый кругляк в ФГИС ЛК. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;В работу входит: ЭСД на рейс, QR код для поста, декларация о сделке, отчёт 1-ИЛ. Если объём не заведён, ставим на учёт.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, маршрут, реквизиты. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Красноярский край, Ангара и Енисей.&lt;br&gt;&lt;br&gt;Напишите, что везёте и куда.</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real234__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Лесосибирск, Красноярский край, ул. Победы, 31</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P91" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB91" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE91" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG91" t="inlineStr">
-        <is>
-          <t>2026-09-15T10:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>2026-08-16T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>4897973128</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Пиловочник ель, ЭСД и QR код на вывоз</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на еловый пиловочник. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Порядок: присылаете маршрут и реквизиты, получаете ЭСД с QR кодом водителю на телефон. На посту проверка занимает минуту.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;ЭСД: 15 минут.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Чусовой, Пермский край, ул. Ленина, 34</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P92" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB92" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC92" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG92" t="inlineStr">
-        <is>
-          <t>2026-09-16T05:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>2026-08-17T07:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>5975623537</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Кругляк сосна и баланс, документы на вывоз</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Оформляем документы на сосновый кругляк и баланс. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Что делаем: ЭСД с QR на рейс, декларация о сделке, постановка объёма на учёт, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Типовой ЭСД 15 минут. По постановке на учёт срок называем после разбора документов.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Красновишерск, Пермский край, ул. Гагарина, 6</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P93" t="n">
-        <v>1400</v>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB93" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC93" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG93" t="inlineStr">
-        <is>
-          <t>2026-09-16T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>2026-08-17T09:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>8561800688</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Баланс ель на комбинат, ЭСД по договору</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Ведём документы по поставкам балансовой древесины на комбинат. Услуга по договору.&lt;br&gt;&lt;br&gt;При регулярных поставках документы идут потоком. Оформляем ЭСД на каждую машину, ведём декларации, закрываем отчётность.&lt;br&gt;&lt;br&gt;Отдельно следим, чтобы объёмы по документам сходились с принятыми. Расхождение всплывает на приёмке.&lt;br&gt;&lt;br&gt;Томская область.&lt;br&gt;&lt;br&gt;Напишите объём в месяц.</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Асино, Томская обл., ул. Ленина, 42</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P94" t="n">
-        <v>1600</v>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB94" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC94" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE94" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF94" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG94" t="inlineStr">
-        <is>
-          <t>2026-09-16T10:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>2026-08-17T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2239987508</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Пиловочник хвойный, оформим вывоз и учёт</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Оформляем документы на хвойный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Берём на себя постановку объёма на учёт, ЭСД с QR на каждую машину, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Работаем и с разовой отгрузкой, и с регулярными поставками. Во втором случае удобнее вести одним исполнителем, чтобы объёмы не разъезжались между документами.&lt;br&gt;&lt;br&gt;Вологодская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Великий Устюг, Вологодская обл., ул. Красная, 12</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P95" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB95" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC95" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG95" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>2026-08-17T14:30:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>8000860251</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Лес кругляк ель, поставим на учёт</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Ставим еловый кругляк на учёт в ФГИС ЛК. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Если объём нигде не числится, партию нельзя ни продать, ни вывезти. Это решается.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём на баланс, оформляем ЭСД с QR на отгрузки, закрываем декларацию и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру.</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Шарья, Костромская обл., ул. Октябрьская, 15</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P96" t="n">
-        <v>2600</v>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB96" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG96" t="inlineStr">
-        <is>
-          <t>2026-09-17T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>2026-08-17T19:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>1901670741</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Пиловочник лиственница, документы на лес</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Оформляем документы на лиственничный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;По лиственнице чаще цепляются к сортименту и кодам. Подбираем ОКПД2 под фактический сортимент, чтобы партия прошла без задержек.&lt;br&gt;&lt;br&gt;Закрываем: ЭСД с QR, декларацию о сделке, постановку объёма на учёт.&lt;br&gt;&lt;br&gt;Челябинская область.&lt;br&gt;&lt;br&gt;Напишите сортимент и объём.</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Кыштым, Челябинская обл., ул. Калинина, 11</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P97" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Лиственница</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB97" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC97" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF97" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG97" t="inlineStr">
-        <is>
-          <t>2026-09-18T10:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>2026-08-19T05:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>5972697353</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Лес кругляк ель, документы ФГИС ЛК</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Оформляем документы на еловый кругляк в ФГИС ЛК. Лес не продаём, продаём услугу оформления.&lt;br&gt;&lt;br&gt;Что закрываем:&lt;br&gt;- ЭСД на каждую машину с QR кодом&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- декларация о сделке&lt;br&gt;- отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Без ЭСД рейс встанет на посту. Делаем документ за 15 минут после ваших данных.&lt;br&gt;&lt;br&gt;Удмуртия и Приуралье.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Игра, Удмуртская Республика, ул. Советская, 29</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P98" t="n">
-        <v>1100</v>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB98" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC98" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG98" t="inlineStr">
-        <is>
-          <t>2026-09-18T12:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
         <is>
           <t>2026-08-19T07:00:00+03:00</t>
         </is>
@@ -20288,7 +15438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD45"/>
+  <dimension ref="B1:AD45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22717,7 +17867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="B1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -7942,7 +7942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ60"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -14142,7 +14142,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9790831721</t>
+          <t>4870626062</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Баланс хвойный, ЭСД и документы на вывоз</t>
+          <t>Пиловочник ель сосна, ЭСД и учёт</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Оформляем документы на хвойный баланс в ФГИС ЛК. Услуга, баланс не продаём.&lt;br&gt;&lt;br&gt;Закрываем: постановку объёма на учёт, ЭСД с QR на каждую отгрузку, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;ЭСД делаем за 15 минут после получения данных.&lt;br&gt;&lt;br&gt;Рязанская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
+          <t>Оформляем документы на пиловочник ели и сосны. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Закрываем учёт и сопроводительные документы: постановка объёма на баланс, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут, реквизиты. ЭСД за 15 минут.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Касимов, Рязанская обл., ул. Советская, 18</t>
+          <t>Мантурово, Костромская обл., ул. Советская, 22</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -14191,7 +14191,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -14251,19 +14251,19 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>2026-09-14T07:00:00+03:00</t>
+          <t>2026-09-15T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>2026-08-17T13:00:00+03:00</t>
+          <t>2026-08-16T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4870626062</t>
+          <t>7622497474</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -14278,17 +14278,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Пиловочник ель сосна, ЭСД и учёт</t>
+          <t>Лес кругляк сосна, документы и ЭСД</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Оформляем документы на пиловочник ели и сосны. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Закрываем учёт и сопроводительные документы: постановка объёма на баланс, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут, реквизиты. ЭСД за 15 минут.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
+          <t>Оформляем документы на сосновый кругляк в ФГИС ЛК. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;В работу входит: ЭСД на рейс, QR код для поста, декларация о сделке, отчёт 1-ИЛ. Если объём не заведён, ставим на учёт.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, маршрут, реквизиты. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Красноярский край, Ангара и Енисей.&lt;br&gt;&lt;br&gt;Напишите, что везёте и куда.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real234__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Мантурово, Костромская обл., ул. Советская, 22</t>
+          <t>Лесосибирск, Красноярский край, ул. Победы, 31</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -14312,7 +14312,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -14372,19 +14372,19 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>2026-09-15T07:00:00+03:00</t>
+          <t>2026-09-15T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>2026-08-16T09:00:00+03:00</t>
+          <t>2026-08-16T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7622497474</t>
+          <t>4897973128</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -14399,17 +14399,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Лес кругляк сосна, документы и ЭСД</t>
+          <t>Пиловочник ель, ЭСД и QR код на вывоз</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Оформляем документы на сосновый кругляк в ФГИС ЛК. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;В работу входит: ЭСД на рейс, QR код для поста, декларация о сделке, отчёт 1-ИЛ. Если объём не заведён, ставим на учёт.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, маршрут, реквизиты. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Красноярский край, Ангара и Енисей.&lt;br&gt;&lt;br&gt;Напишите, что везёте и куда.</t>
+          <t>Оформляем ЭСД на еловый пиловочник. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Порядок: присылаете маршрут и реквизиты, получаете ЭСД с QR кодом водителю на телефон. На посту проверка занимает минуту.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;ЭСД: 15 минут.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real234__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Лесосибирск, Красноярский край, ул. Победы, 31</t>
+          <t>Чусовой, Пермский край, ул. Ленина, 34</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -14433,7 +14433,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -14493,19 +14493,19 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>2026-09-15T10:00:00+03:00</t>
+          <t>2026-09-16T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2026-08-16T12:00:00+03:00</t>
+          <t>2026-08-17T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4897973128</t>
+          <t>5975623537</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -14520,17 +14520,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Пиловочник ель, ЭСД и QR код на вывоз</t>
+          <t>Кругляк сосна и баланс, документы на вывоз</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Оформляем ЭСД на еловый пиловочник. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Порядок: присылаете маршрут и реквизиты, получаете ЭСД с QR кодом водителю на телефон. На посту проверка занимает минуту.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;ЭСД: 15 минут.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
+          <t>Оформляем документы на сосновый кругляк и баланс. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Что делаем: ЭСД с QR на рейс, декларация о сделке, постановка объёма на учёт, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Типовой ЭСД 15 минут. По постановке на учёт срок называем после разбора документов.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Чусовой, Пермский край, ул. Ленина, 34</t>
+          <t>Красновишерск, Пермский край, ул. Гагарина, 6</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -14614,19 +14614,19 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>2026-09-16T05:00:00+03:00</t>
+          <t>2026-09-16T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2026-08-17T07:00:00+03:00</t>
+          <t>2026-08-17T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5975623537</t>
+          <t>8561800688</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -14641,17 +14641,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Кругляк сосна и баланс, документы на вывоз</t>
+          <t>Баланс ель на комбинат, ЭСД по договору</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Оформляем документы на сосновый кругляк и баланс. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Что делаем: ЭСД с QR на рейс, декларация о сделке, постановка объёма на учёт, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Типовой ЭСД 15 минут. По постановке на учёт срок называем после разбора документов.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
+          <t>Ведём документы по поставкам балансовой древесины на комбинат. Услуга по договору.&lt;br&gt;&lt;br&gt;При регулярных поставках документы идут потоком. Оформляем ЭСД на каждую машину, ведём декларации, закрываем отчётность.&lt;br&gt;&lt;br&gt;Отдельно следим, чтобы объёмы по документам сходились с принятыми. Расхождение всплывает на приёмке.&lt;br&gt;&lt;br&gt;Томская область.&lt;br&gt;&lt;br&gt;Напишите объём в месяц.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Красновишерск, Пермский край, ул. Гагарина, 6</t>
+          <t>Асино, Томская обл., ул. Ленина, 42</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -14675,7 +14675,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -14735,19 +14735,19 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>2026-09-16T07:00:00+03:00</t>
+          <t>2026-09-16T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>2026-08-17T09:00:00+03:00</t>
+          <t>2026-08-17T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8561800688</t>
+          <t>2239987508</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -14762,17 +14762,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Баланс ель на комбинат, ЭСД по договору</t>
+          <t>Пиловочник хвойный, оформим вывоз и учёт</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ведём документы по поставкам балансовой древесины на комбинат. Услуга по договору.&lt;br&gt;&lt;br&gt;При регулярных поставках документы идут потоком. Оформляем ЭСД на каждую машину, ведём декларации, закрываем отчётность.&lt;br&gt;&lt;br&gt;Отдельно следим, чтобы объёмы по документам сходились с принятыми. Расхождение всплывает на приёмке.&lt;br&gt;&lt;br&gt;Томская область.&lt;br&gt;&lt;br&gt;Напишите объём в месяц.</t>
+          <t>Оформляем документы на хвойный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Берём на себя постановку объёма на учёт, ЭСД с QR на каждую машину, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Работаем и с разовой отгрузкой, и с регулярными поставками. Во втором случае удобнее вести одним исполнителем, чтобы объёмы не разъезжались между документами.&lt;br&gt;&lt;br&gt;Вологодская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Асино, Томская обл., ул. Ленина, 42</t>
+          <t>Великий Устюг, Вологодская обл., ул. Красная, 12</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -14796,7 +14796,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -14856,19 +14856,19 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>2026-09-16T10:00:00+03:00</t>
+          <t>2026-09-16T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2026-08-17T12:00:00+03:00</t>
+          <t>2026-08-17T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2239987508</t>
+          <t>8000860251</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -14883,17 +14883,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Пиловочник хвойный, оформим вывоз и учёт</t>
+          <t>Лес кругляк ель, поставим на учёт</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Оформляем документы на хвойный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Берём на себя постановку объёма на учёт, ЭСД с QR на каждую машину, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Работаем и с разовой отгрузкой, и с регулярными поставками. Во втором случае удобнее вести одним исполнителем, чтобы объёмы не разъезжались между документами.&lt;br&gt;&lt;br&gt;Вологодская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
+          <t>Ставим еловый кругляк на учёт в ФГИС ЛК. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Если объём нигде не числится, партию нельзя ни продать, ни вывезти. Это решается.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём на баланс, оформляем ЭСД с QR на отгрузки, закрываем декларацию и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Великий Устюг, Вологодская обл., ул. Красная, 12</t>
+          <t>Шарья, Костромская обл., ул. Октябрьская, 15</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -14977,19 +14977,19 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>2026-09-16T12:00:00+03:00</t>
+          <t>2026-09-17T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>2026-08-17T14:30:00+03:00</t>
+          <t>2026-08-17T19:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8000860251</t>
+          <t>1901670741</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -15004,17 +15004,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Лес кругляк ель, поставим на учёт</t>
+          <t>Пиловочник лиственница, документы на лес</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ставим еловый кругляк на учёт в ФГИС ЛК. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Если объём нигде не числится, партию нельзя ни продать, ни вывезти. Это решается.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём на баланс, оформляем ЭСД с QR на отгрузки, закрываем декларацию и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру.</t>
+          <t>Оформляем документы на лиственничный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;По лиственнице чаще цепляются к сортименту и кодам. Подбираем ОКПД2 под фактический сортимент, чтобы партия прошла без задержек.&lt;br&gt;&lt;br&gt;Закрываем: ЭСД с QR, декларацию о сделке, постановку объёма на учёт.&lt;br&gt;&lt;br&gt;Челябинская область.&lt;br&gt;&lt;br&gt;Напишите сортимент и объём.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Шарья, Костромская обл., ул. Октябрьская, 15</t>
+          <t>Кыштым, Челябинская обл., ул. Калинина, 11</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -15038,7 +15038,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Лиственница</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -15098,19 +15098,19 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>2026-09-17T07:00:00+03:00</t>
+          <t>2026-09-18T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2026-08-17T19:00:00+03:00</t>
+          <t>2026-08-19T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1901670741</t>
+          <t>5972697353</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -15125,17 +15125,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Пиловочник лиственница, документы на лес</t>
+          <t>Лес кругляк ель, документы ФГИС ЛК</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Оформляем документы на лиственничный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;По лиственнице чаще цепляются к сортименту и кодам. Подбираем ОКПД2 под фактический сортимент, чтобы партия прошла без задержек.&lt;br&gt;&lt;br&gt;Закрываем: ЭСД с QR, декларацию о сделке, постановку объёма на учёт.&lt;br&gt;&lt;br&gt;Челябинская область.&lt;br&gt;&lt;br&gt;Напишите сортимент и объём.</t>
+          <t>Оформляем документы на еловый кругляк в ФГИС ЛК. Лес не продаём, продаём услугу оформления.&lt;br&gt;&lt;br&gt;Что закрываем:&lt;br&gt;- ЭСД на каждую машину с QR кодом&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- декларация о сделке&lt;br&gt;- отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Без ЭСД рейс встанет на посту. Делаем документ за 15 минут после ваших данных.&lt;br&gt;&lt;br&gt;Удмуртия и Приуралье.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Кыштым, Челябинская обл., ул. Калинина, 11</t>
+          <t>Игра, Удмуртская Республика, ул. Советская, 29</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -15159,7 +15159,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3000</v>
+        <v>1100</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Лиственница</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -15219,131 +15219,10 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>2026-09-18T10:00:00+03:00</t>
+          <t>2026-09-18T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
-        <is>
-          <t>2026-08-19T05:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>5972697353</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Лес кругляк ель, документы ФГИС ЛК</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Оформляем документы на еловый кругляк в ФГИС ЛК. Лес не продаём, продаём услугу оформления.&lt;br&gt;&lt;br&gt;Что закрываем:&lt;br&gt;- ЭСД на каждую машину с QR кодом&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- декларация о сделке&lt;br&gt;- отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Без ЭСД рейс встанет на посту. Делаем документ за 15 минут после ваших данных.&lt;br&gt;&lt;br&gt;Удмуртия и Приуралье.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Игра, Удмуртская Республика, ул. Советская, 29</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P60" t="n">
-        <v>1100</v>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB60" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>2026-09-18T12:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
         <is>
           <t>2026-08-19T07:00:00+03:00</t>
         </is>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -1679,7 +1679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -2717,7 +2717,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4008346466</t>
+          <t>1242403378</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4008346466/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4008346466/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4008346466/05_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/11_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/11_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/11_03.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2745,22 +2745,24 @@
           <t>Предложение услуг</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>350</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ель пиловочник (документы ФГИС ЛК)</t>
+          <t>Документы на лес ФГИС ЛК под ключ</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на лес в ФГИС ЛК. Сам лес не продаём, работаем только по бумагам официально через договор, город Мирный.&lt;br&gt;&lt;br&gt;Если у вас есть заготовленный лес, а в системе его нет, ставим древесину на баланс компании через договор и закрепляем объём в ФГИС ЛК, чтобы можно было законно продавать и возить.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;QR-код и ЭСД на перевозку, чтобы лесовоз шёл с документами.&lt;br&gt;Закрываем расхождения по кубам, когда замеры на деляне не сошлись с системой.&lt;br&gt;Ель, кругляк, пиловочник, балансы, дрова с делянки, вывозка. Если лес есть, а документов нет, оформим.&lt;br&gt;Ведём декларации и отчёты.&lt;br&gt;&lt;br&gt;Пришлите замеры по своей деляне, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Заготовили лес и не хотите тонуть в ФГИС ЛК - ведём документы за вас под ключ. Ставим объём на учёт, оформляем ЭСД и QR на перевозку, проводим сделку.&lt;/p&gt;&lt;p&gt;Можно разово под конкретную задачу или взять ваш аккаунт на постоянное сопровождение. Данные проверяем, чтобы не было отказов и штрафов.&lt;/p&gt;&lt;p&gt;Свой кабинет и электронная подпись вам не нужны, всё делаем сами. От вас исходники по лесу и отгрузкам.&lt;/p&gt;&lt;p&gt;Пакет от 3000 рублей, точная цена по объёму работ. Напишите, что у вас с лесом и документами, разложу по шагам.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Архангельская область, Мирный, ул. Мира, 40</t>
+          <t>Республика Башкортостан, Уфа, ул. Мира, 14</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2825,252 +2827,10 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-21T08:30:00+03:00</t>
+          <t>2026-09-08T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-07-22T10:30:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>4374877725</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4374877725/15_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4374877725/15_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4374877725/15_03.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>300</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Кедр кругляк (QR код на вывоз леса)</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Сразу к делу: мы оформляем документы на лес в системе ФГИС ЛК, а сам лес не продаём. Если у вас есть кедр, кругляк, пиловочник, балансы или дрова, а бумаг на вывозку нет, мы всё посчитаем и оформим.&lt;br&gt;&lt;br&gt;Готовим QR-код и ЭСД на перевозку, чтобы лесовоз прошёл лесной контроль без штрафов. Считаем удалённо по фото ваших замеров: скидываете кубы с деляны, мы переводим в документ.&lt;br&gt;&lt;br&gt;Закрываем расхождения по объёмам, ставим лес на баланс, делаем декларации и отчёты. Работаем как посредник и консультант по всей вывозке, из Молчаново, разберём вашу ситуацию по шагам.&lt;br&gt;&lt;br&gt;Напишите в сообщения, отвечу за пару минут. Пришлите замеры с делянки, посчитаю сегодня.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Томская область, Молчаново, ул. Мира, 20</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Услуги посредников</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Удалённо</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2026-08-23T08:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-07-24T10:30:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1242403378</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/11_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/11_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/11_03.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Документы на лес ФГИС ЛК под ключ</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Заготовили лес и не хотите тонуть в ФГИС ЛК - ведём документы за вас под ключ. Ставим объём на учёт, оформляем ЭСД и QR на перевозку, проводим сделку.&lt;/p&gt;&lt;p&gt;Можно разово под конкретную задачу или взять ваш аккаунт на постоянное сопровождение. Данные проверяем, чтобы не было отказов и штрафов.&lt;/p&gt;&lt;p&gt;Свой кабинет и электронная подпись вам не нужны, всё делаем сами. От вас исходники по лесу и отгрузкам.&lt;/p&gt;&lt;p&gt;Пакет от 3000 рублей, точная цена по объёму работ. Напишите, что у вас с лесом и документами, разложу по шагам.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Республика Башкортостан, Уфа, ул. Мира, 14</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Услуги посредников</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Консультации</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Удалённо</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>2026-09-08T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
         <is>
           <t>2026-08-09T09:00:00+03:00</t>
         </is>
@@ -3699,7 +3459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="25"/>
@@ -4655,7 +4415,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2495576390</t>
+          <t>8130514027</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4670,7 +4430,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2495576390/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2495576390/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2495576390/08_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/10_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/10_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/10_03.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4683,22 +4443,24 @@
           <t>Предложение услуг</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>400</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Берёза кругляк (поставить лес на баланс)</t>
+          <t>ЭСД и QR код на лес через ФГИС ЛК</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сразу по делу: мы оформляем документы на лес в ФГИС ЛК, сам лес не продаём. Если у вас есть берёза, кругляк, пиловочник, балансы или дрова, а бумаг на них нет, приходите, всё сделаем по закону.&lt;br&gt;&lt;br&gt;Что закрываем: QR-код и ЭСД на перевозку, чтобы лесовоз шёл с документами. Расхождения по объёмам и кубам приводим в порядок. Замеры с деляны сверим и пересчитаем.&lt;br&gt;&lt;br&gt;Отдельно про баланс. Лес заготовлен, а в системе его нет: ставим древесину на баланс компании через договор и закрепляем объём в ФГИС ЛК. После этого можно законно возить и продавать.&lt;br&gt;&lt;br&gt;Работаем из Ярославля, консультируем по всем вопросам. Напишите в сообщения, отвечу за пару минут. Пришлите замеры, посчитаю сегодня.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем ЭСД и QR код на перевозку леса через ФГИС ЛК. Коротко: машина под погрузкой, а документа на рейс нет - мы его выпускаем, и водитель едет.&lt;/p&gt;&lt;p&gt;Что делаем: ЭСД и QR на каждую машину, проверяем объём и породу до отгрузки, чтобы на посту не завернули.&lt;/p&gt;&lt;p&gt;Всё с нашей стороны. Свой кабинет в системе, декларация, электронная подпись - ничего заводить не нужно. Работаем и когда своих остатков в системе пока нет.&lt;/p&gt;&lt;p&gt;От 500 рублей за рейс, объём считаем отдельно. Напишите маршрут и кубатуру, скажу срок сегодня.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ярославская область, Ярославль, ул. Транспортная, 61</t>
+          <t>Пермский край, Пермь, ул. Ленина, 50</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4775,19 +4537,19 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-22T04:30:00+03:00</t>
+          <t>2026-09-08T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-07-23T06:30:00+03:00</t>
+          <t>2026-08-09T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8857956292</t>
+          <t>3415388891</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4802,7 +4564,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8857956292/18_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8857956292/18_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8857956292/18_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/13_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4816,21 +4578,21 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Ель кругляк (документы ФГИС ЛК удалённо)</t>
+          <t>Лесная декларация и отчётность по лесу</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на лес в ФГИС ЛК удалённо, сам лес мы не продаём. Если у вас заготовлена ель, кругляк, пиловочник или балансы, а в системе леса нет или бумаги не в порядке, ведём всю документацию за вас.&lt;br&gt;&lt;br&gt;Ставим древесину на баланс компании через договор и закрепляем объём в ФГИС ЛК, чтобы можно было законно возить и продавать. Делаем QR-код и ЭСД на перевозку, закрываем расхождения по кубам, готовим декларации, отчёты и сопроводительные.&lt;br&gt;&lt;br&gt;Работаем по Микуни и всему району, без ваших поездок в кабинет. Достаточно прислать фото замеров с деляны.&lt;br&gt;&lt;br&gt;Напишите в сообщения, что нужно закрыть по бумагам, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Готовим лесную декларацию и отчётность по использованию лесов. Услуга для арендаторов и заготовителей.&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- лесная декларация на период&lt;br&gt;- отчёт 1-ИЛ по фактической заготовке&lt;br&gt;- сверка заявленного с фактическим до подачи&lt;br&gt;- учёт мест складирования&lt;/p&gt;&lt;p&gt;Работаем по срокам, а не в последний день. Если период заканчивается, скажите сразу.&lt;/p&gt;&lt;p&gt;Кемеровская область.&lt;/p&gt;&lt;p&gt;Напишите участок и период.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Республика Коми, Микунь, ул. Транспортная, 41</t>
+          <t>Мариинск, Кемеровская обл., ул. Ленина, 41</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4907,19 +4669,19 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-24T04:30:00+03:00</t>
+          <t>2026-09-12T14:00:00+03:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-07-25T06:30:00+03:00</t>
+          <t>2026-08-13T16:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1505263438</t>
+          <t>2403782347</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4934,7 +4696,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1505263438/22_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1505263438/22_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1505263438/22_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/3_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4948,21 +4710,21 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Берёза кругляк (закрытие расхождений ФГИС)</t>
+          <t>Сопровождение сделок с древесиной</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на лес в ФГИС ЛК. Сам лес мы не продаём и не покупаем, работаем только по бумагам. Если у вас есть берёза, кругляк, пиловочник, балансы или дрова, а документов на них нет или они не сходятся, приводим всё в порядок официально.&lt;br&gt;&lt;br&gt;Делаем QR-код и ЭСД на перевозку, ставим лес на баланс, закрываем расхождения объёмов. Когда по системе один объём, а на деляне или складе по факту другой, сводим цифры через договор купли-продажи, чтобы вывозка лесовозом шла чисто и без вопросов.&lt;br&gt;&lt;br&gt;Работаем по всей Чувашии, база в Чебоксарах. Ведём декларации и отчётность, если своими силами разбираться некогда.&lt;br&gt;&lt;br&gt;Пришлите замеры по кубам, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Ведём документальную часть сделок с древесиной. Услуга от подготовки до закрытия периода.&lt;/p&gt;&lt;p&gt;Что берём:&lt;br&gt;- проверку, что объём на учёте и его хватает под сделку&lt;br&gt;- декларацию о сделке&lt;br&gt;- ЭСД и QR на все отгрузки по сделке&lt;br&gt;- контроль, что отгруженное сошлось с заявленным&lt;br&gt;- отчёт 1-ИЛ по итогам&lt;/p&gt;&lt;p&gt;Нужно, когда сделка крупная и разбита на много рейсов. Там легче всего потерять объём между документами.&lt;/p&gt;&lt;p&gt;Пермский край.&lt;/p&gt;&lt;p&gt;Напишите объём сделки и число отгрузок.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Чувашская Республика, Чебоксары, ул. Заводская, 69</t>
+          <t>Кудымкар, Пермский край, ул. 50 лет Октября, 12</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5039,19 +4801,19 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-24T11:30:00+03:00</t>
+          <t>2026-09-13T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-07-25T13:30:00+03:00</t>
+          <t>2026-08-14T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8130514027</t>
+          <t>6132305285</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5066,7 +4828,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/10_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/10_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/10_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/5_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5079,24 +4841,22 @@
           <t>Предложение услуг</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="I12" t="n">
+        <v>900</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ЭСД и QR код на лес через ФГИС ЛК</t>
+          <t>Сопровождение ФГИС ЛК для лесозаготовителя</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем ЭСД и QR код на перевозку леса через ФГИС ЛК. Коротко: машина под погрузкой, а документа на рейс нет - мы его выпускаем, и водитель едет.&lt;/p&gt;&lt;p&gt;Что делаем: ЭСД и QR на каждую машину, проверяем объём и породу до отгрузки, чтобы на посту не завернули.&lt;/p&gt;&lt;p&gt;Всё с нашей стороны. Свой кабинет в системе, декларация, электронная подпись - ничего заводить не нужно. Работаем и когда своих остатков в системе пока нет.&lt;/p&gt;&lt;p&gt;От 500 рублей за рейс, объём считаем отдельно. Напишите маршрут и кубатуру, скажу срок сегодня.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Ведём документооборот по древесине для лесозаготовителей. Услуга на постоянной основе.&lt;/p&gt;&lt;p&gt;Что закрываем:&lt;br&gt;- постановку объёмов на учёт&lt;br&gt;- ЭСД и QR на отгрузки, в том числе потоком&lt;br&gt;- декларации о сделках&lt;br&gt;- отчёт 1-ИЛ и лесную декларацию&lt;br&gt;- места складирования&lt;/p&gt;&lt;p&gt;Вы отгружаете, мы ведём бумаги. Кабинетов, подписей и обученных людей с вашей стороны не нужно.&lt;/p&gt;&lt;p&gt;Считаем помесячно. При регулярных отгрузках дешевле, чем держать своего специалиста.&lt;/p&gt;&lt;p&gt;Иркутская область.&lt;/p&gt;&lt;p&gt;Напишите объёмы и частоту отгрузок.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Пермский край, Пермь, ул. Ленина, 50</t>
+          <t>Усть-Кут, Иркутская обл., ул. Кирова, 18</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5173,19 +4933,19 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-08T05:00:00+03:00</t>
+          <t>2026-09-13T12:00:00+03:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-09T07:00:00+03:00</t>
+          <t>2026-08-14T14:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3415388891</t>
+          <t>6104679278</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5200,7 +4960,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/13_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__3.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5214,21 +4974,21 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>550</v>
+        <v>1100</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Лесная декларация и отчётность по лесу</t>
+          <t>Учёт древесины в ФГИС ЛК для делянки</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Готовим лесную декларацию и отчётность по использованию лесов. Услуга для арендаторов и заготовителей.&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- лесная декларация на период&lt;br&gt;- отчёт 1-ИЛ по фактической заготовке&lt;br&gt;- сверка заявленного с фактическим до подачи&lt;br&gt;- учёт мест складирования&lt;/p&gt;&lt;p&gt;Работаем по срокам, а не в последний день. Если период заканчивается, скажите сразу.&lt;/p&gt;&lt;p&gt;Кемеровская область.&lt;/p&gt;&lt;p&gt;Напишите участок и период.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Ведём учёт древесины для тех, кто заготавливает сам. Услуга от делянки до отгрузки.&lt;/p&gt;&lt;p&gt;Порядок: ставим заготовленный объём на учёт, привязываем места складирования, дальше каждая отгрузка уходит с ЭСД и QR, сделки закрываются декларациями, период закрывается отчётом 1-ИЛ.&lt;/p&gt;&lt;p&gt;Отдельно сверяем три числа: заготовлено, отгружено, числится в системе. Они должны совпадать.&lt;/p&gt;&lt;p&gt;Красноярский край.&lt;/p&gt;&lt;p&gt;Напишите объёмы заготовки.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Мариинск, Кемеровская обл., ул. Ленина, 41</t>
+          <t>Ачинск, Красноярский край, ул. Назарова, 16</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5305,19 +5065,19 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-12T14:00:00+03:00</t>
+          <t>2026-09-14T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-13T16:00:00+03:00</t>
+          <t>2026-08-15T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2403782347</t>
+          <t>2592034142</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5325,6 +5085,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8263200386</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -5332,7 +5097,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/3_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/17_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5346,21 +5111,21 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>700</v>
+        <v>1300</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Сопровождение сделок с древесиной</t>
+          <t>Документы на древесину удалённо, ФГИС ЛК</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Ведём документальную часть сделок с древесиной. Услуга от подготовки до закрытия периода.&lt;/p&gt;&lt;p&gt;Что берём:&lt;br&gt;- проверку, что объём на учёте и его хватает под сделку&lt;br&gt;- декларацию о сделке&lt;br&gt;- ЭСД и QR на все отгрузки по сделке&lt;br&gt;- контроль, что отгруженное сошлось с заявленным&lt;br&gt;- отчёт 1-ИЛ по итогам&lt;/p&gt;&lt;p&gt;Нужно, когда сделка крупная и разбита на много рейсов. Там легче всего потерять объём между документами.&lt;/p&gt;&lt;p&gt;Пермский край.&lt;/p&gt;&lt;p&gt;Напишите объём сделки и число отгрузок.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на древесину дистанционно. Услуга без личных встреч, всё в электронном виде.&lt;/p&gt;&lt;p&gt;Закрываем: постановку объёмов на учёт, ЭСД и QR на рейсы, декларации о сделках, отчёт 1-ИЛ, лесную декларацию, места складирования.&lt;/p&gt;&lt;p&gt;Как начинаем: описываете ситуацию, мы уточняем детали и называем, что нужно оформить, за какой срок и сколько стоит. Потом беремся.&lt;/p&gt;&lt;p&gt;Свердловская область.&lt;/p&gt;&lt;p&gt;Напишите, что за задача.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Кудымкар, Пермский край, ул. 50 лет Октября, 12</t>
+          <t>Серов, Свердловская обл., ул. Ленина, 128</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -5437,19 +5202,19 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-13T05:00:00+03:00</t>
+          <t>2026-09-19T14:23:00+03:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-14T07:00:00+03:00</t>
+          <t>2026-08-15T14:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6132305285</t>
+          <t>1444249205</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5464,7 +5229,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/5_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real1_1__image2.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -5478,21 +5243,21 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Сопровождение ФГИС ЛК для лесозаготовителя</t>
+          <t>Ведение учёта древесины в ФГИС ЛК</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Ведём документооборот по древесине для лесозаготовителей. Услуга на постоянной основе.&lt;/p&gt;&lt;p&gt;Что закрываем:&lt;br&gt;- постановку объёмов на учёт&lt;br&gt;- ЭСД и QR на отгрузки, в том числе потоком&lt;br&gt;- декларации о сделках&lt;br&gt;- отчёт 1-ИЛ и лесную декларацию&lt;br&gt;- места складирования&lt;/p&gt;&lt;p&gt;Вы отгружаете, мы ведём бумаги. Кабинетов, подписей и обученных людей с вашей стороны не нужно.&lt;/p&gt;&lt;p&gt;Считаем помесячно. При регулярных отгрузках дешевле, чем держать своего специалиста.&lt;/p&gt;&lt;p&gt;Иркутская область.&lt;/p&gt;&lt;p&gt;Напишите объёмы и частоту отгрузок.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Ведём учёт древесины в ФГИС ЛК как внешний исполнитель. Услуга по подписке.&lt;/p&gt;&lt;p&gt;Ежедневно: ЭСД на рейсы, QR коды, контроль остатков по складам.&lt;br&gt;Периодически: декларации о сделках, отчёт 1-ИЛ, сверка объёмов.&lt;br&gt;Разово: постановка на учёт, разбор расхождений с фактом.&lt;/p&gt;&lt;p&gt;Ставка зависит от числа отгрузок в месяц.&lt;/p&gt;&lt;p&gt;Марий Эл.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в месяц.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Усть-Кут, Иркутская обл., ул. Кирова, 18</t>
+          <t>Йошкар-Ола, Республика Марий Эл, ул. Волкова, 60</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -5569,19 +5334,19 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-13T12:00:00+03:00</t>
+          <t>2026-09-15T03:00:00+03:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-14T14:00:00+03:00</t>
+          <t>2026-08-16T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6104679278</t>
+          <t>2893712453</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5596,7 +5361,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__image3.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -5610,21 +5375,21 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Учёт древесины в ФГИС ЛК для делянки</t>
+          <t>Места складирования древесины, МСД и учёт</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Ведём учёт древесины для тех, кто заготавливает сам. Услуга от делянки до отгрузки.&lt;/p&gt;&lt;p&gt;Порядок: ставим заготовленный объём на учёт, привязываем места складирования, дальше каждая отгрузка уходит с ЭСД и QR, сделки закрываются декларациями, период закрывается отчётом 1-ИЛ.&lt;/p&gt;&lt;p&gt;Отдельно сверяем три числа: заготовлено, отгружено, числится в системе. Они должны совпадать.&lt;/p&gt;&lt;p&gt;Красноярский край.&lt;/p&gt;&lt;p&gt;Напишите объёмы заготовки.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Ставим на учёт места складирования древесины и ведём остатки. Услуга по складу.&lt;/p&gt;&lt;p&gt;Если древесина где-то лежит, место должно быть заведено в системе, а объём биться с фактом. Иначе отгрузка со склада встанет.&lt;/p&gt;&lt;p&gt;Что делаем: заводим места складирования, ставим объёмы на учёт, ведём приход и расход, оформляем ЭСД на отгрузки, закрываем отчётность.&lt;/p&gt;&lt;p&gt;Отдельно приводим в порядок склады, где остаток давно разошёлся с реальным.&lt;/p&gt;&lt;p&gt;Татарстан.&lt;/p&gt;&lt;p&gt;Напишите число площадок и объёмы.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ачинск, Красноярский край, ул. Назарова, 16</t>
+          <t>Агрыз, Республика Татарстан, ул. Гагарина, 15</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -5701,19 +5466,19 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-14T10:00:00+03:00</t>
+          <t>2026-09-15T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-15T12:00:00+03:00</t>
+          <t>2026-08-16T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2592034142</t>
+          <t>9984019968</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5721,6 +5486,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8263009754</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -5728,7 +5498,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/17_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/16_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5742,21 +5512,21 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1300</v>
+        <v>700</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Документы на древесину удалённо, ФГИС ЛК</t>
+          <t>ЭСД на древесину, оформление за 15 минут</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на древесину дистанционно. Услуга без личных встреч, всё в электронном виде.&lt;/p&gt;&lt;p&gt;Закрываем: постановку объёмов на учёт, ЭСД и QR на рейсы, декларации о сделках, отчёт 1-ИЛ, лесную декларацию, места складирования.&lt;/p&gt;&lt;p&gt;Как начинаем: описываете ситуацию, мы уточняем детали и называем, что нужно оформить, за какой срок и сколько стоит. Потом беремся.&lt;/p&gt;&lt;p&gt;Свердловская область.&lt;/p&gt;&lt;p&gt;Напишите, что за задача.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем сопроводительные документы на перевозку древесины. Это наша услуга.&lt;/p&gt;&lt;p&gt;Кому нужно:&lt;br&gt;- перевозчику, чтобы рейс не встал на посту&lt;br&gt;- продавцу, чтобы отгрузка была законной&lt;br&gt;- покупателю, чтобы принять объём без вопросов&lt;/p&gt;&lt;p&gt;Что входит: ЭСД с QR, декларация о сделке, постановка на учёт, отчёт 1-ИЛ, места складирования.&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Челябинская область и Урал.&lt;/p&gt;&lt;p&gt;Напишите маршрут и объём.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Серов, Свердловская обл., ул. Ленина, 128</t>
+          <t>Миасс, Челябинская обл., пр-т Автозаводцев, 12</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -5833,19 +5603,19 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-14T12:00:00+03:00</t>
+          <t>2026-09-18T15:25:00+03:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-15T14:00:00+03:00</t>
+          <t>2026-08-16T14:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1444249205</t>
+          <t>2886065351</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5860,7 +5630,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real1_1__image2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_11__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5874,21 +5644,21 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Ведение учёта древесины в ФГИС ЛК</t>
+          <t>Оформление документов на лес ФГИС ЛК</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Ведём учёт древесины в ФГИС ЛК как внешний исполнитель. Услуга по подписке.&lt;/p&gt;&lt;p&gt;Ежедневно: ЭСД на рейсы, QR коды, контроль остатков по складам.&lt;br&gt;Периодически: декларации о сделках, отчёт 1-ИЛ, сверка объёмов.&lt;br&gt;Разово: постановка на учёт, разбор расхождений с фактом.&lt;/p&gt;&lt;p&gt;Ставка зависит от числа отгрузок в месяц.&lt;/p&gt;&lt;p&gt;Марий Эл.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в месяц.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на лес в ФГИС ЛК. Полный пакет, одна услуга, один исполнитель.&lt;/p&gt;&lt;p&gt;В пакет входит:&lt;br&gt;- ЭСД на каждый рейс с QR кодом&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- отчёт 1-ИЛ и места складирования&lt;/p&gt;&lt;p&gt;Работаем от одной машины. Выручаем, когда покупатель ждёт, а оформлять некому.&lt;/p&gt;&lt;p&gt;Чувашия.&lt;/p&gt;&lt;p&gt;Напишите, что нужно и к какому сроку.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Йошкар-Ола, Республика Марий Эл, ул. Волкова, 60</t>
+          <t>Шумерля, Чувашская Республика, ул. Ленина, 22</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -5965,19 +5735,19 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-15T03:00:00+03:00</t>
+          <t>2026-09-16T03:00:00+03:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-16T05:00:00+03:00</t>
+          <t>2026-08-17T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2893712453</t>
+          <t>4413366036</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5985,6 +5755,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>8263595288</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -5992,7 +5767,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__image3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6006,21 +5781,21 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>550</v>
+        <v>1100</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Места складирования древесины, МСД и учёт</t>
+          <t>QR код на перевозку леса, оформим сегодня</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Ставим на учёт места складирования древесины и ведём остатки. Услуга по складу.&lt;/p&gt;&lt;p&gt;Если древесина где-то лежит, место должно быть заведено в системе, а объём биться с фактом. Иначе отгрузка со склада встанет.&lt;/p&gt;&lt;p&gt;Что делаем: заводим места складирования, ставим объёмы на учёт, ведём приход и расход, оформляем ЭСД на отгрузки, закрываем отчётность.&lt;/p&gt;&lt;p&gt;Отдельно приводим в порядок склады, где остаток давно разошёлся с реальным.&lt;/p&gt;&lt;p&gt;Татарстан.&lt;/p&gt;&lt;p&gt;Напишите число площадок и объёмы.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем QR код и ЭСД на перевозку леса. Услуга, делаем в день обращения.&lt;/p&gt;&lt;p&gt;От вас: порода, объём, маршрут, реквизиты сторон, номер машины.&lt;br&gt;Водителю: документ с QR кодом в электронном виде. На посту сканируют и пропускают.&lt;/p&gt;&lt;p&gt;Если объёма нет в системе, сначала ставим на учёт, иначе документ выписывать не на что.&lt;/p&gt;&lt;p&gt;Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите маршрут и объём.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Агрыз, Республика Татарстан, ул. Гагарина, 15</t>
+          <t>Шахунья, Нижегородская обл., ул. Советская, 14</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -6097,19 +5872,19 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-15T05:00:00+03:00</t>
+          <t>2026-09-19T08:12:00+03:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-16T07:00:00+03:00</t>
+          <t>2026-08-17T16:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9984019968</t>
+          <t>2640679107</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6117,6 +5892,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8263322631</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -6124,7 +5904,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/16_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/13_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6138,21 +5918,21 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>700</v>
+        <v>1300</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ЭСД на древесину, оформление за 15 минут</t>
+          <t>Документы на лес ФГИС ЛК под ключ</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем сопроводительные документы на перевозку древесины. Это наша услуга.&lt;/p&gt;&lt;p&gt;Кому нужно:&lt;br&gt;- перевозчику, чтобы рейс не встал на посту&lt;br&gt;- продавцу, чтобы отгрузка была законной&lt;br&gt;- покупателю, чтобы принять объём без вопросов&lt;/p&gt;&lt;p&gt;Что входит: ЭСД с QR, декларация о сделке, постановка на учёт, отчёт 1-ИЛ, места складирования.&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Челябинская область и Урал.&lt;/p&gt;&lt;p&gt;Напишите маршрут и объём.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на древесину в ФГИС ЛК. Услуга: вы отгружаете лес, мы делаем бумаги.&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- ЭСД на рейс с QR кодом для поста&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- отчёт 1-ИЛ, места складирования&lt;/p&gt;&lt;p&gt;От вас: порода, объём, маршрут, реквизиты сторон.&lt;br&gt;От нас: готовый документ водителю до выезда.&lt;/p&gt;&lt;p&gt;ЭСД: 15 минут. Постановка на учёт: срок называем после разбора ситуации.&lt;/p&gt;&lt;p&gt;Кабинет в системе и электронная подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Башкортостан и Приуралье. ИП и ООО.&lt;/p&gt;&lt;p&gt;Напишите объём и маршрут.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Миасс, Челябинская обл., пр-т Автозаводцев, 12</t>
+          <t>Кумертау, Республика Башкортостан, ул. Ленина, 14</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -6229,19 +6009,19 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-15T12:00:00+03:00</t>
+          <t>2026-09-27T09:36:00+03:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-16T14:00:00+03:00</t>
+          <t>2026-08-17T17:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2886065351</t>
+          <t>5708843369</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6249,6 +6029,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8263354624</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -6256,7 +6041,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_11__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/3_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6270,21 +6055,21 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Оформление документов на лес ФГИС ЛК</t>
+          <t>Декларация о сделке с древесиной</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на лес в ФГИС ЛК. Полный пакет, одна услуга, один исполнитель.&lt;/p&gt;&lt;p&gt;В пакет входит:&lt;br&gt;- ЭСД на каждый рейс с QR кодом&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- отчёт 1-ИЛ и места складирования&lt;/p&gt;&lt;p&gt;Работаем от одной машины. Выручаем, когда покупатель ждёт, а оформлять некому.&lt;/p&gt;&lt;p&gt;Чувашия.&lt;/p&gt;&lt;p&gt;Напишите, что нужно и к какому сроку.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Готовим и подаём декларацию о сделке с древесиной. Услуга под ключ.&lt;/p&gt;&lt;p&gt;Без декларации сделка не оформлена, отгружать нельзя.&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- составляем декларацию и подаём в систему&lt;br&gt;- сверяем объёмы и сортименты с фактом&lt;br&gt;- оформляем ЭСД и QR по отгрузкам сделки&lt;/p&gt;&lt;p&gt;Работаем с обеими сторонами. Частый случай: покупатель требует декларацию, у продавца нет ни кабинета, ни подписи.&lt;/p&gt;&lt;p&gt;Башкортостан и соседние регионы.&lt;/p&gt;&lt;p&gt;Напишите объём сделки.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Шумерля, Чувашская Республика, ул. Ленина, 22</t>
+          <t>Стерлитамак, Республика Башкортостан, ул. Мира, 18</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -6361,19 +6146,19 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-16T03:00:00+03:00</t>
+          <t>2026-09-17T14:15:00+03:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-17T05:00:00+03:00</t>
+          <t>2026-08-18T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4413366036</t>
+          <t>4860890388</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6381,6 +6166,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>8263235705</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -6388,7 +6178,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/5_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6402,21 +6192,21 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>QR код на перевозку леса, оформим сегодня</t>
+          <t>Отчёт 1-ИЛ и лесная декларация</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем QR код и ЭСД на перевозку леса. Услуга, делаем в день обращения.&lt;/p&gt;&lt;p&gt;От вас: порода, объём, маршрут, реквизиты сторон, номер машины.&lt;br&gt;Водителю: документ с QR кодом в электронном виде. На посту сканируют и пропускают.&lt;/p&gt;&lt;p&gt;Если объёма нет в системе, сначала ставим на учёт, иначе документ выписывать не на что.&lt;/p&gt;&lt;p&gt;Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите маршрут и объём.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Сдаём отчёт 1-ИЛ и лесную декларацию за вас. Услуга по отчётности.&lt;/p&gt;&lt;p&gt;Что входит:&lt;br&gt;- лесная декларация на период&lt;br&gt;- отчёт 1-ИЛ по фактическим объёмам&lt;br&gt;- сверка заявленного с фактом до подачи&lt;br&gt;- учёт мест складирования&lt;/p&gt;&lt;p&gt;Сверяем до подачи. Разойдётся объём, и вопросы будут уже к вам.&lt;/p&gt;&lt;p&gt;Новосибирская область.&lt;/p&gt;&lt;p&gt;Напишите, что и за какой период сдаём.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Шахунья, Нижегородская обл., ул. Советская, 14</t>
+          <t>Куйбышев, Новосибирская обл., ул. Краскома, 24</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -6493,19 +6283,19 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-17T03:00:00+03:00</t>
+          <t>2026-09-18T08:10:00+03:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-17T16:00:00+03:00</t>
+          <t>2026-08-18T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2640679107</t>
+          <t>2623788059</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6513,6 +6303,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8263683111</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -6520,7 +6315,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/13_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6534,21 +6329,21 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1300</v>
+        <v>700</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Документы на лес ФГИС ЛК под ключ</t>
+          <t>ЭСД на лесовоз, документы на каждый рейс</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на древесину в ФГИС ЛК. Услуга: вы отгружаете лес, мы делаем бумаги.&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- ЭСД на рейс с QR кодом для поста&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- отчёт 1-ИЛ, места складирования&lt;/p&gt;&lt;p&gt;От вас: порода, объём, маршрут, реквизиты сторон.&lt;br&gt;От нас: готовый документ водителю до выезда.&lt;/p&gt;&lt;p&gt;ЭСД: 15 минут. Постановка на учёт: срок называем после разбора ситуации.&lt;/p&gt;&lt;p&gt;Кабинет в системе и электронная подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Башкортостан и Приуралье. ИП и ООО.&lt;/p&gt;&lt;p&gt;Напишите объём и маршрут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем ЭСД на рейсы лесовозов. Услуга для перевозчиков и заготовителей с постоянными отгрузками.&lt;/p&gt;&lt;p&gt;Как на потоке: утром присылаете список машин на день, к выезду каждый водитель получает свой ЭСД с QR кодом. Рейсы не стоят.&lt;/p&gt;&lt;p&gt;Дополнительно: декларации по сделкам, отчёт 1-ИЛ, остатки по складам.&lt;/p&gt;&lt;p&gt;При постоянном объёме считаем помесячно, выходит дешевле поштучного оформления.&lt;/p&gt;&lt;p&gt;Смоленская область.&lt;/p&gt;&lt;p&gt;Напишите число рейсов в неделю.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Кумертау, Республика Башкортостан, ул. Ленина, 14</t>
+          <t>Рославль, Смоленская обл., ул. Пролетарская, 68</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -6625,19 +6420,19 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-09-17T05:00:00+03:00</t>
+          <t>2026-09-30T09:41:00+03:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-17T17:30:00+03:00</t>
+          <t>2026-08-18T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5708843369</t>
+          <t>9660447079</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6645,6 +6440,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8263644801</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -6652,7 +6452,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/3_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/17_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6666,21 +6466,21 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Декларация о сделке с древесиной</t>
+          <t>Документы на лес для ИП и ООО</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Готовим и подаём декларацию о сделке с древесиной. Услуга под ключ.&lt;/p&gt;&lt;p&gt;Без декларации сделка не оформлена, отгружать нельзя.&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- составляем декларацию и подаём в систему&lt;br&gt;- сверяем объёмы и сортименты с фактом&lt;br&gt;- оформляем ЭСД и QR по отгрузкам сделки&lt;/p&gt;&lt;p&gt;Работаем с обеими сторонами. Частый случай: покупатель требует декларацию, у продавца нет ни кабинета, ни подписи.&lt;/p&gt;&lt;p&gt;Башкортостан и соседние регионы.&lt;/p&gt;&lt;p&gt;Напишите объём сделки.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Оформляем документы на древесину для ИП и ООО. Услуга разово и на постоянной основе.&lt;/p&gt;&lt;p&gt;Что чаще всего нужно:&lt;br&gt;- ЭСД и QR коды на отгрузки&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- отчёт 1-ИЛ и лесная декларация&lt;br&gt;- места складирования&lt;/p&gt;&lt;p&gt;Отдельно помогаем тем, кто начинает работать с лесом и не знает, какие документы нужны. Объясним порядок и сделаем первый комплект.&lt;/p&gt;&lt;p&gt;Курганская область.&lt;/p&gt;&lt;p&gt;Напишите задачу и объём.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Стерлитамак, Республика Башкортостан, ул. Мира, 18</t>
+          <t>Шадринск, Курганская обл., ул. Октябрьская, 90</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -6757,540 +6557,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-17T10:00:00+03:00</t>
+          <t>2026-09-20T14:00:00+03:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-18T05:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>4860890388</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/5_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>550</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Отчёт 1-ИЛ и лесная декларация</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Сдаём отчёт 1-ИЛ и лесную декларацию за вас. Услуга по отчётности.&lt;/p&gt;&lt;p&gt;Что входит:&lt;br&gt;- лесная декларация на период&lt;br&gt;- отчёт 1-ИЛ по фактическим объёмам&lt;br&gt;- сверка заявленного с фактом до подачи&lt;br&gt;- учёт мест складирования&lt;/p&gt;&lt;p&gt;Сверяем до подачи. Разойдётся объём, и вопросы будут уже к вам.&lt;/p&gt;&lt;p&gt;Новосибирская область.&lt;/p&gt;&lt;p&gt;Напишите, что и за какой период сдаём.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Куйбышев, Новосибирская обл., ул. Краскома, 24</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Деловые услуги</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Консультирование</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Удалённо</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
-Своя услуга|Отгрузка фгис лес|300|Да|за услугу
-Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-09-17T12:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2026-08-18T07:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2623788059</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>700</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ЭСД на лесовоз, документы на каждый рейс</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Оформляем ЭСД на рейсы лесовозов. Услуга для перевозчиков и заготовителей с постоянными отгрузками.&lt;/p&gt;&lt;p&gt;Как на потоке: утром присылаете список машин на день, к выезду каждый водитель получает свой ЭСД с QR кодом. Рейсы не стоят.&lt;/p&gt;&lt;p&gt;Дополнительно: декларации по сделкам, отчёт 1-ИЛ, остатки по складам.&lt;/p&gt;&lt;p&gt;При постоянном объёме считаем помесячно, выходит дешевле поштучного оформления.&lt;/p&gt;&lt;p&gt;Смоленская область.&lt;/p&gt;&lt;p&gt;Напишите число рейсов в неделю.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Рославль, Смоленская обл., ул. Пролетарская, 68</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Деловые услуги</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Консультирование</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Удалённо</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
-Своя услуга|Отгрузка фгис лес|300|Да|за услугу
-Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2026-08-18T09:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>9660447079</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/17_doc__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>900</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Документы на лес для ИП и ООО</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Оформляем документы на древесину для ИП и ООО. Услуга разово и на постоянной основе.&lt;/p&gt;&lt;p&gt;Что чаще всего нужно:&lt;br&gt;- ЭСД и QR коды на отгрузки&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- отчёт 1-ИЛ и лесная декларация&lt;br&gt;- места складирования&lt;/p&gt;&lt;p&gt;Отдельно помогаем тем, кто начинает работать с лесом и не знает, какие документы нужны. Объясним порядок и сделаем первый комплект.&lt;/p&gt;&lt;p&gt;Курганская область.&lt;/p&gt;&lt;p&gt;Напишите задачу и объём.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Шадринск, Курганская обл., ул. Октябрьская, 90</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Деловые услуги</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Консультирование</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Удалённо</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
-Своя услуга|Отгрузка фгис лес|300|Да|за услугу
-Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-09-18T05:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
           <t>2026-08-18T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>8254940849</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real1_1__image2.jpg</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1100</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Поставить лес на учёт в ФГИС ЛК</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Ставим заготовленную древесину на учёт в ФГИС ЛК. Это услуга, лес не продаём.&lt;/p&gt;&lt;p&gt;Проблема: лес заготовлен, покупатель есть, а в системе объёма нет. Отгрузить нельзя.&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- разбираем происхождение партии, подбираем основание&lt;br&gt;- заводим объём в систему&lt;br&gt;- дальше ведём отгрузки: ЭСД, QR, декларация&lt;/p&gt;&lt;p&gt;Срок зависит от исходных документов: от двух дней до недели. Называем до начала работы.&lt;/p&gt;&lt;p&gt;Тюменская область и юг Западной Сибири.&lt;/p&gt;&lt;p&gt;Опишите ситуацию.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Ишим, Тюменская обл., ул. Республики, 42</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Деловые услуги</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Консультирование</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Другое</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>4–7 лет</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Удалённо</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
-Своя услуга|Отгрузка фгис лес|300|Да|за услугу
-Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2026-09-18T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2026-08-18T14:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -9405,7 +8677,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5937878704</t>
+          <t>2671009093</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9420,17 +8692,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (QR код и ЭСД на перевозку)</t>
+          <t>Лес с делянки бумаг нет(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Раньше система звалась ЛесЕГАИС, суть та же. Если у вас есть сосна, кругляк, пиловочник или балансы с деляны, а бумаг на них нет, всё сделаю по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код и ЭСД на перевозку, чтобы лесовоз прошёл лесной контроль без штрафов. Считаю по фото ваших замеров удалённо, вам никуда ехать не надо.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по кубам, ставлю лес на баланс, готовлю декларации и отчёты. Беломорск и район, объёмы любые.&lt;br&gt;&lt;br&gt;Пришлите замеры с делянки, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>Электронные сопроводительные документы и QR коды на вывоз древесины. Кругляк, пиловочник, баланс.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена, на постах проверяют QR код из ФГИС ЛК. Оформление у нас поставлено на поток.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- документ на каждый рейс при регулярных перевозках&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- отчёт 1-ИЛ, декларация о сделке&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные лесовозной машины, отправителя, получателя и кубатуру, дальше QR код у водителя на экране.&lt;br&gt;&lt;br&gt;Обычно 15 минут.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронная подпись не нужны.&lt;br&gt;&lt;br&gt;Работаем по Красноярскому краю и всей Сибири. Хвойный кругляк с делянки, лиственные породы, древесина оптом, часовой пояс не проблема.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5937878704/01_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_3.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -9445,7 +8717,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Республика Карелия, Беломорск, ул. Лесная, 12</t>
+          <t>Красноярский край, Богучаны, ул. Ленина, 27</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -9454,7 +8726,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -9500,7 +8772,7 @@
         <v>6000</v>
       </c>
       <c r="AC12" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -9514,19 +8786,19 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-08-20T18:00:00+03:00</t>
+          <t>2026-08-30T11:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2026-07-21T20:00:00+03:00</t>
+          <t>2026-08-01T11:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6036836126</t>
+          <t>6664478711</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9541,17 +8813,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Лиственница пиловочник (QR код на вывоз леса)</t>
+          <t>Ель есть документов нет(помощь с учётом леса)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас есть лиственница, кругляк, пиловочник или балансы с деляны, а бумаг на вывозку нет, приведу всё в порядок по закону.&lt;br&gt;&lt;br&gt;Делаю QR-код на вывоз леса, чтобы лесовоз прошёл лесной контроль без штрафов. Считаю по фото ваших замеров удалённо и быстро, вам никуда ехать не надо.&lt;br&gt;&lt;br&gt;Также закрываю расхождения по объёмам, ставлю лес на баланс, готовлю декларации и отчёты. Нижнеудинск и район, объёмы любые.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня. Отвечаю за пару минут.&lt;/p&gt;</t>
+          <t>Учёт древесины и оформление документов в ФГИС ЛК. Кругляк, пиловочник ель и сосна, баланс, дрова.&lt;br&gt;&lt;br&gt;Древесина должна стоять на учёте, иначе её не продать и не вывезти. Ставим объём на баланс, оформляем сопроводительные документы, ведём отчётность.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка объёма древесины на учёт&lt;br&gt;- ЭСД и QR код на транспортировку&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт в местах складирования&lt;br&gt;- сопровождение постоянных отгрузок&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Рутинный ЭСД около 15 минут, задачи по учёту дольше, срок называю до начала работы.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Лесоматериалы круглые, продажа и покупка леса, отгрузка лесовозными машинами.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, отвечу быстро.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/6036836126/02_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_3.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9566,7 +8838,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Иркутская область, Нижнеудинск, ул. Заводская, 19</t>
+          <t>Челябинская область, Сатка, ул. Солнечная, 12</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -9575,7 +8847,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>200</v>
+        <v>550</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -9609,7 +8881,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Лиственница</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -9621,7 +8893,7 @@
         <v>6000</v>
       </c>
       <c r="AC13" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -9635,19 +8907,19 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2026-08-20T19:30:00+03:00</t>
+          <t>2026-08-30T15:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2026-07-21T21:30:00+03:00</t>
+          <t>2026-08-01T15:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3305654333</t>
+          <t>2657040747</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9662,17 +8934,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Берёза пиловочник (не сходятся объёмы ФГИС)</t>
+          <t>Сосна заготовлена бумаг нет(документы фгис лк)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Это услуга по бумагам, а не торговля кругляком.&lt;br&gt;&lt;br&gt;Работаю по Мурашам и району. Если по системе один объём, а на деляне или на складе по факту другой, свожу это официально. Берёза, пиловочник, балансы, дрова, осиновый кругляк, любой сортимент. Замерили лесовоз, а цифры в ФГИС не сходятся, расхождение висит и мешает вывозке, закрою через договор купли-продажи и приведу объём в порядок.&lt;br&gt;&lt;br&gt;Делаю QR и ЭСД на перевозку, ставлю лес на баланс, готовлю декларации и отчёты. Если у вас есть лес, а документов на него нет, оформлю.&lt;br&gt;&lt;br&gt;Пришлите замеры по делянке, посчитаю сегодня и скажу, как свести объёмы. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>Оформление документов на древесину в ФГИС ЛК для заготовителей, продавцов и перевозчиков. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;В работе:&lt;br&gt;- электронный сопроводительный документ на транспортировку древесины&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- лесная декларация, декларация о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования древесины (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Вы присылаете породу, кубатуру, маршрут и данные сторон. Мы оформляем в системе и передаём готовый пакет.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут после получения данных. Учёт и декларация занимают дольше, срок озвучиваю заранее.&lt;br&gt;&lt;br&gt;Свой кабинет, электронная подпись и декларация вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Сосновый пиловочник, лес с делянки, древесина оптом, разовые задачи и постоянное ведение.&lt;br&gt;&lt;br&gt;Напишите кубатуру, скажу срок и порядок.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/3305654333/03_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_3.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9687,7 +8959,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Кировская область, Мураши, ул. Советская, 26</t>
+          <t>Челябинская область, Катав-Ивановск, ул. Ленина, 19</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -9696,7 +8968,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -9730,7 +9002,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -9756,19 +9028,19 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026-08-21T04:30:00+03:00</t>
+          <t>2026-08-30T19:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2026-07-22T06:30:00+03:00</t>
+          <t>2026-08-01T19:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5783794994</t>
+          <t>7029554179</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9783,17 +9055,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (QR код на вывоз леса)</t>
+          <t>Сосна кругляк с делянки(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сразу к делу: мы не продаём лес, мы оформляем на него документы в системе ФГИС ЛК. Если у вас есть кругляк, пиловочник сосны, балансы или дрова с деляны, а бумаг на вывоз нет, мы их сделаем.&lt;br&gt;&lt;br&gt;Готовим QR-код и ЭСД (электронный сопроводительный документ) на перевозку, чтобы лесовоз прошёл лесной контроль и первый же рейс ушёл без штрафов. Работаем удалённо: пришлите фото замеров по кубам, посчитаем объём и оформим сами.&lt;br&gt;&lt;br&gt;Также закрываем расхождения объёмов, ставим лес на баланс, готовим декларации и отчёты. Город Буй, работаем со всеми регионами.&lt;br&gt;&lt;br&gt;Есть делянка, вывозка на носу, а документов нет: напишите в сообщения, отвечу за пару минут. Пришлите замеры сегодня, посчитаю сегодня.&lt;/p&gt;</t>
+          <t>Делаем QR код на вывоз леса и ЭСД через ФГИС ЛК. Машина уже под погрузкой, а документа на рейс нет - обычно решаем в тот же день.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, есть и другой хвойный сортимент.&lt;br&gt;&lt;br&gt;QR код и ЭСД приходят водителю на телефон. Перед этим сверяем объём и породу, чтобы на посту не развернули. Свой кабинет и подпись вам не нужны.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири, разница по времени не мешает. Напишите, что по рейсу, отвечу сразу.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5783794994/06_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_03.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9808,7 +9080,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Костромская область, Буй, ул. Октябрьская, 47</t>
+          <t>Алтайский край, Бийск, ул. Советская, 8</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -9816,8 +9088,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P15" t="n">
-        <v>250</v>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -9863,7 +9137,7 @@
         <v>6000</v>
       </c>
       <c r="AC15" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -9877,19 +9151,19 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2026-08-21T10:00:00+03:00</t>
+          <t>2026-09-06T13:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2026-07-22T12:00:00+03:00</t>
+          <t>2026-08-10T06:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5855275648</t>
+          <t>2323865424</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9904,17 +9178,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Берёза пиловочник (лес на баланс ФГИС)</t>
+          <t>Сосна кругляк под погрузку(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляю документы на лес в ФГИС ЛК, сам лес не продаю. Если у вас на деляне лежит заготовленная берёза, кругляк или пиловочник, а в системе его нет, помогу поставить древесину на баланс. Заключаем договор, закрепляем объём в ФГИС ЛК, и лес становится вашим официально, можно законно возить и продавать.&lt;br&gt;&lt;br&gt;Работаю по Нелидово и району. Балансы, дрова, делянка, вывозка лесовозами, замеры в кубах, любой объём. Сделаю QR и ЭСД на перевозку, закрою расхождение по объёмам, подготовлю декларации и отчёты.&lt;br&gt;&lt;br&gt;Пришлите замеры с делянки, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>Лес есть, а документов нет - обычная история. Оформим QR код на вывоз и ЭСД через ФГИС ЛК, документ придёт водителю на экран перед выездом.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Объём и породу проверяем заранее, чтобы потом не переделывать. Всё оформление на нас, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Кемеровской области и Сибири, часовой пояс не помеха. Напишите объём и куда везёте, отвечу сразу.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_03.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9929,7 +9203,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Тверская область, Нелидово, ул. Промышленная, 13</t>
+          <t>Кемеровская область, Таштагол, ул. Ленина, 22</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -9937,8 +9211,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>250</v>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -9972,7 +9248,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Берёза</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -9984,7 +9260,7 @@
         <v>6000</v>
       </c>
       <c r="AC16" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -9998,19 +9274,19 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026-08-23T06:30:00+03:00</t>
+          <t>2026-09-06T15:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2026-07-24T08:30:00+03:00</t>
+          <t>2026-08-10T08:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7232164186</t>
+          <t>8579049856</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10025,17 +9301,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (ЭСД и QR к сделке)</t>
+          <t>Лиственница кругляк(ЭСД на перевозку)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Сразу главное: сам лес мы не продаём. Мы оформляем документы на лес в системе ФГИС ЛК, работаем из Тихвина удалённо.&lt;br&gt;&lt;br&gt;Если у вас есть сосна, пиловочник, кругляк, балансы или дрова на деляне, а бумаг на них нет, мы всё оформим. Поставим лес на баланс, закроем расхождения по кубам, сделаем декларации и отчёты.&lt;br&gt;&lt;br&gt;Отдельно по вывозке: делаем QR-код и ЭСД к сделке, чтобы лесовоз прошёл лесной контроль без штрафов. Считаем по фото замеров с деляны, ничего никуда везти не нужно.&lt;br&gt;&lt;br&gt;Пришлите замеры в сообщения, посчитаю сегодня и скажу, что нужно для перевозки. Отвечаю за пару минут.&lt;/p&gt;</t>
+          <t>Делаем ЭСД на перевозку леса через ФГИС ЛК. Если возите объёмами, на каждый рейс нужен свой документ - держим это на потоке, чтобы машины не стояли.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см. Есть сосна и ель.&lt;br&gt;&lt;br&gt;Данные проверяем до выпуска, чтобы не было отказа. Оформляем, даже если своей декларации у вас пока нет.&lt;br&gt;&lt;br&gt;Я по Красноярскому краю и Сибири. Напишите объём и маршрут, скажу срок сегодня.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_03.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10050,7 +9326,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Ленинградская область, Тихвин, ул. Гагарина, 48</t>
+          <t>Красноярский край, Богучаны, ул. Октябрьская, 5</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -10058,8 +9334,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P17" t="n">
-        <v>250</v>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -10093,7 +9371,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Лиственница</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -10105,7 +9383,7 @@
         <v>6000</v>
       </c>
       <c r="AC17" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -10119,19 +9397,19 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2026-08-24T06:30:00+03:00</t>
+          <t>2026-09-07T04:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2026-07-25T08:30:00+03:00</t>
+          <t>2026-08-08T06:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2872293673</t>
+          <t>4561483668</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -10146,17 +9424,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (QR код на отгрузку)</t>
+          <t>Ель кругляк с делянки(помощь с учётом)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на лес в системе ФГИС ЛК. Сам лес мы не продаём, делаем только бумаги на него. Если у вас есть своя партия под отгрузку в Галиче, сосна пиловочник, кругляк, балансы или дрова, а документов на неё нет, оформим всё по правилам.&lt;br&gt;&lt;br&gt;Сделаем QR-код и ЭСД на вывозку, чтобы лесовоз с грузом прошёл лесной контроль без штрафов. Закрываем расхождения по кубам, ставим лес на баланс, готовим декларации и отчёты.&lt;br&gt;&lt;br&gt;Считаем по фото ваших замеров, работаем удалённо, деляна может быть где угодно. Напишите в сообщения, отвечу за пару минут. Пришлите замеры с делянки, посчитаю сегодня.&lt;/p&gt;</t>
+          <t>Кто возит лес, тот знает: без учёта в ФГИС ЛК никуда. Поможем с учётом - поставим объём на баланс, оформим ЭСД и QR на рейсы, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, кругляк с делянки, 6 метров, диаметр от 20 см. Любой объём.&lt;br&gt;&lt;br&gt;От вас только данные, остальное на нас. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Челябинской области и Уралу. Напишите породу и кубатуру, подскажу сроки.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_03.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10171,7 +9449,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Костромская область, Галич, ул. Лесная, 62</t>
+          <t>Челябинская область, Сатка, ул. Пролетарская, 12</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -10179,8 +9457,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P18" t="n">
-        <v>200</v>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -10214,7 +9494,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -10240,19 +9520,19 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2026-08-24T10:00:00+03:00</t>
+          <t>2026-09-07T05:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2026-07-25T12:00:00+03:00</t>
+          <t>2026-08-08T07:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6521830331</t>
+          <t>2738165608</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -10267,17 +9547,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Сосна с делянки документов нет(помощь с учётом)</t>
+          <t>Сосна от заготовителя(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Оформление документов на древесину в ФГИС ЛК: кругляк, пиловочник, балансовая древесина, дрова. Работаем с лесозаготовителями, продавцами и покупателями леса.&lt;br&gt;&lt;br&gt;Что оформляем:&lt;br&gt;- электронный сопроводительный документ (ЭСД) на транспортировку древесины&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- постановку объёма на учёт и баланс, если древесина нигде не числится&lt;br&gt;- декларацию о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Присылаете породу, кубатуру, маршрут и данные сторон. Оформляем документ и передаём водителю в электронном виде.&lt;br&gt;&lt;br&gt;Срок по ЭСД обычно 15 минут с момента получения данных. Постановка объёма на учёт занимает дольше, скажу сразу по вашей ситуации.&lt;br&gt;&lt;br&gt;Свой личный кабинет в системе, электронная подпись и лесная декларация вам не нужны, оформление идёт с нашей стороны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Сосна, ель, лиственные породы, любые сортименты и объёмы, от одной лесовозной машины до постоянных отгрузок.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок и срок.</t>
+          <t>Машина готова, лес на месте, а QR кода на вывоз нет. Сделаем QR и ЭСД через ФГИС ЛК на каждую машину, придёт водителю на телефон.&lt;br&gt;&lt;br&gt;Сосновый кругляк напрямую от заготовителя, 6 метров, диаметр от 20 см.&lt;br&gt;&lt;br&gt;Перед отгрузкой сверяем объём и породу. Оформление целиком с нашей стороны, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Башкортостану и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_03.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10292,7 +9572,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Белорецк, ул. Ленина, 24</t>
+          <t>Республика Башкортостан, Сибай, ул. Заводская, 3</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -10300,8 +9580,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P19" t="n">
-        <v>500</v>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -10361,19 +9643,19 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2026-08-27T07:00:00+03:00</t>
+          <t>2026-09-07T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2026-07-29T07:00:00+03:00</t>
+          <t>2026-08-08T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4661388548</t>
+          <t>7680837833</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -10388,17 +9670,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Лес с делянки документов нет(QR код на вывоз леса)</t>
+          <t>Сосна пиловочник с делянки(документы фгис лк)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>QR коды и электронные сопроводительные документы на вывоз древесины через ФГИС ЛК. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена, на постах проверяют QR код с данными рейса. Оформляем его на каждую лесовозную машину.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- сопровождение постоянных перевозок, документ на каждый рейс&lt;br&gt;- постановка древесины на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок работы. От вас данные машины, отправителя и получателя, порода и кубатура в кубометрах. Дальше оформление на нас, QR код приходит водителю на телефон.&lt;br&gt;&lt;br&gt;Обычно занимает 15 минут с момента, когда получили данные.&lt;br&gt;&lt;br&gt;Личный кабинет ФГИС ЛК, электронная подпись и собственная декларация не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и всему Приуралью. Сосновый и еловый пиловочник, лес с делянки, древесина оптом, формат любой.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
+          <t>Кто работает с лесом, тому нужны документы в ФГИС ЛК, а времени на систему нет. Оформим за вас - ЭСД и QR на перевозку, поставим объём на учёт, проведём сделку.&lt;br&gt;&lt;br&gt;Сосновый пиловочник с делянки, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Кабинет и подпись заводить не надо, ведём всё сами.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири. Напишите кубатуру и маршрут, отвечу быстро.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_03.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -10413,7 +9695,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Янаул, ул. Победы, 16</t>
+          <t>Алтайский край, Заринск, ул. Металлургов, 9</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -10421,8 +9703,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P20" t="n">
-        <v>400</v>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -10482,19 +9766,19 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2026-08-27T11:00:00+03:00</t>
+          <t>2026-09-07T08:30:00+03:00</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2026-07-29T11:00:00+03:00</t>
+          <t>2026-08-08T10:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6175129265</t>
+          <t>1951202398</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10509,17 +9793,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Кругляк с делянки бумаг нет(документы фгис лк)</t>
+          <t>Лиственница кругляк с делянки(ЭСД на вывоз)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Полный пакет документов на древесину в ФГИС ЛК для заготовителей, продавцов и перевозчиков леса.&lt;br&gt;&lt;br&gt;В работе:&lt;br&gt;- электронный сопроводительный документ на транспортировку кругляка и пиловочника&lt;br&gt;- QR код на рейс для проверки на посту&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- лесная декларация и декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования древесины&lt;br&gt;&lt;br&gt;Как это работает. Вы присылаете породу, кубатуру, маршрут и реквизиты. Мы оформляем документы в системе и передаём их в готовом виде.&lt;br&gt;&lt;br&gt;ЭСД обычно готов за 15 минут. Постановка объёма на учёт и работа с декларацией занимают дольше, срок называю до начала работы.&lt;br&gt;&lt;br&gt;Заводить свой кабинет и электронную подпись не нужно, оформление ведём со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Хвойный кругляк, лесоматериалы круглые, баланс, любые объёмы с делянки и со склада.&lt;br&gt;&lt;br&gt;Напишите кубатуру и куда везёте, скажу срок.</t>
+          <t>Оформляем ЭСД на вывоз леса через ФГИС ЛК. Лес готов, машина под погрузкой, а документа на рейс нет - выпустим, и водитель едет.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см, плотная древесина.&lt;br&gt;&lt;br&gt;Данные проверяем заранее. Если что-то оформлено с ошибкой, аннулируем и делаем заново по правилам. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Пермскому краю и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_03.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10534,7 +9818,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Дюртюли, ул. Чеверева, 8</t>
+          <t>Пермский край, Чусовой, ул. Ленина, 30</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -10542,8 +9826,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P21" t="n">
-        <v>450</v>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -10577,7 +9863,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Лиственница</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10603,19 +9889,19 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2026-08-27T15:00:00+03:00</t>
+          <t>2026-09-07T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2026-07-29T15:00:00+03:00</t>
+          <t>2026-08-08T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3494661466</t>
+          <t>7192983965</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10630,17 +9916,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Пиловочник от заготовителя(помощь с учётом леса)</t>
+          <t>Ель пиловочник с делянки(помощь с учётом)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Учёт древесины и документы в ФГИС ЛК под ключ. Кругляк, пиловочник сосна и ель, баланс, дрова.&lt;br&gt;&lt;br&gt;Основной запрос: древесина заготовлена, но в системе не отражена, поэтому её нельзя ни продать, ни вывезти. Ставим объём на учёт и дальше ведём документооборот.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка объёма древесины на баланс&lt;br&gt;- ЭСД и QR код на каждую отгрузку лесовозом&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт по местам складирования (МСД)&lt;br&gt;- сопровождение отгрузок на постоянной основе&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и данные сторон. Остальное на нашей стороне.&lt;br&gt;&lt;br&gt;Рутинный ЭСД занимает около 15 минут. Постановка на учёт зависит от ситуации, срок скажу честно до начала.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и Приуралью, берём и разовые задачи, и постоянное ведение по объёмам с лесосеки.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, отвечу быстро.</t>
+          <t>Лес есть, а документов нет, и учёт в ФГИС ЛК висит мёртвым грузом. Разгрузим - поставим объём на баланс, сделаем ЭСД и QR на каждый рейс, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, пиловочник с делянки, 6 метров, диаметр от 20 см. Хвоя.&lt;br&gt;&lt;br&gt;От вас данные, остальное наша забота. Свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Я по Удмуртии и Поволжью. Напишите породу и кубатуру, подскажу сроки.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_03.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10655,7 +9941,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Мелеуз, ул. Ленина, 137</t>
+          <t>Удмуртская Республика, Можга, ул. Наговицына, 7</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -10663,8 +9949,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P22" t="n">
-        <v>500</v>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -10698,7 +9986,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10724,19 +10012,19 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2026-08-27T19:00:00+03:00</t>
+          <t>2026-09-08T03:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2026-07-29T19:00:00+03:00</t>
+          <t>2026-08-09T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2394430844</t>
+          <t>2634568371</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10751,17 +10039,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Лес есть документов нет(QR код на вывоз леса)</t>
+          <t>Лес кругляк ель сосна, ЭСД на отгрузку</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Электронные сопроводительные документы и QR коды на вывоз леса через ФГИС ЛК. Кругляк, пиловочник, лесоматериалы круглые.&lt;br&gt;&lt;br&gt;Без ЭСД перевозка древесины запрещена, на постах смотрят QR код. Оформляем документ на каждый рейс, чтобы машина шла легально.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины&lt;br&gt;- QR код водителю на телефон&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные лесовозной машины, породу, кубатуру и маршрут. Оформляем и отдаём готовый документ.&lt;br&gt;&lt;br&gt;Обычно 15 минут после получения данных.&lt;br&gt;&lt;br&gt;Свой кабинет ФГИС ЛК, электронная подпись и декларация не нужны, работаем со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Алтайскому краю и Сибири. Сосновый и еловый пиловочник, баланс, дрова, древесина оптом, разница во времени не мешает.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
+          <t>Оформляем ЭСД на еловый и сосновый кругляк. Услуга по документам отгрузки.&lt;br&gt;&lt;br&gt;На каждую машину сопроводительный документ с QR кодом, водителю до выезда. Если объём не заведён в системе, сначала ставим на учёт.&lt;br&gt;&lt;br&gt;Закрываем декларацию о сделке и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10776,7 +10064,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Алтайский край, Заринск, ул. Строителей, 21</t>
+          <t>Галич, Костромская обл., ул. Свободы, 11</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10785,7 +10073,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -10845,19 +10133,19 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2026-08-28T07:00:00+03:00</t>
+          <t>2026-09-12T16:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2026-07-30T07:00:00+03:00</t>
+          <t>2026-08-13T18:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3236944872</t>
+          <t>4149246617</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10872,17 +10160,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Сосна есть учёта нет(помощь с учётом леса)</t>
+          <t>Пиловочник сосна, полный пакет документов</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Постановка древесины на учёт и ведение документов в ФГИС ЛК. Работаем с кругляком, пиловочником, балансом и дровами.&lt;br&gt;&lt;br&gt;Если объём не отражён в системе, лес формально не существует: ни продать, ни вывезти его нельзя. Приводим учёт в порядок и дальше сопровождаем отгрузки.&lt;br&gt;&lt;br&gt;Что входит:&lt;br&gt;- постановка объёма древесины на баланс&lt;br&gt;- электронный сопроводительный документ на каждый рейс&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования&lt;br&gt;&lt;br&gt;От вас порода, кубатура в кубометрах, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Сроки честные: ЭСД около 15 минут, работа с учётом дольше, называю срок до начала.&lt;br&gt;&lt;br&gt;Заводить кабинет и электронную подпись не потребуется.&lt;br&gt;&lt;br&gt;Работаем по Алтайскому краю и всей Сибири. Хвойный пиловочник, лес с делянки, любые объёмы под продажу и отгрузку.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок работы.</t>
+          <t>Оформляем полный пакет документов на сосновый пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;В пакет входит: постановка на учёт, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ, места складирования, коды ОКПД2.&lt;br&gt;&lt;br&gt;От вас данные, от нас готовые документы. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Омская область.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -10897,7 +10185,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Алтайский край, Бийск, ул. Советская, 205</t>
+          <t>Тара, Омская обл., ул. Ленина, 9</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -10906,7 +10194,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -10966,19 +10254,19 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>2026-08-28T11:00:00+03:00</t>
+          <t>2026-09-13T03:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2026-07-30T11:00:00+03:00</t>
+          <t>2026-08-14T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2312387978</t>
+          <t>1099424133</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10993,17 +10281,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Кругляк есть документов нет(документы фгис лк)</t>
+          <t>Лес кругляк ель, ЭСД и постановка на учёт</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Документы на древесину в ФГИС ЛК для лесозаготовителей, продавцов и покупателей леса.&lt;br&gt;&lt;br&gt;Оформляем:&lt;br&gt;- электронный сопроводительный документ на транспортировку кругляка&lt;br&gt;- QR код на рейс&lt;br&gt;- постановку объёма на учёт, если древесина не отражена в системе&lt;br&gt;- лесную декларацию и декларацию о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Вы даёте породу, кубатуру, маршрут и данные сторон. Мы оформляем в системе и передаём готовые документы.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут. Задачи по учёту и декларации занимают дольше, срок озвучиваю заранее.&lt;br&gt;&lt;br&gt;Личный кабинет, электронная подпись и своя декларация не нужны.&lt;br&gt;&lt;br&gt;Работаем по Пермскому краю и Приуралью. Пиловочник сосна и ель, балансовая древесина, дрова, отгрузка лесовозом, разовые рейсы и постоянное сопровождение.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу быстро.</t>
+          <t>Оформляем ЭСД на еловый кругляк и ставим объём на учёт. Услуга по документам.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сопроводительный документ выписывать не на что. Поэтому сначала учёт, потом отгрузки.&lt;br&gt;&lt;br&gt;Дальше: ЭСД с QR на каждый рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Нижегородская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -11018,7 +10306,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Пермский край, Чусовой, ул. Ленина, 32</t>
+          <t>Урень, Нижегородская обл., ул. Ленина, 47</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -11027,7 +10315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>450</v>
+        <v>1500</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -11061,7 +10349,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -11087,19 +10375,19 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>2026-08-28T15:00:00+03:00</t>
+          <t>2026-09-13T07:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2026-07-30T15:00:00+03:00</t>
+          <t>2026-08-14T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9553367742</t>
+          <t>1198010038</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11114,17 +10402,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Пиловочник есть учёта нет(помощь с учётом леса)</t>
+          <t>Пиловочник сосна, оформим ЭСД на рейс</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Учёт древесины в ФГИС ЛК и сопровождение отгрузок. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Древесина без учёта в системе не продаётся и не перевозится. Ставим объём на баланс, оформляем документы и дальше ведём отгрузки, чтобы каждый рейс был закрыт.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- постановка объёма древесины на учёт&lt;br&gt;- ЭСД и QR код на транспортировку&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования&lt;br&gt;- постоянное ведение документооборота&lt;br&gt;&lt;br&gt;Нужны порода, кубатура, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Рутинный ЭСД около 15 минут, постановка на учёт дольше, срок называю сразу.&lt;br&gt;&lt;br&gt;Кабинет в системе и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Работаем по Удмуртии и Поволжью. Хвойный кругляк, лесоматериалы, продажа и покупка древесины, от одной машины до постоянного потока.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, скажу срок.</t>
+          <t>Оформляем ЭСД на сосновый пиловочник. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждый рейс: сопроводительный документ с QR кодом, водителю до выезда. Срок 15 минут.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сначала ставим на учёт, потом отгружаете.&lt;br&gt;&lt;br&gt;Ивановская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -11139,7 +10427,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Удмуртская Республика, Глазов, ул. Кирова, 49</t>
+          <t>Юрьевец, Ивановская обл., ул. Советская, 26</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -11148,7 +10436,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>550</v>
+        <v>1800</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -11208,19 +10496,19 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>2026-08-29T07:00:00+03:00</t>
+          <t>2026-09-13T10:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>2026-07-31T07:00:00+03:00</t>
+          <t>2026-08-14T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2285712624</t>
+          <t>3451367236</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11235,17 +10523,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Лес заготовлен бумаг нет(документы фгис лк)</t>
+          <t>Кругляк хвойный, поставим на учёт и вывезем</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Оформление документов на заготовленную древесину в ФГИС ЛК. Кругляк, пиловочник, балансовая древесина.&lt;br&gt;&lt;br&gt;Частая ситуация: лес заготовлен и лежит на делянке, а по документам в системе не проведён. Разбираем и приводим в порядок.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- электронный сопроводительный документ на вывоз&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- лесная декларация, декларация о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования&lt;br&gt;&lt;br&gt;От вас порода, кубатура и данные перевозки.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут после получения данных. Работа с учётом и декларацией занимает дольше, срок скажу до начала.&lt;br&gt;&lt;br&gt;Своя декларация и кабинет в системе не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Удмуртии и соседним регионам. Сосна, ель, лиственные, любые сортименты под продажу и отгрузку лесовозом.&lt;br&gt;&lt;br&gt;Напишите кубатуру, отвечу быстро.</t>
+          <t>Ставим хвойный кругляк на учёт в ФГИС ЛК и оформляем вывоз. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Основная проблема не в лесе, а в бумагах: объём есть, в системе его нет, вывезти нельзя.&lt;br&gt;&lt;br&gt;Ставим на учёт, дальше каждый рейс уходит с ЭСД и QR, сделка закрывается декларацией, период отчётом 1-ИЛ.&lt;br&gt;&lt;br&gt;Владимирская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__3.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -11260,7 +10548,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Удмуртская Республика, Можга, ул. Наговицына, 60</t>
+          <t>Вязники, Владимирская обл., ул. Ленина, 33</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -11269,7 +10557,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -11329,19 +10617,19 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>2026-08-29T11:00:00+03:00</t>
+          <t>2026-09-14T03:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2026-07-31T11:00:00+03:00</t>
+          <t>2026-08-15T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5905323698</t>
+          <t>7655959812</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11356,17 +10644,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Сосна с делянки бумаг нет(QR код на вывоз леса)</t>
+          <t>Лес кругляк сосна, ЭСД на каждый рейс</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>QR коды и электронные сопроводительные документы на древесину. Кругляк, пиловочник сосна и ель, баланс.&lt;br&gt;&lt;br&gt;На постах проверяют QR код ЭСД, без него вывоз леса запрещён. Оформляем документ на каждую лесовозную машину через ФГИС ЛК.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины&lt;br&gt;- QR код водителю в электронном виде&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные машины, отправителя и получателя, породу и кубатуру. Оформление на нас.&lt;br&gt;&lt;br&gt;Обычно 15 минут с момента получения данных.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и Сибири. Лес с делянки и со склада, древесина оптом, часовой пояс не помеха.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
+          <t>Оформляем ЭСД на сосновый кругляк. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждую машину готовим сопроводительный документ с QR кодом. Водитель получает до выезда.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;Алтайский край.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -11381,7 +10669,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Кемеровская область, Таштагол, ул. Ленина, 60</t>
+          <t>Камень-на-Оби, Алтайский край, ул. Ленина, 48</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -11390,7 +10678,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>450</v>
+        <v>2200</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -11450,19 +10738,19 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>2026-08-29T15:00:00+03:00</t>
+          <t>2026-09-14T05:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2026-07-31T15:00:00+03:00</t>
+          <t>2026-08-15T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8540422936</t>
+          <t>4870626062</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11470,6 +10758,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>8262876661</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -11477,17 +10770,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Лес есть учёта нет(помощь с учётом леса)</t>
+          <t>Пиловочник ель сосна, ЭСД и учёт</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Постановка древесины на учёт и документы в ФГИС ЛК. Кругляк, пиловочник, лесоматериалы круглые, дрова.&lt;br&gt;&lt;br&gt;Пока объём не стоит на балансе в системе, лес нельзя ни продать, ни вывезти. Ставим на учёт и дальше ведём документы на отгрузки.&lt;br&gt;&lt;br&gt;Что входит:&lt;br&gt;- постановка объёма древесины на учёт и баланс&lt;br&gt;- ЭСД и QR код на каждый рейс&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и реквизиты.&lt;br&gt;&lt;br&gt;ЭСД около 15 минут, работа с учётом занимает дольше, срок озвучиваю честно.&lt;br&gt;&lt;br&gt;Свой кабинет и электронная подпись не требуются.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и всей Сибири. Хвойный пиловочник, баланс, продажа древесины с лесосеки, разовые и постоянные отгрузки.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу что дальше.</t>
+          <t>Оформляем документы на пиловочник ели и сосны. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Закрываем учёт и сопроводительные документы: постановка объёма на баланс, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут, реквизиты. ЭСД за 15 минут.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -11502,7 +10795,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Кемеровская область, Мыски, ул. Советская, 43</t>
+          <t>Мантурово, Костромская обл., ул. Советская, 22</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -11511,7 +10804,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -11571,19 +10864,19 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>2026-08-29T19:00:00+03:00</t>
+          <t>2026-09-02T13:00:00+03:00</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2026-07-31T19:00:00+03:00</t>
+          <t>2026-08-16T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8088623974</t>
+          <t>7622497474</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11591,6 +10884,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8262890900</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -11598,17 +10896,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Кругляк заготовлен бумаг нет(документы фгис лк)</t>
+          <t>Лес кругляк сосна, документы и ЭСД</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Документы в ФГИС ЛК на заготовленную древесину. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Оформляем:&lt;br&gt;- постановку объёма на учёт&lt;br&gt;- электронный сопроводительный документ на транспортировку&lt;br&gt;- QR код на рейс&lt;br&gt;- лесную декларацию и декларацию о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования&lt;br&gt;&lt;br&gt;Как работаем. От вас порода, кубатура, маршрут и данные сторон. Оформление в системе полностью на нашей стороне, документы приходят готовыми.&lt;br&gt;&lt;br&gt;Срок по ЭСД обычно 15 минут. Постановка на учёт и декларация занимают дольше, называю срок заранее.&lt;br&gt;&lt;br&gt;Заводить кабинет и электронную подпись не нужно.&lt;br&gt;&lt;br&gt;Работаем по Кемеровской области и соседним регионам. Сосновый и еловый кругляк, лесоматериалы, отгрузка лесовозом, любые объёмы.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу быстро.</t>
+          <t>Оформляем документы на сосновый кругляк в ФГИС ЛК. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;В работу входит: ЭСД на рейс, QR код для поста, декларация о сделке, отчёт 1-ИЛ. Если объём не заведён, ставим на учёт.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, маршрут, реквизиты. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Красноярский край, Ангара и Енисей.&lt;br&gt;&lt;br&gt;Напишите, что везёте и куда.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real234__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -11623,7 +10921,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Кемеровская область, Юрга, ул. Машиностроителей, 39</t>
+          <t>Лесосибирск, Красноярский край, ул. Победы, 31</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -11632,7 +10930,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>450</v>
+        <v>3000</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -11692,19 +10990,19 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>2026-08-30T07:00:00+03:00</t>
+          <t>2026-09-03T06:35:00+03:00</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-08-01T07:00:00+03:00</t>
+          <t>2026-08-16T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2671009093</t>
+          <t>4897973128</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11712,6 +11010,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>8263736000</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -11719,17 +11022,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Лес с делянки бумаг нет(QR код на вывоз леса)</t>
+          <t>Пиловочник ель, ЭСД и QR код на вывоз</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Электронные сопроводительные документы и QR коды на вывоз древесины. Кругляк, пиловочник, баланс.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена, на постах проверяют QR код из ФГИС ЛК. Оформление у нас поставлено на поток.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- документ на каждый рейс при регулярных перевозках&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- отчёт 1-ИЛ, декларация о сделке&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные лесовозной машины, отправителя, получателя и кубатуру, дальше QR код у водителя на экране.&lt;br&gt;&lt;br&gt;Обычно 15 минут.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронная подпись не нужны.&lt;br&gt;&lt;br&gt;Работаем по Красноярскому краю и всей Сибири. Хвойный кругляк с делянки, лиственные породы, древесина оптом, часовой пояс не проблема.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
+          <t>Оформляем ЭСД на еловый пиловочник. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Порядок: присылаете маршрут и реквизиты, получаете ЭСД с QR кодом водителю на телефон. На посту проверка занимает минуту.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;ЭСД: 15 минут.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -11744,7 +11047,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Красноярский край, Богучаны, ул. Ленина, 27</t>
+          <t>Чусовой, Пермский край, ул. Ленина, 34</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -11753,7 +11056,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -11787,7 +11090,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -11813,19 +11116,19 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>2026-08-30T11:00:00+03:00</t>
+          <t>2026-09-02T09:40:00+03:00</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-08-01T11:00:00+03:00</t>
+          <t>2026-08-17T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6664478711</t>
+          <t>5975623537</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11833,6 +11136,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8263601318</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -11840,17 +11148,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ель есть документов нет(помощь с учётом леса)</t>
+          <t>Кругляк сосна и баланс, документы на вывоз</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Учёт древесины и оформление документов в ФГИС ЛК. Кругляк, пиловочник ель и сосна, баланс, дрова.&lt;br&gt;&lt;br&gt;Древесина должна стоять на учёте, иначе её не продать и не вывезти. Ставим объём на баланс, оформляем сопроводительные документы, ведём отчётность.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка объёма древесины на учёт&lt;br&gt;- ЭСД и QR код на транспортировку&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт в местах складирования&lt;br&gt;- сопровождение постоянных отгрузок&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Рутинный ЭСД около 15 минут, задачи по учёту дольше, срок называю до начала работы.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Лесоматериалы круглые, продажа и покупка леса, отгрузка лесовозными машинами.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, отвечу быстро.</t>
+          <t>Оформляем документы на сосновый кругляк и баланс. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Что делаем: ЭСД с QR на рейс, декларация о сделке, постановка объёма на учёт, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Типовой ЭСД 15 минут. По постановке на учёт срок называем после разбора документов.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -11865,7 +11173,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Челябинская область, Сатка, ул. Солнечная, 12</t>
+          <t>Красновишерск, Пермский край, ул. Гагарина, 6</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -11874,7 +11182,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>550</v>
+        <v>1400</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -11908,7 +11216,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -11934,19 +11242,19 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>2026-08-30T15:00:00+03:00</t>
+          <t>2026-09-01T16:10:00+03:00</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2026-08-01T15:00:00+03:00</t>
+          <t>2026-08-17T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2657040747</t>
+          <t>8561800688</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11954,6 +11262,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>8263343835</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -11961,17 +11274,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Сосна заготовлена бумаг нет(документы фгис лк)</t>
+          <t>Баланс ель на комбинат, ЭСД по договору</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Оформление документов на древесину в ФГИС ЛК для заготовителей, продавцов и перевозчиков. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;В работе:&lt;br&gt;- электронный сопроводительный документ на транспортировку древесины&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- лесная декларация, декларация о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования древесины (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Вы присылаете породу, кубатуру, маршрут и данные сторон. Мы оформляем в системе и передаём готовый пакет.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут после получения данных. Учёт и декларация занимают дольше, срок озвучиваю заранее.&lt;br&gt;&lt;br&gt;Свой кабинет, электронная подпись и декларация вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Сосновый пиловочник, лес с делянки, древесина оптом, разовые задачи и постоянное ведение.&lt;br&gt;&lt;br&gt;Напишите кубатуру, скажу срок и порядок.</t>
+          <t>Ведём документы по поставкам балансовой древесины на комбинат. Услуга по договору.&lt;br&gt;&lt;br&gt;При регулярных поставках документы идут потоком. Оформляем ЭСД на каждую машину, ведём декларации, закрываем отчётность.&lt;br&gt;&lt;br&gt;Отдельно следим, чтобы объёмы по документам сходились с принятыми. Расхождение всплывает на приёмке.&lt;br&gt;&lt;br&gt;Томская область.&lt;br&gt;&lt;br&gt;Напишите объём в месяц.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -11986,7 +11299,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Челябинская область, Катав-Ивановск, ул. Ленина, 19</t>
+          <t>Асино, Томская обл., ул. Ленина, 42</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -11995,7 +11308,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -12029,7 +11342,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -12055,19 +11368,19 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>2026-08-30T19:00:00+03:00</t>
+          <t>2026-09-04T13:05:00+03:00</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2026-08-01T19:00:00+03:00</t>
+          <t>2026-08-17T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8424443532</t>
+          <t>2239987508</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -12075,6 +11388,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>8263149501</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -12082,17 +11400,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Лес заготовлен документов нет(помощь с учётом)</t>
+          <t>Пиловочник хвойный, оформим вывоз и учёт</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Учёт древесины и оформление документов в ФГИС ЛК. Кругляк, пиловочник сосна и ель, балансовая древесина, дрова.&lt;br&gt;&lt;br&gt;Ситуация, с которой чаще всего приходят: лес заготовлен и лежит, покупатель есть, а в системе объём не проведён. Пока древесина не на учёте, продать и вывезти её нельзя.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка заготовленного объёма на учёт и баланс&lt;br&gt;- электронный сопроводительный документ (ЭСД) на транспортировку&lt;br&gt;- QR код водителю для проверки на посту&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ, учёт в местах складирования (МСД)&lt;br&gt;&lt;br&gt;Порядок. От вас порода, кубатура в кубометрах, маршрут и реквизиты сторон. Оформление в системе полностью на нашей стороне.&lt;br&gt;&lt;br&gt;Рутинный ЭСД занимает около 15 минут после получения данных. Постановка объёма на учёт дольше, срок называю честно до начала работы.&lt;br&gt;&lt;br&gt;Свой личный кабинет, электронная подпись и лесная декларация вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Башкортостану и соседним регионам. Хвойный кругляк с делянки и со склада, лесоматериалы круглые, древесина оптом, отгрузка лесовозными машинами.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру, скажу порядок и срок.</t>
+          <t>Оформляем документы на хвойный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Берём на себя постановку объёма на учёт, ЭСД с QR на каждую машину, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Работаем и с разовой отгрузкой, и с регулярными поставками. Во втором случае удобнее вести одним исполнителем, чтобы объёмы не разъезжались между документами.&lt;br&gt;&lt;br&gt;Вологодская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -12107,7 +11425,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Ишимбай, ул. Советская, 15</t>
+          <t>Великий Устюг, Вологодская обл., ул. Красная, 12</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -12116,7 +11434,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>500</v>
+        <v>2400</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -12176,19 +11494,19 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>2026-08-26T14:00:00+03:00</t>
+          <t>2026-09-03T09:35:00+03:00</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2026-07-28T14:00:00+03:00</t>
+          <t>2026-08-17T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2960453369</t>
+          <t>8000860251</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -12196,6 +11514,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>8263292303</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -12203,17 +11526,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Сосна есть документов нет(QR код на вывоз леса)</t>
+          <t>Лес кругляк ель, поставим на учёт</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>QR коды и электронные сопроводительные документы на вывоз древесины через ФГИС ЛК. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена. На посту проверяют QR код, в нём данные рейса, объёма и сторон сделки. Оформляем документ на каждую лесовозную машину.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- документ на каждый рейс при постоянных перевозках&lt;br&gt;- постановка объёма древесины на учёт в системе&lt;br&gt;- декларация о сделке, отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Порядок работы. Присылаете данные машины, отправителя и получателя, породу и кубатуру. Дальше оформление на нас, QR код приходит водителю на телефон.&lt;br&gt;&lt;br&gt;Обычно занимает 15 минут с момента получения данных.&lt;br&gt;&lt;br&gt;Личный кабинет ФГИС ЛК, электронная подпись и собственная декларация не потребуются, работаем со своей стороны.&lt;br&gt;&lt;br&gt;Работаем по Пермскому краю и Приуралью. Сосновый и еловый пиловочник, лес с делянки, лесоматериалы круглые, продажа и покупка древесины, любые объёмы.&lt;br&gt;&lt;br&gt;Напишите кубатуру и маршрут, отвечу сразу.</t>
+          <t>Ставим еловый кругляк на учёт в ФГИС ЛК. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Если объём нигде не числится, партию нельзя ни продать, ни вывезти. Это решается.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём на баланс, оформляем ЭСД с QR на отгрузки, закрываем декларацию и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -12228,7 +11551,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Пермский край, Кунгур, ул. Ленина, 40</t>
+          <t>Шарья, Костромская обл., ул. Октябрьская, 15</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -12237,7 +11560,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>450</v>
+        <v>2600</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -12271,7 +11594,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -12297,2934 +11620,12 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>2026-08-26T17:00:00+03:00</t>
+          <t>2026-09-01T14:42:00+03:00</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2026-07-28T17:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1936930142</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Ель кругляк с делянки(помощь с учётом)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Лес есть, а с документами в ФГИС ЛК вечно возня. Возьмём её на себя. Поставим ваш объём на баланс, оформим ЭСД и QR код на каждую машину, дальше просто ведём учёт, чтобы вы про это не думали.&lt;br&gt;&lt;br&gt;Лес еловый, кругляк с делянки, 6 метров, диаметр от 20 см. Есть и другие сортименты.&lt;br&gt;&lt;br&gt;От вас только данные по объёму и рейсу. Свой кабинет в системе, декларацию и электронную подпись заводить не нужно, всё оформляем мы.&lt;br&gt;&lt;br&gt;Я по Башкортостану и соседним регионам. Напишите, что у вас по лесу, подскажу порядок и сроки.</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/01_03.jpg</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Республика Башкортостан, Белорецк, ул. Ленина, 15</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB36" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>2026-09-06T12:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>2026-08-07T14:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>7029554179</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Сосна кругляк с делянки(QR код на вывоз леса)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Делаем QR код на вывоз леса и ЭСД через ФГИС ЛК. Машина уже под погрузкой, а документа на рейс нет - обычно решаем в тот же день.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, есть и другой хвойный сортимент.&lt;br&gt;&lt;br&gt;QR код и ЭСД приходят водителю на телефон. Перед этим сверяем объём и породу, чтобы на посту не развернули. Свой кабинет и подпись вам не нужны.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири, разница по времени не мешает. Напишите, что по рейсу, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_03.jpg</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Алтайский край, Бийск, ул. Советская, 8</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB37" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>2026-09-06T13:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>2026-08-10T06:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2323865424</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Сосна кругляк под погрузку(QR код на вывоз леса)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Лес есть, а документов нет - обычная история. Оформим QR код на вывоз и ЭСД через ФГИС ЛК, документ придёт водителю на экран перед выездом.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Объём и породу проверяем заранее, чтобы потом не переделывать. Всё оформление на нас, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Кемеровской области и Сибири, часовой пояс не помеха. Напишите объём и куда везёте, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_03.jpg</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Кемеровская область, Таштагол, ул. Ленина, 22</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB38" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>2026-09-06T15:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>2026-08-10T08:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>8579049856</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Лиственница кругляк(ЭСД на перевозку)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Делаем ЭСД на перевозку леса через ФГИС ЛК. Если возите объёмами, на каждый рейс нужен свой документ - держим это на потоке, чтобы машины не стояли.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см. Есть сосна и ель.&lt;br&gt;&lt;br&gt;Данные проверяем до выпуска, чтобы не было отказа. Оформляем, даже если своей декларации у вас пока нет.&lt;br&gt;&lt;br&gt;Я по Красноярскому краю и Сибири. Напишите объём и маршрут, скажу срок сегодня.</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_03.jpg</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Красноярский край, Богучаны, ул. Октябрьская, 5</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Лиственница</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB39" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>2026-09-07T04:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>2026-08-08T06:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>4561483668</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Ель кругляк с делянки(помощь с учётом)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Кто возит лес, тот знает: без учёта в ФГИС ЛК никуда. Поможем с учётом - поставим объём на баланс, оформим ЭСД и QR на рейсы, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, кругляк с делянки, 6 метров, диаметр от 20 см. Любой объём.&lt;br&gt;&lt;br&gt;От вас только данные, остальное на нас. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Челябинской области и Уралу. Напишите породу и кубатуру, подскажу сроки.</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_03.jpg</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Челябинская область, Сатка, ул. Пролетарская, 12</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB40" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>2026-09-07T05:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>2026-08-08T07:30:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2738165608</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Сосна от заготовителя(QR код на вывоз леса)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Машина готова, лес на месте, а QR кода на вывоз нет. Сделаем QR и ЭСД через ФГИС ЛК на каждую машину, придёт водителю на телефон.&lt;br&gt;&lt;br&gt;Сосновый кругляк напрямую от заготовителя, 6 метров, диаметр от 20 см.&lt;br&gt;&lt;br&gt;Перед отгрузкой сверяем объём и породу. Оформление целиком с нашей стороны, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Башкортостану и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_03.jpg</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Республика Башкортостан, Сибай, ул. Заводская, 3</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB41" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>2026-09-07T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>2026-08-08T09:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>7680837833</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Сосна пиловочник с делянки(документы фгис лк)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Кто работает с лесом, тому нужны документы в ФГИС ЛК, а времени на систему нет. Оформим за вас - ЭСД и QR на перевозку, поставим объём на учёт, проведём сделку.&lt;br&gt;&lt;br&gt;Сосновый пиловочник с делянки, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Кабинет и подпись заводить не надо, ведём всё сами.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири. Напишите кубатуру и маршрут, отвечу быстро.</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_03.jpg</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Алтайский край, Заринск, ул. Металлургов, 9</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB42" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>2026-09-07T08:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>2026-08-08T10:30:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>1951202398</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Лиственница кругляк с делянки(ЭСД на вывоз)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на вывоз леса через ФГИС ЛК. Лес готов, машина под погрузкой, а документа на рейс нет - выпустим, и водитель едет.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см, плотная древесина.&lt;br&gt;&lt;br&gt;Данные проверяем заранее. Если что-то оформлено с ошибкой, аннулируем и делаем заново по правилам. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Пермскому краю и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_03.jpg</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Пермский край, Чусовой, ул. Ленина, 30</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Лиственница</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB43" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr">
-        <is>
-          <t>2026-09-07T10:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>2026-08-08T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>7192983965</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Ель пиловочник с делянки(помощь с учётом)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Лес есть, а документов нет, и учёт в ФГИС ЛК висит мёртвым грузом. Разгрузим - поставим объём на баланс, сделаем ЭСД и QR на каждый рейс, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, пиловочник с делянки, 6 метров, диаметр от 20 см. Хвоя.&lt;br&gt;&lt;br&gt;От вас данные, остальное наша забота. Свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Я по Удмуртии и Поволжью. Напишите породу и кубатуру, подскажу сроки.</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_03.jpg</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Удмуртская Республика, Можга, ул. Наговицына, 7</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB44" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr">
-        <is>
-          <t>2026-09-08T03:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>2026-08-09T05:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2634568371</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Лес кругляк ель сосна, ЭСД на отгрузку</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на еловый и сосновый кругляк. Услуга по документам отгрузки.&lt;br&gt;&lt;br&gt;На каждую машину сопроводительный документ с QR кодом, водителю до выезда. Если объём не заведён в системе, сначала ставим на учёт.&lt;br&gt;&lt;br&gt;Закрываем декларацию о сделке и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Галич, Костромская обл., ул. Свободы, 11</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P45" t="n">
-        <v>900</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB45" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>2026-09-12T16:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>2026-08-13T18:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>4149246617</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Пиловочник сосна, полный пакет документов</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Оформляем полный пакет документов на сосновый пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;В пакет входит: постановка на учёт, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ, места складирования, коды ОКПД2.&lt;br&gt;&lt;br&gt;От вас данные, от нас готовые документы. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Омская область.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить.</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Тара, Омская обл., ул. Ленина, 9</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P46" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB46" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>2026-09-13T03:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>2026-08-14T05:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>1099424133</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Лес кругляк ель, ЭСД и постановка на учёт</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на еловый кругляк и ставим объём на учёт. Услуга по документам.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сопроводительный документ выписывать не на что. Поэтому сначала учёт, потом отгрузки.&lt;br&gt;&lt;br&gt;Дальше: ЭСД с QR на каждый рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Нижегородская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Урень, Нижегородская обл., ул. Ленина, 47</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>1500</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB47" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG47" t="inlineStr">
-        <is>
-          <t>2026-09-13T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>2026-08-14T09:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>1198010038</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Пиловочник сосна, оформим ЭСД на рейс</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на сосновый пиловочник. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждый рейс: сопроводительный документ с QR кодом, водителю до выезда. Срок 15 минут.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сначала ставим на учёт, потом отгружаете.&lt;br&gt;&lt;br&gt;Ивановская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Юрьевец, Ивановская обл., ул. Советская, 26</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>1800</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB48" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr">
-        <is>
-          <t>2026-09-13T10:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>2026-08-14T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>3451367236</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Кругляк хвойный, поставим на учёт и вывезем</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Ставим хвойный кругляк на учёт в ФГИС ЛК и оформляем вывоз. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Основная проблема не в лесе, а в бумагах: объём есть, в системе его нет, вывезти нельзя.&lt;br&gt;&lt;br&gt;Ставим на учёт, дальше каждый рейс уходит с ЭСД и QR, сделка закрывается декларацией, период отчётом 1-ИЛ.&lt;br&gt;&lt;br&gt;Владимирская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__3.jpg</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Вязники, Владимирская обл., ул. Ленина, 33</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB49" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr">
-        <is>
-          <t>2026-09-14T03:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>2026-08-15T05:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>7655959812</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Лес кругляк сосна, ЭСД на каждый рейс</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на сосновый кругляк. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждую машину готовим сопроводительный документ с QR кодом. Водитель получает до выезда.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;Алтайский край.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Камень-на-Оби, Алтайский край, ул. Ленина, 48</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P50" t="n">
-        <v>2200</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB50" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>2026-09-14T05:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>2026-08-15T07:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>4870626062</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Пиловочник ель сосна, ЭСД и учёт</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Оформляем документы на пиловочник ели и сосны. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Закрываем учёт и сопроводительные документы: постановка объёма на баланс, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут, реквизиты. ЭСД за 15 минут.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Мантурово, Костромская обл., ул. Советская, 22</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P51" t="n">
-        <v>2800</v>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB51" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>2026-09-15T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>2026-08-16T09:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>7622497474</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Лес кругляк сосна, документы и ЭСД</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Оформляем документы на сосновый кругляк в ФГИС ЛК. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;В работу входит: ЭСД на рейс, QR код для поста, декларация о сделке, отчёт 1-ИЛ. Если объём не заведён, ставим на учёт.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, маршрут, реквизиты. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Красноярский край, Ангара и Енисей.&lt;br&gt;&lt;br&gt;Напишите, что везёте и куда.</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real234__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Лесосибирск, Красноярский край, ул. Победы, 31</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P52" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB52" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG52" t="inlineStr">
-        <is>
-          <t>2026-09-15T10:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>2026-08-16T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>4897973128</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Пиловочник ель, ЭСД и QR код на вывоз</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Оформляем ЭСД на еловый пиловочник. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Порядок: присылаете маршрут и реквизиты, получаете ЭСД с QR кодом водителю на телефон. На посту проверка занимает минуту.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;ЭСД: 15 минут.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Чусовой, Пермский край, ул. Ленина, 34</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB53" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG53" t="inlineStr">
-        <is>
-          <t>2026-09-16T05:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>2026-08-17T07:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>5975623537</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Кругляк сосна и баланс, документы на вывоз</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Оформляем документы на сосновый кругляк и баланс. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Что делаем: ЭСД с QR на рейс, декларация о сделке, постановка объёма на учёт, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Типовой ЭСД 15 минут. По постановке на учёт срок называем после разбора документов.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Красновишерск, Пермский край, ул. Гагарина, 6</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P54" t="n">
-        <v>1400</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB54" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>2026-09-16T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>2026-08-17T09:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>8561800688</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Баланс ель на комбинат, ЭСД по договору</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Ведём документы по поставкам балансовой древесины на комбинат. Услуга по договору.&lt;br&gt;&lt;br&gt;При регулярных поставках документы идут потоком. Оформляем ЭСД на каждую машину, ведём декларации, закрываем отчётность.&lt;br&gt;&lt;br&gt;Отдельно следим, чтобы объёмы по документам сходились с принятыми. Расхождение всплывает на приёмке.&lt;br&gt;&lt;br&gt;Томская область.&lt;br&gt;&lt;br&gt;Напишите объём в месяц.</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Асино, Томская обл., ул. Ленина, 42</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P55" t="n">
-        <v>1600</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB55" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr">
-        <is>
-          <t>2026-09-16T10:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>2026-08-17T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2239987508</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Пиловочник хвойный, оформим вывоз и учёт</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Оформляем документы на хвойный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Берём на себя постановку объёма на учёт, ЭСД с QR на каждую машину, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Работаем и с разовой отгрузкой, и с регулярными поставками. Во втором случае удобнее вести одним исполнителем, чтобы объёмы не разъезжались между документами.&lt;br&gt;&lt;br&gt;Вологодская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Великий Устюг, Вологодская обл., ул. Красная, 12</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB56" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>2026-09-16T12:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>2026-08-17T14:30:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>8000860251</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Лес кругляк ель, поставим на учёт</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Ставим еловый кругляк на учёт в ФГИС ЛК. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Если объём нигде не числится, партию нельзя ни продать, ни вывезти. Это решается.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём на баланс, оформляем ЭСД с QR на отгрузки, закрываем декларацию и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру.</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Шарья, Костромская обл., ул. Октябрьская, 15</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P57" t="n">
-        <v>2600</v>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB57" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr">
-        <is>
-          <t>2026-09-17T07:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
           <t>2026-08-17T19:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>1901670741</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Пиловочник лиственница, документы на лес</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Оформляем документы на лиственничный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;По лиственнице чаще цепляются к сортименту и кодам. Подбираем ОКПД2 под фактический сортимент, чтобы партия прошла без задержек.&lt;br&gt;&lt;br&gt;Закрываем: ЭСД с QR, декларацию о сделке, постановку объёма на учёт.&lt;br&gt;&lt;br&gt;Челябинская область.&lt;br&gt;&lt;br&gt;Напишите сортимент и объём.</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Кыштым, Челябинская обл., ул. Калинина, 11</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P58" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Лиственница</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB58" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG58" t="inlineStr">
-        <is>
-          <t>2026-09-18T10:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>2026-08-19T05:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>5972697353</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Лес кругляк ель, документы ФГИС ЛК</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Оформляем документы на еловый кругляк в ФГИС ЛК. Лес не продаём, продаём услугу оформления.&lt;br&gt;&lt;br&gt;Что закрываем:&lt;br&gt;- ЭСД на каждую машину с QR кодом&lt;br&gt;- постановка объёма на учёт&lt;br&gt;- декларация о сделке&lt;br&gt;- отчёт 1-ИЛ&lt;br&gt;&lt;br&gt;Без ЭСД рейс встанет на посту. Делаем документ за 15 минут после ваших данных.&lt;br&gt;&lt;br&gt;Удмуртия и Приуралье.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Игра, Удмуртская Республика, ул. Советская, 29</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P59" t="n">
-        <v>1100</v>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB59" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>2026-09-18T12:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>2026-08-19T07:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -16621,7 +13022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="14"/>
@@ -17446,7 +13847,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4287305104</t>
+          <t>7486797323</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -17461,7 +13862,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4287305104/11_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4287305104/11_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/4287305104/11_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/12_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/12_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/12_03.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -17474,22 +13875,24 @@
           <t>Предложение услуг</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>350</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Сосна пиловочник (документы и учёт ФГИС ЛК)</t>
+          <t>Учёт леса в ФГИС ЛК, помощь с балансом</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Оформляем документы на лес в ФГИС ЛК, сам лес мы не продаём и не покупаем. Если у вас есть кругляк, пиловочник сосны, балансы или дрова с деляны, а бумаг на них нет, мы всё проведём по системе.&lt;br&gt;&lt;br&gt;Что делаем: QR-код и ЭСД на перевозку, чтобы лесовоз шёл с чистой вывозкой. Закрываем расхождения по кубам, когда замеры на делянке и в системе не сходятся. Ставим заготовленную древесину на баланс компании через договор и закрепляем объём в ФГИС ЛК, чтобы можно было законно возить и продавать.&lt;br&gt;&lt;br&gt;Работаем по обработке материалов и учёту остатков, город Кунгур. Пришлите свои замеры, посчитаю остаток сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Лес есть, а объём в ФГИС ЛК не сходится или вообще не заведён - приведём в порядок. Поставим древесину на баланс, дальше держим учёт и документы на потоке.&lt;/p&gt;&lt;p&gt;Что берём на себя: постановку объёма на учёт, ЭСД и QR на рейсы, отчётность по вашим отгрузкам.&lt;/p&gt;&lt;p&gt;Оформление с нашей стороны, свой кабинет и подпись заводить не нужно. Работаю по Костромской области и центральным регионам.&lt;/p&gt;&lt;p&gt;От 990 рублей за объём, сопровождение считаем отдельно. Напишите, что по лесу и учёту, подскажу порядок.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Пермский край, Кунгур, ул. Лесная, 82</t>
+          <t>Костромская область, Кострома, ул. Советская, 20</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -17514,7 +13917,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-22T10:00:00+03:00</t>
+          <t>2026-09-08T09:00:00+03:00</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -17523,178 +13926,6 @@
         </is>
       </c>
       <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-07-23T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>8855945319</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8855945319/20_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8855945319/20_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8855945319/20_03.jpg</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>400</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Берёза кругляк (лес на баланс складской учёт)</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Сразу к делу: мы оформляем документы на лес в ФГИС ЛК, сам лес не продаём. Если у вас есть древесина, а бумаг на неё нет, приводим всё в порядок по системе.&lt;br&gt;&lt;br&gt;Работаем по Оренбургу и области, ведём складской учёт по кубам. Берёза, кругляк, пиловочник, балансы, дрова лежат на площадке или на деляне, а в системе их не значится. Ставим заготовленный лес на баланс компании через договор, закрепляем объём в ФГИС ЛК, и дальше его можно законно продавать и возить.&lt;br&gt;&lt;br&gt;Делаем QR и ЭСД на каждую вывозку, чтобы лесовоз шёл с чистыми документами. Закрываем расхождения по объёмам, готовим декларации и отчёты.&lt;br&gt;&lt;br&gt;Пришлите замеры по делянке, посчитаю сегодня. Напишите в сообщения, отвечу за пару минут.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Оренбургская область, Оренбург, ул. Строителей, 55</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Оборудование, производство</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Производство, обработка</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Обработка материалов</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2026-08-24T08:30:00+03:00</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-07-25T10:30:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>7486797323</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/12_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/12_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/12_03.jpg</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Предложение услуг</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>990</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Учёт леса в ФГИС ЛК, помощь с балансом</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Лес есть, а объём в ФГИС ЛК не сходится или вообще не заведён - приведём в порядок. Поставим древесину на баланс, дальше держим учёт и документы на потоке.&lt;/p&gt;&lt;p&gt;Что берём на себя: постановку объёма на учёт, ЭСД и QR на рейсы, отчётность по вашим отгрузкам.&lt;/p&gt;&lt;p&gt;Оформление с нашей стороны, свой кабинет и подпись заводить не нужно. Работаю по Костромской области и центральным регионам.&lt;/p&gt;&lt;p&gt;От 990 рублей за объём, сопровождение считаем отдельно. Напишите, что по лесу и учёту, подскажу порядок.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Костромская область, Кострома, ул. Советская, 20</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Оборудование, производство</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Производство, обработка</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Обработка материалов</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>2026-09-08T09:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
         <is>
           <t>2026-08-09T11:00:00+03:00</t>
         </is>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-07-21T12:35:45+03:00</t>
+          <t>2026-09-05T17:48:15+03:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-02T13:05:49+03:00</t>
+          <t>2026-09-05T18:17:30+03:00</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-07-30T15:05:39+03:00</t>
+          <t>2026-09-05T17:31:49+03:00</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-07-31T13:26:06+03:00</t>
+          <t>2026-09-05T17:37:35+03:00</t>
         </is>
       </c>
     </row>
@@ -2615,6 +2615,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8167795827</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -2713,6 +2718,11 @@
           <t>ЕГАИС ЛЕС документация</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2026-09-13T14:16:44+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2725,6 +2735,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8231391124</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -2827,7 +2842,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-08T07:00:00+03:00</t>
+          <t>2026-09-08T07:05:42+03:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -3993,7 +4008,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-26T10:49:46+03:00</t>
+          <t>2026-09-05T17:28:41+03:00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -4132,7 +4147,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-30T12:05:47+03:00</t>
+          <t>2026-09-05T18:11:54+03:00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -4264,7 +4279,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-06T07:35:20+03:00</t>
+          <t>2026-09-05T17:31:39+03:00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -4403,7 +4418,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-02T15:36:11+03:00</t>
+          <t>2026-09-05T18:23:33+03:00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -4421,6 +4436,11 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>BBL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8230917632</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4537,7 +4557,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-08T05:00:00+03:00</t>
+          <t>2026-09-08T05:05:32+03:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4555,6 +4575,11 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>BBL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8231544992</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4669,7 +4694,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-12T14:00:00+03:00</t>
+          <t>2026-09-12T14:06:30+03:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4687,6 +4712,11 @@
       <c r="B11" t="inlineStr">
         <is>
           <t>BBL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8230893035</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4801,7 +4831,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-13T05:00:00+03:00</t>
+          <t>2026-09-13T05:05:59+03:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -4819,6 +4849,11 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>BBL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8263009703</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4933,7 +4968,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-13T12:00:00+03:00</t>
+          <t>2026-09-13T12:05:37+03:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -4951,6 +4986,11 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>BBL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8263472323</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5065,7 +5105,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-14T10:00:00+03:00</t>
+          <t>2026-09-14T10:06:12+03:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -5202,7 +5242,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-19T14:23:00+03:00</t>
+          <t>2026-09-19T12:24:56+03:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -5220,6 +5260,11 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>BBL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>8263045417</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5334,7 +5379,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-15T03:00:00+03:00</t>
+          <t>2026-09-16T11:36:22+03:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -5352,6 +5397,11 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>BBL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8263014059</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5466,7 +5516,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-15T05:00:00+03:00</t>
+          <t>2026-09-27T10:39:59+03:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -5603,7 +5653,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-18T15:25:00+03:00</t>
+          <t>2026-09-18T13:27:46+03:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -5621,6 +5671,11 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>BBL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8263344127</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5735,7 +5790,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-16T03:00:00+03:00</t>
+          <t>2026-09-16T11:36:22+03:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -5872,7 +5927,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-19T08:12:00+03:00</t>
+          <t>2026-09-19T06:18:38+03:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -6009,7 +6064,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-27T09:36:00+03:00</t>
+          <t>2026-09-27T07:37:04+03:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -6146,7 +6201,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-17T14:15:00+03:00</t>
+          <t>2026-09-17T12:15:03+03:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -6283,7 +6338,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-18T08:10:00+03:00</t>
+          <t>2026-09-18T06:21:17+03:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -6420,7 +6475,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-09-30T09:41:00+03:00</t>
+          <t>2026-09-30T07:42:26+03:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -6557,7 +6612,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-20T14:00:00+03:00</t>
+          <t>2026-09-20T12:02:10+03:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -7214,7 +7269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ35"/>
+  <dimension ref="A1:AJ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -7850,7 +7905,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2026-08-05T17:06:01+03:00</t>
+          <t>2026-09-05T18:05:38+03:00</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -7987,7 +8042,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026-08-01T16:05:08+03:00</t>
+          <t>2026-09-05T17:28:42+03:00</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -8124,7 +8179,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026-08-06T09:06:32+03:00</t>
+          <t>2026-09-05T17:53:50+03:00</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -8261,7 +8316,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026-08-05T14:06:49+03:00</t>
+          <t>2026-09-05T17:48:13+03:00</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -8398,7 +8453,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026-08-06T12:05:58+03:00</t>
+          <t>2026-09-05T18:05:47+03:00</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -8535,7 +8590,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026-08-01T14:05:54+03:00</t>
+          <t>2026-09-05T17:28:42+03:00</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -8560,6 +8615,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8167245859</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -8665,7 +8725,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026-08-16T05:30:00+03:00</t>
+          <t>2026-09-16T11:36:20+03:00</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -8677,7 +8737,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2671009093</t>
+          <t>2657040747</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8685,6 +8745,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8230953809</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -8692,17 +8757,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Лес с делянки бумаг нет(QR код на вывоз леса)</t>
+          <t>Сосна заготовлена бумаг нет(документы фгис лк)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Электронные сопроводительные документы и QR коды на вывоз древесины. Кругляк, пиловочник, баланс.&lt;br&gt;&lt;br&gt;Перевозка леса без ЭСД запрещена, на постах проверяют QR код из ФГИС ЛК. Оформление у нас поставлено на поток.&lt;br&gt;&lt;br&gt;Услуги:&lt;br&gt;- ЭСД на транспортировку древесины с QR кодом&lt;br&gt;- документ на каждый рейс при регулярных перевозках&lt;br&gt;- постановка объёма на учёт в системе&lt;br&gt;- отчёт 1-ИЛ, декларация о сделке&lt;br&gt;&lt;br&gt;Порядок. Присылаете данные лесовозной машины, отправителя, получателя и кубатуру, дальше QR код у водителя на экране.&lt;br&gt;&lt;br&gt;Обычно 15 минут.&lt;br&gt;&lt;br&gt;Свой кабинет в системе и электронная подпись не нужны.&lt;br&gt;&lt;br&gt;Работаем по Красноярскому краю и всей Сибири. Хвойный кругляк с делянки, лиственные породы, древесина оптом, часовой пояс не проблема.&lt;br&gt;&lt;br&gt;Наберите или напишите, отвечу сразу.</t>
+          <t>Оформление документов на древесину в ФГИС ЛК для заготовителей, продавцов и перевозчиков. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;В работе:&lt;br&gt;- электронный сопроводительный документ на транспортировку древесины&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- лесная декларация, декларация о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования древесины (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Вы присылаете породу, кубатуру, маршрут и данные сторон. Мы оформляем в системе и передаём готовый пакет.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут после получения данных. Учёт и декларация занимают дольше, срок озвучиваю заранее.&lt;br&gt;&lt;br&gt;Свой кабинет, электронная подпись и декларация вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Сосновый пиловочник, лес с делянки, древесина оптом, разовые задачи и постоянное ведение.&lt;br&gt;&lt;br&gt;Напишите кубатуру, скажу срок и порядок.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_14_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_3.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8717,7 +8782,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Красноярский край, Богучаны, ул. Ленина, 27</t>
+          <t>Челябинская область, Катав-Ивановск, ул. Ленина, 19</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -8726,7 +8791,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -8786,19 +8851,19 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-08-30T11:00:00+03:00</t>
+          <t>2026-08-31T17:06:02+03:00</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2026-08-01T11:00:00+03:00</t>
+          <t>2026-08-01T19:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6664478711</t>
+          <t>7029554179</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8806,6 +8871,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8231781509</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -8813,17 +8883,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ель есть документов нет(помощь с учётом леса)</t>
+          <t>Сосна кругляк с делянки(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Учёт древесины и оформление документов в ФГИС ЛК. Кругляк, пиловочник ель и сосна, баланс, дрова.&lt;br&gt;&lt;br&gt;Древесина должна стоять на учёте, иначе её не продать и не вывезти. Ставим объём на баланс, оформляем сопроводительные документы, ведём отчётность.&lt;br&gt;&lt;br&gt;Что делаем:&lt;br&gt;- постановка объёма древесины на учёт&lt;br&gt;- ЭСД и QR код на транспортировку&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и учёт в местах складирования&lt;br&gt;- сопровождение постоянных отгрузок&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут и реквизиты сторон.&lt;br&gt;&lt;br&gt;Рутинный ЭСД около 15 минут, задачи по учёту дольше, срок называю до начала работы.&lt;br&gt;&lt;br&gt;Личный кабинет и электронная подпись не потребуются.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Лесоматериалы круглые, продажа и покупка леса, отгрузка лесовозными машинами.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить, отвечу быстро.</t>
+          <t>Делаем QR код на вывоз леса и ЭСД через ФГИС ЛК. Машина уже под погрузкой, а документа на рейс нет - обычно решаем в тот же день.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, есть и другой хвойный сортимент.&lt;br&gt;&lt;br&gt;QR код и ЭСД приходят водителю на телефон. Перед этим сверяем объём и породу, чтобы на посту не развернули. Свой кабинет и подпись вам не нужны.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири, разница по времени не мешает. Напишите, что по рейсу, отвечу сразу.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_03.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -8838,7 +8908,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Челябинская область, Сатка, ул. Солнечная, 12</t>
+          <t>Алтайский край, Бийск, ул. Советская, 8</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -8846,8 +8916,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>550</v>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -8881,7 +8953,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -8907,19 +8979,19 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2026-08-30T15:00:00+03:00</t>
+          <t>2026-09-09T04:05:12+03:00</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2026-08-01T15:00:00+03:00</t>
+          <t>2026-08-10T06:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2657040747</t>
+          <t>2323865424</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8927,6 +8999,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8231583301</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -8934,17 +9011,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Сосна заготовлена бумаг нет(документы фгис лк)</t>
+          <t>Сосна кругляк под погрузку(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Оформление документов на древесину в ФГИС ЛК для заготовителей, продавцов и перевозчиков. Кругляк, пиловочник, баланс, дрова.&lt;br&gt;&lt;br&gt;В работе:&lt;br&gt;- электронный сопроводительный документ на транспортировку древесины&lt;br&gt;- QR код для проверки на посту&lt;br&gt;- постановка заготовленного объёма на учёт&lt;br&gt;- лесная декларация, декларация о сделке&lt;br&gt;- отчёт 1-ИЛ, учёт по местам складирования древесины (МСД)&lt;br&gt;&lt;br&gt;Как работаем. Вы присылаете породу, кубатуру, маршрут и данные сторон. Мы оформляем в системе и передаём готовый пакет.&lt;br&gt;&lt;br&gt;ЭСД обычно 15 минут после получения данных. Учёт и декларация занимают дольше, срок озвучиваю заранее.&lt;br&gt;&lt;br&gt;Свой кабинет, электронная подпись и декларация вам не нужны.&lt;br&gt;&lt;br&gt;Работаем по Челябинской области и Уралу. Сосновый пиловочник, лес с делянки, древесина оптом, разовые задачи и постоянное ведение.&lt;br&gt;&lt;br&gt;Напишите кубатуру, скажу срок и порядок.</t>
+          <t>Лес есть, а документов нет - обычная история. Оформим QR код на вывоз и ЭСД через ФГИС ЛК, документ придёт водителю на экран перед выездом.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Объём и породу проверяем заранее, чтобы потом не переделывать. Всё оформление на нас, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Кемеровской области и Сибири, часовой пояс не помеха. Напишите объём и куда везёте, отвечу сразу.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_16_3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_03.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -8959,7 +9036,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Челябинская область, Катав-Ивановск, ул. Ленина, 19</t>
+          <t>Кемеровская область, Таштагол, ул. Ленина, 22</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -8967,8 +9044,10 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P14" t="n">
-        <v>400</v>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -9028,19 +9107,19 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026-08-30T19:00:00+03:00</t>
+          <t>2026-09-05T17:35:36+03:00</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2026-08-01T19:00:00+03:00</t>
+          <t>2026-08-10T08:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7029554179</t>
+          <t>8579049856</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9048,6 +9127,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>8231651932</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -9055,17 +9139,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Сосна кругляк с делянки(QR код на вывоз леса)</t>
+          <t>Лиственница кругляк(ЭСД на перевозку)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Делаем QR код на вывоз леса и ЭСД через ФГИС ЛК. Машина уже под погрузкой, а документа на рейс нет - обычно решаем в тот же день.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, есть и другой хвойный сортимент.&lt;br&gt;&lt;br&gt;QR код и ЭСД приходят водителю на телефон. Перед этим сверяем объём и породу, чтобы на посту не развернули. Свой кабинет и подпись вам не нужны.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири, разница по времени не мешает. Напишите, что по рейсу, отвечу сразу.</t>
+          <t>Делаем ЭСД на перевозку леса через ФГИС ЛК. Если возите объёмами, на каждый рейс нужен свой документ - держим это на потоке, чтобы машины не стояли.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см. Есть сосна и ель.&lt;br&gt;&lt;br&gt;Данные проверяем до выпуска, чтобы не было отказа. Оформляем, даже если своей декларации у вас пока нет.&lt;br&gt;&lt;br&gt;Я по Красноярскому краю и Сибири. Напишите объём и маршрут, скажу срок сегодня.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/02_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_03.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9080,7 +9164,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Алтайский край, Бийск, ул. Советская, 8</t>
+          <t>Красноярский край, Богучаны, ул. Октябрьская, 5</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -9090,7 +9174,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -9125,7 +9209,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Лиственница</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -9151,19 +9235,19 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2026-09-06T13:30:00+03:00</t>
+          <t>2026-09-07T04:05:22+03:00</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2026-08-10T06:00:00+03:00</t>
+          <t>2026-08-08T06:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2323865424</t>
+          <t>4561483668</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9171,6 +9255,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8231598891</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -9178,17 +9267,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Сосна кругляк под погрузку(QR код на вывоз леса)</t>
+          <t>Ель кругляк с делянки(помощь с учётом)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет - обычная история. Оформим QR код на вывоз и ЭСД через ФГИС ЛК, документ придёт водителю на экран перед выездом.&lt;br&gt;&lt;br&gt;Сосновый кругляк, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Объём и породу проверяем заранее, чтобы потом не переделывать. Всё оформление на нас, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Кемеровской области и Сибири, часовой пояс не помеха. Напишите объём и куда везёте, отвечу сразу.</t>
+          <t>Кто возит лес, тот знает: без учёта в ФГИС ЛК никуда. Поможем с учётом - поставим объём на баланс, оформим ЭСД и QR на рейсы, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, кругляк с делянки, 6 метров, диаметр от 20 см. Любой объём.&lt;br&gt;&lt;br&gt;От вас только данные, остальное на нас. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Челябинской области и Уралу. Напишите породу и кубатуру, подскажу сроки.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/03_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_03.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9203,7 +9292,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Кемеровская область, Таштагол, ул. Ленина, 22</t>
+          <t>Челябинская область, Сатка, ул. Пролетарская, 12</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -9213,7 +9302,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -9248,7 +9337,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -9274,19 +9363,19 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026-09-06T15:00:00+03:00</t>
+          <t>2026-09-07T05:35:06+03:00</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2026-08-10T08:00:00+03:00</t>
+          <t>2026-08-08T07:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8579049856</t>
+          <t>2738165608</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9294,6 +9383,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8231334302</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -9301,17 +9395,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Лиственница кругляк(ЭСД на перевозку)</t>
+          <t>Сосна от заготовителя(QR код на вывоз леса)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Делаем ЭСД на перевозку леса через ФГИС ЛК. Если возите объёмами, на каждый рейс нужен свой документ - держим это на потоке, чтобы машины не стояли.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см. Есть сосна и ель.&lt;br&gt;&lt;br&gt;Данные проверяем до выпуска, чтобы не было отказа. Оформляем, даже если своей декларации у вас пока нет.&lt;br&gt;&lt;br&gt;Я по Красноярскому краю и Сибири. Напишите объём и маршрут, скажу срок сегодня.</t>
+          <t>Машина готова, лес на месте, а QR кода на вывоз нет. Сделаем QR и ЭСД через ФГИС ЛК на каждую машину, придёт водителю на телефон.&lt;br&gt;&lt;br&gt;Сосновый кругляк напрямую от заготовителя, 6 метров, диаметр от 20 см.&lt;br&gt;&lt;br&gt;Перед отгрузкой сверяем объём и породу. Оформление целиком с нашей стороны, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Башкортостану и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/04_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_03.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9326,7 +9420,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Красноярский край, Богучаны, ул. Октябрьская, 5</t>
+          <t>Республика Башкортостан, Сибай, ул. Заводская, 3</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -9336,7 +9430,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -9371,7 +9465,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Лиственница</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -9397,19 +9491,19 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2026-09-07T04:00:00+03:00</t>
+          <t>2026-09-07T07:06:49+03:00</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2026-08-08T06:00:00+03:00</t>
+          <t>2026-08-08T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4561483668</t>
+          <t>7680837833</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9417,6 +9511,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8231333315</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -9424,17 +9523,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ель кругляк с делянки(помощь с учётом)</t>
+          <t>Сосна пиловочник с делянки(документы фгис лк)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Кто возит лес, тот знает: без учёта в ФГИС ЛК никуда. Поможем с учётом - поставим объём на баланс, оформим ЭСД и QR на рейсы, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, кругляк с делянки, 6 метров, диаметр от 20 см. Любой объём.&lt;br&gt;&lt;br&gt;От вас только данные, остальное на нас. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Челябинской области и Уралу. Напишите породу и кубатуру, подскажу сроки.</t>
+          <t>Кто работает с лесом, тому нужны документы в ФГИС ЛК, а времени на систему нет. Оформим за вас - ЭСД и QR на перевозку, поставим объём на учёт, проведём сделку.&lt;br&gt;&lt;br&gt;Сосновый пиловочник с делянки, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Кабинет и подпись заводить не надо, ведём всё сами.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири. Напишите кубатуру и маршрут, отвечу быстро.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/05_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_03.jpg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9449,7 +9548,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Челябинская область, Сатка, ул. Пролетарская, 12</t>
+          <t>Алтайский край, Заринск, ул. Металлургов, 9</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -9459,7 +9558,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -9494,7 +9593,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -9520,19 +9619,19 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2026-09-07T05:30:00+03:00</t>
+          <t>2026-09-07T08:36:15+03:00</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2026-08-08T07:30:00+03:00</t>
+          <t>2026-08-08T10:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2738165608</t>
+          <t>1951202398</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9540,6 +9639,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>8231463002</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -9547,17 +9651,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Сосна от заготовителя(QR код на вывоз леса)</t>
+          <t>Лиственница кругляк с делянки(ЭСД на вывоз)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Машина готова, лес на месте, а QR кода на вывоз нет. Сделаем QR и ЭСД через ФГИС ЛК на каждую машину, придёт водителю на телефон.&lt;br&gt;&lt;br&gt;Сосновый кругляк напрямую от заготовителя, 6 метров, диаметр от 20 см.&lt;br&gt;&lt;br&gt;Перед отгрузкой сверяем объём и породу. Оформление целиком с нашей стороны, свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Башкортостану и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
+          <t>Оформляем ЭСД на вывоз леса через ФГИС ЛК. Лес готов, машина под погрузкой, а документа на рейс нет - выпустим, и водитель едет.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см, плотная древесина.&lt;br&gt;&lt;br&gt;Данные проверяем заранее. Если что-то оформлено с ошибкой, аннулируем и делаем заново по правилам. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Пермскому краю и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/06_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_03.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9572,7 +9676,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Республика Башкортостан, Сибай, ул. Заводская, 3</t>
+          <t>Пермский край, Чусовой, ул. Ленина, 30</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -9582,7 +9686,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -9617,7 +9721,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Лиственница</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9643,19 +9747,19 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2026-09-07T07:00:00+03:00</t>
+          <t>2026-09-07T10:06:19+03:00</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2026-08-08T09:00:00+03:00</t>
+          <t>2026-08-08T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7680837833</t>
+          <t>7192983965</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9663,6 +9767,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8231072609</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -9670,17 +9779,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Сосна пиловочник с делянки(документы фгис лк)</t>
+          <t>Ель пиловочник с делянки(помощь с учётом)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Кто работает с лесом, тому нужны документы в ФГИС ЛК, а времени на систему нет. Оформим за вас - ЭСД и QR на перевозку, поставим объём на учёт, проведём сделку.&lt;br&gt;&lt;br&gt;Сосновый пиловочник с делянки, 6 метров, диаметр от 20 см, лес с делянки и со склада.&lt;br&gt;&lt;br&gt;Кабинет и подпись заводить не надо, ведём всё сами.&lt;br&gt;&lt;br&gt;Я по Алтаю и Сибири. Напишите кубатуру и маршрут, отвечу быстро.</t>
+          <t>Лес есть, а документов нет, и учёт в ФГИС ЛК висит мёртвым грузом. Разгрузим - поставим объём на баланс, сделаем ЭСД и QR на каждый рейс, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, пиловочник с делянки, 6 метров, диаметр от 20 см. Хвоя.&lt;br&gt;&lt;br&gt;От вас данные, остальное наша забота. Свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Я по Удмуртии и Поволжью. Напишите породу и кубатуру, подскажу сроки.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/07_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_03.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9695,7 +9804,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Алтайский край, Заринск, ул. Металлургов, 9</t>
+          <t>Удмуртская Республика, Можга, ул. Наговицына, 7</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -9705,7 +9814,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>550</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -9740,7 +9849,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9766,19 +9875,19 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2026-09-07T08:30:00+03:00</t>
+          <t>2026-09-08T03:05:09+03:00</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2026-08-08T10:30:00+03:00</t>
+          <t>2026-08-09T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1951202398</t>
+          <t>2634568371</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9786,6 +9895,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8231779697</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -9793,17 +9907,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Лиственница кругляк с делянки(ЭСД на вывоз)</t>
+          <t>Лес кругляк ель сосна, ЭСД на отгрузку</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Оформляем ЭСД на вывоз леса через ФГИС ЛК. Лес готов, машина под погрузкой, а документа на рейс нет - выпустим, и водитель едет.&lt;br&gt;&lt;br&gt;Лиственница, кругляк с делянки, 6 метров, диаметр от 20 см, плотная древесина.&lt;br&gt;&lt;br&gt;Данные проверяем заранее. Если что-то оформлено с ошибкой, аннулируем и делаем заново по правилам. Свой кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Я по Пермскому краю и Приуралью. Напишите объём и маршрут, отвечу сразу.</t>
+          <t>Оформляем ЭСД на еловый и сосновый кругляк. Услуга по документам отгрузки.&lt;br&gt;&lt;br&gt;На каждую машину сопроводительный документ с QR кодом, водителю до выезда. Если объём не заведён в системе, сначала ставим на учёт.&lt;br&gt;&lt;br&gt;Закрываем декларацию о сделке и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/08_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9818,7 +9932,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Пермский край, Чусовой, ул. Ленина, 30</t>
+          <t>Галич, Костромская обл., ул. Свободы, 11</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9826,10 +9940,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
+      <c r="P21" t="n">
+        <v>900</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -9863,7 +9975,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Лиственница</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9889,19 +10001,19 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2026-09-07T10:00:00+03:00</t>
+          <t>2026-09-12T16:05:25+03:00</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2026-08-08T12:00:00+03:00</t>
+          <t>2026-08-13T18:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7192983965</t>
+          <t>4149246617</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9909,6 +10021,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>8231761463</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -9916,17 +10033,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ель пиловочник с делянки(помощь с учётом)</t>
+          <t>Пиловочник сосна, полный пакет документов</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Лес есть, а документов нет, и учёт в ФГИС ЛК висит мёртвым грузом. Разгрузим - поставим объём на баланс, сделаем ЭСД и QR на каждый рейс, дальше ведём сами.&lt;br&gt;&lt;br&gt;Ель, пиловочник с делянки, 6 метров, диаметр от 20 см. Хвоя.&lt;br&gt;&lt;br&gt;От вас данные, остальное наша забота. Свой кабинет и электронную подпись заводить не нужно.&lt;br&gt;&lt;br&gt;Я по Удмуртии и Поволжью. Напишите породу и кубатуру, подскажу сроки.</t>
+          <t>Оформляем полный пакет документов на сосновый пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;В пакет входит: постановка на учёт, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ, места складирования, коды ОКПД2.&lt;br&gt;&lt;br&gt;От вас данные, от нас готовые документы. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Омская область.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-08-06/09_03.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9941,7 +10058,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Удмуртская Республика, Можга, ул. Наговицына, 7</t>
+          <t>Тара, Омская обл., ул. Ленина, 9</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9949,10 +10066,8 @@
           <t>ПВЗ</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
+      <c r="P22" t="n">
+        <v>1200</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -9986,7 +10101,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10012,19 +10127,19 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2026-09-08T03:00:00+03:00</t>
+          <t>2026-09-13T03:05:05+03:00</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2026-08-09T05:00:00+03:00</t>
+          <t>2026-08-14T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2634568371</t>
+          <t>1099424133</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10032,6 +10147,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8231379330</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -10039,17 +10159,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Лес кругляк ель сосна, ЭСД на отгрузку</t>
+          <t>Лес кругляк ель, ЭСД и постановка на учёт</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Оформляем ЭСД на еловый и сосновый кругляк. Услуга по документам отгрузки.&lt;br&gt;&lt;br&gt;На каждую машину сопроводительный документ с QR кодом, водителю до выезда. Если объём не заведён в системе, сначала ставим на учёт.&lt;br&gt;&lt;br&gt;Закрываем декларацию о сделке и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
+          <t>Оформляем ЭСД на еловый кругляк и ставим объём на учёт. Услуга по документам.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сопроводительный документ выписывать не на что. Поэтому сначала учёт, потом отгрузки.&lt;br&gt;&lt;br&gt;Дальше: ЭСД с QR на каждый рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Нижегородская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10064,7 +10184,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Галич, Костромская обл., ул. Свободы, 11</t>
+          <t>Урень, Нижегородская обл., ул. Ленина, 47</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10073,7 +10193,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -10107,7 +10227,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10133,19 +10253,19 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2026-09-12T16:00:00+03:00</t>
+          <t>2026-09-13T07:06:27+03:00</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2026-08-13T18:00:00+03:00</t>
+          <t>2026-08-14T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4149246617</t>
+          <t>1198010038</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10153,6 +10273,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8231155797</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -10160,17 +10285,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Пиловочник сосна, полный пакет документов</t>
+          <t>Пиловочник сосна, оформим ЭСД на рейс</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Оформляем полный пакет документов на сосновый пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;В пакет входит: постановка на учёт, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ, места складирования, коды ОКПД2.&lt;br&gt;&lt;br&gt;От вас данные, от нас готовые документы. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Омская область.&lt;br&gt;&lt;br&gt;Напишите, что нужно оформить.</t>
+          <t>Оформляем ЭСД на сосновый пиловочник. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждый рейс: сопроводительный документ с QR кодом, водителю до выезда. Срок 15 минут.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сначала ставим на учёт, потом отгружаете.&lt;br&gt;&lt;br&gt;Ивановская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_2_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -10185,7 +10310,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Тара, Омская обл., ул. Ленина, 9</t>
+          <t>Юрьевец, Ивановская обл., ул. Советская, 26</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -10194,7 +10319,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -10254,19 +10379,19 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>2026-09-13T03:00:00+03:00</t>
+          <t>2026-09-13T10:05:34+03:00</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2026-08-14T05:00:00+03:00</t>
+          <t>2026-08-14T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1099424133</t>
+          <t>3451367236</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10274,6 +10399,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>8263281492</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -10281,17 +10411,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Лес кругляк ель, ЭСД и постановка на учёт</t>
+          <t>Кругляк хвойный, поставим на учёт и вывезем</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Оформляем ЭСД на еловый кругляк и ставим объём на учёт. Услуга по документам.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сопроводительный документ выписывать не на что. Поэтому сначала учёт, потом отгрузки.&lt;br&gt;&lt;br&gt;Дальше: ЭСД с QR на каждый рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Нижегородская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
+          <t>Ставим хвойный кругляк на учёт в ФГИС ЛК и оформляем вывоз. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Основная проблема не в лесе, а в бумагах: объём есть, в системе его нет, вывезти нельзя.&lt;br&gt;&lt;br&gt;Ставим на учёт, дальше каждый рейс уходит с ЭСД и QR, сделка закрывается декларацией, период отчётом 1-ИЛ.&lt;br&gt;&lt;br&gt;Владимирская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__3.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -10306,7 +10436,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Урень, Нижегородская обл., ул. Ленина, 47</t>
+          <t>Вязники, Владимирская обл., ул. Ленина, 33</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -10315,7 +10445,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -10349,7 +10479,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Ель</t>
+          <t>Сосна</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10375,19 +10505,19 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>2026-09-13T07:00:00+03:00</t>
+          <t>2026-09-14T03:05:16+03:00</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2026-08-14T09:00:00+03:00</t>
+          <t>2026-08-15T05:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1198010038</t>
+          <t>7655959812</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -10395,6 +10525,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>8263061905</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -10402,17 +10537,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Пиловочник сосна, оформим ЭСД на рейс</t>
+          <t>Лес кругляк сосна, ЭСД на каждый рейс</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Оформляем ЭСД на сосновый пиловочник. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждый рейс: сопроводительный документ с QR кодом, водителю до выезда. Срок 15 минут.&lt;br&gt;&lt;br&gt;Если объём не заведён в ФГИС ЛК, сначала ставим на учёт, потом отгружаете.&lt;br&gt;&lt;br&gt;Ивановская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
+          <t>Оформляем ЭСД на сосновый кругляк. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждую машину готовим сопроводительный документ с QR кодом. Водитель получает до выезда.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;Алтайский край.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -10427,7 +10562,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Юрьевец, Ивановская обл., ул. Советская, 26</t>
+          <t>Камень-на-Оби, Алтайский край, ул. Ленина, 48</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -10436,7 +10571,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -10496,19 +10631,19 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>2026-09-13T10:00:00+03:00</t>
+          <t>2026-09-14T05:05:44+03:00</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>2026-08-14T12:00:00+03:00</t>
+          <t>2026-08-15T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3451367236</t>
+          <t>4870626062</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -10516,6 +10651,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8262876661</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -10523,17 +10663,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Кругляк хвойный, поставим на учёт и вывезем</t>
+          <t>Пиловочник ель сосна, ЭСД и учёт</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ставим хвойный кругляк на учёт в ФГИС ЛК и оформляем вывоз. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Основная проблема не в лесе, а в бумагах: объём есть, в системе его нет, вывезти нельзя.&lt;br&gt;&lt;br&gt;Ставим на учёт, дальше каждый рейс уходит с ЭСД и QR, сделка закрывается декларацией, период отчётом 1-ИЛ.&lt;br&gt;&lt;br&gt;Владимирская область.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
+          <t>Оформляем документы на пиловочник ели и сосны. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Закрываем учёт и сопроводительные документы: постановка объёма на баланс, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут, реквизиты. ЭСД за 15 минут.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_12__0.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__3.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -10548,7 +10688,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Вязники, Владимирская обл., ул. Ленина, 33</t>
+          <t>Мантурово, Костромская обл., ул. Советская, 22</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -10557,7 +10697,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2000</v>
+        <v>2800</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -10617,19 +10757,19 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>2026-09-14T03:00:00+03:00</t>
+          <t>2026-09-02T11:02:24+03:00</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2026-08-15T05:00:00+03:00</t>
+          <t>2026-08-16T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7655959812</t>
+          <t>7622497474</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -10637,6 +10777,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8262890900</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -10644,17 +10789,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Лес кругляк сосна, ЭСД на каждый рейс</t>
+          <t>Лес кругляк сосна, документы и ЭСД</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Оформляем ЭСД на сосновый кругляк. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;На каждую машину готовим сопроводительный документ с QR кодом. Водитель получает до выезда.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;Алтайский край.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
+          <t>Оформляем документы на сосновый кругляк в ФГИС ЛК. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;В работу входит: ЭСД на рейс, QR код для поста, декларация о сделке, отчёт 1-ИЛ. Если объём не заведён, ставим на учёт.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, маршрут, реквизиты. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Красноярский край, Ангара и Енисей.&lt;br&gt;&lt;br&gt;Напишите, что везёте и куда.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real234__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -10669,7 +10814,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Камень-на-Оби, Алтайский край, ул. Ленина, 48</t>
+          <t>Лесосибирск, Красноярский край, ул. Победы, 31</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -10678,7 +10823,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2200</v>
+        <v>3000</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -10738,19 +10883,19 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>2026-09-14T05:00:00+03:00</t>
+          <t>2026-09-03T04:37:01+03:00</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2026-08-15T07:00:00+03:00</t>
+          <t>2026-08-16T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4870626062</t>
+          <t>4897973128</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -10760,7 +10905,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8262876661</t>
+          <t>8263736000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -10770,17 +10915,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Пиловочник ель сосна, ЭСД и учёт</t>
+          <t>Пиловочник ель, ЭСД и QR код на вывоз</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Оформляем документы на пиловочник ели и сосны. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Закрываем учёт и сопроводительные документы: постановка объёма на баланс, ЭСД с QR на рейс, декларация о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;От вас порода, кубатура, маршрут, реквизиты. ЭСД за 15 минут.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
+          <t>Оформляем ЭСД на еловый пиловочник. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Порядок: присылаете маршрут и реквизиты, получаете ЭСД с QR кодом водителю на телефон. На посту проверка занимает минуту.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;ЭСД: 15 минут.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real22__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -10795,7 +10940,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Мантурово, Костромская обл., ул. Советская, 22</t>
+          <t>Чусовой, Пермский край, ул. Ленина, 34</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -10804,7 +10949,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2800</v>
+        <v>1000</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -10838,7 +10983,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Сосна</t>
+          <t>Ель</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -10864,19 +11009,19 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>2026-09-02T13:00:00+03:00</t>
+          <t>2026-09-02T07:42:11+03:00</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2026-08-16T09:00:00+03:00</t>
+          <t>2026-08-17T07:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7622497474</t>
+          <t>5975623537</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -10886,7 +11031,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8262890900</t>
+          <t>8263601318</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -10896,17 +11041,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Лес кругляк сосна, документы и ЭСД</t>
+          <t>Кругляк сосна и баланс, документы на вывоз</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Оформляем документы на сосновый кругляк в ФГИС ЛК. Услуга по документам, лес не продаём.&lt;br&gt;&lt;br&gt;В работу входит: ЭСД на рейс, QR код для поста, декларация о сделке, отчёт 1-ИЛ. Если объём не заведён, ставим на учёт.&lt;br&gt;&lt;br&gt;От вас: порода, кубатура, маршрут, реквизиты. Кабинет и подпись не нужны.&lt;br&gt;&lt;br&gt;Красноярский край, Ангара и Енисей.&lt;br&gt;&lt;br&gt;Напишите, что везёте и куда.</t>
+          <t>Оформляем документы на сосновый кругляк и баланс. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Что делаем: ЭСД с QR на рейс, декларация о сделке, постановка объёма на учёт, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Типовой ЭСД 15 минут. По постановке на учёт срок называем после разбора документов.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/real234__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -10921,7 +11066,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Лесосибирск, Красноярский край, ул. Победы, 31</t>
+          <t>Красновишерск, Пермский край, ул. Гагарина, 6</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -10930,7 +11075,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3000</v>
+        <v>1400</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -10990,19 +11135,19 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>2026-09-03T06:35:00+03:00</t>
+          <t>2026-09-01T14:11:29+03:00</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-08-16T12:00:00+03:00</t>
+          <t>2026-08-17T09:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4897973128</t>
+          <t>8561800688</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11012,7 +11157,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8263736000</t>
+          <t>8263343835</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -11022,17 +11167,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Пиловочник ель, ЭСД и QR код на вывоз</t>
+          <t>Баланс ель на комбинат, ЭСД по договору</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Оформляем ЭСД на еловый пиловочник. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Порядок: присылаете маршрут и реквизиты, получаете ЭСД с QR кодом водителю на телефон. На посту проверка занимает минуту.&lt;br&gt;&lt;br&gt;Дополнительно: декларация о сделке, отчёт 1-ИЛ, постановка объёма на учёт.&lt;br&gt;&lt;br&gt;ЭСД: 15 минут.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и маршрут.</t>
+          <t>Ведём документы по поставкам балансовой древесины на комбинат. Услуга по договору.&lt;br&gt;&lt;br&gt;При регулярных поставках документы идут потоком. Оформляем ЭСД на каждую машину, ведём декларации, закрываем отчётность.&lt;br&gt;&lt;br&gt;Отдельно следим, чтобы объёмы по документам сходились с принятыми. Расхождение всплывает на приёмке.&lt;br&gt;&lt;br&gt;Томская область.&lt;br&gt;&lt;br&gt;Напишите объём в месяц.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -11047,7 +11192,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Чусовой, Пермский край, ул. Ленина, 34</t>
+          <t>Асино, Томская обл., ул. Ленина, 42</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -11056,7 +11201,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -11116,19 +11261,19 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>2026-09-02T09:40:00+03:00</t>
+          <t>2026-09-04T11:05:03+03:00</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-08-17T07:00:00+03:00</t>
+          <t>2026-08-17T12:00:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5975623537</t>
+          <t>2239987508</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11138,7 +11283,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8263601318</t>
+          <t>8263149501</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -11148,17 +11293,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Кругляк сосна и баланс, документы на вывоз</t>
+          <t>Пиловочник хвойный, оформим вывоз и учёт</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Оформляем документы на сосновый кругляк и баланс. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Что делаем: ЭСД с QR на рейс, декларация о сделке, постановка объёма на учёт, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Типовой ЭСД 15 минут. По постановке на учёт срок называем после разбора документов.&lt;br&gt;&lt;br&gt;Пермский край.&lt;br&gt;&lt;br&gt;Напишите объём и куда везёте.</t>
+          <t>Оформляем документы на хвойный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Берём на себя постановку объёма на учёт, ЭСД с QR на каждую машину, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Работаем и с разовой отгрузкой, и с регулярными поставками. Во втором случае удобнее вести одним исполнителем, чтобы объёмы не разъезжались между документами.&lt;br&gt;&lt;br&gt;Вологодская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_5__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_3__2.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -11173,7 +11318,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Красновишерск, Пермский край, ул. Гагарина, 6</t>
+          <t>Великий Устюг, Вологодская обл., ул. Красная, 12</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -11182,7 +11327,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -11242,19 +11387,19 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>2026-09-01T16:10:00+03:00</t>
+          <t>2026-09-03T07:55:16+03:00</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2026-08-17T09:00:00+03:00</t>
+          <t>2026-08-17T14:30:00+03:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8561800688</t>
+          <t>8000860251</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -11264,7 +11409,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8263343835</t>
+          <t>8263292303</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -11274,17 +11419,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Баланс ель на комбинат, ЭСД по договору</t>
+          <t>Лес кругляк ель, поставим на учёт</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ведём документы по поставкам балансовой древесины на комбинат. Услуга по договору.&lt;br&gt;&lt;br&gt;При регулярных поставках документы идут потоком. Оформляем ЭСД на каждую машину, ведём декларации, закрываем отчётность.&lt;br&gt;&lt;br&gt;Отдельно следим, чтобы объёмы по документам сходились с принятыми. Расхождение всплывает на приёмке.&lt;br&gt;&lt;br&gt;Томская область.&lt;br&gt;&lt;br&gt;Напишите объём в месяц.</t>
+          <t>Ставим еловый кругляк на учёт в ФГИС ЛК. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Если объём нигде не числится, партию нельзя ни продать, ни вывезти. Это решается.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём на баланс, оформляем ЭСД с QR на отгрузки, закрываем декларацию и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/start_1__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_6__1.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -11299,7 +11444,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Асино, Томская обл., ул. Ленина, 42</t>
+          <t>Шарья, Костромская обл., ул. Октябрьская, 15</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -11308,7 +11453,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1600</v>
+        <v>2600</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -11368,262 +11513,10 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>2026-09-04T13:05:00+03:00</t>
+          <t>2026-09-01T12:43:57+03:00</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
-        <is>
-          <t>2026-08-17T12:00:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2239987508</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>8263149501</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Пиловочник хвойный, оформим вывоз и учёт</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Оформляем документы на хвойный пиловочник. Услуга, лес не продаём.&lt;br&gt;&lt;br&gt;Берём на себя постановку объёма на учёт, ЭСД с QR на каждую машину, декларацию о сделке, отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Работаем и с разовой отгрузкой, и с регулярными поставками. Во втором случае удобнее вести одним исполнителем, чтобы объёмы не разъезжались между документами.&lt;br&gt;&lt;br&gt;Вологодская область.&lt;br&gt;&lt;br&gt;Напишите объём и направление.</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/doc_14__0.jpg</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Великий Устюг, Вологодская обл., ул. Красная, 12</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>2400</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Сосна</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB34" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>2026-09-03T09:35:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>2026-08-17T14:30:00+03:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>8000860251</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>8263292303</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>79852671426</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Лес кругляк ель, поставим на учёт</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Ставим еловый кругляк на учёт в ФГИС ЛК. Услуга, древесину не продаём.&lt;br&gt;&lt;br&gt;Если объём нигде не числится, партию нельзя ни продать, ни вывезти. Это решается.&lt;br&gt;&lt;br&gt;Что делаем: заводим объём на баланс, оформляем ЭСД с QR на отгрузки, закрываем декларацию и отчёт 1-ИЛ.&lt;br&gt;&lt;br&gt;Костромская область.&lt;br&gt;&lt;br&gt;Напишите породу и кубатуру.</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/kr_4__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>По телефону и в сообщениях</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Ремонт и строительство</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Шарья, Костромская обл., ул. Октябрьская, 15</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>ПВЗ</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>2600</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Стройматериалы</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>В наличии</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Пиломатериалы</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Лес-кругляк</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Ель</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="AB35" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>230</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>orbizona-shop@yandex.ru</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>ЕГАИС ЛЕС документация</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>2026-09-01T14:42:00+03:00</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
         <is>
           <t>2026-08-17T19:00:00+03:00</t>
         </is>
@@ -13375,7 +13268,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-07-24T16:06:34+03:00</t>
+          <t>2026-09-05T17:37:37+03:00</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -13467,7 +13360,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-07-30T11:36:45+03:00</t>
+          <t>2026-09-05T17:48:14+03:00</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -13559,7 +13452,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-08-06T15:06:02+03:00</t>
+          <t>2026-09-05T17:37:31+03:00</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -13651,7 +13544,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-08-02T08:06:18+03:00</t>
+          <t>2026-09-05T17:37:31+03:00</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -13743,7 +13636,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-08-02T10:50:49+03:00</t>
+          <t>2026-09-05T17:28:36+03:00</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -13835,7 +13728,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-08-05T14:06:16+03:00</t>
+          <t>2026-09-05T17:59:49+03:00</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -13855,6 +13748,11 @@
           <t>BBL</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8231854664</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>79852671426</t>
@@ -13917,7 +13815,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-08T09:00:00+03:00</t>
+          <t>2026-09-08T09:06:12+03:00</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -1679,7 +1679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="21"/>
@@ -1841,6 +1841,11 @@
           <t>DateBegin</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>DateEnd</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -2212,6 +2217,11 @@
           <t>2026-09-05T17:48:15+03:00</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:48:15+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2339,6 +2349,11 @@
           <t>2026-09-05T18:17:30+03:00</t>
         </is>
       </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2026-09-05T18:17:30+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2471,6 +2486,11 @@
           <t>2026-09-05T17:31:49+03:00</t>
         </is>
       </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:31:49+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2603,6 +2623,11 @@
           <t>2026-09-05T17:37:35+03:00</t>
         </is>
       </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:37:35+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2723,6 +2748,11 @@
           <t>2026-09-13T14:16:44+03:00</t>
         </is>
       </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2026-09-13T14:16:44+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2848,6 +2878,11 @@
       <c r="AC10" t="inlineStr">
         <is>
           <t>2026-08-09T09:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2026-09-08T07:05:42+03:00</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="25"/>
@@ -3633,6 +3668,11 @@
           <t>DateBegin</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>DateEnd</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -4016,6 +4056,11 @@
           <t>Активно</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:28:41+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4155,6 +4200,11 @@
           <t>Активно</t>
         </is>
       </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2026-09-05T18:11:54+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4285,6 +4335,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>Активно</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:31:39+03:00</t>
         </is>
       </c>
     </row>
@@ -4426,6 +4481,11 @@
           <t>Активно</t>
         </is>
       </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2026-09-05T18:23:33+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4565,6 +4625,11 @@
           <t>2026-08-09T07:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2026-09-08T05:05:32+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4702,6 +4767,11 @@
           <t>2026-08-13T16:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2026-09-12T14:06:30+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4839,6 +4909,11 @@
           <t>2026-08-14T07:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2026-09-13T05:05:59+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4976,6 +5051,11 @@
           <t>2026-08-14T14:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:05:37+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5113,6 +5193,11 @@
           <t>2026-08-15T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>2026-09-14T10:06:12+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5250,6 +5335,11 @@
           <t>2026-08-15T14:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>2026-09-19T12:24:56+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5387,6 +5477,11 @@
           <t>2026-08-16T05:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>2026-09-16T11:36:22+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5524,6 +5619,11 @@
           <t>2026-08-16T07:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2026-09-27T10:39:59+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5661,6 +5761,11 @@
           <t>2026-08-16T14:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:27:46+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5798,6 +5903,11 @@
           <t>2026-08-17T05:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>2026-09-16T11:36:22+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5935,6 +6045,11 @@
           <t>2026-08-17T16:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>2026-09-19T06:18:38+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6072,6 +6187,11 @@
           <t>2026-08-17T17:30:00+03:00</t>
         </is>
       </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>2026-09-27T07:37:04+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6209,6 +6329,11 @@
           <t>2026-08-18T05:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>2026-09-17T12:15:03+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6346,6 +6471,11 @@
           <t>2026-08-18T07:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>2026-09-18T06:21:17+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6483,6 +6613,11 @@
           <t>2026-08-18T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>2026-09-30T07:42:26+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6618,6 +6753,11 @@
       <c r="AC24" t="inlineStr">
         <is>
           <t>2026-08-18T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>2026-09-20T12:02:10+03:00</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ33"/>
+  <dimension ref="A1:AK33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -7475,6 +7615,11 @@
           <t>DateBegin</t>
         </is>
       </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>DateEnd</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -7918,6 +8063,11 @@
           <t>Активно</t>
         </is>
       </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2026-09-05T18:05:38+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8055,6 +8205,11 @@
           <t>Активно</t>
         </is>
       </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:28:42+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8192,6 +8347,11 @@
           <t>Активно</t>
         </is>
       </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:53:50+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8329,6 +8489,11 @@
           <t>Активно</t>
         </is>
       </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:48:13+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8466,6 +8631,11 @@
           <t>Активно</t>
         </is>
       </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2026-09-05T18:05:47+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8603,6 +8773,11 @@
           <t>Активно</t>
         </is>
       </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:28:42+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8733,6 +8908,11 @@
           <t>2026-07-17T07:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2026-09-16T11:36:20+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8851,12 +9031,17 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026-08-31T17:06:02+03:00</t>
+          <t>2026-09-30T18:05:25+03:00</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>2026-08-01T19:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2026-09-30T18:05:25+03:00</t>
         </is>
       </c>
     </row>
@@ -8987,6 +9172,11 @@
           <t>2026-08-10T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2026-09-09T04:05:12+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9115,6 +9305,11 @@
           <t>2026-08-10T08:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:35:36+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9243,6 +9438,11 @@
           <t>2026-08-08T06:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2026-09-07T04:05:22+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9371,6 +9571,11 @@
           <t>2026-08-08T07:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2026-09-07T05:35:06+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9499,6 +9704,11 @@
           <t>2026-08-08T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2026-09-07T07:06:49+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9627,6 +9837,11 @@
           <t>2026-08-08T10:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2026-09-07T08:36:15+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9755,6 +9970,11 @@
           <t>2026-08-08T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2026-09-07T10:06:19+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9883,6 +10103,11 @@
           <t>2026-08-09T05:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-09-08T03:05:09+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10009,6 +10234,11 @@
           <t>2026-08-13T18:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2026-09-12T16:05:25+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10135,6 +10365,11 @@
           <t>2026-08-14T05:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2026-09-13T03:05:05+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10261,6 +10496,11 @@
           <t>2026-08-14T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2026-09-13T07:06:27+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10387,6 +10627,11 @@
           <t>2026-08-14T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2026-09-13T10:05:34+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10513,6 +10758,11 @@
           <t>2026-08-15T05:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-09-14T03:05:16+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10639,6 +10889,11 @@
           <t>2026-08-15T07:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-09-14T05:05:44+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10765,6 +11020,11 @@
           <t>2026-08-16T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-09-02T11:02:24+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10891,6 +11151,11 @@
           <t>2026-08-16T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-09-03T04:37:01+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11017,6 +11282,11 @@
           <t>2026-08-17T07:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-09-02T07:42:11+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11143,6 +11413,11 @@
           <t>2026-08-17T09:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-09-01T14:11:29+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11269,6 +11544,11 @@
           <t>2026-08-17T12:00:00+03:00</t>
         </is>
       </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2026-09-04T11:05:03+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11395,6 +11675,11 @@
           <t>2026-08-17T14:30:00+03:00</t>
         </is>
       </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-09-03T07:55:16+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11519,6 +11804,11 @@
       <c r="AJ33" t="inlineStr">
         <is>
           <t>2026-08-17T19:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>2026-09-01T12:43:57+03:00</t>
         </is>
       </c>
     </row>
@@ -12915,7 +13205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="14"/>
@@ -13030,6 +13320,11 @@
           <t>DateBegin</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>DateEnd</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customFormat="1" customHeight="1" s="6">
       <c r="A3" s="6" t="inlineStr">
@@ -13276,6 +13571,11 @@
           <t>ЕГАИС ЛЕС документация</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:37:37+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13368,6 +13668,11 @@
           <t>ЕГАИС ЛЕС документация</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:48:14+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13460,6 +13765,11 @@
           <t>ЕГАИС ЛЕС документация</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:37:31+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13552,6 +13862,11 @@
           <t>ЕГАИС ЛЕС документация</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:37:31+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13644,6 +13959,11 @@
           <t>ЕГАИС ЛЕС документация</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:28:36+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13736,6 +14056,11 @@
           <t>ЕГАИС ЛЕС документация</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-09-05T17:59:49+03:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13826,6 +14151,11 @@
       <c r="T11" t="inlineStr">
         <is>
           <t>2026-08-09T11:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-09-08T09:06:12+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -3509,7 +3509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AD27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="25"/>
@@ -6758,6 +6758,417 @@
       <c r="AD24" t="inlineStr">
         <is>
           <t>2026-09-20T12:02:10+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4525704698</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/5855275648/14_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_11_3.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Документы на лес для ИП и ООО</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Поможем ИП и ООО работать с лесом так, чтобы вопросов не было ни у покупателя, ни на дороге.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Нужно тем, у кого древесина есть, а в ФГИС ЛК по ней пусто: купили у населения, взяли по порубочному билету, заготовили сами.&lt;/p&gt;&lt;p&gt;Заведём ваш объём в систему, дальше ЭСД с QR за 15 минут, декларация о сделке, отчёт 1-ИЛ и места складирования.&lt;/p&gt;&lt;p&gt;Свой кабинет и электронная подпись вам не нужны, работы от 3000 рублей.&lt;/p&gt;&lt;p&gt;Нижний Ломов, Нижнеломовский район, Пензенская область.&lt;br&gt;Напишите, что у вас за партия.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Нижний Ломов, Нижнеломовский р-н, Пензенская обл., ул. Розы Люксембург, 4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-04T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2026-09-04T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>2026-10-04T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6693225801</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/2872293673/21_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_12_3.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>700</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ЭСД на древесину для заготовителей</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Сделаем так, чтобы каждый рейс уходил с законным документом на руках, а не ждал бумаг.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Как это работает:&lt;br&gt;1. Вы называете породу, кубатуру и маршрут&lt;br&gt;2. Сделаем QR код на перевозку в течение 15 минут, хоть перед самым выездом&lt;br&gt;3. Дальше держим декларацию о сделке, отчёт 1-ИЛ и места складирования&lt;/p&gt;&lt;p&gt;Свой кабинет в ФГИС ЛК и электронная подпись не понадобятся, всё делаем со своей стороны.&lt;/p&gt;&lt;p&gt;Спас-Клепики, Клепиковский район, Рязанская область.&lt;br&gt;Напишите, когда выезд.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Спас-Клепики, Клепиковский р-н, Рязанская обл., ул. Просвещения, 8</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-05T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2026-09-05T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>2026-10-05T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2957273391</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/8857956292/18_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_13_3.jpg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Предложение услуг</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>800</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Отчёт 1-ИЛ и лесная декларация</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Поможем сдать отчётность по лесу вовремя и без отказов, даже если сроки уже поджимают.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- сдадим отчёт 1-ИЛ, от 3000 руб&lt;br&gt;- подготовим и подадим лесную декларацию&lt;br&gt;- проведём декларацию о сделке с древесиной&lt;br&gt;- оформим ЭСД с QR на рейс за 15 минут&lt;/p&gt;&lt;p&gt;Точную цену называем после разбора вашей ситуации. Свой кабинет в ФГИС ЛК и подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Инза, Инзенский район, Ульяновская область.&lt;br&gt;Напишите, какой период надо закрыть.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Инза, Инзенский р-н, Ульяновская обл., ул. Красных Бойцов, 2</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Деловые услуги</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Консультирование</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Другое</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>4–7 лет</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Удалённо</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Физические лица | ИП | ООО | АО | НКО | Другие юридические лица</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Понедельник | Вторник | Среда | Четверг | Пятница | Суббота | Воскресенье</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Своя услуга|Ведение фгис ЕГАИС лк|5000|Да|за услугу
+Своя услуга|Отгрузка фгис лес|300|Да|за услугу
+Своя услуга|Оформление путевых листов для перевозки леса|350|Да|за услугу</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-05T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2026-09-05T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>2026-10-05T08:00:00+03:00</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK33"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -11809,6 +12220,2778 @@
       <c r="AK33" t="inlineStr">
         <is>
           <t>2026-09-01T12:43:57+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9242345372</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (оформим ЭСД на рейс)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Закроем бумаги по лесу чужими руками: вы заготавливаете и возите, документы ведём мы.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Что берём на себя и сколько стоит:&lt;br&gt;- происхождение древесины по договору купли-продажи, от 2400 руб&lt;br&gt;- ЭСД с QR на каждый рейс, 15 минут&lt;br&gt;- декларация о сделке&lt;br&gt;- отчёт 1-ИЛ и места складирования&lt;/p&gt;&lt;p&gt;Свой кабинет в системе и электронная подпись вам не понадобятся. Срок по учёту назовём, когда разберём ситуацию.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Чайковский городской округ, Пермский край.&lt;/p&gt;&lt;p&gt;Напишите, куда идёт машина.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Чайковский, Чайковский городской округ, Пермский край, ул. Ленина, 61</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>2026-10-01T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>2026-09-01T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2026-10-01T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>6234777324</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Пиловочник хвойный, документы на вывоз</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Поможем вывезти и продать лес законно, даже если в ФГИС ЛК по вам сейчас пусто.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Оформим происхождение вашей древесины по договору купли-продажи от нашего объёма, дальше выпишем ЭСД с QR на рейс за 15 минут, подадим декларацию о сделке, закроем отчёт 1-ИЛ и места складирования.&lt;/p&gt;&lt;p&gt;Кабинет в системе и подпись вам не нужны, работы от 3000 рублей.&lt;/p&gt;&lt;p&gt;Берём хвойный пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Оса, Осинский городской округ, Пермский край. Напишите, сколько кубов и куда рейс.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/15/15_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_03_3.jpg</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Оса, Осинский городской округ, Пермский край, ул. Свердлова, 21</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>1900</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB35" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>2026-10-01T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>2026-09-01T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-10-01T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3180295914</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ель кругляк, поставим объём на учёт</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Чтобы машины не простаивали без документа, &lt;strong&gt;заведём ваш лес в ФГИС ЛК&lt;/strong&gt; и дальше ведём его сами.&lt;/p&gt;&lt;p&gt;1. Смотрим, что у вас на руках по лесу&lt;br&gt;2. Оформляем древесину по договору купли-продажи от нашего объёма, кубатура встаёт на баланс&lt;br&gt;3. Выписываем ЭСД с QR на рейс за 15 минут, подаём декларацию о сделке, закрываем отчёт 1-ИЛ&lt;/p&gt;&lt;p&gt;От вас нужны объём и маршрут. Кабинет и электронная подпись не потребуются.&lt;/p&gt;&lt;p&gt;Еловый кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Верещагинский городской округ, Пермский край.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов лежит.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_02.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Верещагино, Верещагинский городской округ, Пермский край, ул. Октябрьская, 26</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB36" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>2026-10-01T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>2026-09-01T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2026-10-01T14:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>8662935969</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Пиловочник еловый, учёт объёмов в ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Закроем бумажную часть по лесу за вас: вы возите и продаёте, мы держим ФГИС ЛК.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- ставим вашу кубатуру на баланс по договору купли-продажи, от 3000 руб&lt;br&gt;- ЭСД с QR на рейс, 15 минут&lt;br&gt;- декларация о сделке&lt;br&gt;- отчёт 1-ИЛ и места складирования&lt;/p&gt;&lt;p&gt;Точная цена по объёму. Свой кабинет и электронная подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Берём еловый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Пучеж, Пучежский район, Ивановская область. Напишите объём партии, посчитаем.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_17_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_04_3.jpg</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Пучеж, Пучежский р-н, Ивановская обл., ул. Заводская, 27</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB37" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>2026-10-01T16:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>2026-09-01T18:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2026-10-01T16:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7741718925</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Баланс берёзовый (QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Поможем продать лес, который нигде не числится, и спокойно получить за него деньги.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Купили у населения, а по бумагам древесины нет? Закроем происхождение через свой объём и договор купли-продажи.&lt;br&gt;Машина под погрузкой? Выпишем накладную на перевозку с QR за 15 минут.&lt;br&gt;Просят декларацию о сделке, отчёт 1-ИЛ и места складирования? Ведём сами.&lt;/p&gt;&lt;p&gt;Свой кабинет и электронная подпись не нужны.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Чернушинский городской округ, Пермский край.&lt;/p&gt;&lt;p&gt;Напишите объём и плечо вывоза.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_03.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__3.jpg</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Чернушка, Чернушинский городской округ, Пермский край, ул. Мира, 13</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>650</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB38" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>2026-10-02T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>2026-09-02T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-10-02T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3048976380</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Пиловочник сосна, поставим объём на учёт</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Поможем продать лес, который нигде не числится, и довести партию до отгрузки.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;1. Разбираем, что у вас есть по лесу, и оформляем происхождение договором купли-продажи&lt;br&gt;2. Проводим сделку в ФГИС ЛК и подаём декларацию&lt;br&gt;3. Дальше QR код на каждый рейс за 15 минут, отчёт 1-ИЛ, места складирования&lt;/p&gt;&lt;p&gt;От вас данные по лесу и маршруту, кабинет и подпись не нужны.&lt;/p&gt;&lt;p&gt;Берём сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Воткинск, Воткинский район, Удмуртия. Напишите, сколько кубов лежит.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_18_1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_06_3.jpg</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Воткинск, Воткинский р-н, Удмуртская Республика, ул. Кирова, 7</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB39" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>2026-10-02T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>2026-09-02T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>2026-10-02T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7259825157</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Лес кругляк сосна, документы ФГИС ЛК</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Сделаем так, чтобы комбинат принял партию с первого раза и не развернул по бумагам.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Пригодится, если:&lt;br&gt;- лес заготовлен или куплен, а в ФГИС ЛК по вам пусто&lt;br&gt;- покупатель просит декларацию о сделке и ЭСД&lt;br&gt;- машина готова, а документа на рейс нет&lt;/p&gt;&lt;p&gt;Поможем с документацией на вашу древесину: подадим декларацию о сделке, поставим кубатуру на баланс, дадим ЭСД с QR за 15 минут, закроем 1-ИЛ. Кабинет и подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Кинешемский район, Ивановская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_05.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_3.jpg</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Кинешма, Кинешемский р-н, Ивановская обл., ул. Советская, 1</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>2200</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB40" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>2026-10-02T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>2026-09-02T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>2026-10-02T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>9302262641</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Лес кругляк хвойный (QR код на вывоз)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Сделаем так, чтобы машины не простаивали под погрузкой без документа.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Нужен QR код на вывоз? Сделаем в течение 15 минут, хоть перед самым выездом.&lt;br&gt;Древесина нигде не числится? Оформим её по договору купли-продажи от нашего объёма.&lt;br&gt;Покупатель просит декларацию о сделке? Подадим.&lt;br&gt;Спрашивают 1-ИЛ и места складирования? Ведём сами.&lt;/p&gt;&lt;p&gt;Кабинета и подписи от вас не потребуется.&lt;/p&gt;&lt;p&gt;Берём хвойный кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Солигалич, Солигаличский округ, Костромская область. Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/mln/14/14_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_05_3.jpg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Солигалич, Солигаличский муниципальный округ, Костромская обл., ул. Коммунистическая, 3</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB41" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>2026-10-02T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>2026-09-02T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>2026-10-02T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2805852131</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Доска обрезная и брус (документы ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Поможем спокойно отгружать пиломатериал, когда по системе за вами древесина не числится.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Пригодится тем, кто:&lt;br&gt;- пилит на своей раме&lt;br&gt;- купил кругляк у населения&lt;br&gt;- слышит от покупателя просьбу дать декларацию&lt;/p&gt;&lt;p&gt;Выпишем накладную на перевозку с QR за 15 минут, проведём сделку в ФГИС ЛК, отчитаемся по 1-ИЛ, заведём места складирования. Кабинет и подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Берём доску обрезную и брус хвойных пород.&lt;/p&gt;&lt;p&gt;Шуя, Шуйский район, Ивановская область. Напишите кубатуру и адрес выгрузки.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_06.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Шуя, Шуйский р-н, Ивановская обл., ул. Свердлова, 14</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Доска</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB42" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>2026-10-02T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>2026-09-02T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>2026-10-02T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>7453866442</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Сосна кругляк (декларация о сделке)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Сделаем так, чтобы покупатель принял партию с первого раза и не развернул машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Как идёт работа:&lt;br&gt;1. Разбираем, откуда у вас лес и чего не хватает в бумагах&lt;br&gt;2. Оформляем древесину по договору купли-продажи от нашего объёма&lt;br&gt;3. Проводим декларацию о сделке, а на каждый рейс даём ЭСД с QR за 15 минут&lt;/p&gt;&lt;p&gt;Ни своего кабинета, ни электронной подписи от вас не потребуется, всё удалённо.&lt;/p&gt;&lt;p&gt;Работаем по сосновому кругляку 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Алатырь, Алатырский округ, Чувашия.&lt;br&gt;Напишите, кому и куда отгружаете.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1803116670/16_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_07_3.jpg</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Алатырь, Алатырский муниципальный округ, Чувашская Республика, ул. Ленина, 12</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>2800</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>2026-10-03T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>2026-09-03T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>2026-10-03T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>7452193497</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Берёза кругляк (накладная на перевозку)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Поможем вывезти и продать лес законно, даже если сейчас в ФГИС ЛК по вам пусто.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Выпишем накладную на перевозку с QR на каждый рейс за 15 минут, а происхождение вашей древесины закроем своим объёмом и договором купли-продажи. Дальше держим бумаги сами: декларация о сделке, отчёт 1-ИЛ, места складирования.&lt;/p&gt;&lt;p&gt;Кабинет в системе и электронная подпись вам не нужны, срок по учёту назовём после разбора ситуации.&lt;/p&gt;&lt;p&gt;Берёзовый кругляк 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Вичугский район, Ивановская область.&lt;/p&gt;&lt;p&gt;Напишите объём рейса.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_07.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Вичуга, Вичугский р-н, Ивановская обл., ул. Коминтерна, 25</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>550</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB44" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>2026-10-03T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>2026-09-03T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-10-03T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>7959113642</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (QR код на отгрузку)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Поможем работать с лесом, когда своего кабинета в ФГИС ЛК у вас нет и заводить его некогда.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Древесина есть, а в документах её нет? Поможем с документацией на вашу партию от начала до отгрузки.&lt;br&gt;Нужен QR на отгрузку? Сделаем ЭСД за 15 минут, хоть перед самым выездом.&lt;br&gt;Требуют декларацию о сделке и отчёт 1-ИЛ? Подаём и закрываем сами.&lt;/p&gt;&lt;p&gt;Электронная подпись не нужна, ездить никуда не надо.&lt;/p&gt;&lt;p&gt;Берём сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Городище, Городищенский район, Пензенская область.&lt;br&gt;Напишите объём рейса.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/7232164186/19_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_09_3.jpg</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Городище, Городищенский р-н, Пензенская обл., ул. Полевая, 8</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>850</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>2026-10-03T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>2026-09-03T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-10-03T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>8379167567</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Баланс еловый (ЭСД на каждую машину)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;С лесом можно работать и без своего кабинета в ФГИС ЛК, всё оформим на своей стороне.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Подойдёт вам, если:&lt;br&gt;- древесина лежит на площадке, а в системе её нет&lt;br&gt;- комбинат просит декларацию и ЭСД на каждую машину&lt;br&gt;- некому вести отчёт 1-ИЛ и места складирования&lt;/p&gt;&lt;p&gt;Поставим вашу кубатуру на баланс, заведём места складирования, выпишем ЭСД с QR за 15 минут и будем держать отчётность в порядке.&lt;/p&gt;&lt;p&gt;Еловый баланс 2 и 4 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Поназыревский округ, Костромская область.&lt;/p&gt;&lt;p&gt;Напишите объём в неделю.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_11.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_3.jpg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Поназырево, Поназыревский муниципальный округ, Костромская обл., ул. Свободы, 1</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>700</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>2026-10-03T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>2026-09-03T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-10-03T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6623524838</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, накладная на перевозку</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Перестанете бояться проверок на дороге: у водителя будет документ, который читается по QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Выпишем накладную на перевозку вашей древесины и сопроводительный документ на рейс за 15 минут, следом подадим декларацию о сделке и закроем отчёт 1-ИЛ. Происхождение леса подтверждаем своим объёмом, поэтому машина идёт с чистыми бумагами.&lt;/p&gt;&lt;p&gt;Кабинет в ФГИС ЛК и подпись вам не нужны, работы от 3000 рублей.&lt;/p&gt;&lt;p&gt;Берём еловый пиловочник 4 и 6 метров, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Ядрин, Ядринский округ, Чувашия.&lt;br&gt;Напишите, откуда и куда идёт лес.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/9140846526/17_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_08_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_08_3.jpg</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Ядрин, Ядринский муниципальный округ, Чувашская Республика, ул. Молодёжная, 3</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>2026-10-03T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>2026-09-03T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2026-10-03T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6312395486</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Пиловочник хвойный, QR код за 15 минут</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Перестанете бояться проверок на дороге: на каждый рейс будет свой документ с QR.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Машина под погрузкой? Сделаем QR код в течение 15 минут.&lt;br&gt;Древесины нет в ФГИС ЛК? Проведём её по договору купли-продажи от нашего объёма.&lt;br&gt;Просят декларацию о сделке и отчёт 1-ИЛ? Подадим за вас.&lt;br&gt;Что нужно от вас? Порода, объём и маршрут, ни кабинета, ни подписи.&lt;/p&gt;&lt;p&gt;Хвойный пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Кологривский округ, Костромская область.&lt;/p&gt;&lt;p&gt;Напишите, когда выезд.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_09.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__3.jpg</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Кологрив, Кологривский муниципальный округ, Костромская обл., ул. Набережная, 25</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB48" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>2026-10-04T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>2026-09-04T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-10-04T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4914944791</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Пиловочник сосновый, ЭСД на каждый рейс</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Не будете тратить недели на разбор с документами: заберём лесные бумаги на себя.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Что делаем:&lt;br&gt;- проведём сделку от начала до отгрузки, от 3000 руб&lt;br&gt;- ЭСД с QR на каждый рейс, 15 минут&lt;br&gt;- декларация о сделке с древесиной&lt;br&gt;- отчёт 1-ИЛ и места складирования&lt;/p&gt;&lt;p&gt;Цена по объёму работ. Свой кабинет и электронная подпись вам не понадобятся.&lt;/p&gt;&lt;p&gt;Берём сосновый пиловочник 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Барыш, Барышский район, Ульяновская область.&lt;br&gt;Напишите, сколько кубов и когда рейс.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/egais_2026-07-21/1505263438/22_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_10_3.jpg</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Барыш, Барышский р-н, Ульяновская обл., ул. Радищева, 30</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB49" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>2026-10-04T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>2026-09-04T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2026-10-04T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4806613432</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ель баланс на комбинат (декларация сделки)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Сдадите отчётность вовремя и без отказов, разбираться в системе самому не придётся.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;1. Смотрим, что у вас на руках по лесу&lt;br&gt;2. Берём древесину на себя по договору купли-продажи, кубатура встаёт на баланс&lt;br&gt;3. Проводим сделку до отгрузки: декларация о сделке, ЭСД с QR на рейс за 15 минут, отчёт 1-ИЛ, места складирования&lt;/p&gt;&lt;p&gt;Кабинет и электронная подпись вам не нужны, работаем удалённо.&lt;/p&gt;&lt;p&gt;Еловый баланс на комбинат 2 и 4 метра.&lt;/p&gt;&lt;p&gt;Балезинский район, Удмуртия.&lt;/p&gt;&lt;p&gt;Напишите, на какой комбинат везёте.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_13.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Балезино, Балезинский р-н, Удмуртская Республика, ул. Кирова, 2</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>750</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB50" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>2026-10-04T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>2026-09-04T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>2026-10-04T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7032017608</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Кряж берёзовый (объём на баланс ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Не придётся тратить недели на разбор с документами, сделаем всё за вас, пока вы возите лес.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Заведём ваш объём в систему через договор купли-продажи, дальше выпишем ЭСД с QR на каждый рейс за 15 минут, подадим декларацию о сделке, сдадим отчёт 1-ИЛ и лесную декларацию, заведём места складирования. Свой кабинет и электронная подпись вам не нужны, срок по учёту скажем после разбора.&lt;/p&gt;&lt;p&gt;Берём берёзовый кряж 3 метра, диаметр от 26 см.&lt;/p&gt;&lt;p&gt;Горномарийский район, Марий Эл. Напишите, сколько кубов готово.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_14.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Козьмодемьянск, Горномарийский р-н, Республика Марий Эл, ул. Советская, 20</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB51" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>2026-10-04T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>2026-09-04T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>2026-10-04T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2952172850</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник, документы на вывоз</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Продавайте лес спокойно и получайте деньги без задержек из-за бумаг.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Работы и цены:&lt;br&gt;- оформление леса по договору купли-продажи от нашего объёма, от 2600 руб&lt;br&gt;- накладная на перевозку с QR, 15 минут&lt;br&gt;- декларация о сделке в ФГИС ЛК&lt;br&gt;- отчёт 1-ИЛ и места складирования&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут. Свой кабинет и электронная подпись не нужны.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Звениговский район, Марий Эл. Напишите, какой объём набирается за месяц.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_15.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__3.jpg</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Звенигово, Звениговский р-н, Республика Марий Эл, ул. Ленина, 39</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>2600</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB52" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>2026-10-05T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>2026-09-05T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>2026-10-05T06:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1891551216</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Лес пиловочник сосна (декларация и учёт)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Ваш водитель выедет с готовым документом на рейс, а не на авось.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;1. Присылаете объём и то, что есть у вас по лесу&lt;br&gt;2. Оформляем происхождение древесины и подаём декларацию о сделке&lt;br&gt;3. Выписываем накладную на перевозку с QR за 15 минут, ведём отчёт 1-ИЛ и места складирования&lt;/p&gt;&lt;p&gt;Свой кабинет в системе и электронная подпись не нужны.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Ковылкинский район, Мордовия. Напишите, сколько рейсов в неделю.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_16.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_01_3.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_02_3.jpg</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Ковылкино, Ковылкинский р-н, Республика Мордовия, ул. Большевистская, 22</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB53" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>2026-10-05T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>2026-09-05T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>2026-10-05T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>8759273463</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Дрова берёзовые и баланс, накладная и QR</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Покупатель заберёт партию без единого вопроса к бумагам.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Поможем с документацией на вашу древесину: покажем её происхождение через наш объём, проведём сделку в ФГИС ЛК, сделаем QR код на каждый рейс за 15 минут, сдадим отчёт 1-ИЛ и лесную декларацию, заведём места складирования. Кабинет в системе и электронная подпись вам не нужны, всё делаем удалённо, срок по учёту скажем после разбора.&lt;/p&gt;&lt;p&gt;Берём берёзовые дрова и баланс 2 и 3 метра.&lt;/p&gt;&lt;p&gt;Краснослободский район, Мордовия. Напишите, сколько машин в месяц.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_17.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Краснослободск, Краснослободский р-н, Республика Мордовия, ул. Интернациональная, 41</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Дрова</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB54" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>2026-10-05T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>2026-09-05T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>2026-10-05T12:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>7606201262</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Сосна кругляк (поставим объём на баланс)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Сделка не сорвётся из-за недостающей бумаги: документы по вашему лесу ведём заранее.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Это про вас, если:&lt;br&gt;- лес куплен у населения или взят по билету, а по бумагам его нет&lt;br&gt;- покупатель просит ЭСД и декларацию о сделке&lt;br&gt;- горят сроки по отчётности&lt;/p&gt;&lt;p&gt;Поставим вашу кубатуру на баланс, дальше ЭСД с QR за 15 минут и отчёт 1-ИЛ. Кабинет и подпись не нужны.&lt;/p&gt;&lt;p&gt;Работаем по сосновому кругляку 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Сасовский район, Рязанская область.&lt;br&gt;Напишите, куда идёт машина.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-01/w0901_21.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Сасово, Сасовский р-н, Рязанская обл., ул. Вокзальная, 14</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>2300</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>2026-10-06T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>2026-09-06T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>2026-10-06T04:00:00+03:00</t>
         </is>
       </c>
     </row>

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -13312,7 +13312,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Доска</t>
+          <t>Лес-кругляк</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Дрова</t>
+          <t>Лес-кругляк</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -12760,7 +12760,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -13642,7 +13642,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -16885,7 +16885,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -17176,7 +17176,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>По телефону и в сообщениях</t>
+          <t>В сообщениях</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/egais.xlsx
+++ b/egais.xlsx
@@ -7820,7 +7820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK55"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28.33" customWidth="1" min="1" max="1"/>
@@ -14992,6 +14992,888 @@
       <c r="AK55" t="inlineStr">
         <is>
           <t>2026-10-06T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>6969026724</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ель пиловочник, оформим ЭСД на рейс</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Возите и продавайте лес спокойно: бумажную часть в ФГИС ЛК держим мы.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Работы и цены:&lt;br&gt;- оформим происхождение вашей древесины по договору купли-продажи, от 1900 руб&lt;br&gt;- ЭСД с QR на каждый рейс, 15 минут&lt;br&gt;- подадим декларацию о сделке&lt;br&gt;- закроем отчёт 1-ИЛ и места складирования&lt;/p&gt;&lt;p&gt;От вас порода, кубатура и маршрут. Свой кабинет и электронная подпись не понадобятся.&lt;/p&gt;&lt;p&gt;Еловый пиловочник 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Ветлужский район, Нижегородская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов лежит.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_1_vetluga.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_2__1.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/radss__3.jpg</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Ветлуга, Ветлужский р-н, Нижегородская обл., ул. Пионерская, 14</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1900</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>2026-09-10T17:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>8157186603</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Сосна пиловочник (QR код на перевозку)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Машина не будет стоять под погрузкой из-за того, что на рейс нет документа.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Нужен QR код на перевозку? Сделаем за 15 минут, хоть перед самым выездом.&lt;br&gt;Лес куплен у населения и нигде не числится? Покажем происхождение своим объёмом, от 2300 руб.&lt;br&gt;Покупатель просит декларацию о сделке? Подадим.&lt;br&gt;Некому вести 1-ИЛ и места складирования? Ведём сами.&lt;/p&gt;&lt;p&gt;Кабинет в системе и подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Сосновый пиловочник 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Гусь-Хрустальный район, Владимирская область.&lt;/p&gt;&lt;p&gt;Напишите, когда выезд.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_2_gus.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__4.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__3.jpg</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Гусь-Хрустальный, Гусь-Хрустальный р-н, Владимирская обл., ул. Лесная, 8</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>2300</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>2026-10-10T17:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>2026-09-10T19:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>2026-10-10T17:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>7236924498</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Лес кругляк сосна, накладная на перевозку</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Поможем вывезти и продать лес законно, даже если сейчас в ФГИС ЛК по вам пусто.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;1. Разбираем, откуда у вас древесина и чего не хватает по бумагам&lt;br&gt;2. Оформляем её договором купли-продажи от нашего объёма, работа от 2500 руб&lt;br&gt;3. Выписываем накладную на перевозку с QR за 15 минут, подаём декларацию о сделке, закрываем 1-ИЛ&lt;/p&gt;&lt;p&gt;От вас данные по партии и маршруту, ни кабинета, ни подписи.&lt;/p&gt;&lt;p&gt;Сосновый и лиственничный кругляк 6 метров, диаметр от 20 см.&lt;/p&gt;&lt;p&gt;Белорецкий район, Башкортостан.&lt;/p&gt;&lt;p&gt;Напишите, куда идёт машина.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_3_beloretsk.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/qr_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/tr_1__2.jpg</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Белорецк, Белорецкий р-н, Республика Башкортостан, ул. Ленина, 71</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>2026-09-11T06:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>6686650421</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Баланс еловый (декларация о сделке)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Комбинат примет вашу партию с первого раза и не развернёт машину.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Пригодится, если:&lt;br&gt;- баланс лежит на площадке, а в системе его нет&lt;br&gt;- приёмка просит декларацию о сделке на каждую поставку&lt;br&gt;- некогда сидеть в ФГИС ЛК самому&lt;/p&gt;&lt;p&gt;Подадим декларацию о сделке, поставим кубатуру на баланс, выпишем ЭСД с QR на рейс за 15 минут, сдадим отчёт 1-ИЛ. Работа от 1200 руб, кабинет и подпись не нужны.&lt;/p&gt;&lt;p&gt;Еловый баланс 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Игринский район, Удмуртия.&lt;/p&gt;&lt;p&gt;Напишите, на какой комбинат везёте.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_4_igra.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_1__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image2.jpg</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Игра, Игринский р-н, Удмуртская Республика, ул. Советская, 30</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ель</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB59" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>2026-10-11T06:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>2026-09-11T08:30:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>2026-10-11T06:30:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>9980655614</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Сосна кругляк, поставим древесину на учёт</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Заберём лесные бумаги на себя: вы работаете в лесу и в рейсе, отчётность держим мы.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Поставим вашу древесину на учёт в ФГИС ЛК через договор купли-продажи от нашего объёма, дальше выпишем ЭСД с QR на каждый рейс за 15 минут, подадим декларацию о сделке и закроем отчёт 1-ИЛ. Работаем удалённо, от 1700 руб. Кабинет и электронная подпись вам не нужны, срок по учёту назовём после разбора ситуации.&lt;/p&gt;&lt;p&gt;Сосновый кругляк 4 и 6 метров, диаметр от 18 см.&lt;/p&gt;&lt;p&gt;Максатихинский район, Тверская область.&lt;/p&gt;&lt;p&gt;Напишите, сколько машин в неделю.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_5_maksatiha.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/reel_2__2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/15_qr__3.jpg</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Максатиха, Максатихинский р-н, Тверская обл., ул. Больничная, 5</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1700</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Сосна</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB60" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>2026-10-11T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>2026-09-11T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>2026-10-11T08:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>9642863659</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Баланс берёзовый (документы ФГИС ЛК)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Ваш лес станет товаром, который можно спокойно продать и вывезти.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Что будет у вас на руках:&lt;br&gt;- документ с QR на каждый рейс, делаем за 15 минут&lt;br&gt;- проведённая декларация о сделке в ФГИС ЛК&lt;br&gt;- кубатура, которая числится за вами&lt;br&gt;- сданный отчёт 1-ИЛ и заведённые места складирования&lt;/p&gt;&lt;p&gt;От вас порода, объём и маршрут, работа от 950 руб. Заводить кабинет и покупать электронную подпись не нужно.&lt;/p&gt;&lt;p&gt;Берёзовый баланс 2 и 3 метра, диаметр от 6 см.&lt;/p&gt;&lt;p&gt;Гайнский район, Пермский край.&lt;/p&gt;&lt;p&gt;Напишите, сколько кубов набирается.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_6_gayny.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/inf_1_1__image.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-08-13/12_qr__2.jpg</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Гайны, Гайнский р-н, Пермский край, ул. Кашина, 41</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>950</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB61" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>2026-10-11T10:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>2026-09-11T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>2026-10-11T10:00:00+03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>6060078734</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>79852671426</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Кругляк берёза и осина, объём на баланс</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Даже если бумаг по лесу нет совсем, доведём партию до отгрузки.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;В день обращения разберём вашу ситуацию и оформим древесину договором купли-продажи от нашего объёма, чтобы кубатура встала на баланс.&lt;br&gt;В тот же день выпишем ЭСД с QR на рейс, на это уходит 15 минут.&lt;br&gt;Дальше подаём декларацию о сделке и закрываем отчёт 1-ИЛ, работа от 1100 руб.&lt;/p&gt;&lt;p&gt;Кабинет в системе и подпись вам не нужны.&lt;/p&gt;&lt;p&gt;Берёзовый и осиновый кругляк 3 метра, диаметр от 16 см.&lt;/p&gt;&lt;p&gt;Мамадышский район, Татарстан.&lt;/p&gt;&lt;p&gt;Напишите, куда отгружаете.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/wave_2026-09-10/w1009_7_mamadysh.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_2.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/361353162/campaign_2026-07-29/egais_0729_15_3.jpg</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Ремонт и строительство</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Мамадыш, Мамадышский р-н, Республика Татарстан, ул. Давыдова, 21</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>ПВЗ</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Стройматериалы</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>В наличии</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Пиломатериалы</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Лес-кругляк</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Берёза</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="AB62" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>orbizona-shop@yandex.ru</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>ЕГАИС ЛЕС документация</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>2026-10-11T12:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>2026-09-11T14:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>2026-10-11T12:00:00+03:00</t>
         </is>
       </c>
     </row>
